--- a/Conteudos_Site_Casa_Porches.xlsx
+++ b/Conteudos_Site_Casa_Porches.xlsx
@@ -20,11 +20,11 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Casa'!$A$1:$C$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Textos'!$A$1:$G$111</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Restaurantes'!$A$1:$M$41</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Eventos'!$A$1:$AC$65</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Restaurantes'!$A$1:$N$41</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Eventos'!$A$1:$AD$65</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Sessoes'!$A$1:$D$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Localidades'!$A$1:$D$28</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Mapa'!$A$1:$M$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Mapa'!$A$1:$N$23</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Pagina_Principal'!$A$1:$F$128</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -483,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A32"/>
+  <dimension ref="A1:A36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="130" customWidth="1" min="1" max="1"/>
@@ -613,81 +613,105 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>DATAS DOS EVENTOS</t>
+          <t>IMAGENS</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>data_inicio / data_fim: só quando a data está CONFIRMADA → o evento aparece em 'Próximos eventos' e desaparece sozinho quando passa.</t>
+          <t>Coluna 'imagem' (Restaurantes, Eventos, Mapa): deixe em branco para usar a ilustração da categoria. Para uma fotografia própria, copie-a para a pasta images do site (ex.: images/restaurantes/rolha.jpg) e escreva esse caminho na coluna.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>Use só fotografias vossas ou com autorização — não copie fotografias de sites de restaurantes ou de terceiros. Tamanho ideal: horizontal, ~1200×600 px, até 300 KB.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>DATAS DOS EVENTOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>data_inicio / data_fim: só quando a data está CONFIRMADA → o evento aparece em 'Próximos eventos' e desaparece sozinho quando passa.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
           <t>ultima_inicio / ultima_fim: datas da última edição, quando a próxima ainda não foi anunciada.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>habitual_*: quando costuma acontecer (ex.: 'final de junho'). epoca_*: época/horário de atrações (ex.: 'Verão').</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>Quando sair a data do ano seguinte: escreva-a em data_inicio/data_fim. As datas usam o formato dd/mm/aaaa.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t>CÓDIGOS</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>Restaurantes › categoria: michelin, fine (requintados), wine (vinhos e petiscos), sea (peixe e vista mar), trad (tradicionais), intl (internacional e famílias), cafe (cafés).</t>
+          <t>habitual_*: quando costuma acontecer (ex.: 'final de junho'). epoca_*: época/horário de atrações (ex.: 'Verão').</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Eventos › categoria: events (festivais), water (parques e atrações), nature (natureza e praias), sea (mar e aventura), indoor (piscinas e chuva), markets (mercados e tradições).</t>
+          <t>Quando sair a data do ano seguinte: escreva-a em data_inicio/data_fim. As datas usam o formato dd/mm/aaaa.</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>Eventos › para_quem (separar por vírgulas): fam (famílias), teen (jovens), couple (casais), food (gastronomia), free (natureza/grátis), winter (outono e inverno).</t>
-        </is>
-      </c>
+      <c r="A29" s="2" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>Mapa › categoria: beach, food, fun, see, help.</t>
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>CÓDIGOS</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr"/>
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>Restaurantes › categoria: michelin, fine (requintados), wine (vinhos e petiscos), sea (peixe e vista mar), trad (tradicionais), intl (internacional e famílias), cafe (cafés).</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>Eventos › categoria: events (festivais), water (parques e atrações), nature (natureza e praias), sea (mar e aventura), indoor (piscinas e chuva), markets (mercados e tradições).</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>Eventos › para_quem (separar por vírgulas): fam (famílias), teen (jovens), couple (casais), food (gastronomia), free (natureza/grátis), winter (outono e inverno).</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>Mapa › categoria: beach, food, fun, see, help.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>As células amarelas são o português (texto de referência).</t>
         </is>
@@ -4908,7 +4932,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M41"/>
+  <dimension ref="A1:N41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -4918,12 +4942,13 @@
     <col width="9" customWidth="1" min="5" max="5"/>
     <col width="28" customWidth="1" min="6" max="6"/>
     <col width="9" customWidth="1" min="7" max="7"/>
-    <col width="50" customWidth="1" min="8" max="8"/>
+    <col width="26" customWidth="1" min="8" max="8"/>
     <col width="50" customWidth="1" min="9" max="9"/>
     <col width="50" customWidth="1" min="10" max="10"/>
     <col width="50" customWidth="1" min="11" max="11"/>
     <col width="50" customWidth="1" min="12" max="12"/>
     <col width="50" customWidth="1" min="13" max="13"/>
+    <col width="50" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -4964,30 +4989,35 @@
       </c>
       <c r="H1" s="4" t="inlineStr">
         <is>
+          <t>imagem</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
           <t>desc_pt</t>
         </is>
       </c>
-      <c r="I1" s="4" t="inlineStr">
+      <c r="J1" s="4" t="inlineStr">
         <is>
           <t>desc_en</t>
         </is>
       </c>
-      <c r="J1" s="4" t="inlineStr">
+      <c r="K1" s="4" t="inlineStr">
         <is>
           <t>desc_es</t>
         </is>
       </c>
-      <c r="K1" s="4" t="inlineStr">
+      <c r="L1" s="4" t="inlineStr">
         <is>
           <t>desc_fr</t>
         </is>
       </c>
-      <c r="L1" s="4" t="inlineStr">
+      <c r="M1" s="4" t="inlineStr">
         <is>
           <t>desc_de</t>
         </is>
       </c>
-      <c r="M1" s="4" t="inlineStr">
+      <c r="N1" s="4" t="inlineStr">
         <is>
           <t>desc_it</t>
         </is>
@@ -5029,32 +5059,33 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="H2" s="6" t="inlineStr">
+      <c r="H2" s="5" t="inlineStr"/>
+      <c r="I2" s="6" t="inlineStr">
         <is>
           <t>2 estrelas Michelin. Chef Hans Neuner, cozinha criativa, menus de degustação e harmonização de vinhos, vista mar.</t>
         </is>
       </c>
-      <c r="I2" s="5" t="inlineStr">
+      <c r="J2" s="5" t="inlineStr">
         <is>
           <t>2 Michelin stars. Chef Hans Neuner, creative cuisine, tasting menus with wine pairing, ocean views.</t>
         </is>
       </c>
-      <c r="J2" s="5" t="inlineStr">
+      <c r="K2" s="5" t="inlineStr">
         <is>
           <t>2 estrellas Michelin. Chef Hans Neuner, cocina creativa, menús degustación con maridaje y vistas al mar.</t>
         </is>
       </c>
-      <c r="K2" s="5" t="inlineStr">
+      <c r="L2" s="5" t="inlineStr">
         <is>
           <t>2 étoiles Michelin. Chef Hans Neuner, cuisine créative, menus dégustation avec accords mets-vins, vue sur l’océan.</t>
         </is>
       </c>
-      <c r="L2" s="5" t="inlineStr">
+      <c r="M2" s="5" t="inlineStr">
         <is>
           <t>2 Michelin-Sterne. Küchenchef Hans Neuner, kreative Küche, Degustationsmenüs mit Weinbegleitung, Meerblick.</t>
         </is>
       </c>
-      <c r="M2" s="5" t="inlineStr">
+      <c r="N2" s="5" t="inlineStr">
         <is>
           <t>2 stelle Michelin. Chef Hans Neuner, cucina creativa, menù degustazione con abbinamento vini, vista oceano.</t>
         </is>
@@ -5096,32 +5127,33 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="H3" s="6" t="inlineStr">
+      <c r="H3" s="5" t="inlineStr"/>
+      <c r="I3" s="6" t="inlineStr">
         <is>
           <t>2 estrelas Michelin. Cozinha de autor internacional, excelente garrafeira e vista mar. Para ocasiões especiais.</t>
         </is>
       </c>
-      <c r="I3" s="5" t="inlineStr">
+      <c r="J3" s="5" t="inlineStr">
         <is>
           <t>2 Michelin stars. International signature cuisine, outstanding wine cellar and sea views. For special occasions.</t>
         </is>
       </c>
-      <c r="J3" s="5" t="inlineStr">
+      <c r="K3" s="5" t="inlineStr">
         <is>
           <t>2 estrellas Michelin. Cocina de autor internacional, excelente bodega y vistas al mar. Para ocasiones especiales.</t>
         </is>
       </c>
-      <c r="K3" s="5" t="inlineStr">
+      <c r="L3" s="5" t="inlineStr">
         <is>
           <t>2 étoiles Michelin. Cuisine d’auteur internationale, superbe cave et vue sur la mer. Pour les grandes occasions.</t>
         </is>
       </c>
-      <c r="L3" s="5" t="inlineStr">
+      <c r="M3" s="5" t="inlineStr">
         <is>
           <t>2 Michelin-Sterne. Internationale Autorenküche, hervorragender Weinkeller und Meerblick. Für besondere Anlässe.</t>
         </is>
       </c>
-      <c r="M3" s="5" t="inlineStr">
+      <c r="N3" s="5" t="inlineStr">
         <is>
           <t>2 stelle Michelin. Cucina d’autore internazionale, ottima cantina e vista mare. Per occasioni speciali.</t>
         </is>
@@ -5163,32 +5195,33 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="H4" s="6" t="inlineStr">
+      <c r="H4" s="5" t="inlineStr"/>
+      <c r="I4" s="6" t="inlineStr">
         <is>
           <t>1 estrela Michelin. Cozinha portuguesa contemporânea com ingredientes regionais. Ambiente intimista.</t>
         </is>
       </c>
-      <c r="I4" s="5" t="inlineStr">
+      <c r="J4" s="5" t="inlineStr">
         <is>
           <t>1 Michelin star. Contemporary Portuguese cuisine with regional produce. Intimate setting.</t>
         </is>
       </c>
-      <c r="J4" s="5" t="inlineStr">
+      <c r="K4" s="5" t="inlineStr">
         <is>
           <t>1 estrella Michelin. Cocina portuguesa contemporánea con productos regionales. Ambiente íntimo.</t>
         </is>
       </c>
-      <c r="K4" s="5" t="inlineStr">
+      <c r="L4" s="5" t="inlineStr">
         <is>
           <t>1 étoile Michelin. Cuisine portugaise contemporaine aux produits régionaux. Cadre intimiste.</t>
         </is>
       </c>
-      <c r="L4" s="5" t="inlineStr">
+      <c r="M4" s="5" t="inlineStr">
         <is>
           <t>1 Michelin-Stern. Zeitgemäße portugiesische Küche mit regionalen Zutaten. Intime Atmosphäre.</t>
         </is>
       </c>
-      <c r="M4" s="5" t="inlineStr">
+      <c r="N4" s="5" t="inlineStr">
         <is>
           <t>1 stella Michelin. Cucina portoghese contemporanea con prodotti regionali. Ambiente intimo.</t>
         </is>
@@ -5230,32 +5263,33 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="H5" s="6" t="inlineStr">
+      <c r="H5" s="5" t="inlineStr"/>
+      <c r="I5" s="6" t="inlineStr">
         <is>
           <t>1 estrela Michelin. Alta gastronomia de peixe e marisco com vista sobre o Atlântico. Ótimo para jantares românticos.</t>
         </is>
       </c>
-      <c r="I5" s="5" t="inlineStr">
+      <c r="J5" s="5" t="inlineStr">
         <is>
           <t>1 Michelin star. Fine dining focused on fish and seafood, overlooking the Atlantic. Great for a romantic dinner.</t>
         </is>
       </c>
-      <c r="J5" s="5" t="inlineStr">
+      <c r="K5" s="5" t="inlineStr">
         <is>
           <t>1 estrella Michelin. Alta cocina de pescado y marisco con vistas al Atlántico. Ideal para una cena romántica.</t>
         </is>
       </c>
-      <c r="K5" s="5" t="inlineStr">
+      <c r="L5" s="5" t="inlineStr">
         <is>
           <t>1 étoile Michelin. Haute gastronomie de poisson et fruits de mer face à l’Atlantique. Idéal pour un dîner romantique.</t>
         </is>
       </c>
-      <c r="L5" s="5" t="inlineStr">
+      <c r="M5" s="5" t="inlineStr">
         <is>
           <t>1 Michelin-Stern. Gehobene Fisch- und Meeresfrüchteküche mit Blick auf den Atlantik. Ideal für ein romantisches Dinner.</t>
         </is>
       </c>
-      <c r="M5" s="5" t="inlineStr">
+      <c r="N5" s="5" t="inlineStr">
         <is>
           <t>1 stella Michelin. Alta cucina di pesce e frutti di mare con vista sull’Atlantico. Ideale per una cena romantica.</t>
         </is>
@@ -5297,32 +5331,33 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="H6" s="6" t="inlineStr">
+      <c r="H6" s="5" t="inlineStr"/>
+      <c r="I6" s="6" t="inlineStr">
         <is>
           <t>Recomendado pelo Guia Michelin, numa casa histórica. Cozinha criativa portuguesa e mediterrânica, ambiente romântico.</t>
         </is>
       </c>
-      <c r="I6" s="5" t="inlineStr">
+      <c r="J6" s="5" t="inlineStr">
         <is>
           <t>Michelin Guide recommended, in a historic house. Creative Portuguese and Mediterranean cuisine, romantic setting.</t>
         </is>
       </c>
-      <c r="J6" s="5" t="inlineStr">
+      <c r="K6" s="5" t="inlineStr">
         <is>
           <t>Recomendado por la Guía Michelin, en una casa histórica. Cocina creativa portuguesa y mediterránea, ambiente romántico.</t>
         </is>
       </c>
-      <c r="K6" s="5" t="inlineStr">
+      <c r="L6" s="5" t="inlineStr">
         <is>
           <t>Recommandé par le Guide Michelin, dans une maison historique. Cuisine créative portugaise et méditerranéenne, cadre romantique.</t>
         </is>
       </c>
-      <c r="L6" s="5" t="inlineStr">
+      <c r="M6" s="5" t="inlineStr">
         <is>
           <t>Vom Guide Michelin empfohlen, in einem historischen Haus. Kreative portugiesische und mediterrane Küche, romantisches Ambiente.</t>
         </is>
       </c>
-      <c r="M6" s="5" t="inlineStr">
+      <c r="N6" s="5" t="inlineStr">
         <is>
           <t>Consigliato dalla Guida Michelin, in una casa storica. Cucina creativa portoghese e mediterranea, atmosfera romantica.</t>
         </is>
@@ -5364,32 +5399,33 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="H7" s="6" t="inlineStr">
+      <c r="H7" s="5" t="inlineStr"/>
+      <c r="I7" s="6" t="inlineStr">
         <is>
           <t>Recomendado pelo Guia Michelin. Cozinha atlântica contemporânea e menus de degustação à beira-mar.</t>
         </is>
       </c>
-      <c r="I7" s="5" t="inlineStr">
+      <c r="J7" s="5" t="inlineStr">
         <is>
           <t>Michelin Guide recommended. Contemporary Atlantic cuisine and tasting menus by the sea.</t>
         </is>
       </c>
-      <c r="J7" s="5" t="inlineStr">
+      <c r="K7" s="5" t="inlineStr">
         <is>
           <t>Recomendado por la Guía Michelin. Cocina atlántica contemporánea y menús degustación junto al mar.</t>
         </is>
       </c>
-      <c r="K7" s="5" t="inlineStr">
+      <c r="L7" s="5" t="inlineStr">
         <is>
           <t>Recommandé par le Guide Michelin. Cuisine atlantique contemporaine et menus dégustation en bord de mer.</t>
         </is>
       </c>
-      <c r="L7" s="5" t="inlineStr">
+      <c r="M7" s="5" t="inlineStr">
         <is>
           <t>Vom Guide Michelin empfohlen. Zeitgemäße atlantische Küche und Degustationsmenüs am Meer.</t>
         </is>
       </c>
-      <c r="M7" s="5" t="inlineStr">
+      <c r="N7" s="5" t="inlineStr">
         <is>
           <t>Consigliato dalla Guida Michelin. Cucina atlantica contemporanea e menù degustazione sul mare.</t>
         </is>
@@ -5431,32 +5467,33 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="H8" s="6" t="inlineStr">
+      <c r="H8" s="5" t="inlineStr"/>
+      <c r="I8" s="6" t="inlineStr">
         <is>
           <t>Recomendado pelo Guia Michelin. Cozinha mediterrânica contemporânea com influências do Levante e vista mar.</t>
         </is>
       </c>
-      <c r="I8" s="5" t="inlineStr">
+      <c r="J8" s="5" t="inlineStr">
         <is>
           <t>Michelin Guide recommended. Contemporary Mediterranean cuisine with Levantine influences and sea views.</t>
         </is>
       </c>
-      <c r="J8" s="5" t="inlineStr">
+      <c r="K8" s="5" t="inlineStr">
         <is>
           <t>Recomendado por la Guía Michelin. Cocina mediterránea contemporánea con influencias de Levante y vistas al mar.</t>
         </is>
       </c>
-      <c r="K8" s="5" t="inlineStr">
+      <c r="L8" s="5" t="inlineStr">
         <is>
           <t>Recommandé par le Guide Michelin. Cuisine méditerranéenne contemporaine aux influences levantines, vue mer.</t>
         </is>
       </c>
-      <c r="L8" s="5" t="inlineStr">
+      <c r="M8" s="5" t="inlineStr">
         <is>
           <t>Vom Guide Michelin empfohlen. Moderne mediterrane Küche mit levantinischen Einflüssen und Meerblick.</t>
         </is>
       </c>
-      <c r="M8" s="5" t="inlineStr">
+      <c r="N8" s="5" t="inlineStr">
         <is>
           <t>Consigliato dalla Guida Michelin. Cucina mediterranea contemporanea con influenze levantine e vista mare.</t>
         </is>
@@ -5498,32 +5535,33 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="H9" s="6" t="inlineStr">
+      <c r="H9" s="5" t="inlineStr"/>
+      <c r="I9" s="6" t="inlineStr">
         <is>
           <t>Recomendado pelo Guia Michelin. Cozinha portuguesa moderna, menus criativos e harmonizações de vinhos.</t>
         </is>
       </c>
-      <c r="I9" s="5" t="inlineStr">
+      <c r="J9" s="5" t="inlineStr">
         <is>
           <t>Michelin Guide recommended. Modern Portuguese cuisine, creative menus and wine pairings.</t>
         </is>
       </c>
-      <c r="J9" s="5" t="inlineStr">
+      <c r="K9" s="5" t="inlineStr">
         <is>
           <t>Recomendado por la Guía Michelin. Cocina portuguesa moderna, menús creativos y maridajes.</t>
         </is>
       </c>
-      <c r="K9" s="5" t="inlineStr">
+      <c r="L9" s="5" t="inlineStr">
         <is>
           <t>Recommandé par le Guide Michelin. Cuisine portugaise moderne, menus créatifs et accords mets-vins.</t>
         </is>
       </c>
-      <c r="L9" s="5" t="inlineStr">
+      <c r="M9" s="5" t="inlineStr">
         <is>
           <t>Vom Guide Michelin empfohlen. Moderne portugiesische Küche, kreative Menüs und Weinbegleitung.</t>
         </is>
       </c>
-      <c r="M9" s="5" t="inlineStr">
+      <c r="N9" s="5" t="inlineStr">
         <is>
           <t>Consigliato dalla Guida Michelin. Cucina portoghese moderna, menù creativi e abbinamenti di vini.</t>
         </is>
@@ -5565,32 +5603,33 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="H10" s="6" t="inlineStr">
+      <c r="H10" s="5" t="inlineStr"/>
+      <c r="I10" s="6" t="inlineStr">
         <is>
           <t>Restaurante de referência em ambiente rural, entre laranjais. Carnes e peixes portugueses e boa oferta de vinhos.</t>
         </is>
       </c>
-      <c r="I10" s="5" t="inlineStr">
+      <c r="J10" s="5" t="inlineStr">
         <is>
           <t>A renowned restaurant in the countryside among orange groves. Portuguese meat and fish, good wine list.</t>
         </is>
       </c>
-      <c r="J10" s="5" t="inlineStr">
+      <c r="K10" s="5" t="inlineStr">
         <is>
           <t>Restaurante de referencia en un entorno rural, entre naranjos. Carnes y pescados portugueses y buena carta de vinos.</t>
         </is>
       </c>
-      <c r="K10" s="5" t="inlineStr">
+      <c r="L10" s="5" t="inlineStr">
         <is>
           <t>Adresse réputée à la campagne, au milieu des orangers. Viandes et poissons portugais, belle carte des vins.</t>
         </is>
       </c>
-      <c r="L10" s="5" t="inlineStr">
+      <c r="M10" s="5" t="inlineStr">
         <is>
           <t>Renommiertes Restaurant auf dem Land zwischen Orangenhainen. Portugiesisches Fleisch und Fisch, gute Weinkarte.</t>
         </is>
       </c>
-      <c r="M10" s="5" t="inlineStr">
+      <c r="N10" s="5" t="inlineStr">
         <is>
           <t>Ristorante rinomato in campagna, tra gli aranceti. Carne e pesce portoghesi, buona carta dei vini.</t>
         </is>
@@ -5632,32 +5671,37 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="H11" s="6" t="inlineStr">
+      <c r="H11" s="5" t="inlineStr">
+        <is>
+          <t>images/attractions_1.jpg</t>
+        </is>
+      </c>
+      <c r="I11" s="6" t="inlineStr">
         <is>
           <t>Vinhos portugueses e petiscos de qualidade num ambiente acolhedor. Ótimo para partilhar pratos.</t>
         </is>
       </c>
-      <c r="I11" s="5" t="inlineStr">
+      <c r="J11" s="5" t="inlineStr">
         <is>
           <t>Portuguese wines and quality small plates in a cosy setting. Great for sharing.</t>
         </is>
       </c>
-      <c r="J11" s="5" t="inlineStr">
+      <c r="K11" s="5" t="inlineStr">
         <is>
           <t>Vinos portugueses y tapas de calidad en un ambiente acogedor. Ideal para compartir.</t>
         </is>
       </c>
-      <c r="K11" s="5" t="inlineStr">
+      <c r="L11" s="5" t="inlineStr">
         <is>
           <t>Vins portugais et petites assiettes de qualité dans un cadre chaleureux. Parfait pour partager.</t>
         </is>
       </c>
-      <c r="L11" s="5" t="inlineStr">
+      <c r="M11" s="5" t="inlineStr">
         <is>
           <t>Portugiesische Weine und hochwertige Häppchen in gemütlicher Atmosphäre. Ideal zum Teilen.</t>
         </is>
       </c>
-      <c r="M11" s="5" t="inlineStr">
+      <c r="N11" s="5" t="inlineStr">
         <is>
           <t>Vini portoghesi e stuzzichini di qualità in un ambiente accogliente. Perfetto per condividere.</t>
         </is>
@@ -5699,32 +5743,33 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="H12" s="6" t="inlineStr">
+      <c r="H12" s="5" t="inlineStr"/>
+      <c r="I12" s="6" t="inlineStr">
         <is>
           <t>Cozinha portuguesa contemporânea, menus de degustação e excelente seleção de vinhos. Muito bem avaliado.</t>
         </is>
       </c>
-      <c r="I12" s="5" t="inlineStr">
+      <c r="J12" s="5" t="inlineStr">
         <is>
           <t>Contemporary Portuguese cuisine, tasting menus and an excellent wine selection. Very highly rated.</t>
         </is>
       </c>
-      <c r="J12" s="5" t="inlineStr">
+      <c r="K12" s="5" t="inlineStr">
         <is>
           <t>Cocina portuguesa contemporánea, menús degustación y excelente selección de vinos. Muy bien valorado.</t>
         </is>
       </c>
-      <c r="K12" s="5" t="inlineStr">
+      <c r="L12" s="5" t="inlineStr">
         <is>
           <t>Cuisine portugaise contemporaine, menus dégustation et excellente sélection de vins. Très bien noté.</t>
         </is>
       </c>
-      <c r="L12" s="5" t="inlineStr">
+      <c r="M12" s="5" t="inlineStr">
         <is>
           <t>Moderne portugiesische Küche, Degustationsmenüs und exzellente Weinauswahl. Sehr gut bewertet.</t>
         </is>
       </c>
-      <c r="M12" s="5" t="inlineStr">
+      <c r="N12" s="5" t="inlineStr">
         <is>
           <t>Cucina portoghese contemporanea, menù degustazione e ottima selezione di vini. Valutazioni eccellenti.</t>
         </is>
@@ -5766,32 +5811,37 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="H13" s="6" t="inlineStr">
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>images/ilustracoes/rest-grill.svg</t>
+        </is>
+      </c>
+      <c r="I13" s="6" t="inlineStr">
         <is>
           <t>Carnes nobres, cozinha mediterrânica e boa garrafeira. Ambiente elegante.</t>
         </is>
       </c>
-      <c r="I13" s="5" t="inlineStr">
+      <c r="J13" s="5" t="inlineStr">
         <is>
           <t>Prime meats, Mediterranean cuisine and a good wine cellar. Elegant setting.</t>
         </is>
       </c>
-      <c r="J13" s="5" t="inlineStr">
+      <c r="K13" s="5" t="inlineStr">
         <is>
           <t>Carnes selectas, cocina mediterránea y buena bodega. Ambiente elegante.</t>
         </is>
       </c>
-      <c r="K13" s="5" t="inlineStr">
+      <c r="L13" s="5" t="inlineStr">
         <is>
           <t>Viandes d’exception, cuisine méditerranéenne et belle cave. Cadre élégant.</t>
         </is>
       </c>
-      <c r="L13" s="5" t="inlineStr">
+      <c r="M13" s="5" t="inlineStr">
         <is>
           <t>Edle Fleischgerichte, mediterrane Küche und guter Weinkeller. Elegantes Ambiente.</t>
         </is>
       </c>
-      <c r="M13" s="5" t="inlineStr">
+      <c r="N13" s="5" t="inlineStr">
         <is>
           <t>Carni pregiate, cucina mediterranea e buona cantina. Ambiente elegante.</t>
         </is>
@@ -5833,32 +5883,33 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="H14" s="6" t="inlineStr">
+      <c r="H14" s="5" t="inlineStr"/>
+      <c r="I14" s="6" t="inlineStr">
         <is>
           <t>Cozinha portuguesa contemporânea, peixe, marisco e cataplanas, com vista mar e boa carta de vinhos.</t>
         </is>
       </c>
-      <c r="I14" s="5" t="inlineStr">
+      <c r="J14" s="5" t="inlineStr">
         <is>
           <t>Contemporary Portuguese cuisine, fish, seafood and cataplanas, with sea views and a good wine list.</t>
         </is>
       </c>
-      <c r="J14" s="5" t="inlineStr">
+      <c r="K14" s="5" t="inlineStr">
         <is>
           <t>Cocina portuguesa contemporánea, pescado, marisco y cataplanas, con vistas al mar y buena carta de vinos.</t>
         </is>
       </c>
-      <c r="K14" s="5" t="inlineStr">
+      <c r="L14" s="5" t="inlineStr">
         <is>
           <t>Cuisine portugaise contemporaine, poisson, fruits de mer et cataplanas, vue mer et belle carte des vins.</t>
         </is>
       </c>
-      <c r="L14" s="5" t="inlineStr">
+      <c r="M14" s="5" t="inlineStr">
         <is>
           <t>Moderne portugiesische Küche, Fisch, Meeresfrüchte und Cataplanas, mit Meerblick und guter Weinkarte.</t>
         </is>
       </c>
-      <c r="M14" s="5" t="inlineStr">
+      <c r="N14" s="5" t="inlineStr">
         <is>
           <t>Cucina portoghese contemporanea, pesce, frutti di mare e cataplane, con vista mare e buona carta dei vini.</t>
         </is>
@@ -5900,32 +5951,33 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="H15" s="6" t="inlineStr">
+      <c r="H15" s="5" t="inlineStr"/>
+      <c r="I15" s="6" t="inlineStr">
         <is>
           <t>Restaurante tradicional famoso pela extraordinária garrafeira de vinhos portugueses e pela cozinha regional.</t>
         </is>
       </c>
-      <c r="I15" s="5" t="inlineStr">
+      <c r="J15" s="5" t="inlineStr">
         <is>
           <t>Traditional restaurant famous for its extraordinary Portuguese wine cellar and regional cooking.</t>
         </is>
       </c>
-      <c r="J15" s="5" t="inlineStr">
+      <c r="K15" s="5" t="inlineStr">
         <is>
           <t>Restaurante tradicional famoso por su extraordinaria bodega de vinos portugueses y su cocina regional.</t>
         </is>
       </c>
-      <c r="K15" s="5" t="inlineStr">
+      <c r="L15" s="5" t="inlineStr">
         <is>
           <t>Restaurant traditionnel réputé pour son extraordinaire cave de vins portugais et sa cuisine régionale.</t>
         </is>
       </c>
-      <c r="L15" s="5" t="inlineStr">
+      <c r="M15" s="5" t="inlineStr">
         <is>
           <t>Traditionelles Restaurant, berühmt für seinen außergewöhnlichen portugiesischen Weinkeller und regionale Küche.</t>
         </is>
       </c>
-      <c r="M15" s="5" t="inlineStr">
+      <c r="N15" s="5" t="inlineStr">
         <is>
           <t>Ristorante tradizionale famoso per la straordinaria cantina di vini portoghesi e la cucina regionale.</t>
         </is>
@@ -5967,32 +6019,33 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="H16" s="6" t="inlineStr">
+      <c r="H16" s="5" t="inlineStr"/>
+      <c r="I16" s="6" t="inlineStr">
         <is>
           <t>Pequeno restaurante de tapas criativas e vinhos portugueses. Descontraído e intimista.</t>
         </is>
       </c>
-      <c r="I16" s="5" t="inlineStr">
+      <c r="J16" s="5" t="inlineStr">
         <is>
           <t>Small spot for creative tapas and Portuguese wines. Relaxed and intimate.</t>
         </is>
       </c>
-      <c r="J16" s="5" t="inlineStr">
+      <c r="K16" s="5" t="inlineStr">
         <is>
           <t>Pequeño local de tapas creativas y vinos portugueses. Relajado e íntimo.</t>
         </is>
       </c>
-      <c r="K16" s="5" t="inlineStr">
+      <c r="L16" s="5" t="inlineStr">
         <is>
           <t>Petit restaurant de tapas créatives et vins portugais. Décontracté et intimiste.</t>
         </is>
       </c>
-      <c r="L16" s="5" t="inlineStr">
+      <c r="M16" s="5" t="inlineStr">
         <is>
           <t>Kleines Lokal mit kreativen Tapas und portugiesischen Weinen. Entspannt und gemütlich.</t>
         </is>
       </c>
-      <c r="M16" s="5" t="inlineStr">
+      <c r="N16" s="5" t="inlineStr">
         <is>
           <t>Piccolo locale di tapas creative e vini portoghesi. Rilassato e intimo.</t>
         </is>
@@ -6034,32 +6087,33 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="H17" s="6" t="inlineStr">
+      <c r="H17" s="5" t="inlineStr"/>
+      <c r="I17" s="6" t="inlineStr">
         <is>
           <t>Cozinha mediterrânica e internacional, carnes e peixe, em ambiente tranquilo.</t>
         </is>
       </c>
-      <c r="I17" s="5" t="inlineStr">
+      <c r="J17" s="5" t="inlineStr">
         <is>
           <t>Mediterranean and international cuisine, meat and fish, in a peaceful setting.</t>
         </is>
       </c>
-      <c r="J17" s="5" t="inlineStr">
+      <c r="K17" s="5" t="inlineStr">
         <is>
           <t>Cocina mediterránea e internacional, carnes y pescado, en un ambiente tranquilo.</t>
         </is>
       </c>
-      <c r="K17" s="5" t="inlineStr">
+      <c r="L17" s="5" t="inlineStr">
         <is>
           <t>Cuisine méditerranéenne et internationale, viandes et poissons, dans un cadre paisible.</t>
         </is>
       </c>
-      <c r="L17" s="5" t="inlineStr">
+      <c r="M17" s="5" t="inlineStr">
         <is>
           <t>Mediterrane und internationale Küche, Fleisch und Fisch, in ruhiger Umgebung.</t>
         </is>
       </c>
-      <c r="M17" s="5" t="inlineStr">
+      <c r="N17" s="5" t="inlineStr">
         <is>
           <t>Cucina mediterranea e internazionale, carne e pesce, in un ambiente tranquillo.</t>
         </is>
@@ -6101,32 +6155,37 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="H18" s="6" t="inlineStr">
+      <c r="H18" s="5" t="inlineStr">
+        <is>
+          <t>images/ilustracoes/rest-sardines.svg</t>
+        </is>
+      </c>
+      <c r="I18" s="6" t="inlineStr">
         <is>
           <t>Mesmo na praia. Peixe grelhado, marisco e cozinha algarvia. Ótimo para almoçar com vista mar.</t>
         </is>
       </c>
-      <c r="I18" s="5" t="inlineStr">
+      <c r="J18" s="5" t="inlineStr">
         <is>
           <t>Right on the beach. Grilled fish, seafood and Algarve cooking. Great for lunch with a sea view.</t>
         </is>
       </c>
-      <c r="J18" s="5" t="inlineStr">
+      <c r="K18" s="5" t="inlineStr">
         <is>
           <t>En la misma playa. Pescado a la parrilla, marisco y cocina del Algarve. Ideal para comer con vistas al mar.</t>
         </is>
       </c>
-      <c r="K18" s="5" t="inlineStr">
+      <c r="L18" s="5" t="inlineStr">
         <is>
           <t>Directement sur la plage. Poisson grillé, fruits de mer et cuisine de l’Algarve. Idéal pour déjeuner face à la mer.</t>
         </is>
       </c>
-      <c r="L18" s="5" t="inlineStr">
+      <c r="M18" s="5" t="inlineStr">
         <is>
           <t>Direkt am Strand. Gegrillter Fisch, Meeresfrüchte und Algarve-Küche. Ideal zum Mittagessen mit Meerblick.</t>
         </is>
       </c>
-      <c r="M18" s="5" t="inlineStr">
+      <c r="N18" s="5" t="inlineStr">
         <is>
           <t>Direttamente sulla spiaggia. Pesce alla griglia, frutti di mare e cucina dell’Algarve. Ideale per pranzo vista mare.</t>
         </is>
@@ -6168,32 +6227,33 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="H19" s="6" t="inlineStr">
+      <c r="H19" s="5" t="inlineStr"/>
+      <c r="I19" s="6" t="inlineStr">
         <is>
           <t>Restaurante moderno junto ao mar: peixe fresco, marisco e cataplanas, esplanada e pôr do sol.</t>
         </is>
       </c>
-      <c r="I19" s="5" t="inlineStr">
+      <c r="J19" s="5" t="inlineStr">
         <is>
           <t>Modern seaside restaurant: fresh fish, seafood and cataplanas, terrace and sunsets.</t>
         </is>
       </c>
-      <c r="J19" s="5" t="inlineStr">
+      <c r="K19" s="5" t="inlineStr">
         <is>
           <t>Restaurante moderno junto al mar: pescado fresco, marisco y cataplanas, terraza y puestas de sol.</t>
         </is>
       </c>
-      <c r="K19" s="5" t="inlineStr">
+      <c r="L19" s="5" t="inlineStr">
         <is>
           <t>Restaurant moderne en bord de mer : poisson frais, fruits de mer et cataplanas, terrasse et coucher de soleil.</t>
         </is>
       </c>
-      <c r="L19" s="5" t="inlineStr">
+      <c r="M19" s="5" t="inlineStr">
         <is>
           <t>Modernes Restaurant am Meer: frischer Fisch, Meeresfrüchte und Cataplanas, Terrasse und Sonnenuntergang.</t>
         </is>
       </c>
-      <c r="M19" s="5" t="inlineStr">
+      <c r="N19" s="5" t="inlineStr">
         <is>
           <t>Ristorante moderno sul mare: pesce fresco, frutti di mare e cataplane, terrazza e tramonti.</t>
         </is>
@@ -6235,32 +6295,33 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="H20" s="6" t="inlineStr">
+      <c r="H20" s="5" t="inlineStr"/>
+      <c r="I20" s="6" t="inlineStr">
         <is>
           <t>Restaurante de praia do grupo Vila Vita. Peixe fresco, marisco e esplanada junto ao mar.</t>
         </is>
       </c>
-      <c r="I20" s="5" t="inlineStr">
+      <c r="J20" s="5" t="inlineStr">
         <is>
           <t>Beach restaurant run by Vila Vita. Fresh fish, seafood and a seafront terrace.</t>
         </is>
       </c>
-      <c r="J20" s="5" t="inlineStr">
+      <c r="K20" s="5" t="inlineStr">
         <is>
           <t>Restaurante de playa del grupo Vila Vita. Pescado fresco, marisco y terraza junto al mar.</t>
         </is>
       </c>
-      <c r="K20" s="5" t="inlineStr">
+      <c r="L20" s="5" t="inlineStr">
         <is>
           <t>Restaurant de plage du groupe Vila Vita. Poisson frais, fruits de mer et terrasse face à la mer.</t>
         </is>
       </c>
-      <c r="L20" s="5" t="inlineStr">
+      <c r="M20" s="5" t="inlineStr">
         <is>
           <t>Strandrestaurant der Vila-Vita-Gruppe. Frischer Fisch, Meeresfrüchte und Terrasse am Meer.</t>
         </is>
       </c>
-      <c r="M20" s="5" t="inlineStr">
+      <c r="N20" s="5" t="inlineStr">
         <is>
           <t>Ristorante sulla spiaggia del gruppo Vila Vita. Pesce fresco, frutti di mare e terrazza sul mare.</t>
         </is>
@@ -6302,32 +6363,33 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="H21" s="6" t="inlineStr">
+      <c r="H21" s="5" t="inlineStr"/>
+      <c r="I21" s="6" t="inlineStr">
         <is>
           <t>Restaurante de praia descontraído: peixe, marisco e cozinha internacional, com esplanada.</t>
         </is>
       </c>
-      <c r="I21" s="5" t="inlineStr">
+      <c r="J21" s="5" t="inlineStr">
         <is>
           <t>Relaxed beach restaurant: fish, seafood and international dishes, with a terrace.</t>
         </is>
       </c>
-      <c r="J21" s="5" t="inlineStr">
+      <c r="K21" s="5" t="inlineStr">
         <is>
           <t>Restaurante de playa informal: pescado, marisco y cocina internacional, con terraza.</t>
         </is>
       </c>
-      <c r="K21" s="5" t="inlineStr">
+      <c r="L21" s="5" t="inlineStr">
         <is>
           <t>Restaurant de plage décontracté : poisson, fruits de mer et cuisine internationale, en terrasse.</t>
         </is>
       </c>
-      <c r="L21" s="5" t="inlineStr">
+      <c r="M21" s="5" t="inlineStr">
         <is>
           <t>Entspanntes Strandrestaurant: Fisch, Meeresfrüchte und internationale Küche, mit Terrasse.</t>
         </is>
       </c>
-      <c r="M21" s="5" t="inlineStr">
+      <c r="N21" s="5" t="inlineStr">
         <is>
           <t>Ristorante sulla spiaggia informale: pesce, frutti di mare e cucina internazionale, con terrazza.</t>
         </is>
@@ -6369,32 +6431,33 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="H22" s="6" t="inlineStr">
+      <c r="H22" s="5" t="inlineStr"/>
+      <c r="I22" s="6" t="inlineStr">
         <is>
           <t>Um dos restaurantes de praia mais conhecidos da região. Peixe e marisco com vista espetacular.</t>
         </is>
       </c>
-      <c r="I22" s="5" t="inlineStr">
+      <c r="J22" s="5" t="inlineStr">
         <is>
           <t>One of the best-known beach restaurants in the region. Fish and seafood with a spectacular view.</t>
         </is>
       </c>
-      <c r="J22" s="5" t="inlineStr">
+      <c r="K22" s="5" t="inlineStr">
         <is>
           <t>Uno de los restaurantes de playa más conocidos de la zona. Pescado y marisco con vistas espectaculares.</t>
         </is>
       </c>
-      <c r="K22" s="5" t="inlineStr">
+      <c r="L22" s="5" t="inlineStr">
         <is>
           <t>L’un des restaurants de plage les plus connus de la région. Poisson et fruits de mer avec une vue spectaculaire.</t>
         </is>
       </c>
-      <c r="L22" s="5" t="inlineStr">
+      <c r="M22" s="5" t="inlineStr">
         <is>
           <t>Eines der bekanntesten Strandrestaurants der Region. Fisch und Meeresfrüchte mit spektakulärer Aussicht.</t>
         </is>
       </c>
-      <c r="M22" s="5" t="inlineStr">
+      <c r="N22" s="5" t="inlineStr">
         <is>
           <t>Uno dei ristoranti sulla spiaggia più noti della zona. Pesce e frutti di mare con una vista spettacolare.</t>
         </is>
@@ -6436,32 +6499,33 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="H23" s="6" t="inlineStr">
+      <c r="H23" s="5" t="inlineStr"/>
+      <c r="I23" s="6" t="inlineStr">
         <is>
           <t>Marisqueira tradicional muito conhecida: marisco, arroz de marisco e cataplanas. Boa para grupos.</t>
         </is>
       </c>
-      <c r="I23" s="5" t="inlineStr">
+      <c r="J23" s="5" t="inlineStr">
         <is>
           <t>Famous traditional seafood house: shellfish, seafood rice and cataplanas. Good for groups.</t>
         </is>
       </c>
-      <c r="J23" s="5" t="inlineStr">
+      <c r="K23" s="5" t="inlineStr">
         <is>
           <t>Marisquería tradicional muy conocida: marisco, arroz con marisco y cataplanas. Buena para grupos.</t>
         </is>
       </c>
-      <c r="K23" s="5" t="inlineStr">
+      <c r="L23" s="5" t="inlineStr">
         <is>
           <t>Célèbre maison de fruits de mer : coquillages, riz aux fruits de mer et cataplanas. Idéale en groupe.</t>
         </is>
       </c>
-      <c r="L23" s="5" t="inlineStr">
+      <c r="M23" s="5" t="inlineStr">
         <is>
           <t>Bekanntes traditionelles Meeresfrüchte-Lokal: Meeresfrüchte, Meeresfrüchtereis und Cataplanas. Gut für Gruppen.</t>
         </is>
       </c>
-      <c r="M23" s="5" t="inlineStr">
+      <c r="N23" s="5" t="inlineStr">
         <is>
           <t>Famosa marisqueira tradizionale: frutti di mare, riso ai frutti di mare e cataplane. Ottima per gruppi.</t>
         </is>
@@ -6503,32 +6567,33 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="H24" s="6" t="inlineStr">
+      <c r="H24" s="5" t="inlineStr"/>
+      <c r="I24" s="6" t="inlineStr">
         <is>
           <t>Casa típica com cozinha regional algarvia: peixe, cataplanas e carnes. Ambiente rústico e acolhedor.</t>
         </is>
       </c>
-      <c r="I24" s="5" t="inlineStr">
+      <c r="J24" s="5" t="inlineStr">
         <is>
           <t>Typical house serving regional Algarve food: fish, cataplanas and meat. Rustic and cosy.</t>
         </is>
       </c>
-      <c r="J24" s="5" t="inlineStr">
+      <c r="K24" s="5" t="inlineStr">
         <is>
           <t>Casa típica con cocina regional del Algarve: pescado, cataplanas y carnes. Rústico y acogedor.</t>
         </is>
       </c>
-      <c r="K24" s="5" t="inlineStr">
+      <c r="L24" s="5" t="inlineStr">
         <is>
           <t>Maison typique, cuisine régionale de l’Algarve : poisson, cataplanas et viandes. Rustique et chaleureux.</t>
         </is>
       </c>
-      <c r="L24" s="5" t="inlineStr">
+      <c r="M24" s="5" t="inlineStr">
         <is>
           <t>Typisches Haus mit regionaler Algarve-Küche: Fisch, Cataplanas und Fleisch. Rustikal und gemütlich.</t>
         </is>
       </c>
-      <c r="M24" s="5" t="inlineStr">
+      <c r="N24" s="5" t="inlineStr">
         <is>
           <t>Casa tipica con cucina regionale dell’Algarve: pesce, cataplane e carne. Rustico e accogliente.</t>
         </is>
@@ -6570,32 +6635,37 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="H25" s="6" t="inlineStr">
+      <c r="H25" s="5" t="inlineStr">
+        <is>
+          <t>images/ilustracoes/rest-grill.svg</t>
+        </is>
+      </c>
+      <c r="I25" s="6" t="inlineStr">
         <is>
           <t>Carnes grelhadas, tábuas para partilhar e vinhos. Muito bem avaliado, ótimo para famílias e grupos.</t>
         </is>
       </c>
-      <c r="I25" s="5" t="inlineStr">
+      <c r="J25" s="5" t="inlineStr">
         <is>
           <t>Grilled meats, sharing boards and wine. Very well rated, great for families and groups.</t>
         </is>
       </c>
-      <c r="J25" s="5" t="inlineStr">
+      <c r="K25" s="5" t="inlineStr">
         <is>
           <t>Carnes a la parrilla, tablas para compartir y vinos. Muy bien valorado, ideal para familias y grupos.</t>
         </is>
       </c>
-      <c r="K25" s="5" t="inlineStr">
+      <c r="L25" s="5" t="inlineStr">
         <is>
           <t>Grillades, planches à partager et vins. Très bien noté, idéal pour familles et groupes.</t>
         </is>
       </c>
-      <c r="L25" s="5" t="inlineStr">
+      <c r="M25" s="5" t="inlineStr">
         <is>
           <t>Grillfleisch, Platten zum Teilen und Wein. Sehr gut bewertet, ideal für Familien und Gruppen.</t>
         </is>
       </c>
-      <c r="M25" s="5" t="inlineStr">
+      <c r="N25" s="5" t="inlineStr">
         <is>
           <t>Carni alla griglia, taglieri da condividere e vini. Ottime recensioni, ideale per famiglie e gruppi.</t>
         </is>
@@ -6637,32 +6707,37 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="H26" s="6" t="inlineStr">
+      <c r="H26" s="5" t="inlineStr">
+        <is>
+          <t>images/ilustracoes/rest-grill.svg</t>
+        </is>
+      </c>
+      <c r="I26" s="6" t="inlineStr">
         <is>
           <t>Muito bem avaliado: carnes, tapas e pratos internacionais. Ambiente informal e bom serviço.</t>
         </is>
       </c>
-      <c r="I26" s="5" t="inlineStr">
+      <c r="J26" s="5" t="inlineStr">
         <is>
           <t>Highly rated: meat, tapas and international dishes. Informal atmosphere and good service.</t>
         </is>
       </c>
-      <c r="J26" s="5" t="inlineStr">
+      <c r="K26" s="5" t="inlineStr">
         <is>
           <t>Muy bien valorado: carnes, tapas y platos internacionales. Ambiente informal y buen servicio.</t>
         </is>
       </c>
-      <c r="K26" s="5" t="inlineStr">
+      <c r="L26" s="5" t="inlineStr">
         <is>
           <t>Très bien noté : viandes, tapas et plats internationaux. Ambiance décontractée et bon service.</t>
         </is>
       </c>
-      <c r="L26" s="5" t="inlineStr">
+      <c r="M26" s="5" t="inlineStr">
         <is>
           <t>Sehr gut bewertet: Fleisch, Tapas und internationale Gerichte. Ungezwungene Atmosphäre, guter Service.</t>
         </is>
       </c>
-      <c r="M26" s="5" t="inlineStr">
+      <c r="N26" s="5" t="inlineStr">
         <is>
           <t>Ottime recensioni: carne, tapas e piatti internazionali. Ambiente informale e buon servizio.</t>
         </is>
@@ -6704,32 +6779,33 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="H27" s="6" t="inlineStr">
+      <c r="H27" s="5" t="inlineStr"/>
+      <c r="I27" s="6" t="inlineStr">
         <is>
           <t>Comida portuguesa caseira e ambiente familiar. Boa relação qualidade/preço.</t>
         </is>
       </c>
-      <c r="I27" s="5" t="inlineStr">
+      <c r="J27" s="5" t="inlineStr">
         <is>
           <t>Home-style Portuguese food in a family atmosphere. Good value for money.</t>
         </is>
       </c>
-      <c r="J27" s="5" t="inlineStr">
+      <c r="K27" s="5" t="inlineStr">
         <is>
           <t>Comida portuguesa casera y ambiente familiar. Buena relación calidad-precio.</t>
         </is>
       </c>
-      <c r="K27" s="5" t="inlineStr">
+      <c r="L27" s="5" t="inlineStr">
         <is>
           <t>Cuisine portugaise maison dans une ambiance familiale. Bon rapport qualité-prix.</t>
         </is>
       </c>
-      <c r="L27" s="5" t="inlineStr">
+      <c r="M27" s="5" t="inlineStr">
         <is>
           <t>Portugiesische Hausmannskost in familiärer Atmosphäre. Gutes Preis-Leistungs-Verhältnis.</t>
         </is>
       </c>
-      <c r="M27" s="5" t="inlineStr">
+      <c r="N27" s="5" t="inlineStr">
         <is>
           <t>Cucina portoghese casalinga in un ambiente familiare. Buon rapporto qualità-prezzo.</t>
         </is>
@@ -6771,32 +6847,33 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="H28" s="6" t="inlineStr">
+      <c r="H28" s="5" t="inlineStr"/>
+      <c r="I28" s="6" t="inlineStr">
         <is>
           <t>Pequeno restaurante muito apreciado pela comida caseira, simpatia e excelente relação qualidade/preço.</t>
         </is>
       </c>
-      <c r="I28" s="5" t="inlineStr">
+      <c r="J28" s="5" t="inlineStr">
         <is>
           <t>Small, much-loved restaurant for home cooking, friendly service and excellent value.</t>
         </is>
       </c>
-      <c r="J28" s="5" t="inlineStr">
+      <c r="K28" s="5" t="inlineStr">
         <is>
           <t>Pequeño restaurante muy apreciado por su comida casera, su simpatía y su excelente relación calidad-precio.</t>
         </is>
       </c>
-      <c r="K28" s="5" t="inlineStr">
+      <c r="L28" s="5" t="inlineStr">
         <is>
           <t>Petit restaurant très apprécié pour sa cuisine maison, son accueil et son excellent rapport qualité-prix.</t>
         </is>
       </c>
-      <c r="L28" s="5" t="inlineStr">
+      <c r="M28" s="5" t="inlineStr">
         <is>
           <t>Kleines, beliebtes Lokal mit Hausmannskost, freundlichem Service und sehr gutem Preis-Leistungs-Verhältnis.</t>
         </is>
       </c>
-      <c r="M28" s="5" t="inlineStr">
+      <c r="N28" s="5" t="inlineStr">
         <is>
           <t>Piccolo ristorante molto apprezzato per la cucina casalinga, la cordialità e l’ottimo rapporto qualità-prezzo.</t>
         </is>
@@ -6838,32 +6915,37 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="H29" s="6" t="inlineStr">
+      <c r="H29" s="5" t="inlineStr">
+        <is>
+          <t>images/ilustracoes/rest-sardines.svg</t>
+        </is>
+      </c>
+      <c r="I29" s="6" t="inlineStr">
         <is>
           <t>Muito conhecido pelos almoços económicos: pratos do dia, peixe grelhado e comida caseira. Ótimo para famílias.</t>
         </is>
       </c>
-      <c r="I29" s="5" t="inlineStr">
+      <c r="J29" s="5" t="inlineStr">
         <is>
           <t>Well known for good-value lunches: dish of the day, grilled fish and home cooking. Great for families.</t>
         </is>
       </c>
-      <c r="J29" s="5" t="inlineStr">
+      <c r="K29" s="5" t="inlineStr">
         <is>
           <t>Muy conocido por sus comidas económicas: plato del día, pescado a la parrilla y comida casera. Ideal para familias.</t>
         </is>
       </c>
-      <c r="K29" s="5" t="inlineStr">
+      <c r="L29" s="5" t="inlineStr">
         <is>
           <t>Réputé pour ses déjeuners bon marché : plat du jour, poisson grillé et cuisine maison. Idéal en famille.</t>
         </is>
       </c>
-      <c r="L29" s="5" t="inlineStr">
+      <c r="M29" s="5" t="inlineStr">
         <is>
           <t>Bekannt für günstige Mittagessen: Tagesgericht, gegrillter Fisch und Hausmannskost. Ideal für Familien.</t>
         </is>
       </c>
-      <c r="M29" s="5" t="inlineStr">
+      <c r="N29" s="5" t="inlineStr">
         <is>
           <t>Famoso per i pranzi economici: piatto del giorno, pesce alla griglia e cucina casalinga. Ideale per famiglie.</t>
         </is>
@@ -6905,32 +6987,37 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="H30" s="6" t="inlineStr">
+      <c r="H30" s="5" t="inlineStr">
+        <is>
+          <t>images/ilustracoes/rest-sardines.svg</t>
+        </is>
+      </c>
+      <c r="I30" s="6" t="inlineStr">
         <is>
           <t>Cozinha portuguesa simples, peixe grelhado e pratos caseiros. Económico, ideal para almoços.</t>
         </is>
       </c>
-      <c r="I30" s="5" t="inlineStr">
+      <c r="J30" s="5" t="inlineStr">
         <is>
           <t>Simple Portuguese food, grilled fish and home-made dishes. Inexpensive, ideal for lunch.</t>
         </is>
       </c>
-      <c r="J30" s="5" t="inlineStr">
+      <c r="K30" s="5" t="inlineStr">
         <is>
           <t>Cocina portuguesa sencilla, pescado a la parrilla y platos caseros. Económico, ideal para comer.</t>
         </is>
       </c>
-      <c r="K30" s="5" t="inlineStr">
+      <c r="L30" s="5" t="inlineStr">
         <is>
           <t>Cuisine portugaise simple, poisson grillé et plats maison. Bon marché, idéal le midi.</t>
         </is>
       </c>
-      <c r="L30" s="5" t="inlineStr">
+      <c r="M30" s="5" t="inlineStr">
         <is>
           <t>Einfache portugiesische Küche, gegrillter Fisch und Hausmannskost. Günstig, ideal zum Mittagessen.</t>
         </is>
       </c>
-      <c r="M30" s="5" t="inlineStr">
+      <c r="N30" s="5" t="inlineStr">
         <is>
           <t>Cucina portoghese semplice, pesce alla griglia e piatti casalinghi. Economico, ideale per pranzo.</t>
         </is>
@@ -6972,32 +7059,33 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="H31" s="6" t="inlineStr">
+      <c r="H31" s="5" t="inlineStr"/>
+      <c r="I31" s="6" t="inlineStr">
         <is>
           <t>Comida tradicional portuguesa, doses generosas e preços acessíveis.</t>
         </is>
       </c>
-      <c r="I31" s="5" t="inlineStr">
+      <c r="J31" s="5" t="inlineStr">
         <is>
           <t>Traditional Portuguese food, generous portions and affordable prices.</t>
         </is>
       </c>
-      <c r="J31" s="5" t="inlineStr">
+      <c r="K31" s="5" t="inlineStr">
         <is>
           <t>Comida tradicional portuguesa, raciones generosas y precios asequibles.</t>
         </is>
       </c>
-      <c r="K31" s="5" t="inlineStr">
+      <c r="L31" s="5" t="inlineStr">
         <is>
           <t>Cuisine traditionnelle portugaise, portions généreuses et prix abordables.</t>
         </is>
       </c>
-      <c r="L31" s="5" t="inlineStr">
+      <c r="M31" s="5" t="inlineStr">
         <is>
           <t>Traditionelle portugiesische Küche, große Portionen und günstige Preise.</t>
         </is>
       </c>
-      <c r="M31" s="5" t="inlineStr">
+      <c r="N31" s="5" t="inlineStr">
         <is>
           <t>Cucina tradizionale portoghese, porzioni abbondanti e prezzi accessibili.</t>
         </is>
@@ -7039,32 +7127,37 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="H32" s="6" t="inlineStr">
+      <c r="H32" s="5" t="inlineStr">
+        <is>
+          <t>images/ilustracoes/rest-sardines.svg</t>
+        </is>
+      </c>
+      <c r="I32" s="6" t="inlineStr">
         <is>
           <t>Restaurante típico frequentado pelos locais: comida caseira e peixe grelhado a preços económicos.</t>
         </is>
       </c>
-      <c r="I32" s="5" t="inlineStr">
+      <c r="J32" s="5" t="inlineStr">
         <is>
           <t>Typical local eatery: home cooking and grilled fish at low prices.</t>
         </is>
       </c>
-      <c r="J32" s="5" t="inlineStr">
+      <c r="K32" s="5" t="inlineStr">
         <is>
           <t>Restaurante típico frecuentado por los vecinos: comida casera y pescado a la parrilla a buen precio.</t>
         </is>
       </c>
-      <c r="K32" s="5" t="inlineStr">
+      <c r="L32" s="5" t="inlineStr">
         <is>
           <t>Restaurant typique fréquenté par les habitants : cuisine maison et poisson grillé à petits prix.</t>
         </is>
       </c>
-      <c r="L32" s="5" t="inlineStr">
+      <c r="M32" s="5" t="inlineStr">
         <is>
           <t>Typisches Lokal der Einheimischen: Hausmannskost und gegrillter Fisch zu kleinen Preisen.</t>
         </is>
       </c>
-      <c r="M32" s="5" t="inlineStr">
+      <c r="N32" s="5" t="inlineStr">
         <is>
           <t>Trattoria tipica frequentata dai locali: cucina casalinga e pesce alla griglia a prezzi economici.</t>
         </is>
@@ -7106,32 +7199,37 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="H33" s="6" t="inlineStr">
+      <c r="H33" s="5" t="inlineStr">
+        <is>
+          <t>images/ilustracoes/rest-beer.svg</t>
+        </is>
+      </c>
+      <c r="I33" s="6" t="inlineStr">
         <is>
           <t>Inspiração bávara: cervejas, salsichas e schnitzel. Espaço animado, ótimo para famílias e grupos.</t>
         </is>
       </c>
-      <c r="I33" s="5" t="inlineStr">
+      <c r="J33" s="5" t="inlineStr">
         <is>
           <t>Bavarian-style: beers, sausages and schnitzel. Lively place, great for families and groups.</t>
         </is>
       </c>
-      <c r="J33" s="5" t="inlineStr">
+      <c r="K33" s="5" t="inlineStr">
         <is>
           <t>Inspiración bávara: cervezas, salchichas y schnitzel. Ambiente animado, ideal para familias y grupos.</t>
         </is>
       </c>
-      <c r="K33" s="5" t="inlineStr">
+      <c r="L33" s="5" t="inlineStr">
         <is>
           <t>Esprit bavarois : bières, saucisses et schnitzel. Lieu animé, idéal pour familles et groupes.</t>
         </is>
       </c>
-      <c r="L33" s="5" t="inlineStr">
+      <c r="M33" s="5" t="inlineStr">
         <is>
           <t>Bayerischer Stil: Bier, Würstchen und Schnitzel. Lebhaft, ideal für Familien und Gruppen.</t>
         </is>
       </c>
-      <c r="M33" s="5" t="inlineStr">
+      <c r="N33" s="5" t="inlineStr">
         <is>
           <t>Ispirazione bavarese: birre, salsicce e schnitzel. Ambiente vivace, ideale per famiglie e gruppi.</t>
         </is>
@@ -7173,32 +7271,37 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="H34" s="6" t="inlineStr">
+      <c r="H34" s="5" t="inlineStr">
+        <is>
+          <t>images/ilustracoes/rest-pizza.svg</t>
+        </is>
+      </c>
+      <c r="I34" s="6" t="inlineStr">
         <is>
           <t>Italiano informal: pizzas, massas e especialidades mediterrânicas. Bom para crianças.</t>
         </is>
       </c>
-      <c r="I34" s="5" t="inlineStr">
+      <c r="J34" s="5" t="inlineStr">
         <is>
           <t>Casual Italian: pizzas, pasta and Mediterranean dishes. Child-friendly.</t>
         </is>
       </c>
-      <c r="J34" s="5" t="inlineStr">
+      <c r="K34" s="5" t="inlineStr">
         <is>
           <t>Italiano informal: pizzas, pastas y especialidades mediterráneas. Adecuado para niños.</t>
         </is>
       </c>
-      <c r="K34" s="5" t="inlineStr">
+      <c r="L34" s="5" t="inlineStr">
         <is>
           <t>Italien décontracté : pizzas, pâtes et spécialités méditerranéennes. Adapté aux enfants.</t>
         </is>
       </c>
-      <c r="L34" s="5" t="inlineStr">
+      <c r="M34" s="5" t="inlineStr">
         <is>
           <t>Ungezwungener Italiener: Pizza, Pasta und mediterrane Spezialitäten. Kinderfreundlich.</t>
         </is>
       </c>
-      <c r="M34" s="5" t="inlineStr">
+      <c r="N34" s="5" t="inlineStr">
         <is>
           <t>Italiano informale: pizze, pasta e specialità mediterranee. Adatto ai bambini.</t>
         </is>
@@ -7240,32 +7343,37 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="H35" s="6" t="inlineStr">
+      <c r="H35" s="5" t="inlineStr">
+        <is>
+          <t>images/ilustracoes/rest-pizza.svg</t>
+        </is>
+      </c>
+      <c r="I35" s="6" t="inlineStr">
         <is>
           <t>Italiano com pizzas, massas e cozinha mediterrânica, com vista sobre as falésias.</t>
         </is>
       </c>
-      <c r="I35" s="5" t="inlineStr">
+      <c r="J35" s="5" t="inlineStr">
         <is>
           <t>Italian with pizzas, pasta and Mediterranean dishes, overlooking the cliffs.</t>
         </is>
       </c>
-      <c r="J35" s="5" t="inlineStr">
+      <c r="K35" s="5" t="inlineStr">
         <is>
           <t>Italiano con pizzas, pastas y cocina mediterránea, con vistas a los acantilados.</t>
         </is>
       </c>
-      <c r="K35" s="5" t="inlineStr">
+      <c r="L35" s="5" t="inlineStr">
         <is>
           <t>Italien avec pizzas, pâtes et cuisine méditerranéenne, vue sur les falaises.</t>
         </is>
       </c>
-      <c r="L35" s="5" t="inlineStr">
+      <c r="M35" s="5" t="inlineStr">
         <is>
           <t>Italiener mit Pizza, Pasta und mediterraner Küche, mit Blick auf die Klippen.</t>
         </is>
       </c>
-      <c r="M35" s="5" t="inlineStr">
+      <c r="N35" s="5" t="inlineStr">
         <is>
           <t>Italiano con pizze, pasta e cucina mediterranea, con vista sulle scogliere.</t>
         </is>
@@ -7307,32 +7415,37 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="H36" s="6" t="inlineStr">
+      <c r="H36" s="5" t="inlineStr">
+        <is>
+          <t>images/ilustracoes/rest-curry.svg</t>
+        </is>
+      </c>
+      <c r="I36" s="6" t="inlineStr">
         <is>
           <t>Cozinha indiana: caril, tandoori e pratos vegetarianos. Informal e a preços moderados.</t>
         </is>
       </c>
-      <c r="I36" s="5" t="inlineStr">
+      <c r="J36" s="5" t="inlineStr">
         <is>
           <t>Indian cuisine: curries, tandoori and vegetarian dishes. Informal and moderately priced.</t>
         </is>
       </c>
-      <c r="J36" s="5" t="inlineStr">
+      <c r="K36" s="5" t="inlineStr">
         <is>
           <t>Cocina india: curris, tandoori y platos vegetarianos. Informal y a precios moderados.</t>
         </is>
       </c>
-      <c r="K36" s="5" t="inlineStr">
+      <c r="L36" s="5" t="inlineStr">
         <is>
           <t>Cuisine indienne : currys, tandoori et plats végétariens. Décontracté et prix modérés.</t>
         </is>
       </c>
-      <c r="L36" s="5" t="inlineStr">
+      <c r="M36" s="5" t="inlineStr">
         <is>
           <t>Indische Küche: Currys, Tandoori und vegetarische Gerichte. Ungezwungen und preiswert.</t>
         </is>
       </c>
-      <c r="M36" s="5" t="inlineStr">
+      <c r="N36" s="5" t="inlineStr">
         <is>
           <t>Cucina indiana: curry, tandoori e piatti vegetariani. Informale e a prezzi moderati.</t>
         </is>
@@ -7374,32 +7487,33 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="H37" s="6" t="inlineStr">
+      <c r="H37" s="5" t="inlineStr"/>
+      <c r="I37" s="6" t="inlineStr">
         <is>
           <t>Cozinha portuguesa e internacional, carnes e peixe. Ambiente familiar e tranquilo.</t>
         </is>
       </c>
-      <c r="I37" s="5" t="inlineStr">
+      <c r="J37" s="5" t="inlineStr">
         <is>
           <t>Portuguese and international food, meat and fish. Quiet, family atmosphere.</t>
         </is>
       </c>
-      <c r="J37" s="5" t="inlineStr">
+      <c r="K37" s="5" t="inlineStr">
         <is>
           <t>Cocina portuguesa e internacional, carnes y pescado. Ambiente familiar y tranquilo.</t>
         </is>
       </c>
-      <c r="K37" s="5" t="inlineStr">
+      <c r="L37" s="5" t="inlineStr">
         <is>
           <t>Cuisine portugaise et internationale, viandes et poissons. Ambiance familiale et calme.</t>
         </is>
       </c>
-      <c r="L37" s="5" t="inlineStr">
+      <c r="M37" s="5" t="inlineStr">
         <is>
           <t>Portugiesische und internationale Küche, Fleisch und Fisch. Ruhige, familiäre Atmosphäre.</t>
         </is>
       </c>
-      <c r="M37" s="5" t="inlineStr">
+      <c r="N37" s="5" t="inlineStr">
         <is>
           <t>Cucina portoghese e internazionale, carne e pesce. Ambiente familiare e tranquillo.</t>
         </is>
@@ -7441,32 +7555,37 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="H38" s="6" t="inlineStr">
+      <c r="H38" s="5" t="inlineStr">
+        <is>
+          <t>images/ilustracoes/rest-grill.svg</t>
+        </is>
+      </c>
+      <c r="I38" s="6" t="inlineStr">
         <is>
           <t>Restaurante informal com grelhados e cozinha portuguesa simples. Opção económica.</t>
         </is>
       </c>
-      <c r="I38" s="5" t="inlineStr">
+      <c r="J38" s="5" t="inlineStr">
         <is>
           <t>Casual restaurant with grills and simple Portuguese food. A budget option.</t>
         </is>
       </c>
-      <c r="J38" s="5" t="inlineStr">
+      <c r="K38" s="5" t="inlineStr">
         <is>
           <t>Restaurante informal con parrilla y cocina portuguesa sencilla. Opción económica.</t>
         </is>
       </c>
-      <c r="K38" s="5" t="inlineStr">
+      <c r="L38" s="5" t="inlineStr">
         <is>
           <t>Restaurant décontracté, grillades et cuisine portugaise simple. Option économique.</t>
         </is>
       </c>
-      <c r="L38" s="5" t="inlineStr">
+      <c r="M38" s="5" t="inlineStr">
         <is>
           <t>Ungezwungenes Lokal mit Grillgerichten und einfacher portugiesischer Küche. Günstig.</t>
         </is>
       </c>
-      <c r="M38" s="5" t="inlineStr">
+      <c r="N38" s="5" t="inlineStr">
         <is>
           <t>Ristorante informale con grigliate e cucina portoghese semplice. Opzione economica.</t>
         </is>
@@ -7508,32 +7627,37 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="H39" s="6" t="inlineStr">
+      <c r="H39" s="5" t="inlineStr">
+        <is>
+          <t>images/ilustracoes/rest-chicken.svg</t>
+        </is>
+      </c>
+      <c r="I39" s="6" t="inlineStr">
         <is>
           <t>Restaurante histórico, famoso pelo frango piri-piri da Guia. Simples, familiar e muito popular.</t>
         </is>
       </c>
-      <c r="I39" s="5" t="inlineStr">
+      <c r="J39" s="5" t="inlineStr">
         <is>
           <t>Historic restaurant famous for Guia-style piri-piri chicken. Simple, family-friendly and very popular.</t>
         </is>
       </c>
-      <c r="J39" s="5" t="inlineStr">
+      <c r="K39" s="5" t="inlineStr">
         <is>
           <t>Restaurante histórico, famoso por el pollo piri-piri de Guia. Sencillo, familiar y muy popular.</t>
         </is>
       </c>
-      <c r="K39" s="5" t="inlineStr">
+      <c r="L39" s="5" t="inlineStr">
         <is>
           <t>Restaurant historique célèbre pour le poulet piri-piri de Guia. Simple, familial et très populaire.</t>
         </is>
       </c>
-      <c r="L39" s="5" t="inlineStr">
+      <c r="M39" s="5" t="inlineStr">
         <is>
           <t>Traditionsrestaurant, berühmt für Piri-Piri-Hähnchen aus Guia. Einfach, familiär und sehr beliebt.</t>
         </is>
       </c>
-      <c r="M39" s="5" t="inlineStr">
+      <c r="N39" s="5" t="inlineStr">
         <is>
           <t>Ristorante storico famoso per il pollo piri-piri di Guia. Semplice, familiare e molto popolare.</t>
         </is>
@@ -7575,32 +7699,33 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="H40" s="6" t="inlineStr">
+      <c r="H40" s="5" t="inlineStr"/>
+      <c r="I40" s="6" t="inlineStr">
         <is>
           <t>Muito bem avaliado: pequenos-almoços, café, quiches, tostas e refeições leves.</t>
         </is>
       </c>
-      <c r="I40" s="5" t="inlineStr">
+      <c r="J40" s="5" t="inlineStr">
         <is>
           <t>Highly rated: breakfasts, coffee, quiches, toasties and light meals.</t>
         </is>
       </c>
-      <c r="J40" s="5" t="inlineStr">
+      <c r="K40" s="5" t="inlineStr">
         <is>
           <t>Muy bien valorado: desayunos, café, quiches, tostadas y comidas ligeras.</t>
         </is>
       </c>
-      <c r="K40" s="5" t="inlineStr">
+      <c r="L40" s="5" t="inlineStr">
         <is>
           <t>Très bien noté : petits-déjeuners, café, quiches, croque-monsieur et repas légers.</t>
         </is>
       </c>
-      <c r="L40" s="5" t="inlineStr">
+      <c r="M40" s="5" t="inlineStr">
         <is>
           <t>Sehr gut bewertet: Frühstück, Kaffee, Quiches, Toasts und leichte Gerichte.</t>
         </is>
       </c>
-      <c r="M40" s="5" t="inlineStr">
+      <c r="N40" s="5" t="inlineStr">
         <is>
           <t>Ottime recensioni: colazioni, caffè, quiche, toast e pasti leggeri.</t>
         </is>
@@ -7642,39 +7767,40 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="H41" s="6" t="inlineStr">
+      <c r="H41" s="5" t="inlineStr"/>
+      <c r="I41" s="6" t="inlineStr">
         <is>
           <t>Pequenos-almoços, panquecas, hambúrgueres, wraps e cocktails. Bom para famílias.</t>
         </is>
       </c>
-      <c r="I41" s="5" t="inlineStr">
+      <c r="J41" s="5" t="inlineStr">
         <is>
           <t>Breakfasts, pancakes, burgers, wraps and cocktails. Family-friendly.</t>
         </is>
       </c>
-      <c r="J41" s="5" t="inlineStr">
+      <c r="K41" s="5" t="inlineStr">
         <is>
           <t>Desayunos, tortitas, hamburguesas, wraps y cócteles. Para familias.</t>
         </is>
       </c>
-      <c r="K41" s="5" t="inlineStr">
+      <c r="L41" s="5" t="inlineStr">
         <is>
           <t>Petits-déjeuners, pancakes, burgers, wraps et cocktails. Adapté aux familles.</t>
         </is>
       </c>
-      <c r="L41" s="5" t="inlineStr">
+      <c r="M41" s="5" t="inlineStr">
         <is>
           <t>Frühstück, Pancakes, Burger, Wraps und Cocktails. Familienfreundlich.</t>
         </is>
       </c>
-      <c r="M41" s="5" t="inlineStr">
+      <c r="N41" s="5" t="inlineStr">
         <is>
           <t>Colazioni, pancake, hamburger, wrap e cocktail. Adatto alle famiglie.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M41"/>
+  <autoFilter ref="A1:N41"/>
   <dataValidations count="3">
     <dataValidation sqref="A2:A500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Escolha um valor da lista" type="list">
       <formula1>"michelin,fine,wine,sea,trad,intl,cafe"</formula1>
@@ -7697,7 +7823,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC65"/>
+  <dimension ref="A1:AD65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -7711,13 +7837,13 @@
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="24" customWidth="1" min="10" max="10"/>
     <col width="9" customWidth="1" min="11" max="11"/>
-    <col width="44" customWidth="1" min="12" max="12"/>
+    <col width="26" customWidth="1" min="12" max="12"/>
     <col width="44" customWidth="1" min="13" max="13"/>
     <col width="44" customWidth="1" min="14" max="14"/>
     <col width="44" customWidth="1" min="15" max="15"/>
     <col width="44" customWidth="1" min="16" max="16"/>
     <col width="44" customWidth="1" min="17" max="17"/>
-    <col width="26" customWidth="1" min="18" max="18"/>
+    <col width="44" customWidth="1" min="18" max="18"/>
     <col width="26" customWidth="1" min="19" max="19"/>
     <col width="26" customWidth="1" min="20" max="20"/>
     <col width="26" customWidth="1" min="21" max="21"/>
@@ -7729,6 +7855,7 @@
     <col width="26" customWidth="1" min="27" max="27"/>
     <col width="26" customWidth="1" min="28" max="28"/>
     <col width="26" customWidth="1" min="29" max="29"/>
+    <col width="26" customWidth="1" min="30" max="30"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -7789,90 +7916,95 @@
       </c>
       <c r="L1" s="4" t="inlineStr">
         <is>
+          <t>imagem</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
           <t>desc_pt</t>
         </is>
       </c>
-      <c r="M1" s="4" t="inlineStr">
+      <c r="N1" s="4" t="inlineStr">
         <is>
           <t>desc_en</t>
         </is>
       </c>
-      <c r="N1" s="4" t="inlineStr">
+      <c r="O1" s="4" t="inlineStr">
         <is>
           <t>desc_es</t>
         </is>
       </c>
-      <c r="O1" s="4" t="inlineStr">
+      <c r="P1" s="4" t="inlineStr">
         <is>
           <t>desc_fr</t>
         </is>
       </c>
-      <c r="P1" s="4" t="inlineStr">
+      <c r="Q1" s="4" t="inlineStr">
         <is>
           <t>desc_de</t>
         </is>
       </c>
-      <c r="Q1" s="4" t="inlineStr">
+      <c r="R1" s="4" t="inlineStr">
         <is>
           <t>desc_it</t>
         </is>
       </c>
-      <c r="R1" s="4" t="inlineStr">
+      <c r="S1" s="4" t="inlineStr">
         <is>
           <t>habitual_pt</t>
         </is>
       </c>
-      <c r="S1" s="4" t="inlineStr">
+      <c r="T1" s="4" t="inlineStr">
         <is>
           <t>habitual_en</t>
         </is>
       </c>
-      <c r="T1" s="4" t="inlineStr">
+      <c r="U1" s="4" t="inlineStr">
         <is>
           <t>habitual_es</t>
         </is>
       </c>
-      <c r="U1" s="4" t="inlineStr">
+      <c r="V1" s="4" t="inlineStr">
         <is>
           <t>habitual_fr</t>
         </is>
       </c>
-      <c r="V1" s="4" t="inlineStr">
+      <c r="W1" s="4" t="inlineStr">
         <is>
           <t>habitual_de</t>
         </is>
       </c>
-      <c r="W1" s="4" t="inlineStr">
+      <c r="X1" s="4" t="inlineStr">
         <is>
           <t>habitual_it</t>
         </is>
       </c>
-      <c r="X1" s="4" t="inlineStr">
+      <c r="Y1" s="4" t="inlineStr">
         <is>
           <t>epoca_pt</t>
         </is>
       </c>
-      <c r="Y1" s="4" t="inlineStr">
+      <c r="Z1" s="4" t="inlineStr">
         <is>
           <t>epoca_en</t>
         </is>
       </c>
-      <c r="Z1" s="4" t="inlineStr">
+      <c r="AA1" s="4" t="inlineStr">
         <is>
           <t>epoca_es</t>
         </is>
       </c>
-      <c r="AA1" s="4" t="inlineStr">
+      <c r="AB1" s="4" t="inlineStr">
         <is>
           <t>epoca_fr</t>
         </is>
       </c>
-      <c r="AB1" s="4" t="inlineStr">
+      <c r="AC1" s="4" t="inlineStr">
         <is>
           <t>epoca_de</t>
         </is>
       </c>
-      <c r="AC1" s="4" t="inlineStr">
+      <c r="AD1" s="4" t="inlineStr">
         <is>
           <t>epoca_it</t>
         </is>
@@ -7918,48 +8050,53 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="L2" s="6" t="inlineStr">
+      <c r="L2" s="5" t="inlineStr">
+        <is>
+          <t>images/ilustracoes/ev-racing.svg</t>
+        </is>
+      </c>
+      <c r="M2" s="6" t="inlineStr">
         <is>
           <t>O Mundial de Fórmula 1 regressa ao Algarve: treinos, corridas e ambiente internacional. Edição de 2028 também confirmada.</t>
         </is>
       </c>
-      <c r="M2" s="5" t="inlineStr">
+      <c r="N2" s="5" t="inlineStr">
         <is>
           <t>Formula 1 returns to the Algarve: practice, races and an international atmosphere. A 2028 race is also confirmed.</t>
         </is>
       </c>
-      <c r="N2" s="5" t="inlineStr">
+      <c r="O2" s="5" t="inlineStr">
         <is>
           <t>La Fórmula 1 vuelve al Algarve: entrenamientos, carreras y ambiente internacional. También confirmada para 2028.</t>
         </is>
       </c>
-      <c r="O2" s="5" t="inlineStr">
+      <c r="P2" s="5" t="inlineStr">
         <is>
           <t>La Formule 1 revient en Algarve : essais, courses et ambiance internationale. Édition 2028 également confirmée.</t>
         </is>
       </c>
-      <c r="P2" s="5" t="inlineStr">
+      <c r="Q2" s="5" t="inlineStr">
         <is>
           <t>Die Formel 1 kehrt an die Algarve zurück: Training, Rennen und internationales Flair. Auch 2028 bestätigt.</t>
         </is>
       </c>
-      <c r="Q2" s="5" t="inlineStr">
+      <c r="R2" s="5" t="inlineStr">
         <is>
           <t>La Formula 1 torna in Algarve: prove, gare e atmosfera internazionale. Confermata anche l’edizione 2028.</t>
         </is>
       </c>
-      <c r="R2" s="6" t="inlineStr"/>
-      <c r="S2" s="5" t="inlineStr"/>
+      <c r="S2" s="6" t="inlineStr"/>
       <c r="T2" s="5" t="inlineStr"/>
       <c r="U2" s="5" t="inlineStr"/>
       <c r="V2" s="5" t="inlineStr"/>
       <c r="W2" s="5" t="inlineStr"/>
-      <c r="X2" s="6" t="inlineStr"/>
-      <c r="Y2" s="5" t="inlineStr"/>
+      <c r="X2" s="5" t="inlineStr"/>
+      <c r="Y2" s="6" t="inlineStr"/>
       <c r="Z2" s="5" t="inlineStr"/>
       <c r="AA2" s="5" t="inlineStr"/>
       <c r="AB2" s="5" t="inlineStr"/>
       <c r="AC2" s="5" t="inlineStr"/>
+      <c r="AD2" s="5" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
@@ -8001,48 +8138,53 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="L3" s="6" t="inlineStr">
+      <c r="L3" s="5" t="inlineStr">
+        <is>
+          <t>images/ilustracoes/ev-racing.svg</t>
+        </is>
+      </c>
+      <c r="M3" s="6" t="inlineStr">
         <is>
           <t>Um dos maiores eventos desportivos do Algarve, com os melhores pilotos de motociclismo do mundo.</t>
         </is>
       </c>
-      <c r="M3" s="5" t="inlineStr">
+      <c r="N3" s="5" t="inlineStr">
         <is>
           <t>One of the Algarve’s biggest sporting events, with the world’s best motorcycle riders.</t>
         </is>
       </c>
-      <c r="N3" s="5" t="inlineStr">
+      <c r="O3" s="5" t="inlineStr">
         <is>
           <t>Uno de los mayores eventos deportivos del Algarve, con los mejores pilotos de motociclismo del mundo.</t>
         </is>
       </c>
-      <c r="O3" s="5" t="inlineStr">
+      <c r="P3" s="5" t="inlineStr">
         <is>
           <t>L’un des plus grands événements sportifs de l’Algarve, avec les meilleurs pilotes moto du monde.</t>
         </is>
       </c>
-      <c r="P3" s="5" t="inlineStr">
+      <c r="Q3" s="5" t="inlineStr">
         <is>
           <t>Eines der größten Sportevents der Algarve mit den besten Motorradfahrern der Welt.</t>
         </is>
       </c>
-      <c r="Q3" s="5" t="inlineStr">
+      <c r="R3" s="5" t="inlineStr">
         <is>
           <t>Uno dei più grandi eventi sportivi dell’Algarve, con i migliori piloti di moto al mondo.</t>
         </is>
       </c>
-      <c r="R3" s="6" t="inlineStr"/>
-      <c r="S3" s="5" t="inlineStr"/>
+      <c r="S3" s="6" t="inlineStr"/>
       <c r="T3" s="5" t="inlineStr"/>
       <c r="U3" s="5" t="inlineStr"/>
       <c r="V3" s="5" t="inlineStr"/>
       <c r="W3" s="5" t="inlineStr"/>
-      <c r="X3" s="6" t="inlineStr"/>
-      <c r="Y3" s="5" t="inlineStr"/>
+      <c r="X3" s="5" t="inlineStr"/>
+      <c r="Y3" s="6" t="inlineStr"/>
       <c r="Z3" s="5" t="inlineStr"/>
       <c r="AA3" s="5" t="inlineStr"/>
       <c r="AB3" s="5" t="inlineStr"/>
       <c r="AC3" s="5" t="inlineStr"/>
+      <c r="AD3" s="5" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
@@ -8080,48 +8222,53 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="L4" s="6" t="inlineStr">
+      <c r="L4" s="5" t="inlineStr">
+        <is>
+          <t>images/ilustracoes/ev-racing.svg</t>
+        </is>
+      </c>
+      <c r="M4" s="6" t="inlineStr">
         <is>
           <t>Corridas de automóveis clássicos, competição histórica e exposições de carros emblemáticos.</t>
         </is>
       </c>
-      <c r="M4" s="5" t="inlineStr">
+      <c r="N4" s="5" t="inlineStr">
         <is>
           <t>Classic car racing, historic motorsport and displays of iconic cars.</t>
         </is>
       </c>
-      <c r="N4" s="5" t="inlineStr">
+      <c r="O4" s="5" t="inlineStr">
         <is>
           <t>Carreras de coches clásicos, competición histórica y exposiciones de coches emblemáticos.</t>
         </is>
       </c>
-      <c r="O4" s="5" t="inlineStr">
+      <c r="P4" s="5" t="inlineStr">
         <is>
           <t>Courses de voitures classiques, compétition historique et expositions de voitures mythiques.</t>
         </is>
       </c>
-      <c r="P4" s="5" t="inlineStr">
+      <c r="Q4" s="5" t="inlineStr">
         <is>
           <t>Oldtimerrennen, historischer Motorsport und Ausstellungen legendärer Autos.</t>
         </is>
       </c>
-      <c r="Q4" s="5" t="inlineStr">
+      <c r="R4" s="5" t="inlineStr">
         <is>
           <t>Gare di auto d’epoca, competizioni storiche ed esposizioni di auto iconiche.</t>
         </is>
       </c>
-      <c r="R4" s="6" t="inlineStr"/>
-      <c r="S4" s="5" t="inlineStr"/>
+      <c r="S4" s="6" t="inlineStr"/>
       <c r="T4" s="5" t="inlineStr"/>
       <c r="U4" s="5" t="inlineStr"/>
       <c r="V4" s="5" t="inlineStr"/>
       <c r="W4" s="5" t="inlineStr"/>
-      <c r="X4" s="6" t="inlineStr"/>
-      <c r="Y4" s="5" t="inlineStr"/>
+      <c r="X4" s="5" t="inlineStr"/>
+      <c r="Y4" s="6" t="inlineStr"/>
       <c r="Z4" s="5" t="inlineStr"/>
       <c r="AA4" s="5" t="inlineStr"/>
       <c r="AB4" s="5" t="inlineStr"/>
       <c r="AC4" s="5" t="inlineStr"/>
+      <c r="AD4" s="5" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
@@ -8163,48 +8310,49 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="L5" s="6" t="inlineStr">
+      <c r="L5" s="5" t="inlineStr"/>
+      <c r="M5" s="6" t="inlineStr">
         <is>
           <t>Uma das maiores feiras do sul de Portugal: concertos, gastronomia, artesanato, agricultura e atividades equestres.</t>
         </is>
       </c>
-      <c r="M5" s="5" t="inlineStr">
+      <c r="N5" s="5" t="inlineStr">
         <is>
           <t>One of southern Portugal’s biggest fairs: concerts, food, crafts, farming and equestrian shows.</t>
         </is>
       </c>
-      <c r="N5" s="5" t="inlineStr">
+      <c r="O5" s="5" t="inlineStr">
         <is>
           <t>Una de las mayores ferias del sur de Portugal: conciertos, gastronomía, artesanía, agricultura y espectáculos ecuestres.</t>
         </is>
       </c>
-      <c r="O5" s="5" t="inlineStr">
+      <c r="P5" s="5" t="inlineStr">
         <is>
           <t>L’une des plus grandes foires du sud du Portugal : concerts, gastronomie, artisanat, agriculture et spectacles équestres.</t>
         </is>
       </c>
-      <c r="P5" s="5" t="inlineStr">
+      <c r="Q5" s="5" t="inlineStr">
         <is>
           <t>Eine der größten Messen Südportugals: Konzerte, Essen, Kunsthandwerk, Landwirtschaft und Reitvorführungen.</t>
         </is>
       </c>
-      <c r="Q5" s="5" t="inlineStr">
+      <c r="R5" s="5" t="inlineStr">
         <is>
           <t>Una delle più grandi fiere del sud del Portogallo: concerti, gastronomia, artigianato, agricoltura e spettacoli equestri.</t>
         </is>
       </c>
-      <c r="R5" s="6" t="inlineStr"/>
-      <c r="S5" s="5" t="inlineStr"/>
+      <c r="S5" s="6" t="inlineStr"/>
       <c r="T5" s="5" t="inlineStr"/>
       <c r="U5" s="5" t="inlineStr"/>
       <c r="V5" s="5" t="inlineStr"/>
       <c r="W5" s="5" t="inlineStr"/>
-      <c r="X5" s="6" t="inlineStr"/>
-      <c r="Y5" s="5" t="inlineStr"/>
+      <c r="X5" s="5" t="inlineStr"/>
+      <c r="Y5" s="6" t="inlineStr"/>
       <c r="Z5" s="5" t="inlineStr"/>
       <c r="AA5" s="5" t="inlineStr"/>
       <c r="AB5" s="5" t="inlineStr"/>
       <c r="AC5" s="5" t="inlineStr"/>
+      <c r="AD5" s="5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
@@ -8242,72 +8390,73 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="L6" s="6" t="inlineStr">
+      <c r="L6" s="5" t="inlineStr"/>
+      <c r="M6" s="6" t="inlineStr">
         <is>
           <t>A festa gastronómica mais tradicional da vila: caracóis, petiscos, artesanato e concertos populares.</t>
         </is>
       </c>
-      <c r="M6" s="5" t="inlineStr">
+      <c r="N6" s="5" t="inlineStr">
         <is>
           <t>The village’s most traditional food festival: snails, petiscos, crafts and live music.</t>
         </is>
       </c>
-      <c r="N6" s="5" t="inlineStr">
+      <c r="O6" s="5" t="inlineStr">
         <is>
           <t>La fiesta gastronómica más tradicional del pueblo: caracoles, tapas, artesanía y conciertos populares.</t>
         </is>
       </c>
-      <c r="O6" s="5" t="inlineStr">
+      <c r="P6" s="5" t="inlineStr">
         <is>
           <t>La fête gastronomique la plus traditionnelle du village : escargots, petiscos, artisanat et concerts.</t>
         </is>
       </c>
-      <c r="P6" s="5" t="inlineStr">
+      <c r="Q6" s="5" t="inlineStr">
         <is>
           <t>Das traditionellste Fest des Ortes: Schnecken, Häppchen, Kunsthandwerk und Volksmusik.</t>
         </is>
       </c>
-      <c r="Q6" s="5" t="inlineStr">
+      <c r="R6" s="5" t="inlineStr">
         <is>
           <t>La festa gastronomica più tradizionale del paese: lumache, stuzzichini, artigianato e concerti.</t>
         </is>
       </c>
-      <c r="R6" s="6" t="inlineStr">
+      <c r="S6" s="6" t="inlineStr">
         <is>
           <t>final de junho / início de julho</t>
         </is>
       </c>
-      <c r="S6" s="5" t="inlineStr">
+      <c r="T6" s="5" t="inlineStr">
         <is>
           <t>late June / early July</t>
         </is>
       </c>
-      <c r="T6" s="5" t="inlineStr">
+      <c r="U6" s="5" t="inlineStr">
         <is>
           <t>finales de junio / principios de julio</t>
         </is>
       </c>
-      <c r="U6" s="5" t="inlineStr">
+      <c r="V6" s="5" t="inlineStr">
         <is>
           <t>fin juin / début juillet</t>
         </is>
       </c>
-      <c r="V6" s="5" t="inlineStr">
+      <c r="W6" s="5" t="inlineStr">
         <is>
           <t>Ende Juni / Anfang Juli</t>
         </is>
       </c>
-      <c r="W6" s="5" t="inlineStr">
+      <c r="X6" s="5" t="inlineStr">
         <is>
           <t>fine giugno / inizio luglio</t>
         </is>
       </c>
-      <c r="X6" s="6" t="inlineStr"/>
-      <c r="Y6" s="5" t="inlineStr"/>
+      <c r="Y6" s="6" t="inlineStr"/>
       <c r="Z6" s="5" t="inlineStr"/>
       <c r="AA6" s="5" t="inlineStr"/>
       <c r="AB6" s="5" t="inlineStr"/>
       <c r="AC6" s="5" t="inlineStr"/>
+      <c r="AD6" s="5" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
@@ -8341,72 +8490,73 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="L7" s="6" t="inlineStr">
+      <c r="L7" s="5" t="inlineStr"/>
+      <c r="M7" s="6" t="inlineStr">
         <is>
           <t>Festa dedicada aos pratos de polvo, petiscos regionais, música e animação.</t>
         </is>
       </c>
-      <c r="M7" s="5" t="inlineStr">
+      <c r="N7" s="5" t="inlineStr">
         <is>
           <t>A festival of octopus dishes, regional snacks, music and entertainment.</t>
         </is>
       </c>
-      <c r="N7" s="5" t="inlineStr">
+      <c r="O7" s="5" t="inlineStr">
         <is>
           <t>Fiesta dedicada a los platos de pulpo, tapas regionales, música y animación.</t>
         </is>
       </c>
-      <c r="O7" s="5" t="inlineStr">
+      <c r="P7" s="5" t="inlineStr">
         <is>
           <t>Fête dédiée aux plats de poulpe, petiscos régionaux, musique et animations.</t>
         </is>
       </c>
-      <c r="P7" s="5" t="inlineStr">
+      <c r="Q7" s="5" t="inlineStr">
         <is>
           <t>Fest rund um Oktopus-Gerichte, regionale Häppchen, Musik und Unterhaltung.</t>
         </is>
       </c>
-      <c r="Q7" s="5" t="inlineStr">
+      <c r="R7" s="5" t="inlineStr">
         <is>
           <t>Festa dedicata ai piatti di polpo, stuzzichini regionali, musica e animazione.</t>
         </is>
       </c>
-      <c r="R7" s="6" t="inlineStr">
+      <c r="S7" s="6" t="inlineStr">
         <is>
           <t>agosto (confirmar com a Junta de Freguesia)</t>
         </is>
       </c>
-      <c r="S7" s="5" t="inlineStr">
+      <c r="T7" s="5" t="inlineStr">
         <is>
           <t>August (check with the parish council)</t>
         </is>
       </c>
-      <c r="T7" s="5" t="inlineStr">
+      <c r="U7" s="5" t="inlineStr">
         <is>
           <t>agosto (confirmar con la Junta de Freguesia)</t>
         </is>
       </c>
-      <c r="U7" s="5" t="inlineStr">
+      <c r="V7" s="5" t="inlineStr">
         <is>
           <t>août (à confirmer auprès de la mairie)</t>
         </is>
       </c>
-      <c r="V7" s="5" t="inlineStr">
+      <c r="W7" s="5" t="inlineStr">
         <is>
           <t>August (bei der Gemeinde nachfragen)</t>
         </is>
       </c>
-      <c r="W7" s="5" t="inlineStr">
+      <c r="X7" s="5" t="inlineStr">
         <is>
           <t>agosto (verificare con la Junta de Freguesia)</t>
         </is>
       </c>
-      <c r="X7" s="6" t="inlineStr"/>
-      <c r="Y7" s="5" t="inlineStr"/>
+      <c r="Y7" s="6" t="inlineStr"/>
       <c r="Z7" s="5" t="inlineStr"/>
       <c r="AA7" s="5" t="inlineStr"/>
       <c r="AB7" s="5" t="inlineStr"/>
       <c r="AC7" s="5" t="inlineStr"/>
+      <c r="AD7" s="5" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
@@ -8444,72 +8594,73 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="L8" s="6" t="inlineStr">
+      <c r="L8" s="5" t="inlineStr"/>
+      <c r="M8" s="6" t="inlineStr">
         <is>
           <t>Festa popular com caracóis, gastronomia, concertos, humor e animação familiar.</t>
         </is>
       </c>
-      <c r="M8" s="5" t="inlineStr">
+      <c r="N8" s="5" t="inlineStr">
         <is>
           <t>Popular festival with snails, food, concerts, comedy and family fun.</t>
         </is>
       </c>
-      <c r="N8" s="5" t="inlineStr">
+      <c r="O8" s="5" t="inlineStr">
         <is>
           <t>Fiesta popular con caracoles, gastronomía, conciertos, humor y animación familiar.</t>
         </is>
       </c>
-      <c r="O8" s="5" t="inlineStr">
+      <c r="P8" s="5" t="inlineStr">
         <is>
           <t>Fête populaire avec escargots, gastronomie, concerts, humour et animations familiales.</t>
         </is>
       </c>
-      <c r="P8" s="5" t="inlineStr">
+      <c r="Q8" s="5" t="inlineStr">
         <is>
           <t>Volksfest mit Schnecken, Essen, Konzerten, Comedy und Familienprogramm.</t>
         </is>
       </c>
-      <c r="Q8" s="5" t="inlineStr">
+      <c r="R8" s="5" t="inlineStr">
         <is>
           <t>Festa popolare con lumache, gastronomia, concerti, comicità e animazione per famiglie.</t>
         </is>
       </c>
-      <c r="R8" s="6" t="inlineStr">
+      <c r="S8" s="6" t="inlineStr">
         <is>
           <t>início de junho</t>
         </is>
       </c>
-      <c r="S8" s="5" t="inlineStr">
+      <c r="T8" s="5" t="inlineStr">
         <is>
           <t>early June</t>
         </is>
       </c>
-      <c r="T8" s="5" t="inlineStr">
+      <c r="U8" s="5" t="inlineStr">
         <is>
           <t>principios de junio</t>
         </is>
       </c>
-      <c r="U8" s="5" t="inlineStr">
+      <c r="V8" s="5" t="inlineStr">
         <is>
           <t>début juin</t>
         </is>
       </c>
-      <c r="V8" s="5" t="inlineStr">
+      <c r="W8" s="5" t="inlineStr">
         <is>
           <t>Anfang Juni</t>
         </is>
       </c>
-      <c r="W8" s="5" t="inlineStr">
+      <c r="X8" s="5" t="inlineStr">
         <is>
           <t>inizio giugno</t>
         </is>
       </c>
-      <c r="X8" s="6" t="inlineStr"/>
-      <c r="Y8" s="5" t="inlineStr"/>
+      <c r="Y8" s="6" t="inlineStr"/>
       <c r="Z8" s="5" t="inlineStr"/>
       <c r="AA8" s="5" t="inlineStr"/>
       <c r="AB8" s="5" t="inlineStr"/>
       <c r="AC8" s="5" t="inlineStr"/>
+      <c r="AD8" s="5" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
@@ -8551,72 +8702,77 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="L9" s="6" t="inlineStr">
+      <c r="L9" s="5" t="inlineStr">
+        <is>
+          <t>images/ilustracoes/rest-beer.svg</t>
+        </is>
+      </c>
+      <c r="M9" s="6" t="inlineStr">
         <is>
           <t>Cerveja bávara, comida típica, mesas comunitárias e música ao vivo, mesmo ao lado de Porches.</t>
         </is>
       </c>
-      <c r="M9" s="5" t="inlineStr">
+      <c r="N9" s="5" t="inlineStr">
         <is>
           <t>Bavarian beer, traditional food, long tables and live music, right next to Porches.</t>
         </is>
       </c>
-      <c r="N9" s="5" t="inlineStr">
+      <c r="O9" s="5" t="inlineStr">
         <is>
           <t>Cerveza bávara, comida típica, mesas compartidas y música en directo, junto a Porches.</t>
         </is>
       </c>
-      <c r="O9" s="5" t="inlineStr">
+      <c r="P9" s="5" t="inlineStr">
         <is>
           <t>Bière bavaroise, plats typiques, grandes tablées et musique live, tout près de Porches.</t>
         </is>
       </c>
-      <c r="P9" s="5" t="inlineStr">
+      <c r="Q9" s="5" t="inlineStr">
         <is>
           <t>Bayerisches Bier, typisches Essen, lange Tische und Livemusik direkt bei Porches.</t>
         </is>
       </c>
-      <c r="Q9" s="5" t="inlineStr">
+      <c r="R9" s="5" t="inlineStr">
         <is>
           <t>Birra bavarese, cibo tipico, tavolate e musica dal vivo, a due passi da Porches.</t>
         </is>
       </c>
-      <c r="R9" s="6" t="inlineStr">
+      <c r="S9" s="6" t="inlineStr">
         <is>
           <t>final de setembro / início de outubro</t>
         </is>
       </c>
-      <c r="S9" s="5" t="inlineStr">
+      <c r="T9" s="5" t="inlineStr">
         <is>
           <t>late September / early October</t>
         </is>
       </c>
-      <c r="T9" s="5" t="inlineStr">
+      <c r="U9" s="5" t="inlineStr">
         <is>
           <t>finales de septiembre / principios de octubre</t>
         </is>
       </c>
-      <c r="U9" s="5" t="inlineStr">
+      <c r="V9" s="5" t="inlineStr">
         <is>
           <t>fin septembre / début octobre</t>
         </is>
       </c>
-      <c r="V9" s="5" t="inlineStr">
+      <c r="W9" s="5" t="inlineStr">
         <is>
           <t>Ende September / Anfang Oktober</t>
         </is>
       </c>
-      <c r="W9" s="5" t="inlineStr">
+      <c r="X9" s="5" t="inlineStr">
         <is>
           <t>fine settembre / inizio ottobre</t>
         </is>
       </c>
-      <c r="X9" s="6" t="inlineStr"/>
-      <c r="Y9" s="5" t="inlineStr"/>
+      <c r="Y9" s="6" t="inlineStr"/>
       <c r="Z9" s="5" t="inlineStr"/>
       <c r="AA9" s="5" t="inlineStr"/>
       <c r="AB9" s="5" t="inlineStr"/>
       <c r="AC9" s="5" t="inlineStr"/>
+      <c r="AD9" s="5" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
@@ -8654,72 +8810,77 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="L10" s="6" t="inlineStr">
+      <c r="L10" s="5" t="inlineStr">
+        <is>
+          <t>images/ilustracoes/rest-beer.svg</t>
+        </is>
+      </c>
+      <c r="M10" s="6" t="inlineStr">
         <is>
           <t>Cerveja, street food, DJs e concertos na Praça Al-Muthamid. Entrada habitualmente gratuita.</t>
         </is>
       </c>
-      <c r="M10" s="5" t="inlineStr">
+      <c r="N10" s="5" t="inlineStr">
         <is>
           <t>Beer, street food, DJs and concerts in Praça Al-Muthamid. Usually free entry.</t>
         </is>
       </c>
-      <c r="N10" s="5" t="inlineStr">
+      <c r="O10" s="5" t="inlineStr">
         <is>
           <t>Cerveza, street food, DJs y conciertos en la Praça Al-Muthamid. Entrada normalmente gratuita.</t>
         </is>
       </c>
-      <c r="O10" s="5" t="inlineStr">
+      <c r="P10" s="5" t="inlineStr">
         <is>
           <t>Bière, street food, DJ et concerts place Al-Muthamid. Entrée généralement gratuite.</t>
         </is>
       </c>
-      <c r="P10" s="5" t="inlineStr">
+      <c r="Q10" s="5" t="inlineStr">
         <is>
           <t>Bier, Streetfood, DJs und Konzerte auf der Praça Al-Muthamid. Meist freier Eintritt.</t>
         </is>
       </c>
-      <c r="Q10" s="5" t="inlineStr">
+      <c r="R10" s="5" t="inlineStr">
         <is>
           <t>Birra, street food, DJ e concerti in Praça Al-Muthamid. Ingresso di solito gratuito.</t>
         </is>
       </c>
-      <c r="R10" s="6" t="inlineStr">
+      <c r="S10" s="6" t="inlineStr">
         <is>
           <t>meados de julho</t>
         </is>
       </c>
-      <c r="S10" s="5" t="inlineStr">
+      <c r="T10" s="5" t="inlineStr">
         <is>
           <t>mid-July</t>
         </is>
       </c>
-      <c r="T10" s="5" t="inlineStr">
+      <c r="U10" s="5" t="inlineStr">
         <is>
           <t>mediados de julio</t>
         </is>
       </c>
-      <c r="U10" s="5" t="inlineStr">
+      <c r="V10" s="5" t="inlineStr">
         <is>
           <t>mi-juillet</t>
         </is>
       </c>
-      <c r="V10" s="5" t="inlineStr">
+      <c r="W10" s="5" t="inlineStr">
         <is>
           <t>Mitte Juli</t>
         </is>
       </c>
-      <c r="W10" s="5" t="inlineStr">
+      <c r="X10" s="5" t="inlineStr">
         <is>
           <t>metà luglio</t>
         </is>
       </c>
-      <c r="X10" s="6" t="inlineStr"/>
-      <c r="Y10" s="5" t="inlineStr"/>
+      <c r="Y10" s="6" t="inlineStr"/>
       <c r="Z10" s="5" t="inlineStr"/>
       <c r="AA10" s="5" t="inlineStr"/>
       <c r="AB10" s="5" t="inlineStr"/>
       <c r="AC10" s="5" t="inlineStr"/>
+      <c r="AD10" s="5" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
@@ -8757,72 +8918,77 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="L11" s="6" t="inlineStr">
+      <c r="L11" s="5" t="inlineStr">
+        <is>
+          <t>images/ilustracoes/rest-beer.svg</t>
+        </is>
+      </c>
+      <c r="M11" s="6" t="inlineStr">
         <is>
           <t>Cervejas internacionais, comida de rua e música na Fortaleza de Santa Catarina, Praia da Rocha.</t>
         </is>
       </c>
-      <c r="M11" s="5" t="inlineStr">
+      <c r="N11" s="5" t="inlineStr">
         <is>
           <t>International beers, street food and music at the Santa Catarina fortress, Praia da Rocha.</t>
         </is>
       </c>
-      <c r="N11" s="5" t="inlineStr">
+      <c r="O11" s="5" t="inlineStr">
         <is>
           <t>Cervezas internacionales, comida callejera y música en la Fortaleza de Santa Catarina, Praia da Rocha.</t>
         </is>
       </c>
-      <c r="O11" s="5" t="inlineStr">
+      <c r="P11" s="5" t="inlineStr">
         <is>
           <t>Bières internationales, street food et musique à la forteresse de Santa Catarina, Praia da Rocha.</t>
         </is>
       </c>
-      <c r="P11" s="5" t="inlineStr">
+      <c r="Q11" s="5" t="inlineStr">
         <is>
           <t>Internationale Biere, Streetfood und Musik in der Festung Santa Catarina, Praia da Rocha.</t>
         </is>
       </c>
-      <c r="Q11" s="5" t="inlineStr">
+      <c r="R11" s="5" t="inlineStr">
         <is>
           <t>Birre internazionali, street food e musica alla fortezza di Santa Catarina, Praia da Rocha.</t>
         </is>
       </c>
-      <c r="R11" s="6" t="inlineStr">
+      <c r="S11" s="6" t="inlineStr">
         <is>
           <t>setembro (1.ª edição em 2026; confirmar)</t>
         </is>
       </c>
-      <c r="S11" s="5" t="inlineStr">
+      <c r="T11" s="5" t="inlineStr">
         <is>
           <t>September (first held 2026; check)</t>
         </is>
       </c>
-      <c r="T11" s="5" t="inlineStr">
+      <c r="U11" s="5" t="inlineStr">
         <is>
           <t>septiembre (1.ª edición en 2026; confirmar)</t>
         </is>
       </c>
-      <c r="U11" s="5" t="inlineStr">
+      <c r="V11" s="5" t="inlineStr">
         <is>
           <t>septembre (1re édition en 2026 ; à confirmer)</t>
         </is>
       </c>
-      <c r="V11" s="5" t="inlineStr">
+      <c r="W11" s="5" t="inlineStr">
         <is>
           <t>September (erstmals 2026; bitte prüfen)</t>
         </is>
       </c>
-      <c r="W11" s="5" t="inlineStr">
+      <c r="X11" s="5" t="inlineStr">
         <is>
           <t>settembre (1ª edizione nel 2026; da confermare)</t>
         </is>
       </c>
-      <c r="X11" s="6" t="inlineStr"/>
-      <c r="Y11" s="5" t="inlineStr"/>
+      <c r="Y11" s="6" t="inlineStr"/>
       <c r="Z11" s="5" t="inlineStr"/>
       <c r="AA11" s="5" t="inlineStr"/>
       <c r="AB11" s="5" t="inlineStr"/>
       <c r="AC11" s="5" t="inlineStr"/>
+      <c r="AD11" s="5" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
@@ -8864,48 +9030,53 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="L12" s="6" t="inlineStr">
+      <c r="L12" s="5" t="inlineStr">
+        <is>
+          <t>images/ilustracoes/rest-sardines.svg</t>
+        </is>
+      </c>
+      <c r="M12" s="6" t="inlineStr">
         <is>
           <t>Grande festa popular da sardinha assada junto ao rio, com tasquinhas, espetáculos e concertos.</t>
         </is>
       </c>
-      <c r="M12" s="5" t="inlineStr">
+      <c r="N12" s="5" t="inlineStr">
         <is>
           <t>Big riverside festival of grilled sardines, with food stalls, shows and concerts.</t>
         </is>
       </c>
-      <c r="N12" s="5" t="inlineStr">
+      <c r="O12" s="5" t="inlineStr">
         <is>
           <t>Gran fiesta popular de la sardina asada junto al río, con puestos, espectáculos y conciertos.</t>
         </is>
       </c>
-      <c r="O12" s="5" t="inlineStr">
+      <c r="P12" s="5" t="inlineStr">
         <is>
           <t>Grande fête populaire de la sardine grillée au bord du fleuve, avec stands, spectacles et concerts.</t>
         </is>
       </c>
-      <c r="P12" s="5" t="inlineStr">
+      <c r="Q12" s="5" t="inlineStr">
         <is>
           <t>Großes Sardinenfest am Fluss mit Essensständen, Shows und Konzerten.</t>
         </is>
       </c>
-      <c r="Q12" s="5" t="inlineStr">
+      <c r="R12" s="5" t="inlineStr">
         <is>
           <t>Grande festa popolare della sardina alla griglia sul fiume, con stand, spettacoli e concerti.</t>
         </is>
       </c>
-      <c r="R12" s="6" t="inlineStr"/>
-      <c r="S12" s="5" t="inlineStr"/>
+      <c r="S12" s="6" t="inlineStr"/>
       <c r="T12" s="5" t="inlineStr"/>
       <c r="U12" s="5" t="inlineStr"/>
       <c r="V12" s="5" t="inlineStr"/>
       <c r="W12" s="5" t="inlineStr"/>
-      <c r="X12" s="6" t="inlineStr"/>
-      <c r="Y12" s="5" t="inlineStr"/>
+      <c r="X12" s="5" t="inlineStr"/>
+      <c r="Y12" s="6" t="inlineStr"/>
       <c r="Z12" s="5" t="inlineStr"/>
       <c r="AA12" s="5" t="inlineStr"/>
       <c r="AB12" s="5" t="inlineStr"/>
       <c r="AC12" s="5" t="inlineStr"/>
+      <c r="AD12" s="5" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
@@ -8943,72 +9114,73 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="L13" s="6" t="inlineStr">
+      <c r="L13" s="5" t="inlineStr"/>
+      <c r="M13" s="6" t="inlineStr">
         <is>
           <t>Recriação medieval no castelo e centro histórico: torneios, mercados, trajes de época e espetáculos.</t>
         </is>
       </c>
-      <c r="M13" s="5" t="inlineStr">
+      <c r="N13" s="5" t="inlineStr">
         <is>
           <t>Medieval re-enactment at the castle and old town: tournaments, markets, costumes and shows.</t>
         </is>
       </c>
-      <c r="N13" s="5" t="inlineStr">
+      <c r="O13" s="5" t="inlineStr">
         <is>
           <t>Recreación medieval en el castillo y el casco histórico: torneos, mercados, trajes de época y espectáculos.</t>
         </is>
       </c>
-      <c r="O13" s="5" t="inlineStr">
+      <c r="P13" s="5" t="inlineStr">
         <is>
           <t>Reconstitution médiévale au château et dans la vieille ville : tournois, marchés, costumes et spectacles.</t>
         </is>
       </c>
-      <c r="P13" s="5" t="inlineStr">
+      <c r="Q13" s="5" t="inlineStr">
         <is>
           <t>Mittelalterfest an der Burg und in der Altstadt: Turniere, Märkte, Kostüme und Shows.</t>
         </is>
       </c>
-      <c r="Q13" s="5" t="inlineStr">
+      <c r="R13" s="5" t="inlineStr">
         <is>
           <t>Rievocazione medievale al castello e nel centro storico: tornei, mercati, costumi e spettacoli.</t>
         </is>
       </c>
-      <c r="R13" s="6" t="inlineStr">
+      <c r="S13" s="6" t="inlineStr">
         <is>
           <t>agosto</t>
         </is>
       </c>
-      <c r="S13" s="5" t="inlineStr">
+      <c r="T13" s="5" t="inlineStr">
         <is>
           <t>August</t>
         </is>
       </c>
-      <c r="T13" s="5" t="inlineStr">
+      <c r="U13" s="5" t="inlineStr">
         <is>
           <t>agosto</t>
         </is>
       </c>
-      <c r="U13" s="5" t="inlineStr">
+      <c r="V13" s="5" t="inlineStr">
         <is>
           <t>août</t>
         </is>
       </c>
-      <c r="V13" s="5" t="inlineStr">
+      <c r="W13" s="5" t="inlineStr">
         <is>
           <t>August</t>
         </is>
       </c>
-      <c r="W13" s="5" t="inlineStr">
+      <c r="X13" s="5" t="inlineStr">
         <is>
           <t>agosto</t>
         </is>
       </c>
-      <c r="X13" s="6" t="inlineStr"/>
-      <c r="Y13" s="5" t="inlineStr"/>
+      <c r="Y13" s="6" t="inlineStr"/>
       <c r="Z13" s="5" t="inlineStr"/>
       <c r="AA13" s="5" t="inlineStr"/>
       <c r="AB13" s="5" t="inlineStr"/>
       <c r="AC13" s="5" t="inlineStr"/>
+      <c r="AD13" s="5" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -9046,72 +9218,73 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="L14" s="6" t="inlineStr">
+      <c r="L14" s="5" t="inlineStr"/>
+      <c r="M14" s="6" t="inlineStr">
         <is>
           <t>Grande festa de verão com vários palcos, DJs e milhares de pessoas vestidas de preto e branco. Entrada habitualmente gratuita.</t>
         </is>
       </c>
-      <c r="M14" s="5" t="inlineStr">
+      <c r="N14" s="5" t="inlineStr">
         <is>
           <t>Huge summer party with several stages, DJs and thousands dressed in black and white. Usually free.</t>
         </is>
       </c>
-      <c r="N14" s="5" t="inlineStr">
+      <c r="O14" s="5" t="inlineStr">
         <is>
           <t>Gran fiesta de verano con varios escenarios, DJs y miles de personas vestidas de blanco y negro. Normalmente gratis.</t>
         </is>
       </c>
-      <c r="O14" s="5" t="inlineStr">
+      <c r="P14" s="5" t="inlineStr">
         <is>
           <t>Grande fête d’été avec plusieurs scènes, DJ et des milliers de personnes en noir et blanc. Généralement gratuit.</t>
         </is>
       </c>
-      <c r="P14" s="5" t="inlineStr">
+      <c r="Q14" s="5" t="inlineStr">
         <is>
           <t>Große Sommerparty mit mehreren Bühnen, DJs und Tausenden in Schwarz-Weiß. Meist gratis.</t>
         </is>
       </c>
-      <c r="Q14" s="5" t="inlineStr">
+      <c r="R14" s="5" t="inlineStr">
         <is>
           <t>Grande festa d’estate con più palchi, DJ e migliaia di persone vestite di bianco e nero. Di solito gratuita.</t>
         </is>
       </c>
-      <c r="R14" s="6" t="inlineStr">
+      <c r="S14" s="6" t="inlineStr">
         <is>
           <t>junho</t>
         </is>
       </c>
-      <c r="S14" s="5" t="inlineStr">
+      <c r="T14" s="5" t="inlineStr">
         <is>
           <t>June</t>
         </is>
       </c>
-      <c r="T14" s="5" t="inlineStr">
+      <c r="U14" s="5" t="inlineStr">
         <is>
           <t>junio</t>
         </is>
       </c>
-      <c r="U14" s="5" t="inlineStr">
+      <c r="V14" s="5" t="inlineStr">
         <is>
           <t>juin</t>
         </is>
       </c>
-      <c r="V14" s="5" t="inlineStr">
+      <c r="W14" s="5" t="inlineStr">
         <is>
           <t>Juni</t>
         </is>
       </c>
-      <c r="W14" s="5" t="inlineStr">
+      <c r="X14" s="5" t="inlineStr">
         <is>
           <t>giugno</t>
         </is>
       </c>
-      <c r="X14" s="6" t="inlineStr"/>
-      <c r="Y14" s="5" t="inlineStr"/>
+      <c r="Y14" s="6" t="inlineStr"/>
       <c r="Z14" s="5" t="inlineStr"/>
       <c r="AA14" s="5" t="inlineStr"/>
       <c r="AB14" s="5" t="inlineStr"/>
       <c r="AC14" s="5" t="inlineStr"/>
+      <c r="AD14" s="5" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
@@ -9149,72 +9322,73 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="L15" s="6" t="inlineStr">
+      <c r="L15" s="5" t="inlineStr"/>
+      <c r="M15" s="6" t="inlineStr">
         <is>
           <t>Festival de vinhos portugueses com provas comentadas, produtores, gastronomia e música ao vivo.</t>
         </is>
       </c>
-      <c r="M15" s="5" t="inlineStr">
+      <c r="N15" s="5" t="inlineStr">
         <is>
           <t>Portuguese wine festival with guided tastings, producers, food and live music.</t>
         </is>
       </c>
-      <c r="N15" s="5" t="inlineStr">
+      <c r="O15" s="5" t="inlineStr">
         <is>
           <t>Festival de vinos portugueses con catas comentadas, productores, gastronomía y música en directo.</t>
         </is>
       </c>
-      <c r="O15" s="5" t="inlineStr">
+      <c r="P15" s="5" t="inlineStr">
         <is>
           <t>Festival des vins portugais : dégustations commentées, producteurs, gastronomie et musique live.</t>
         </is>
       </c>
-      <c r="P15" s="5" t="inlineStr">
+      <c r="Q15" s="5" t="inlineStr">
         <is>
           <t>Fest der portugiesischen Weine mit geführten Verkostungen, Winzern, Essen und Livemusik.</t>
         </is>
       </c>
-      <c r="Q15" s="5" t="inlineStr">
+      <c r="R15" s="5" t="inlineStr">
         <is>
           <t>Festival dei vini portoghesi con degustazioni guidate, produttori, gastronomia e musica dal vivo.</t>
         </is>
       </c>
-      <c r="R15" s="6" t="inlineStr">
+      <c r="S15" s="6" t="inlineStr">
         <is>
           <t>início de junho</t>
         </is>
       </c>
-      <c r="S15" s="5" t="inlineStr">
+      <c r="T15" s="5" t="inlineStr">
         <is>
           <t>early June</t>
         </is>
       </c>
-      <c r="T15" s="5" t="inlineStr">
+      <c r="U15" s="5" t="inlineStr">
         <is>
           <t>principios de junio</t>
         </is>
       </c>
-      <c r="U15" s="5" t="inlineStr">
+      <c r="V15" s="5" t="inlineStr">
         <is>
           <t>début juin</t>
         </is>
       </c>
-      <c r="V15" s="5" t="inlineStr">
+      <c r="W15" s="5" t="inlineStr">
         <is>
           <t>Anfang Juni</t>
         </is>
       </c>
-      <c r="W15" s="5" t="inlineStr">
+      <c r="X15" s="5" t="inlineStr">
         <is>
           <t>inizio giugno</t>
         </is>
       </c>
-      <c r="X15" s="6" t="inlineStr"/>
-      <c r="Y15" s="5" t="inlineStr"/>
+      <c r="Y15" s="6" t="inlineStr"/>
       <c r="Z15" s="5" t="inlineStr"/>
       <c r="AA15" s="5" t="inlineStr"/>
       <c r="AB15" s="5" t="inlineStr"/>
       <c r="AC15" s="5" t="inlineStr"/>
+      <c r="AD15" s="5" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
@@ -9252,72 +9426,73 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="L16" s="6" t="inlineStr">
+      <c r="L16" s="5" t="inlineStr"/>
+      <c r="M16" s="6" t="inlineStr">
         <is>
           <t>Mercado noturno iluminado por milhares de velas, com artesanato, gastronomia e espetáculos do mundo.</t>
         </is>
       </c>
-      <c r="M16" s="5" t="inlineStr">
+      <c r="N16" s="5" t="inlineStr">
         <is>
           <t>Night market lit by thousands of candles, with crafts, food and performances from around the world.</t>
         </is>
       </c>
-      <c r="N16" s="5" t="inlineStr">
+      <c r="O16" s="5" t="inlineStr">
         <is>
           <t>Mercado nocturno iluminado por miles de velas, con artesanía, gastronomía y espectáculos del mundo.</t>
         </is>
       </c>
-      <c r="O16" s="5" t="inlineStr">
+      <c r="P16" s="5" t="inlineStr">
         <is>
           <t>Marché nocturne éclairé par des milliers de bougies : artisanat, gastronomie et spectacles du monde.</t>
         </is>
       </c>
-      <c r="P16" s="5" t="inlineStr">
+      <c r="Q16" s="5" t="inlineStr">
         <is>
           <t>Nachtmarkt im Licht tausender Kerzen mit Kunsthandwerk, Essen und Darbietungen aus aller Welt.</t>
         </is>
       </c>
-      <c r="Q16" s="5" t="inlineStr">
+      <c r="R16" s="5" t="inlineStr">
         <is>
           <t>Mercato notturno illuminato da migliaia di candele, con artigianato, gastronomia e spettacoli dal mondo.</t>
         </is>
       </c>
-      <c r="R16" s="6" t="inlineStr">
+      <c r="S16" s="6" t="inlineStr">
         <is>
           <t>início de julho</t>
         </is>
       </c>
-      <c r="S16" s="5" t="inlineStr">
+      <c r="T16" s="5" t="inlineStr">
         <is>
           <t>early July</t>
         </is>
       </c>
-      <c r="T16" s="5" t="inlineStr">
+      <c r="U16" s="5" t="inlineStr">
         <is>
           <t>principios de julio</t>
         </is>
       </c>
-      <c r="U16" s="5" t="inlineStr">
+      <c r="V16" s="5" t="inlineStr">
         <is>
           <t>début juillet</t>
         </is>
       </c>
-      <c r="V16" s="5" t="inlineStr">
+      <c r="W16" s="5" t="inlineStr">
         <is>
           <t>Anfang Juli</t>
         </is>
       </c>
-      <c r="W16" s="5" t="inlineStr">
+      <c r="X16" s="5" t="inlineStr">
         <is>
           <t>inizio luglio</t>
         </is>
       </c>
-      <c r="X16" s="6" t="inlineStr"/>
-      <c r="Y16" s="5" t="inlineStr"/>
+      <c r="Y16" s="6" t="inlineStr"/>
       <c r="Z16" s="5" t="inlineStr"/>
       <c r="AA16" s="5" t="inlineStr"/>
       <c r="AB16" s="5" t="inlineStr"/>
       <c r="AC16" s="5" t="inlineStr"/>
+      <c r="AD16" s="5" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
@@ -9355,72 +9530,77 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="L17" s="6" t="inlineStr">
+      <c r="L17" s="5" t="inlineStr">
+        <is>
+          <t>images/ilustracoes/ev-music.svg</t>
+        </is>
+      </c>
+      <c r="M17" s="6" t="inlineStr">
         <is>
           <t>Jazz internacional ao ar livre no Parque do Sítio das Fontes, com gastronomia e ambiente descontraído.</t>
         </is>
       </c>
-      <c r="M17" s="5" t="inlineStr">
+      <c r="N17" s="5" t="inlineStr">
         <is>
           <t>International open-air jazz at Sítio das Fontes park, with food and a relaxed atmosphere.</t>
         </is>
       </c>
-      <c r="N17" s="5" t="inlineStr">
+      <c r="O17" s="5" t="inlineStr">
         <is>
           <t>Jazz internacional al aire libre en el parque Sítio das Fontes, con gastronomía y ambiente relajado.</t>
         </is>
       </c>
-      <c r="O17" s="5" t="inlineStr">
+      <c r="P17" s="5" t="inlineStr">
         <is>
           <t>Jazz international en plein air au parc de Sítio das Fontes, avec gastronomie et ambiance détendue.</t>
         </is>
       </c>
-      <c r="P17" s="5" t="inlineStr">
+      <c r="Q17" s="5" t="inlineStr">
         <is>
           <t>Internationaler Open-Air-Jazz im Park Sítio das Fontes, mit Essen und entspannter Atmosphäre.</t>
         </is>
       </c>
-      <c r="Q17" s="5" t="inlineStr">
+      <c r="R17" s="5" t="inlineStr">
         <is>
           <t>Jazz internazionale all’aperto nel parco di Sítio das Fontes, con gastronomia e atmosfera rilassata.</t>
         </is>
       </c>
-      <c r="R17" s="6" t="inlineStr">
+      <c r="S17" s="6" t="inlineStr">
         <is>
           <t>meados de julho</t>
         </is>
       </c>
-      <c r="S17" s="5" t="inlineStr">
+      <c r="T17" s="5" t="inlineStr">
         <is>
           <t>mid-July</t>
         </is>
       </c>
-      <c r="T17" s="5" t="inlineStr">
+      <c r="U17" s="5" t="inlineStr">
         <is>
           <t>mediados de julio</t>
         </is>
       </c>
-      <c r="U17" s="5" t="inlineStr">
+      <c r="V17" s="5" t="inlineStr">
         <is>
           <t>mi-juillet</t>
         </is>
       </c>
-      <c r="V17" s="5" t="inlineStr">
+      <c r="W17" s="5" t="inlineStr">
         <is>
           <t>Mitte Juli</t>
         </is>
       </c>
-      <c r="W17" s="5" t="inlineStr">
+      <c r="X17" s="5" t="inlineStr">
         <is>
           <t>metà luglio</t>
         </is>
       </c>
-      <c r="X17" s="6" t="inlineStr"/>
-      <c r="Y17" s="5" t="inlineStr"/>
+      <c r="Y17" s="6" t="inlineStr"/>
       <c r="Z17" s="5" t="inlineStr"/>
       <c r="AA17" s="5" t="inlineStr"/>
       <c r="AB17" s="5" t="inlineStr"/>
       <c r="AC17" s="5" t="inlineStr"/>
+      <c r="AD17" s="5" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
@@ -9458,72 +9638,73 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="L18" s="6" t="inlineStr">
+      <c r="L18" s="5" t="inlineStr"/>
+      <c r="M18" s="6" t="inlineStr">
         <is>
           <t>Doçaria conventual portuguesa: doces de amêndoa e ovos, compotas e licores, no Convento de São José.</t>
         </is>
       </c>
-      <c r="M18" s="5" t="inlineStr">
+      <c r="N18" s="5" t="inlineStr">
         <is>
           <t>Traditional Portuguese convent sweets: almond and egg pastries, jams and liqueurs, at the São José convent.</t>
         </is>
       </c>
-      <c r="N18" s="5" t="inlineStr">
+      <c r="O18" s="5" t="inlineStr">
         <is>
           <t>Dulces conventuales portugueses: almendra y huevo, mermeladas y licores, en el Convento de São José.</t>
         </is>
       </c>
-      <c r="O18" s="5" t="inlineStr">
+      <c r="P18" s="5" t="inlineStr">
         <is>
           <t>Douceurs conventuelles portugaises : amande, œuf, confitures et liqueurs, au couvent de São José.</t>
         </is>
       </c>
-      <c r="P18" s="5" t="inlineStr">
+      <c r="Q18" s="5" t="inlineStr">
         <is>
           <t>Portugiesische Klostersüßigkeiten aus Mandeln und Ei, Marmeladen und Liköre im Kloster São José.</t>
         </is>
       </c>
-      <c r="Q18" s="5" t="inlineStr">
+      <c r="R18" s="5" t="inlineStr">
         <is>
           <t>Dolci conventuali portoghesi a base di mandorle e uova, marmellate e liquori, al Convento di São José.</t>
         </is>
       </c>
-      <c r="R18" s="6" t="inlineStr">
+      <c r="S18" s="6" t="inlineStr">
         <is>
           <t>final de julho / início de agosto</t>
         </is>
       </c>
-      <c r="S18" s="5" t="inlineStr">
+      <c r="T18" s="5" t="inlineStr">
         <is>
           <t>late July / early August</t>
         </is>
       </c>
-      <c r="T18" s="5" t="inlineStr">
+      <c r="U18" s="5" t="inlineStr">
         <is>
           <t>finales de julio / principios de agosto</t>
         </is>
       </c>
-      <c r="U18" s="5" t="inlineStr">
+      <c r="V18" s="5" t="inlineStr">
         <is>
           <t>fin juillet / début août</t>
         </is>
       </c>
-      <c r="V18" s="5" t="inlineStr">
+      <c r="W18" s="5" t="inlineStr">
         <is>
           <t>Ende Juli / Anfang August</t>
         </is>
       </c>
-      <c r="W18" s="5" t="inlineStr">
+      <c r="X18" s="5" t="inlineStr">
         <is>
           <t>fine luglio / inizio agosto</t>
         </is>
       </c>
-      <c r="X18" s="6" t="inlineStr"/>
-      <c r="Y18" s="5" t="inlineStr"/>
+      <c r="Y18" s="6" t="inlineStr"/>
       <c r="Z18" s="5" t="inlineStr"/>
       <c r="AA18" s="5" t="inlineStr"/>
       <c r="AB18" s="5" t="inlineStr"/>
       <c r="AC18" s="5" t="inlineStr"/>
+      <c r="AD18" s="5" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
@@ -9561,72 +9742,73 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="L19" s="6" t="inlineStr">
+      <c r="L19" s="5" t="inlineStr"/>
+      <c r="M19" s="6" t="inlineStr">
         <is>
           <t>Festival da laranja de Silves: produtores, gastronomia regional, produtos locais e concertos.</t>
         </is>
       </c>
-      <c r="M19" s="5" t="inlineStr">
+      <c r="N19" s="5" t="inlineStr">
         <is>
           <t>Silves orange festival: growers, regional food, local produce and concerts.</t>
         </is>
       </c>
-      <c r="N19" s="5" t="inlineStr">
+      <c r="O19" s="5" t="inlineStr">
         <is>
           <t>Festival de la naranja de Silves: productores, gastronomía regional, productos locales y conciertos.</t>
         </is>
       </c>
-      <c r="O19" s="5" t="inlineStr">
+      <c r="P19" s="5" t="inlineStr">
         <is>
           <t>Fête de l’orange de Silves : producteurs, gastronomie régionale, produits locaux et concerts.</t>
         </is>
       </c>
-      <c r="P19" s="5" t="inlineStr">
+      <c r="Q19" s="5" t="inlineStr">
         <is>
           <t>Orangenfest in Silves: Erzeuger, regionale Küche, lokale Produkte und Konzerte.</t>
         </is>
       </c>
-      <c r="Q19" s="5" t="inlineStr">
+      <c r="R19" s="5" t="inlineStr">
         <is>
           <t>Festa dell’arancia di Silves: produttori, gastronomia regionale, prodotti locali e concerti.</t>
         </is>
       </c>
-      <c r="R19" s="6" t="inlineStr">
+      <c r="S19" s="6" t="inlineStr">
         <is>
           <t>fevereiro</t>
         </is>
       </c>
-      <c r="S19" s="5" t="inlineStr">
+      <c r="T19" s="5" t="inlineStr">
         <is>
           <t>February</t>
         </is>
       </c>
-      <c r="T19" s="5" t="inlineStr">
+      <c r="U19" s="5" t="inlineStr">
         <is>
           <t>febrero</t>
         </is>
       </c>
-      <c r="U19" s="5" t="inlineStr">
+      <c r="V19" s="5" t="inlineStr">
         <is>
           <t>février</t>
         </is>
       </c>
-      <c r="V19" s="5" t="inlineStr">
+      <c r="W19" s="5" t="inlineStr">
         <is>
           <t>Februar</t>
         </is>
       </c>
-      <c r="W19" s="5" t="inlineStr">
+      <c r="X19" s="5" t="inlineStr">
         <is>
           <t>febbraio</t>
         </is>
       </c>
-      <c r="X19" s="6" t="inlineStr"/>
-      <c r="Y19" s="5" t="inlineStr"/>
+      <c r="Y19" s="6" t="inlineStr"/>
       <c r="Z19" s="5" t="inlineStr"/>
       <c r="AA19" s="5" t="inlineStr"/>
       <c r="AB19" s="5" t="inlineStr"/>
       <c r="AC19" s="5" t="inlineStr"/>
+      <c r="AD19" s="5" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
@@ -9664,72 +9846,73 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="L20" s="6" t="inlineStr">
+      <c r="L20" s="5" t="inlineStr"/>
+      <c r="M20" s="6" t="inlineStr">
         <is>
           <t>Festa medieval de inverno com encenações, torneios, mercados, artesanato e gastronomia.</t>
         </is>
       </c>
-      <c r="M20" s="5" t="inlineStr">
+      <c r="N20" s="5" t="inlineStr">
         <is>
           <t>Winter medieval fair with re-enactments, tournaments, markets, crafts and food.</t>
         </is>
       </c>
-      <c r="N20" s="5" t="inlineStr">
+      <c r="O20" s="5" t="inlineStr">
         <is>
           <t>Fiesta medieval de invierno con representaciones, torneos, mercados, artesanía y gastronomía.</t>
         </is>
       </c>
-      <c r="O20" s="5" t="inlineStr">
+      <c r="P20" s="5" t="inlineStr">
         <is>
           <t>Fête médiévale d’hiver : reconstitutions, tournois, marchés, artisanat et gastronomie.</t>
         </is>
       </c>
-      <c r="P20" s="5" t="inlineStr">
+      <c r="Q20" s="5" t="inlineStr">
         <is>
           <t>Mittelalterfest im Winter mit Inszenierungen, Turnieren, Märkten, Kunsthandwerk und Essen.</t>
         </is>
       </c>
-      <c r="Q20" s="5" t="inlineStr">
+      <c r="R20" s="5" t="inlineStr">
         <is>
           <t>Festa medievale invernale con rievocazioni, tornei, mercati, artigianato e gastronomia.</t>
         </is>
       </c>
-      <c r="R20" s="6" t="inlineStr">
+      <c r="S20" s="6" t="inlineStr">
         <is>
           <t>início de janeiro</t>
         </is>
       </c>
-      <c r="S20" s="5" t="inlineStr">
+      <c r="T20" s="5" t="inlineStr">
         <is>
           <t>early January</t>
         </is>
       </c>
-      <c r="T20" s="5" t="inlineStr">
+      <c r="U20" s="5" t="inlineStr">
         <is>
           <t>principios de enero</t>
         </is>
       </c>
-      <c r="U20" s="5" t="inlineStr">
+      <c r="V20" s="5" t="inlineStr">
         <is>
           <t>début janvier</t>
         </is>
       </c>
-      <c r="V20" s="5" t="inlineStr">
+      <c r="W20" s="5" t="inlineStr">
         <is>
           <t>Anfang Januar</t>
         </is>
       </c>
-      <c r="W20" s="5" t="inlineStr">
+      <c r="X20" s="5" t="inlineStr">
         <is>
           <t>inizio gennaio</t>
         </is>
       </c>
-      <c r="X20" s="6" t="inlineStr"/>
-      <c r="Y20" s="5" t="inlineStr"/>
+      <c r="Y20" s="6" t="inlineStr"/>
       <c r="Z20" s="5" t="inlineStr"/>
       <c r="AA20" s="5" t="inlineStr"/>
       <c r="AB20" s="5" t="inlineStr"/>
       <c r="AC20" s="5" t="inlineStr"/>
+      <c r="AD20" s="5" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
@@ -9767,48 +9950,49 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="L21" s="6" t="inlineStr">
+      <c r="L21" s="5" t="inlineStr"/>
+      <c r="M21" s="6" t="inlineStr">
         <is>
           <t>Feira tradicional com carrosséis, castanhas, farturas, tasquinhas e música. Ótima para famílias.</t>
         </is>
       </c>
-      <c r="M21" s="5" t="inlineStr">
+      <c r="N21" s="5" t="inlineStr">
         <is>
           <t>Traditional fair with rides, roast chestnuts, churros, food stalls and music. Great for families.</t>
         </is>
       </c>
-      <c r="N21" s="5" t="inlineStr">
+      <c r="O21" s="5" t="inlineStr">
         <is>
           <t>Feria tradicional con atracciones, castañas, churros, puestos de comida y música. Ideal para familias.</t>
         </is>
       </c>
-      <c r="O21" s="5" t="inlineStr">
+      <c r="P21" s="5" t="inlineStr">
         <is>
           <t>Foire traditionnelle : manèges, châtaignes, churros, stands et musique. Idéale en famille.</t>
         </is>
       </c>
-      <c r="P21" s="5" t="inlineStr">
+      <c r="Q21" s="5" t="inlineStr">
         <is>
           <t>Traditioneller Jahrmarkt mit Karussells, Maronen, Churros, Essensständen und Musik. Ideal für Familien.</t>
         </is>
       </c>
-      <c r="Q21" s="5" t="inlineStr">
+      <c r="R21" s="5" t="inlineStr">
         <is>
           <t>Fiera tradizionale con giostre, caldarroste, churros, stand e musica. Ideale per famiglie.</t>
         </is>
       </c>
-      <c r="R21" s="6" t="inlineStr"/>
-      <c r="S21" s="5" t="inlineStr"/>
+      <c r="S21" s="6" t="inlineStr"/>
       <c r="T21" s="5" t="inlineStr"/>
       <c r="U21" s="5" t="inlineStr"/>
       <c r="V21" s="5" t="inlineStr"/>
       <c r="W21" s="5" t="inlineStr"/>
-      <c r="X21" s="6" t="inlineStr"/>
-      <c r="Y21" s="5" t="inlineStr"/>
+      <c r="X21" s="5" t="inlineStr"/>
+      <c r="Y21" s="6" t="inlineStr"/>
       <c r="Z21" s="5" t="inlineStr"/>
       <c r="AA21" s="5" t="inlineStr"/>
       <c r="AB21" s="5" t="inlineStr"/>
       <c r="AC21" s="5" t="inlineStr"/>
+      <c r="AD21" s="5" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
@@ -9846,72 +10030,73 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="L22" s="6" t="inlineStr">
+      <c r="L22" s="5" t="inlineStr"/>
+      <c r="M22" s="6" t="inlineStr">
         <is>
           <t>Festival de magia e ilusionismo com espetáculos para todos os públicos.</t>
         </is>
       </c>
-      <c r="M22" s="5" t="inlineStr">
+      <c r="N22" s="5" t="inlineStr">
         <is>
           <t>Magic and illusion festival with shows for all ages.</t>
         </is>
       </c>
-      <c r="N22" s="5" t="inlineStr">
+      <c r="O22" s="5" t="inlineStr">
         <is>
           <t>Festival de magia e ilusionismo con espectáculos para todos los públicos.</t>
         </is>
       </c>
-      <c r="O22" s="5" t="inlineStr">
+      <c r="P22" s="5" t="inlineStr">
         <is>
           <t>Festival de magie et d’illusionnisme avec des spectacles pour tous.</t>
         </is>
       </c>
-      <c r="P22" s="5" t="inlineStr">
+      <c r="Q22" s="5" t="inlineStr">
         <is>
           <t>Zauber- und Illusionsfestival mit Shows für jedes Alter.</t>
         </is>
       </c>
-      <c r="Q22" s="5" t="inlineStr">
+      <c r="R22" s="5" t="inlineStr">
         <is>
           <t>Festival di magia e illusionismo con spettacoli per tutti.</t>
         </is>
       </c>
-      <c r="R22" s="6" t="inlineStr">
+      <c r="S22" s="6" t="inlineStr">
         <is>
           <t>outubro</t>
         </is>
       </c>
-      <c r="S22" s="5" t="inlineStr">
+      <c r="T22" s="5" t="inlineStr">
         <is>
           <t>October</t>
         </is>
       </c>
-      <c r="T22" s="5" t="inlineStr">
+      <c r="U22" s="5" t="inlineStr">
         <is>
           <t>octubre</t>
         </is>
       </c>
-      <c r="U22" s="5" t="inlineStr">
+      <c r="V22" s="5" t="inlineStr">
         <is>
           <t>octobre</t>
         </is>
       </c>
-      <c r="V22" s="5" t="inlineStr">
+      <c r="W22" s="5" t="inlineStr">
         <is>
           <t>Oktober</t>
         </is>
       </c>
-      <c r="W22" s="5" t="inlineStr">
+      <c r="X22" s="5" t="inlineStr">
         <is>
           <t>ottobre</t>
         </is>
       </c>
-      <c r="X22" s="6" t="inlineStr"/>
-      <c r="Y22" s="5" t="inlineStr"/>
+      <c r="Y22" s="6" t="inlineStr"/>
       <c r="Z22" s="5" t="inlineStr"/>
       <c r="AA22" s="5" t="inlineStr"/>
       <c r="AB22" s="5" t="inlineStr"/>
       <c r="AC22" s="5" t="inlineStr"/>
+      <c r="AD22" s="5" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
@@ -9949,72 +10134,77 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="L23" s="6" t="inlineStr">
+      <c r="L23" s="5" t="inlineStr">
+        <is>
+          <t>images/ilustracoes/ev-music.svg</t>
+        </is>
+      </c>
+      <c r="M23" s="6" t="inlineStr">
         <is>
           <t>Um dos principais festivais de músicas do mundo, no centro histórico de Loulé.</t>
         </is>
       </c>
-      <c r="M23" s="5" t="inlineStr">
+      <c r="N23" s="5" t="inlineStr">
         <is>
           <t>One of Portugal’s leading world music festivals, in Loulé’s old town.</t>
         </is>
       </c>
-      <c r="N23" s="5" t="inlineStr">
+      <c r="O23" s="5" t="inlineStr">
         <is>
           <t>Uno de los principales festivales de músicas del mundo, en el casco antiguo de Loulé.</t>
         </is>
       </c>
-      <c r="O23" s="5" t="inlineStr">
+      <c r="P23" s="5" t="inlineStr">
         <is>
           <t>L’un des grands festivals de musiques du monde, dans la vieille ville de Loulé.</t>
         </is>
       </c>
-      <c r="P23" s="5" t="inlineStr">
+      <c r="Q23" s="5" t="inlineStr">
         <is>
           <t>Eines der wichtigsten Weltmusikfestivals, in der Altstadt von Loulé.</t>
         </is>
       </c>
-      <c r="Q23" s="5" t="inlineStr">
+      <c r="R23" s="5" t="inlineStr">
         <is>
           <t>Uno dei principali festival di world music, nel centro storico di Loulé.</t>
         </is>
       </c>
-      <c r="R23" s="6" t="inlineStr">
+      <c r="S23" s="6" t="inlineStr">
         <is>
           <t>final de junho</t>
         </is>
       </c>
-      <c r="S23" s="5" t="inlineStr">
+      <c r="T23" s="5" t="inlineStr">
         <is>
           <t>late June</t>
         </is>
       </c>
-      <c r="T23" s="5" t="inlineStr">
+      <c r="U23" s="5" t="inlineStr">
         <is>
           <t>finales de junio</t>
         </is>
       </c>
-      <c r="U23" s="5" t="inlineStr">
+      <c r="V23" s="5" t="inlineStr">
         <is>
           <t>fin juin</t>
         </is>
       </c>
-      <c r="V23" s="5" t="inlineStr">
+      <c r="W23" s="5" t="inlineStr">
         <is>
           <t>Ende Juni</t>
         </is>
       </c>
-      <c r="W23" s="5" t="inlineStr">
+      <c r="X23" s="5" t="inlineStr">
         <is>
           <t>fine giugno</t>
         </is>
       </c>
-      <c r="X23" s="6" t="inlineStr"/>
-      <c r="Y23" s="5" t="inlineStr"/>
+      <c r="Y23" s="6" t="inlineStr"/>
       <c r="Z23" s="5" t="inlineStr"/>
       <c r="AA23" s="5" t="inlineStr"/>
       <c r="AB23" s="5" t="inlineStr"/>
       <c r="AC23" s="5" t="inlineStr"/>
+      <c r="AD23" s="5" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
@@ -10048,72 +10238,73 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="L24" s="6" t="inlineStr">
+      <c r="L24" s="5" t="inlineStr"/>
+      <c r="M24" s="6" t="inlineStr">
         <is>
           <t>Desfile tradicional com carros alegóricos, música e fantasias.</t>
         </is>
       </c>
-      <c r="M24" s="5" t="inlineStr">
+      <c r="N24" s="5" t="inlineStr">
         <is>
           <t>Traditional parade with floats, music and costumes.</t>
         </is>
       </c>
-      <c r="N24" s="5" t="inlineStr">
+      <c r="O24" s="5" t="inlineStr">
         <is>
           <t>Desfile tradicional con carrozas, música y disfraces.</t>
         </is>
       </c>
-      <c r="O24" s="5" t="inlineStr">
+      <c r="P24" s="5" t="inlineStr">
         <is>
           <t>Défilé traditionnel avec chars, musique et costumes.</t>
         </is>
       </c>
-      <c r="P24" s="5" t="inlineStr">
+      <c r="Q24" s="5" t="inlineStr">
         <is>
           <t>Traditioneller Umzug mit Festwagen, Musik und Kostümen.</t>
         </is>
       </c>
-      <c r="Q24" s="5" t="inlineStr">
+      <c r="R24" s="5" t="inlineStr">
         <is>
           <t>Sfilata tradizionale con carri allegorici, musica e costumi.</t>
         </is>
       </c>
-      <c r="R24" s="6" t="inlineStr">
+      <c r="S24" s="6" t="inlineStr">
         <is>
           <t>fevereiro (2027: previsivelmente 7 a 9 de fevereiro, programa por confirmar)</t>
         </is>
       </c>
-      <c r="S24" s="5" t="inlineStr">
+      <c r="T24" s="5" t="inlineStr">
         <is>
           <t>February (2027: expected 7–9 February, programme TBC)</t>
         </is>
       </c>
-      <c r="T24" s="5" t="inlineStr">
+      <c r="U24" s="5" t="inlineStr">
         <is>
           <t>febrero (2027: previsiblemente del 7 al 9 de febrero, programa por confirmar)</t>
         </is>
       </c>
-      <c r="U24" s="5" t="inlineStr">
+      <c r="V24" s="5" t="inlineStr">
         <is>
           <t>février (2027 : probablement du 7 au 9 février, programme à confirmer)</t>
         </is>
       </c>
-      <c r="V24" s="5" t="inlineStr">
+      <c r="W24" s="5" t="inlineStr">
         <is>
           <t>Februar (2027: voraussichtlich 7.–9. Februar, Programm folgt)</t>
         </is>
       </c>
-      <c r="W24" s="5" t="inlineStr">
+      <c r="X24" s="5" t="inlineStr">
         <is>
           <t>febbraio (2027: presumibilmente 7–9 febbraio, programma da confermare)</t>
         </is>
       </c>
-      <c r="X24" s="6" t="inlineStr"/>
-      <c r="Y24" s="5" t="inlineStr"/>
+      <c r="Y24" s="6" t="inlineStr"/>
       <c r="Z24" s="5" t="inlineStr"/>
       <c r="AA24" s="5" t="inlineStr"/>
       <c r="AB24" s="5" t="inlineStr"/>
       <c r="AC24" s="5" t="inlineStr"/>
+      <c r="AD24" s="5" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
@@ -10147,72 +10338,73 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="L25" s="6" t="inlineStr">
+      <c r="L25" s="5" t="inlineStr"/>
+      <c r="M25" s="6" t="inlineStr">
         <is>
           <t>Festival da famosa batata-doce de Aljezur, com produtores, doces regionais e espetáculos. Excursão mais longa.</t>
         </is>
       </c>
-      <c r="M25" s="5" t="inlineStr">
+      <c r="N25" s="5" t="inlineStr">
         <is>
           <t>Festival of Aljezur’s famous sweet potato, with producers, local sweets and shows. A longer day trip.</t>
         </is>
       </c>
-      <c r="N25" s="5" t="inlineStr">
+      <c r="O25" s="5" t="inlineStr">
         <is>
           <t>Festival del famoso boniato de Aljezur, con productores, dulces regionales y espectáculos. Excursión más larga.</t>
         </is>
       </c>
-      <c r="O25" s="5" t="inlineStr">
+      <c r="P25" s="5" t="inlineStr">
         <is>
           <t>Fête de la célèbre patate douce d’Aljezur : producteurs, douceurs locales et spectacles. Excursion plus longue.</t>
         </is>
       </c>
-      <c r="P25" s="5" t="inlineStr">
+      <c r="Q25" s="5" t="inlineStr">
         <is>
           <t>Fest der berühmten Süßkartoffel aus Aljezur mit Erzeugern, Süßem und Shows. Längerer Ausflug.</t>
         </is>
       </c>
-      <c r="Q25" s="5" t="inlineStr">
+      <c r="R25" s="5" t="inlineStr">
         <is>
           <t>Festa della famosa patata dolce di Aljezur, con produttori, dolci locali e spettacoli. Gita più lunga.</t>
         </is>
       </c>
-      <c r="R25" s="6" t="inlineStr">
+      <c r="S25" s="6" t="inlineStr">
         <is>
           <t>final de novembro</t>
         </is>
       </c>
-      <c r="S25" s="5" t="inlineStr">
+      <c r="T25" s="5" t="inlineStr">
         <is>
           <t>late November</t>
         </is>
       </c>
-      <c r="T25" s="5" t="inlineStr">
+      <c r="U25" s="5" t="inlineStr">
         <is>
           <t>finales de noviembre</t>
         </is>
       </c>
-      <c r="U25" s="5" t="inlineStr">
+      <c r="V25" s="5" t="inlineStr">
         <is>
           <t>fin novembre</t>
         </is>
       </c>
-      <c r="V25" s="5" t="inlineStr">
+      <c r="W25" s="5" t="inlineStr">
         <is>
           <t>Ende November</t>
         </is>
       </c>
-      <c r="W25" s="5" t="inlineStr">
+      <c r="X25" s="5" t="inlineStr">
         <is>
           <t>fine novembre</t>
         </is>
       </c>
-      <c r="X25" s="6" t="inlineStr"/>
-      <c r="Y25" s="5" t="inlineStr"/>
+      <c r="Y25" s="6" t="inlineStr"/>
       <c r="Z25" s="5" t="inlineStr"/>
       <c r="AA25" s="5" t="inlineStr"/>
       <c r="AB25" s="5" t="inlineStr"/>
       <c r="AC25" s="5" t="inlineStr"/>
+      <c r="AD25" s="5" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
@@ -10250,72 +10442,77 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="L26" s="6" t="inlineStr">
+      <c r="L26" s="5" t="inlineStr">
+        <is>
+          <t>images/ilustracoes/ev-music.svg</t>
+        </is>
+      </c>
+      <c r="M26" s="6" t="inlineStr">
         <is>
           <t>Concertos de jazz intimistas em quintas e adegas, com provas de vinho e petiscos.</t>
         </is>
       </c>
-      <c r="M26" s="5" t="inlineStr">
+      <c r="N26" s="5" t="inlineStr">
         <is>
           <t>Intimate jazz concerts at wine estates, with wine tasting and snacks.</t>
         </is>
       </c>
-      <c r="N26" s="5" t="inlineStr">
+      <c r="O26" s="5" t="inlineStr">
         <is>
           <t>Conciertos íntimos de jazz en bodegas y fincas, con cata de vinos y tapas.</t>
         </is>
       </c>
-      <c r="O26" s="5" t="inlineStr">
+      <c r="P26" s="5" t="inlineStr">
         <is>
           <t>Concerts de jazz intimistes dans des domaines viticoles, avec dégustation et petiscos.</t>
         </is>
       </c>
-      <c r="P26" s="5" t="inlineStr">
+      <c r="Q26" s="5" t="inlineStr">
         <is>
           <t>Intime Jazzkonzerte auf Weingütern mit Weinprobe und Häppchen.</t>
         </is>
       </c>
-      <c r="Q26" s="5" t="inlineStr">
+      <c r="R26" s="5" t="inlineStr">
         <is>
           <t>Concerti jazz intimi in cantine e tenute, con degustazione di vini e stuzzichini.</t>
         </is>
       </c>
-      <c r="R26" s="6" t="inlineStr">
+      <c r="S26" s="6" t="inlineStr">
         <is>
           <t>novembro a maio</t>
         </is>
       </c>
-      <c r="S26" s="5" t="inlineStr">
+      <c r="T26" s="5" t="inlineStr">
         <is>
           <t>November to May</t>
         </is>
       </c>
-      <c r="T26" s="5" t="inlineStr">
+      <c r="U26" s="5" t="inlineStr">
         <is>
           <t>de noviembre a mayo</t>
         </is>
       </c>
-      <c r="U26" s="5" t="inlineStr">
+      <c r="V26" s="5" t="inlineStr">
         <is>
           <t>de novembre à mai</t>
         </is>
       </c>
-      <c r="V26" s="5" t="inlineStr">
+      <c r="W26" s="5" t="inlineStr">
         <is>
           <t>November bis Mai</t>
         </is>
       </c>
-      <c r="W26" s="5" t="inlineStr">
+      <c r="X26" s="5" t="inlineStr">
         <is>
           <t>da novembre a maggio</t>
         </is>
       </c>
-      <c r="X26" s="6" t="inlineStr"/>
-      <c r="Y26" s="5" t="inlineStr"/>
+      <c r="Y26" s="6" t="inlineStr"/>
       <c r="Z26" s="5" t="inlineStr"/>
       <c r="AA26" s="5" t="inlineStr"/>
       <c r="AB26" s="5" t="inlineStr"/>
       <c r="AC26" s="5" t="inlineStr"/>
+      <c r="AD26" s="5" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
@@ -10353,68 +10550,73 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="L27" s="6" t="inlineStr">
+      <c r="L27" s="5" t="inlineStr">
+        <is>
+          <t>images/waterparks_0.jpg</t>
+        </is>
+      </c>
+      <c r="M27" s="6" t="inlineStr">
         <is>
           <t>Um dos maiores parques aquáticos do Algarve: escorregas gigantes, atrações radicais e zonas para crianças.</t>
         </is>
       </c>
-      <c r="M27" s="5" t="inlineStr">
+      <c r="N27" s="5" t="inlineStr">
         <is>
           <t>One of the Algarve’s largest water parks: giant slides, thrill rides and kids’ areas.</t>
         </is>
       </c>
-      <c r="N27" s="5" t="inlineStr">
+      <c r="O27" s="5" t="inlineStr">
         <is>
           <t>Uno de los mayores parques acuáticos del Algarve: toboganes gigantes, atracciones extremas y zonas infantiles.</t>
         </is>
       </c>
-      <c r="O27" s="5" t="inlineStr">
+      <c r="P27" s="5" t="inlineStr">
         <is>
           <t>L’un des plus grands parcs aquatiques de l’Algarve : toboggans géants, attractions à sensations et espaces enfants.</t>
         </is>
       </c>
-      <c r="P27" s="5" t="inlineStr">
+      <c r="Q27" s="5" t="inlineStr">
         <is>
           <t>Einer der größten Wasserparks der Algarve: Riesenrutschen, Adrenalin-Attraktionen und Kinderbereiche.</t>
         </is>
       </c>
-      <c r="Q27" s="5" t="inlineStr">
+      <c r="R27" s="5" t="inlineStr">
         <is>
           <t>Uno dei parchi acquatici più grandi dell’Algarve: scivoli giganti, attrazioni adrenaliniche e aree bimbi.</t>
         </is>
       </c>
-      <c r="R27" s="6" t="inlineStr"/>
-      <c r="S27" s="5" t="inlineStr"/>
+      <c r="S27" s="6" t="inlineStr"/>
       <c r="T27" s="5" t="inlineStr"/>
       <c r="U27" s="5" t="inlineStr"/>
       <c r="V27" s="5" t="inlineStr"/>
       <c r="W27" s="5" t="inlineStr"/>
-      <c r="X27" s="6" t="inlineStr">
+      <c r="X27" s="5" t="inlineStr"/>
+      <c r="Y27" s="6" t="inlineStr">
         <is>
           <t>Abril a outubro (referência 2026)</t>
         </is>
       </c>
-      <c r="Y27" s="5" t="inlineStr">
+      <c r="Z27" s="5" t="inlineStr">
         <is>
           <t>April to October (2026 season)</t>
         </is>
       </c>
-      <c r="Z27" s="5" t="inlineStr">
+      <c r="AA27" s="5" t="inlineStr">
         <is>
           <t>De abril a octubre (temporada 2026)</t>
         </is>
       </c>
-      <c r="AA27" s="5" t="inlineStr">
+      <c r="AB27" s="5" t="inlineStr">
         <is>
           <t>D’avril à octobre (saison 2026)</t>
         </is>
       </c>
-      <c r="AB27" s="5" t="inlineStr">
+      <c r="AC27" s="5" t="inlineStr">
         <is>
           <t>April bis Oktober (Saison 2026)</t>
         </is>
       </c>
-      <c r="AC27" s="5" t="inlineStr">
+      <c r="AD27" s="5" t="inlineStr">
         <is>
           <t>Da aprile a ottobre (stagione 2026)</t>
         </is>
@@ -10456,68 +10658,73 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="L28" s="6" t="inlineStr">
+      <c r="L28" s="5" t="inlineStr">
+        <is>
+          <t>images/waterparks_2.jpg</t>
+        </is>
+      </c>
+      <c r="M28" s="6" t="inlineStr">
         <is>
           <t>King Cobra, Kamikaze, piscina de ondas, rio lento e áreas infantis — a 5 minutos de casa.</t>
         </is>
       </c>
-      <c r="M28" s="5" t="inlineStr">
+      <c r="N28" s="5" t="inlineStr">
         <is>
           <t>King Cobra, Kamikaze, wave pool, lazy river and kids’ areas — 5 minutes from the house.</t>
         </is>
       </c>
-      <c r="N28" s="5" t="inlineStr">
+      <c r="O28" s="5" t="inlineStr">
         <is>
           <t>King Cobra, Kamikaze, piscina de olas, río lento y zonas infantiles, a 5 minutos de casa.</t>
         </is>
       </c>
-      <c r="O28" s="5" t="inlineStr">
+      <c r="P28" s="5" t="inlineStr">
         <is>
           <t>King Cobra, Kamikaze, piscine à vagues, rivière lente et espaces enfants — à 5 minutes.</t>
         </is>
       </c>
-      <c r="P28" s="5" t="inlineStr">
+      <c r="Q28" s="5" t="inlineStr">
         <is>
           <t>King Cobra, Kamikaze, Wellenbad, Lazy River und Kinderbereiche – 5 Minuten vom Haus.</t>
         </is>
       </c>
-      <c r="Q28" s="5" t="inlineStr">
+      <c r="R28" s="5" t="inlineStr">
         <is>
           <t>King Cobra, Kamikaze, piscina a onde, fiume lento e aree bimbi, a 5 minuti da casa.</t>
         </is>
       </c>
-      <c r="R28" s="6" t="inlineStr"/>
-      <c r="S28" s="5" t="inlineStr"/>
+      <c r="S28" s="6" t="inlineStr"/>
       <c r="T28" s="5" t="inlineStr"/>
       <c r="U28" s="5" t="inlineStr"/>
       <c r="V28" s="5" t="inlineStr"/>
       <c r="W28" s="5" t="inlineStr"/>
-      <c r="X28" s="6" t="inlineStr">
+      <c r="X28" s="5" t="inlineStr"/>
+      <c r="Y28" s="6" t="inlineStr">
         <is>
           <t>Verão (habitualmente junho a setembro)</t>
         </is>
       </c>
-      <c r="Y28" s="5" t="inlineStr">
+      <c r="Z28" s="5" t="inlineStr">
         <is>
           <t>Summer (usually June–September)</t>
         </is>
       </c>
-      <c r="Z28" s="5" t="inlineStr">
+      <c r="AA28" s="5" t="inlineStr">
         <is>
           <t>Verano (normalmente de junio a septiembre)</t>
         </is>
       </c>
-      <c r="AA28" s="5" t="inlineStr">
+      <c r="AB28" s="5" t="inlineStr">
         <is>
           <t>Été (généralement juin à septembre)</t>
         </is>
       </c>
-      <c r="AB28" s="5" t="inlineStr">
+      <c r="AC28" s="5" t="inlineStr">
         <is>
           <t>Sommer (meist Juni–September)</t>
         </is>
       </c>
-      <c r="AC28" s="5" t="inlineStr">
+      <c r="AD28" s="5" t="inlineStr">
         <is>
           <t>Estate (di solito giugno–settembre)</t>
         </is>
@@ -10559,68 +10766,73 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="L29" s="6" t="inlineStr">
+      <c r="L29" s="5" t="inlineStr">
+        <is>
+          <t>images/zoomarine_1.jpg</t>
+        </is>
+      </c>
+      <c r="M29" s="6" t="inlineStr">
         <is>
           <t>Parque temático e aquático com apresentações educativas de animais, aquários e piscinas.</t>
         </is>
       </c>
-      <c r="M29" s="5" t="inlineStr">
+      <c r="N29" s="5" t="inlineStr">
         <is>
           <t>Theme and water park with educational animal presentations, aquariums and pools.</t>
         </is>
       </c>
-      <c r="N29" s="5" t="inlineStr">
+      <c r="O29" s="5" t="inlineStr">
         <is>
           <t>Parque temático y acuático con presentaciones educativas de animales, acuarios y piscinas.</t>
         </is>
       </c>
-      <c r="O29" s="5" t="inlineStr">
+      <c r="P29" s="5" t="inlineStr">
         <is>
           <t>Parc à thème et aquatique avec présentations pédagogiques d’animaux, aquariums et piscines.</t>
         </is>
       </c>
-      <c r="P29" s="5" t="inlineStr">
+      <c r="Q29" s="5" t="inlineStr">
         <is>
           <t>Themen- und Wasserpark mit lehrreichen Tiervorführungen, Aquarien und Pools.</t>
         </is>
       </c>
-      <c r="Q29" s="5" t="inlineStr">
+      <c r="R29" s="5" t="inlineStr">
         <is>
           <t>Parco tematico e acquatico con presentazioni educative di animali, acquari e piscine.</t>
         </is>
       </c>
-      <c r="R29" s="6" t="inlineStr"/>
-      <c r="S29" s="5" t="inlineStr"/>
+      <c r="S29" s="6" t="inlineStr"/>
       <c r="T29" s="5" t="inlineStr"/>
       <c r="U29" s="5" t="inlineStr"/>
       <c r="V29" s="5" t="inlineStr"/>
       <c r="W29" s="5" t="inlineStr"/>
-      <c r="X29" s="6" t="inlineStr">
+      <c r="X29" s="5" t="inlineStr"/>
+      <c r="Y29" s="6" t="inlineStr">
         <is>
           <t>Março a novembro (atrações de água só no verão)</t>
         </is>
       </c>
-      <c r="Y29" s="5" t="inlineStr">
+      <c r="Z29" s="5" t="inlineStr">
         <is>
           <t>March to November (water rides in summer only)</t>
         </is>
       </c>
-      <c r="Z29" s="5" t="inlineStr">
+      <c r="AA29" s="5" t="inlineStr">
         <is>
           <t>De marzo a noviembre (atracciones acuáticas solo en verano)</t>
         </is>
       </c>
-      <c r="AA29" s="5" t="inlineStr">
+      <c r="AB29" s="5" t="inlineStr">
         <is>
           <t>De mars à novembre (attractions aquatiques l’été seulement)</t>
         </is>
       </c>
-      <c r="AB29" s="5" t="inlineStr">
+      <c r="AC29" s="5" t="inlineStr">
         <is>
           <t>März bis November (Wasserattraktionen nur im Sommer)</t>
         </is>
       </c>
-      <c r="AC29" s="5" t="inlineStr">
+      <c r="AD29" s="5" t="inlineStr">
         <is>
           <t>Da marzo a novembre (attrazioni d’acqua solo d’estate)</t>
         </is>
@@ -10662,48 +10874,53 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="L30" s="6" t="inlineStr">
+      <c r="L30" s="5" t="inlineStr">
+        <is>
+          <t>images/ilustracoes/ev-halloween.svg</t>
+        </is>
+      </c>
+      <c r="M30" s="6" t="inlineStr">
         <is>
           <t>Decorações, personagens, atividades infantis e atrações de sustos (para maiores de 14 anos).</t>
         </is>
       </c>
-      <c r="M30" s="5" t="inlineStr">
+      <c r="N30" s="5" t="inlineStr">
         <is>
           <t>Decorations, characters, kids’ activities and scare attractions (14+).</t>
         </is>
       </c>
-      <c r="N30" s="5" t="inlineStr">
+      <c r="O30" s="5" t="inlineStr">
         <is>
           <t>Decoración, personajes, actividades infantiles y atracciones de miedo (mayores de 14).</t>
         </is>
       </c>
-      <c r="O30" s="5" t="inlineStr">
+      <c r="P30" s="5" t="inlineStr">
         <is>
           <t>Décors, personnages, activités enfants et attractions qui font peur (14 ans et +).</t>
         </is>
       </c>
-      <c r="P30" s="5" t="inlineStr">
+      <c r="Q30" s="5" t="inlineStr">
         <is>
           <t>Deko, Figuren, Kinderprogramm und Grusel-Attraktionen (ab 14).</t>
         </is>
       </c>
-      <c r="Q30" s="5" t="inlineStr">
+      <c r="R30" s="5" t="inlineStr">
         <is>
           <t>Decorazioni, personaggi, attività per bambini e attrazioni da brivido (14+).</t>
         </is>
       </c>
-      <c r="R30" s="6" t="inlineStr"/>
-      <c r="S30" s="5" t="inlineStr"/>
+      <c r="S30" s="6" t="inlineStr"/>
       <c r="T30" s="5" t="inlineStr"/>
       <c r="U30" s="5" t="inlineStr"/>
       <c r="V30" s="5" t="inlineStr"/>
       <c r="W30" s="5" t="inlineStr"/>
-      <c r="X30" s="6" t="inlineStr"/>
-      <c r="Y30" s="5" t="inlineStr"/>
+      <c r="X30" s="5" t="inlineStr"/>
+      <c r="Y30" s="6" t="inlineStr"/>
       <c r="Z30" s="5" t="inlineStr"/>
       <c r="AA30" s="5" t="inlineStr"/>
       <c r="AB30" s="5" t="inlineStr"/>
       <c r="AC30" s="5" t="inlineStr"/>
+      <c r="AD30" s="5" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
@@ -10741,68 +10958,69 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="L31" s="6" t="inlineStr">
+      <c r="L31" s="5" t="inlineStr"/>
+      <c r="M31" s="6" t="inlineStr">
         <is>
           <t>Escorregas radicais, piscinas de ondas e atrações para toda a família.</t>
         </is>
       </c>
-      <c r="M31" s="5" t="inlineStr">
+      <c r="N31" s="5" t="inlineStr">
         <is>
           <t>Thrill slides, wave pools and attractions for the whole family.</t>
         </is>
       </c>
-      <c r="N31" s="5" t="inlineStr">
+      <c r="O31" s="5" t="inlineStr">
         <is>
           <t>Toboganes extremos, piscinas de olas y atracciones para toda la familia.</t>
         </is>
       </c>
-      <c r="O31" s="5" t="inlineStr">
+      <c r="P31" s="5" t="inlineStr">
         <is>
           <t>Toboggans à sensations, piscines à vagues et attractions pour toute la famille.</t>
         </is>
       </c>
-      <c r="P31" s="5" t="inlineStr">
+      <c r="Q31" s="5" t="inlineStr">
         <is>
           <t>Rasante Rutschen, Wellenbecken und Attraktionen für die ganze Familie.</t>
         </is>
       </c>
-      <c r="Q31" s="5" t="inlineStr">
+      <c r="R31" s="5" t="inlineStr">
         <is>
           <t>Scivoli adrenalinici, piscine a onde e attrazioni per tutta la famiglia.</t>
         </is>
       </c>
-      <c r="R31" s="6" t="inlineStr"/>
-      <c r="S31" s="5" t="inlineStr"/>
+      <c r="S31" s="6" t="inlineStr"/>
       <c r="T31" s="5" t="inlineStr"/>
       <c r="U31" s="5" t="inlineStr"/>
       <c r="V31" s="5" t="inlineStr"/>
       <c r="W31" s="5" t="inlineStr"/>
-      <c r="X31" s="6" t="inlineStr">
+      <c r="X31" s="5" t="inlineStr"/>
+      <c r="Y31" s="6" t="inlineStr">
         <is>
           <t>Primavera e verão</t>
         </is>
       </c>
-      <c r="Y31" s="5" t="inlineStr">
+      <c r="Z31" s="5" t="inlineStr">
         <is>
           <t>Spring and summer</t>
         </is>
       </c>
-      <c r="Z31" s="5" t="inlineStr">
+      <c r="AA31" s="5" t="inlineStr">
         <is>
           <t>Primavera y verano</t>
         </is>
       </c>
-      <c r="AA31" s="5" t="inlineStr">
+      <c r="AB31" s="5" t="inlineStr">
         <is>
           <t>Printemps et été</t>
         </is>
       </c>
-      <c r="AB31" s="5" t="inlineStr">
+      <c r="AC31" s="5" t="inlineStr">
         <is>
           <t>Frühling und Sommer</t>
         </is>
       </c>
-      <c r="AC31" s="5" t="inlineStr">
+      <c r="AD31" s="5" t="inlineStr">
         <is>
           <t>Primavera ed estate</t>
         </is>
@@ -10848,68 +11066,69 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="L32" s="6" t="inlineStr">
+      <c r="L32" s="5" t="inlineStr"/>
+      <c r="M32" s="6" t="inlineStr">
         <is>
           <t>Parque aquático coberto e aquecido com escorregas, piscinas e spa. Ótimo em dias de chuva.</t>
         </is>
       </c>
-      <c r="M32" s="5" t="inlineStr">
+      <c r="N32" s="5" t="inlineStr">
         <is>
           <t>Covered, heated water park with slides, pools and spa. Perfect on rainy days.</t>
         </is>
       </c>
-      <c r="N32" s="5" t="inlineStr">
+      <c r="O32" s="5" t="inlineStr">
         <is>
           <t>Parque acuático cubierto y climatizado con toboganes, piscinas y spa. Ideal en días de lluvia.</t>
         </is>
       </c>
-      <c r="O32" s="5" t="inlineStr">
+      <c r="P32" s="5" t="inlineStr">
         <is>
           <t>Parc aquatique couvert et chauffé avec toboggans, piscines et spa. Parfait les jours de pluie.</t>
         </is>
       </c>
-      <c r="P32" s="5" t="inlineStr">
+      <c r="Q32" s="5" t="inlineStr">
         <is>
           <t>Überdachter, beheizter Wasserpark mit Rutschen, Pools und Spa. Ideal bei Regen.</t>
         </is>
       </c>
-      <c r="Q32" s="5" t="inlineStr">
+      <c r="R32" s="5" t="inlineStr">
         <is>
           <t>Parco acquatico coperto e riscaldato con scivoli, piscine e spa. Perfetto nei giorni di pioggia.</t>
         </is>
       </c>
-      <c r="R32" s="6" t="inlineStr"/>
-      <c r="S32" s="5" t="inlineStr"/>
+      <c r="S32" s="6" t="inlineStr"/>
       <c r="T32" s="5" t="inlineStr"/>
       <c r="U32" s="5" t="inlineStr"/>
       <c r="V32" s="5" t="inlineStr"/>
       <c r="W32" s="5" t="inlineStr"/>
-      <c r="X32" s="6" t="inlineStr">
+      <c r="X32" s="5" t="inlineStr"/>
+      <c r="Y32" s="6" t="inlineStr">
         <is>
           <t>Desde 1 de outubro de 2026, 10h–18h</t>
         </is>
       </c>
-      <c r="Y32" s="5" t="inlineStr">
+      <c r="Z32" s="5" t="inlineStr">
         <is>
           <t>From 1 October 2026, 10 am–6 pm</t>
         </is>
       </c>
-      <c r="Z32" s="5" t="inlineStr">
+      <c r="AA32" s="5" t="inlineStr">
         <is>
           <t>Desde el 1 de octubre de 2026, 10–18 h</t>
         </is>
       </c>
-      <c r="AA32" s="5" t="inlineStr">
+      <c r="AB32" s="5" t="inlineStr">
         <is>
           <t>Depuis le 1er octobre 2026, 10h–18h</t>
         </is>
       </c>
-      <c r="AB32" s="5" t="inlineStr">
+      <c r="AC32" s="5" t="inlineStr">
         <is>
           <t>Ab 1. Oktober 2026, 10–18 Uhr</t>
         </is>
       </c>
-      <c r="AC32" s="5" t="inlineStr">
+      <c r="AD32" s="5" t="inlineStr">
         <is>
           <t>Dal 1° ottobre 2026, 10–18</t>
         </is>
@@ -10951,68 +11170,69 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="L33" s="6" t="inlineStr">
+      <c r="L33" s="5" t="inlineStr"/>
+      <c r="M33" s="6" t="inlineStr">
         <is>
           <t>Zoo interativo com animais, minigolfe, piscinas, arborismo e passeios de pónei.</t>
         </is>
       </c>
-      <c r="M33" s="5" t="inlineStr">
+      <c r="N33" s="5" t="inlineStr">
         <is>
           <t>Interactive zoo with animals, mini golf, pools, tree-top course and pony rides.</t>
         </is>
       </c>
-      <c r="N33" s="5" t="inlineStr">
+      <c r="O33" s="5" t="inlineStr">
         <is>
           <t>Zoo interactivo con animales, minigolf, piscinas, circuito de árboles y paseos en poni.</t>
         </is>
       </c>
-      <c r="O33" s="5" t="inlineStr">
+      <c r="P33" s="5" t="inlineStr">
         <is>
           <t>Zoo interactif avec animaux, minigolf, piscines, accrobranche et balades à poney.</t>
         </is>
       </c>
-      <c r="P33" s="5" t="inlineStr">
+      <c r="Q33" s="5" t="inlineStr">
         <is>
           <t>Interaktiver Zoo mit Tieren, Minigolf, Pools, Kletterpark und Ponyreiten.</t>
         </is>
       </c>
-      <c r="Q33" s="5" t="inlineStr">
+      <c r="R33" s="5" t="inlineStr">
         <is>
           <t>Zoo interattivo con animali, minigolf, piscine, percorso sugli alberi e giri in pony.</t>
         </is>
       </c>
-      <c r="R33" s="6" t="inlineStr"/>
-      <c r="S33" s="5" t="inlineStr"/>
+      <c r="S33" s="6" t="inlineStr"/>
       <c r="T33" s="5" t="inlineStr"/>
       <c r="U33" s="5" t="inlineStr"/>
       <c r="V33" s="5" t="inlineStr"/>
       <c r="W33" s="5" t="inlineStr"/>
-      <c r="X33" s="6" t="inlineStr">
+      <c r="X33" s="5" t="inlineStr"/>
+      <c r="Y33" s="6" t="inlineStr">
         <is>
           <t>Todo o ano</t>
         </is>
       </c>
-      <c r="Y33" s="5" t="inlineStr">
+      <c r="Z33" s="5" t="inlineStr">
         <is>
           <t>All year round</t>
         </is>
       </c>
-      <c r="Z33" s="5" t="inlineStr">
+      <c r="AA33" s="5" t="inlineStr">
         <is>
           <t>Todo el año</t>
         </is>
       </c>
-      <c r="AA33" s="5" t="inlineStr">
+      <c r="AB33" s="5" t="inlineStr">
         <is>
           <t>Toute l’année</t>
         </is>
       </c>
-      <c r="AB33" s="5" t="inlineStr">
+      <c r="AC33" s="5" t="inlineStr">
         <is>
           <t>Ganzjährig</t>
         </is>
       </c>
-      <c r="AC33" s="5" t="inlineStr">
+      <c r="AD33" s="5" t="inlineStr">
         <is>
           <t>Tutto l’anno</t>
         </is>
@@ -11062,48 +11282,53 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="L34" s="6" t="inlineStr">
+      <c r="L34" s="5" t="inlineStr">
+        <is>
+          <t>images/ilustracoes/ev-sand.svg</t>
+        </is>
+      </c>
+      <c r="M34" s="6" t="inlineStr">
         <is>
           <t>Mais de 120 esculturas gigantes em areia ao ar livre, junto à EN125.</t>
         </is>
       </c>
-      <c r="M34" s="5" t="inlineStr">
+      <c r="N34" s="5" t="inlineStr">
         <is>
           <t>Over 120 giant open-air sand sculptures, by the EN125 road.</t>
         </is>
       </c>
-      <c r="N34" s="5" t="inlineStr">
+      <c r="O34" s="5" t="inlineStr">
         <is>
           <t>Más de 120 esculturas gigantes de arena al aire libre, junto a la EN125.</t>
         </is>
       </c>
-      <c r="O34" s="5" t="inlineStr">
+      <c r="P34" s="5" t="inlineStr">
         <is>
           <t>Plus de 120 sculptures géantes en sable en plein air, le long de l’EN125.</t>
         </is>
       </c>
-      <c r="P34" s="5" t="inlineStr">
+      <c r="Q34" s="5" t="inlineStr">
         <is>
           <t>Über 120 riesige Sandskulpturen unter freiem Himmel an der EN125.</t>
         </is>
       </c>
-      <c r="Q34" s="5" t="inlineStr">
+      <c r="R34" s="5" t="inlineStr">
         <is>
           <t>Oltre 120 sculture giganti di sabbia all’aperto, lungo la EN125.</t>
         </is>
       </c>
-      <c r="R34" s="6" t="inlineStr"/>
-      <c r="S34" s="5" t="inlineStr"/>
+      <c r="S34" s="6" t="inlineStr"/>
       <c r="T34" s="5" t="inlineStr"/>
       <c r="U34" s="5" t="inlineStr"/>
       <c r="V34" s="5" t="inlineStr"/>
       <c r="W34" s="5" t="inlineStr"/>
-      <c r="X34" s="6" t="inlineStr"/>
-      <c r="Y34" s="5" t="inlineStr"/>
+      <c r="X34" s="5" t="inlineStr"/>
+      <c r="Y34" s="6" t="inlineStr"/>
       <c r="Z34" s="5" t="inlineStr"/>
       <c r="AA34" s="5" t="inlineStr"/>
       <c r="AB34" s="5" t="inlineStr"/>
       <c r="AC34" s="5" t="inlineStr"/>
+      <c r="AD34" s="5" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
@@ -11141,68 +11366,73 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="L35" s="6" t="inlineStr">
+      <c r="L35" s="5" t="inlineStr">
+        <is>
+          <t>images/ilustracoes/ev-racing.svg</t>
+        </is>
+      </c>
+      <c r="M35" s="6" t="inlineStr">
         <is>
           <t>Karting individual ou em grupo no circuito do Autódromo, mediante disponibilidade.</t>
         </is>
       </c>
-      <c r="M35" s="5" t="inlineStr">
+      <c r="N35" s="5" t="inlineStr">
         <is>
           <t>Karting for individuals or groups at the Algarve circuit, subject to availability.</t>
         </is>
       </c>
-      <c r="N35" s="5" t="inlineStr">
+      <c r="O35" s="5" t="inlineStr">
         <is>
           <t>Karting individual o en grupo en el circuito del Autódromo, según disponibilidad.</t>
         </is>
       </c>
-      <c r="O35" s="5" t="inlineStr">
+      <c r="P35" s="5" t="inlineStr">
         <is>
           <t>Karting en solo ou en groupe sur le circuit, selon disponibilité.</t>
         </is>
       </c>
-      <c r="P35" s="5" t="inlineStr">
+      <c r="Q35" s="5" t="inlineStr">
         <is>
           <t>Kartfahren allein oder in Gruppen an der Rennstrecke, je nach Verfügbarkeit.</t>
         </is>
       </c>
-      <c r="Q35" s="5" t="inlineStr">
+      <c r="R35" s="5" t="inlineStr">
         <is>
           <t>Kart individuale o di gruppo sul circuito, secondo disponibilità.</t>
         </is>
       </c>
-      <c r="R35" s="6" t="inlineStr"/>
-      <c r="S35" s="5" t="inlineStr"/>
+      <c r="S35" s="6" t="inlineStr"/>
       <c r="T35" s="5" t="inlineStr"/>
       <c r="U35" s="5" t="inlineStr"/>
       <c r="V35" s="5" t="inlineStr"/>
       <c r="W35" s="5" t="inlineStr"/>
-      <c r="X35" s="6" t="inlineStr">
+      <c r="X35" s="5" t="inlineStr"/>
+      <c r="Y35" s="6" t="inlineStr">
         <is>
           <t>Todo o ano</t>
         </is>
       </c>
-      <c r="Y35" s="5" t="inlineStr">
+      <c r="Z35" s="5" t="inlineStr">
         <is>
           <t>All year round</t>
         </is>
       </c>
-      <c r="Z35" s="5" t="inlineStr">
+      <c r="AA35" s="5" t="inlineStr">
         <is>
           <t>Todo el año</t>
         </is>
       </c>
-      <c r="AA35" s="5" t="inlineStr">
+      <c r="AB35" s="5" t="inlineStr">
         <is>
           <t>Toute l’année</t>
         </is>
       </c>
-      <c r="AB35" s="5" t="inlineStr">
+      <c r="AC35" s="5" t="inlineStr">
         <is>
           <t>Ganzjährig</t>
         </is>
       </c>
-      <c r="AC35" s="5" t="inlineStr">
+      <c r="AD35" s="5" t="inlineStr">
         <is>
           <t>Tutto l’anno</t>
         </is>
@@ -11240,68 +11470,69 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="L36" s="6" t="inlineStr">
+      <c r="L36" s="5" t="inlineStr"/>
+      <c r="M36" s="6" t="inlineStr">
         <is>
           <t>Piscinas cobertas com natação livre, aulas e atividades aquáticas.</t>
         </is>
       </c>
-      <c r="M36" s="5" t="inlineStr">
+      <c r="N36" s="5" t="inlineStr">
         <is>
           <t>Indoor pools with public swimming, classes and water activities.</t>
         </is>
       </c>
-      <c r="N36" s="5" t="inlineStr">
+      <c r="O36" s="5" t="inlineStr">
         <is>
           <t>Piscinas cubiertas con baño libre, clases y actividades acuáticas.</t>
         </is>
       </c>
-      <c r="O36" s="5" t="inlineStr">
+      <c r="P36" s="5" t="inlineStr">
         <is>
           <t>Piscines couvertes : nage libre, cours et activités aquatiques.</t>
         </is>
       </c>
-      <c r="P36" s="5" t="inlineStr">
+      <c r="Q36" s="5" t="inlineStr">
         <is>
           <t>Hallenbad mit freiem Schwimmen, Kursen und Wasseraktivitäten.</t>
         </is>
       </c>
-      <c r="Q36" s="5" t="inlineStr">
+      <c r="R36" s="5" t="inlineStr">
         <is>
           <t>Piscine coperte con nuoto libero, corsi e attività in acqua.</t>
         </is>
       </c>
-      <c r="R36" s="6" t="inlineStr"/>
-      <c r="S36" s="5" t="inlineStr"/>
+      <c r="S36" s="6" t="inlineStr"/>
       <c r="T36" s="5" t="inlineStr"/>
       <c r="U36" s="5" t="inlineStr"/>
       <c r="V36" s="5" t="inlineStr"/>
       <c r="W36" s="5" t="inlineStr"/>
-      <c r="X36" s="6" t="inlineStr">
+      <c r="X36" s="5" t="inlineStr"/>
+      <c r="Y36" s="6" t="inlineStr">
         <is>
           <t>Confirmar horários de utilização livre</t>
         </is>
       </c>
-      <c r="Y36" s="5" t="inlineStr">
+      <c r="Z36" s="5" t="inlineStr">
         <is>
           <t>Check public swimming times</t>
         </is>
       </c>
-      <c r="Z36" s="5" t="inlineStr">
+      <c r="AA36" s="5" t="inlineStr">
         <is>
           <t>Consulte los horarios de baño libre</t>
         </is>
       </c>
-      <c r="AA36" s="5" t="inlineStr">
+      <c r="AB36" s="5" t="inlineStr">
         <is>
           <t>Vérifier les horaires de nage libre</t>
         </is>
       </c>
-      <c r="AB36" s="5" t="inlineStr">
+      <c r="AC36" s="5" t="inlineStr">
         <is>
           <t>Öffnungszeiten für freies Schwimmen prüfen</t>
         </is>
       </c>
-      <c r="AC36" s="5" t="inlineStr">
+      <c r="AD36" s="5" t="inlineStr">
         <is>
           <t>Verificare gli orari di nuoto libero</t>
         </is>
@@ -11339,68 +11570,69 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="L37" s="6" t="inlineStr">
+      <c r="L37" s="5" t="inlineStr"/>
+      <c r="M37" s="6" t="inlineStr">
         <is>
           <t>Piscina interior e bem-estar: sauna, banho turco e jacuzzi (conforme disponibilidade).</t>
         </is>
       </c>
-      <c r="M37" s="5" t="inlineStr">
+      <c r="N37" s="5" t="inlineStr">
         <is>
           <t>Indoor pool and wellness: sauna, steam room and jacuzzi (subject to availability).</t>
         </is>
       </c>
-      <c r="N37" s="5" t="inlineStr">
+      <c r="O37" s="5" t="inlineStr">
         <is>
           <t>Piscina cubierta y bienestar: sauna, baño turco y jacuzzi (según disponibilidad).</t>
         </is>
       </c>
-      <c r="O37" s="5" t="inlineStr">
+      <c r="P37" s="5" t="inlineStr">
         <is>
           <t>Piscine couverte et bien-être : sauna, hammam et jacuzzi (selon disponibilité).</t>
         </is>
       </c>
-      <c r="P37" s="5" t="inlineStr">
+      <c r="Q37" s="5" t="inlineStr">
         <is>
           <t>Hallenbad und Wellness: Sauna, Dampfbad und Whirlpool (je nach Verfügbarkeit).</t>
         </is>
       </c>
-      <c r="Q37" s="5" t="inlineStr">
+      <c r="R37" s="5" t="inlineStr">
         <is>
           <t>Piscina coperta e benessere: sauna, bagno turco e jacuzzi (secondo disponibilità).</t>
         </is>
       </c>
-      <c r="R37" s="6" t="inlineStr"/>
-      <c r="S37" s="5" t="inlineStr"/>
+      <c r="S37" s="6" t="inlineStr"/>
       <c r="T37" s="5" t="inlineStr"/>
       <c r="U37" s="5" t="inlineStr"/>
       <c r="V37" s="5" t="inlineStr"/>
       <c r="W37" s="5" t="inlineStr"/>
-      <c r="X37" s="6" t="inlineStr">
+      <c r="X37" s="5" t="inlineStr"/>
+      <c r="Y37" s="6" t="inlineStr">
         <is>
           <t>Confirmar horários de utilização livre</t>
         </is>
       </c>
-      <c r="Y37" s="5" t="inlineStr">
+      <c r="Z37" s="5" t="inlineStr">
         <is>
           <t>Check public swimming times</t>
         </is>
       </c>
-      <c r="Z37" s="5" t="inlineStr">
+      <c r="AA37" s="5" t="inlineStr">
         <is>
           <t>Consulte los horarios de baño libre</t>
         </is>
       </c>
-      <c r="AA37" s="5" t="inlineStr">
+      <c r="AB37" s="5" t="inlineStr">
         <is>
           <t>Vérifier les horaires de nage libre</t>
         </is>
       </c>
-      <c r="AB37" s="5" t="inlineStr">
+      <c r="AC37" s="5" t="inlineStr">
         <is>
           <t>Öffnungszeiten für freies Schwimmen prüfen</t>
         </is>
       </c>
-      <c r="AC37" s="5" t="inlineStr">
+      <c r="AD37" s="5" t="inlineStr">
         <is>
           <t>Verificare gli orari di nuoto libero</t>
         </is>
@@ -11438,68 +11670,69 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="L38" s="6" t="inlineStr">
+      <c r="L38" s="5" t="inlineStr"/>
+      <c r="M38" s="6" t="inlineStr">
         <is>
           <t>Piscina coberta e aquecida com seis pistas, para manter o treino nas férias.</t>
         </is>
       </c>
-      <c r="M38" s="5" t="inlineStr">
+      <c r="N38" s="5" t="inlineStr">
         <is>
           <t>Covered, heated six-lane pool — keep up your training on holiday.</t>
         </is>
       </c>
-      <c r="N38" s="5" t="inlineStr">
+      <c r="O38" s="5" t="inlineStr">
         <is>
           <t>Piscina cubierta y climatizada de seis calles, para no perder el ritmo en vacaciones.</t>
         </is>
       </c>
-      <c r="O38" s="5" t="inlineStr">
+      <c r="P38" s="5" t="inlineStr">
         <is>
           <t>Piscine couverte et chauffée de six couloirs, pour garder la forme en vacances.</t>
         </is>
       </c>
-      <c r="P38" s="5" t="inlineStr">
+      <c r="Q38" s="5" t="inlineStr">
         <is>
           <t>Überdachtes, beheiztes 6-Bahnen-Becken – fit bleiben im Urlaub.</t>
         </is>
       </c>
-      <c r="Q38" s="5" t="inlineStr">
+      <c r="R38" s="5" t="inlineStr">
         <is>
           <t>Piscina coperta e riscaldata a sei corsie, per allenarsi anche in vacanza.</t>
         </is>
       </c>
-      <c r="R38" s="6" t="inlineStr"/>
-      <c r="S38" s="5" t="inlineStr"/>
+      <c r="S38" s="6" t="inlineStr"/>
       <c r="T38" s="5" t="inlineStr"/>
       <c r="U38" s="5" t="inlineStr"/>
       <c r="V38" s="5" t="inlineStr"/>
       <c r="W38" s="5" t="inlineStr"/>
-      <c r="X38" s="6" t="inlineStr">
+      <c r="X38" s="5" t="inlineStr"/>
+      <c r="Y38" s="6" t="inlineStr">
         <is>
           <t>Confirmar horários de utilização livre</t>
         </is>
       </c>
-      <c r="Y38" s="5" t="inlineStr">
+      <c r="Z38" s="5" t="inlineStr">
         <is>
           <t>Check public swimming times</t>
         </is>
       </c>
-      <c r="Z38" s="5" t="inlineStr">
+      <c r="AA38" s="5" t="inlineStr">
         <is>
           <t>Consulte los horarios de baño libre</t>
         </is>
       </c>
-      <c r="AA38" s="5" t="inlineStr">
+      <c r="AB38" s="5" t="inlineStr">
         <is>
           <t>Vérifier les horaires de nage libre</t>
         </is>
       </c>
-      <c r="AB38" s="5" t="inlineStr">
+      <c r="AC38" s="5" t="inlineStr">
         <is>
           <t>Öffnungszeiten für freies Schwimmen prüfen</t>
         </is>
       </c>
-      <c r="AC38" s="5" t="inlineStr">
+      <c r="AD38" s="5" t="inlineStr">
         <is>
           <t>Verificare gli orari di nuoto libero</t>
         </is>
@@ -11537,68 +11770,69 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="L39" s="6" t="inlineStr">
+      <c r="L39" s="5" t="inlineStr"/>
+      <c r="M39" s="6" t="inlineStr">
         <is>
           <t>Piscina coberta, campos de ténis e outras instalações desportivas.</t>
         </is>
       </c>
-      <c r="M39" s="5" t="inlineStr">
+      <c r="N39" s="5" t="inlineStr">
         <is>
           <t>Indoor pool, tennis courts and other sports facilities.</t>
         </is>
       </c>
-      <c r="N39" s="5" t="inlineStr">
+      <c r="O39" s="5" t="inlineStr">
         <is>
           <t>Piscina cubierta, pistas de tenis y otras instalaciones deportivas.</t>
         </is>
       </c>
-      <c r="O39" s="5" t="inlineStr">
+      <c r="P39" s="5" t="inlineStr">
         <is>
           <t>Piscine couverte, courts de tennis et autres équipements sportifs.</t>
         </is>
       </c>
-      <c r="P39" s="5" t="inlineStr">
+      <c r="Q39" s="5" t="inlineStr">
         <is>
           <t>Hallenbad, Tennisplätze und weitere Sportanlagen.</t>
         </is>
       </c>
-      <c r="Q39" s="5" t="inlineStr">
+      <c r="R39" s="5" t="inlineStr">
         <is>
           <t>Piscina coperta, campi da tennis e altri impianti sportivi.</t>
         </is>
       </c>
-      <c r="R39" s="6" t="inlineStr"/>
-      <c r="S39" s="5" t="inlineStr"/>
+      <c r="S39" s="6" t="inlineStr"/>
       <c r="T39" s="5" t="inlineStr"/>
       <c r="U39" s="5" t="inlineStr"/>
       <c r="V39" s="5" t="inlineStr"/>
       <c r="W39" s="5" t="inlineStr"/>
-      <c r="X39" s="6" t="inlineStr">
+      <c r="X39" s="5" t="inlineStr"/>
+      <c r="Y39" s="6" t="inlineStr">
         <is>
           <t>Confirmar horários de utilização livre</t>
         </is>
       </c>
-      <c r="Y39" s="5" t="inlineStr">
+      <c r="Z39" s="5" t="inlineStr">
         <is>
           <t>Check public swimming times</t>
         </is>
       </c>
-      <c r="Z39" s="5" t="inlineStr">
+      <c r="AA39" s="5" t="inlineStr">
         <is>
           <t>Consulte los horarios de baño libre</t>
         </is>
       </c>
-      <c r="AA39" s="5" t="inlineStr">
+      <c r="AB39" s="5" t="inlineStr">
         <is>
           <t>Vérifier les horaires de nage libre</t>
         </is>
       </c>
-      <c r="AB39" s="5" t="inlineStr">
+      <c r="AC39" s="5" t="inlineStr">
         <is>
           <t>Öffnungszeiten für freies Schwimmen prüfen</t>
         </is>
       </c>
-      <c r="AC39" s="5" t="inlineStr">
+      <c r="AD39" s="5" t="inlineStr">
         <is>
           <t>Verificare gli orari di nuoto libero</t>
         </is>
@@ -11636,68 +11870,69 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="L40" s="6" t="inlineStr">
+      <c r="L40" s="5" t="inlineStr"/>
+      <c r="M40" s="6" t="inlineStr">
         <is>
           <t>Complexo coberto com piscinas, ginásio, jacuzzi, sauna e banho turco.</t>
         </is>
       </c>
-      <c r="M40" s="5" t="inlineStr">
+      <c r="N40" s="5" t="inlineStr">
         <is>
           <t>Indoor complex with pools, gym, jacuzzi, sauna and steam room.</t>
         </is>
       </c>
-      <c r="N40" s="5" t="inlineStr">
+      <c r="O40" s="5" t="inlineStr">
         <is>
           <t>Complejo cubierto con piscinas, gimnasio, jacuzzi, sauna y baño turco.</t>
         </is>
       </c>
-      <c r="O40" s="5" t="inlineStr">
+      <c r="P40" s="5" t="inlineStr">
         <is>
           <t>Complexe couvert avec piscines, salle de sport, jacuzzi, sauna et hammam.</t>
         </is>
       </c>
-      <c r="P40" s="5" t="inlineStr">
+      <c r="Q40" s="5" t="inlineStr">
         <is>
           <t>Hallenkomplex mit Pools, Fitnessraum, Whirlpool, Sauna und Dampfbad.</t>
         </is>
       </c>
-      <c r="Q40" s="5" t="inlineStr">
+      <c r="R40" s="5" t="inlineStr">
         <is>
           <t>Complesso coperto con piscine, palestra, jacuzzi, sauna e bagno turco.</t>
         </is>
       </c>
-      <c r="R40" s="6" t="inlineStr"/>
-      <c r="S40" s="5" t="inlineStr"/>
+      <c r="S40" s="6" t="inlineStr"/>
       <c r="T40" s="5" t="inlineStr"/>
       <c r="U40" s="5" t="inlineStr"/>
       <c r="V40" s="5" t="inlineStr"/>
       <c r="W40" s="5" t="inlineStr"/>
-      <c r="X40" s="6" t="inlineStr">
+      <c r="X40" s="5" t="inlineStr"/>
+      <c r="Y40" s="6" t="inlineStr">
         <is>
           <t>Interrupções entre outubro e novembro de 2026 (competições) — confirmar</t>
         </is>
       </c>
-      <c r="Y40" s="5" t="inlineStr">
+      <c r="Z40" s="5" t="inlineStr">
         <is>
           <t>Closures in October–November 2026 (competitions) — check</t>
         </is>
       </c>
-      <c r="Z40" s="5" t="inlineStr">
+      <c r="AA40" s="5" t="inlineStr">
         <is>
           <t>Cierres entre octubre y noviembre de 2026 (competiciones): confirmar</t>
         </is>
       </c>
-      <c r="AA40" s="5" t="inlineStr">
+      <c r="AB40" s="5" t="inlineStr">
         <is>
           <t>Fermetures en octobre–novembre 2026 (compétitions) — vérifier</t>
         </is>
       </c>
-      <c r="AB40" s="5" t="inlineStr">
+      <c r="AC40" s="5" t="inlineStr">
         <is>
           <t>Schließungen Oktober–November 2026 (Wettkämpfe) – bitte prüfen</t>
         </is>
       </c>
-      <c r="AC40" s="5" t="inlineStr">
+      <c r="AD40" s="5" t="inlineStr">
         <is>
           <t>Chiusure tra ottobre e novembre 2026 (gare): verificare</t>
         </is>
@@ -11735,68 +11970,69 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="L41" s="6" t="inlineStr">
+      <c r="L41" s="5" t="inlineStr"/>
+      <c r="M41" s="6" t="inlineStr">
         <is>
           <t>A história e a ocupação islâmica de Silves em peças arqueológicas. Ótimo para um dia de chuva.</t>
         </is>
       </c>
-      <c r="M41" s="5" t="inlineStr">
+      <c r="N41" s="5" t="inlineStr">
         <is>
           <t>Silves’ history and Islamic heritage told through archaeological finds. Ideal on a rainy day.</t>
         </is>
       </c>
-      <c r="N41" s="5" t="inlineStr">
+      <c r="O41" s="5" t="inlineStr">
         <is>
           <t>La historia y el pasado islámico de Silves a través de piezas arqueológicas. Ideal en un día de lluvia.</t>
         </is>
       </c>
-      <c r="O41" s="5" t="inlineStr">
+      <c r="P41" s="5" t="inlineStr">
         <is>
           <t>L’histoire et le passé islamique de Silves à travers des pièces archéologiques. Idéal par temps de pluie.</t>
         </is>
       </c>
-      <c r="P41" s="5" t="inlineStr">
+      <c r="Q41" s="5" t="inlineStr">
         <is>
           <t>Geschichte und islamisches Erbe von Silves in archäologischen Funden. Ideal an Regentagen.</t>
         </is>
       </c>
-      <c r="Q41" s="5" t="inlineStr">
+      <c r="R41" s="5" t="inlineStr">
         <is>
           <t>La storia e il passato islamico di Silves attraverso reperti archeologici. Ideale nei giorni di pioggia.</t>
         </is>
       </c>
-      <c r="R41" s="6" t="inlineStr"/>
-      <c r="S41" s="5" t="inlineStr"/>
+      <c r="S41" s="6" t="inlineStr"/>
       <c r="T41" s="5" t="inlineStr"/>
       <c r="U41" s="5" t="inlineStr"/>
       <c r="V41" s="5" t="inlineStr"/>
       <c r="W41" s="5" t="inlineStr"/>
-      <c r="X41" s="6" t="inlineStr">
+      <c r="X41" s="5" t="inlineStr"/>
+      <c r="Y41" s="6" t="inlineStr">
         <is>
           <t>Todo o ano</t>
         </is>
       </c>
-      <c r="Y41" s="5" t="inlineStr">
+      <c r="Z41" s="5" t="inlineStr">
         <is>
           <t>All year round</t>
         </is>
       </c>
-      <c r="Z41" s="5" t="inlineStr">
+      <c r="AA41" s="5" t="inlineStr">
         <is>
           <t>Todo el año</t>
         </is>
       </c>
-      <c r="AA41" s="5" t="inlineStr">
+      <c r="AB41" s="5" t="inlineStr">
         <is>
           <t>Toute l’année</t>
         </is>
       </c>
-      <c r="AB41" s="5" t="inlineStr">
+      <c r="AC41" s="5" t="inlineStr">
         <is>
           <t>Ganzjährig</t>
         </is>
       </c>
-      <c r="AC41" s="5" t="inlineStr">
+      <c r="AD41" s="5" t="inlineStr">
         <is>
           <t>Tutto l’anno</t>
         </is>
@@ -11834,68 +12070,73 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="L42" s="6" t="inlineStr">
+      <c r="L42" s="5" t="inlineStr">
+        <is>
+          <t>images/beaches_0.jpg</t>
+        </is>
+      </c>
+      <c r="M42" s="6" t="inlineStr">
         <is>
           <t>Uma das praias mais emblemáticas de Portugal: falésias, rochas esculpidas e água transparente.</t>
         </is>
       </c>
-      <c r="M42" s="5" t="inlineStr">
+      <c r="N42" s="5" t="inlineStr">
         <is>
           <t>One of Portugal’s most iconic beaches: cliffs, sculpted rocks and clear water.</t>
         </is>
       </c>
-      <c r="N42" s="5" t="inlineStr">
+      <c r="O42" s="5" t="inlineStr">
         <is>
           <t>Una de las playas más emblemáticas de Portugal: acantilados, rocas esculpidas y agua transparente.</t>
         </is>
       </c>
-      <c r="O42" s="5" t="inlineStr">
+      <c r="P42" s="5" t="inlineStr">
         <is>
           <t>L’une des plages les plus emblématiques du Portugal : falaises, rochers sculptés et eau limpide.</t>
         </is>
       </c>
-      <c r="P42" s="5" t="inlineStr">
+      <c r="Q42" s="5" t="inlineStr">
         <is>
           <t>Einer der bekanntesten Strände Portugals: Klippen, Felsformationen und klares Wasser.</t>
         </is>
       </c>
-      <c r="Q42" s="5" t="inlineStr">
+      <c r="R42" s="5" t="inlineStr">
         <is>
           <t>Una delle spiagge più iconiche del Portogallo: scogliere, rocce scolpite e acqua trasparente.</t>
         </is>
       </c>
-      <c r="R42" s="6" t="inlineStr"/>
-      <c r="S42" s="5" t="inlineStr"/>
+      <c r="S42" s="6" t="inlineStr"/>
       <c r="T42" s="5" t="inlineStr"/>
       <c r="U42" s="5" t="inlineStr"/>
       <c r="V42" s="5" t="inlineStr"/>
       <c r="W42" s="5" t="inlineStr"/>
-      <c r="X42" s="6" t="inlineStr">
+      <c r="X42" s="5" t="inlineStr"/>
+      <c r="Y42" s="6" t="inlineStr">
         <is>
           <t>Todo o ano</t>
         </is>
       </c>
-      <c r="Y42" s="5" t="inlineStr">
+      <c r="Z42" s="5" t="inlineStr">
         <is>
           <t>All year round</t>
         </is>
       </c>
-      <c r="Z42" s="5" t="inlineStr">
+      <c r="AA42" s="5" t="inlineStr">
         <is>
           <t>Todo el año</t>
         </is>
       </c>
-      <c r="AA42" s="5" t="inlineStr">
+      <c r="AB42" s="5" t="inlineStr">
         <is>
           <t>Toute l’année</t>
         </is>
       </c>
-      <c r="AB42" s="5" t="inlineStr">
+      <c r="AC42" s="5" t="inlineStr">
         <is>
           <t>Ganzjährig</t>
         </is>
       </c>
-      <c r="AC42" s="5" t="inlineStr">
+      <c r="AD42" s="5" t="inlineStr">
         <is>
           <t>Tutto l’anno</t>
         </is>
@@ -11933,68 +12174,73 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="L43" s="6" t="inlineStr">
+      <c r="L43" s="5" t="inlineStr">
+        <is>
+          <t>images/beaches_3.jpg</t>
+        </is>
+      </c>
+      <c r="M43" s="6" t="inlineStr">
         <is>
           <t>Gruta marítima com abertura circular no teto. Só se visita de barco ou caiaque guiado — não é permitido nadar até lá nem desembarcar.</t>
         </is>
       </c>
-      <c r="M43" s="5" t="inlineStr">
+      <c r="N43" s="5" t="inlineStr">
         <is>
           <t>Sea cave with a round opening in its roof. Visit only by guided boat or kayak — swimming in or landing is not allowed.</t>
         </is>
       </c>
-      <c r="N43" s="5" t="inlineStr">
+      <c r="O43" s="5" t="inlineStr">
         <is>
           <t>Cueva marina con una abertura circular en el techo. Solo en barco o kayak guiado: no se permite nadar hasta ella ni desembarcar.</t>
         </is>
       </c>
-      <c r="O43" s="5" t="inlineStr">
+      <c r="P43" s="5" t="inlineStr">
         <is>
           <t>Grotte marine au plafond percé d’une ouverture ronde. Accès en bateau ou kayak guidé uniquement — baignade et débarquement interdits.</t>
         </is>
       </c>
-      <c r="P43" s="5" t="inlineStr">
+      <c r="Q43" s="5" t="inlineStr">
         <is>
           <t>Meereshöhle mit runder Deckenöffnung. Nur per geführter Boots- oder Kajaktour – Hinschwimmen und Anlanden verboten.</t>
         </is>
       </c>
-      <c r="Q43" s="5" t="inlineStr">
+      <c r="R43" s="5" t="inlineStr">
         <is>
           <t>Grotta marina con un’apertura circolare nel soffitto. Solo in barca o kayak guidato: vietato nuotare fin lì o sbarcare.</t>
         </is>
       </c>
-      <c r="R43" s="6" t="inlineStr"/>
-      <c r="S43" s="5" t="inlineStr"/>
+      <c r="S43" s="6" t="inlineStr"/>
       <c r="T43" s="5" t="inlineStr"/>
       <c r="U43" s="5" t="inlineStr"/>
       <c r="V43" s="5" t="inlineStr"/>
       <c r="W43" s="5" t="inlineStr"/>
-      <c r="X43" s="6" t="inlineStr">
+      <c r="X43" s="5" t="inlineStr"/>
+      <c r="Y43" s="6" t="inlineStr">
         <is>
           <t>Primavera a início do outono, conforme o mar</t>
         </is>
       </c>
-      <c r="Y43" s="5" t="inlineStr">
+      <c r="Z43" s="5" t="inlineStr">
         <is>
           <t>Spring to early autumn, sea permitting</t>
         </is>
       </c>
-      <c r="Z43" s="5" t="inlineStr">
+      <c r="AA43" s="5" t="inlineStr">
         <is>
           <t>De primavera a principios de otoño, según el mar</t>
         </is>
       </c>
-      <c r="AA43" s="5" t="inlineStr">
+      <c r="AB43" s="5" t="inlineStr">
         <is>
           <t>Du printemps au début de l’automne, selon la mer</t>
         </is>
       </c>
-      <c r="AB43" s="5" t="inlineStr">
+      <c r="AC43" s="5" t="inlineStr">
         <is>
           <t>Frühling bis Frühherbst, je nach Seegang</t>
         </is>
       </c>
-      <c r="AC43" s="5" t="inlineStr">
+      <c r="AD43" s="5" t="inlineStr">
         <is>
           <t>Dalla primavera all’inizio dell’autunno, mare permettendo</t>
         </is>
@@ -12032,68 +12278,73 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="L44" s="6" t="inlineStr">
+      <c r="L44" s="5" t="inlineStr">
+        <is>
+          <t>images/beaches_1.jpg</t>
+        </is>
+      </c>
+      <c r="M44" s="6" t="inlineStr">
         <is>
           <t>A praia mais perto de casa, com a capela na falésia e miradouros para o pôr do sol.</t>
         </is>
       </c>
-      <c r="M44" s="5" t="inlineStr">
+      <c r="N44" s="5" t="inlineStr">
         <is>
           <t>The beach closest to the house, with the clifftop chapel and sunset viewpoints.</t>
         </is>
       </c>
-      <c r="N44" s="5" t="inlineStr">
+      <c r="O44" s="5" t="inlineStr">
         <is>
           <t>La playa más cercana a la casa, con la capilla en el acantilado y miradores para el atardecer.</t>
         </is>
       </c>
-      <c r="O44" s="5" t="inlineStr">
+      <c r="P44" s="5" t="inlineStr">
         <is>
           <t>La plage la plus proche, avec la chapelle sur la falaise et des belvédères pour le coucher du soleil.</t>
         </is>
       </c>
-      <c r="P44" s="5" t="inlineStr">
+      <c r="Q44" s="5" t="inlineStr">
         <is>
           <t>Der nächste Strand zum Haus, mit Klippenkapelle und Aussichtspunkten zum Sonnenuntergang.</t>
         </is>
       </c>
-      <c r="Q44" s="5" t="inlineStr">
+      <c r="R44" s="5" t="inlineStr">
         <is>
           <t>La spiaggia più vicina a casa, con la cappella sulla scogliera e belvedere per il tramonto.</t>
         </is>
       </c>
-      <c r="R44" s="6" t="inlineStr"/>
-      <c r="S44" s="5" t="inlineStr"/>
+      <c r="S44" s="6" t="inlineStr"/>
       <c r="T44" s="5" t="inlineStr"/>
       <c r="U44" s="5" t="inlineStr"/>
       <c r="V44" s="5" t="inlineStr"/>
       <c r="W44" s="5" t="inlineStr"/>
-      <c r="X44" s="6" t="inlineStr">
+      <c r="X44" s="5" t="inlineStr"/>
+      <c r="Y44" s="6" t="inlineStr">
         <is>
           <t>Todo o ano</t>
         </is>
       </c>
-      <c r="Y44" s="5" t="inlineStr">
+      <c r="Z44" s="5" t="inlineStr">
         <is>
           <t>All year round</t>
         </is>
       </c>
-      <c r="Z44" s="5" t="inlineStr">
+      <c r="AA44" s="5" t="inlineStr">
         <is>
           <t>Todo el año</t>
         </is>
       </c>
-      <c r="AA44" s="5" t="inlineStr">
+      <c r="AB44" s="5" t="inlineStr">
         <is>
           <t>Toute l’année</t>
         </is>
       </c>
-      <c r="AB44" s="5" t="inlineStr">
+      <c r="AC44" s="5" t="inlineStr">
         <is>
           <t>Ganzjährig</t>
         </is>
       </c>
-      <c r="AC44" s="5" t="inlineStr">
+      <c r="AD44" s="5" t="inlineStr">
         <is>
           <t>Tutto l’anno</t>
         </is>
@@ -12131,68 +12382,69 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="L45" s="6" t="inlineStr">
+      <c r="L45" s="5" t="inlineStr"/>
+      <c r="M45" s="6" t="inlineStr">
         <is>
           <t>Pequena praia entre falésias, famosa pelo arco natural na rocha.</t>
         </is>
       </c>
-      <c r="M45" s="5" t="inlineStr">
+      <c r="N45" s="5" t="inlineStr">
         <is>
           <t>Small beach between cliffs, famous for its natural rock arch.</t>
         </is>
       </c>
-      <c r="N45" s="5" t="inlineStr">
+      <c r="O45" s="5" t="inlineStr">
         <is>
           <t>Pequeña playa entre acantilados, famosa por su arco natural de roca.</t>
         </is>
       </c>
-      <c r="O45" s="5" t="inlineStr">
+      <c r="P45" s="5" t="inlineStr">
         <is>
           <t>Petite plage entre falaises, célèbre pour son arche rocheuse naturelle.</t>
         </is>
       </c>
-      <c r="P45" s="5" t="inlineStr">
+      <c r="Q45" s="5" t="inlineStr">
         <is>
           <t>Kleiner Strand zwischen Klippen, bekannt für seinen natürlichen Felsbogen.</t>
         </is>
       </c>
-      <c r="Q45" s="5" t="inlineStr">
+      <c r="R45" s="5" t="inlineStr">
         <is>
           <t>Piccola spiaggia tra le scogliere, famosa per il suo arco naturale.</t>
         </is>
       </c>
-      <c r="R45" s="6" t="inlineStr"/>
-      <c r="S45" s="5" t="inlineStr"/>
+      <c r="S45" s="6" t="inlineStr"/>
       <c r="T45" s="5" t="inlineStr"/>
       <c r="U45" s="5" t="inlineStr"/>
       <c r="V45" s="5" t="inlineStr"/>
       <c r="W45" s="5" t="inlineStr"/>
-      <c r="X45" s="6" t="inlineStr">
+      <c r="X45" s="5" t="inlineStr"/>
+      <c r="Y45" s="6" t="inlineStr">
         <is>
           <t>Todo o ano</t>
         </is>
       </c>
-      <c r="Y45" s="5" t="inlineStr">
+      <c r="Z45" s="5" t="inlineStr">
         <is>
           <t>All year round</t>
         </is>
       </c>
-      <c r="Z45" s="5" t="inlineStr">
+      <c r="AA45" s="5" t="inlineStr">
         <is>
           <t>Todo el año</t>
         </is>
       </c>
-      <c r="AA45" s="5" t="inlineStr">
+      <c r="AB45" s="5" t="inlineStr">
         <is>
           <t>Toute l’année</t>
         </is>
       </c>
-      <c r="AB45" s="5" t="inlineStr">
+      <c r="AC45" s="5" t="inlineStr">
         <is>
           <t>Ganzjährig</t>
         </is>
       </c>
-      <c r="AC45" s="5" t="inlineStr">
+      <c r="AD45" s="5" t="inlineStr">
         <is>
           <t>Tutto l’anno</t>
         </is>
@@ -12230,68 +12482,73 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="L46" s="6" t="inlineStr">
+      <c r="L46" s="5" t="inlineStr">
+        <is>
+          <t>images/beaches_0.jpg</t>
+        </is>
+      </c>
+      <c r="M46" s="6" t="inlineStr">
         <is>
           <t>Trilho de 5–6 km (por sentido) entre a Praia da Marinha e Vale de Centeanes, com vistas espetaculares.</t>
         </is>
       </c>
-      <c r="M46" s="5" t="inlineStr">
+      <c r="N46" s="5" t="inlineStr">
         <is>
           <t>5–6 km trail (each way) from Praia da Marinha to Vale de Centeanes, with spectacular views.</t>
         </is>
       </c>
-      <c r="N46" s="5" t="inlineStr">
+      <c r="O46" s="5" t="inlineStr">
         <is>
           <t>Sendero de 5–6 km (por trayecto) entre la Praia da Marinha y Vale de Centeanes, con vistas espectaculares.</t>
         </is>
       </c>
-      <c r="O46" s="5" t="inlineStr">
+      <c r="P46" s="5" t="inlineStr">
         <is>
           <t>Sentier de 5–6 km (aller) entre Praia da Marinha et Vale de Centeanes, vues spectaculaires.</t>
         </is>
       </c>
-      <c r="P46" s="5" t="inlineStr">
+      <c r="Q46" s="5" t="inlineStr">
         <is>
           <t>5–6 km Wanderweg (einfach) von der Praia da Marinha nach Vale de Centeanes mit spektakulären Ausblicken.</t>
         </is>
       </c>
-      <c r="Q46" s="5" t="inlineStr">
+      <c r="R46" s="5" t="inlineStr">
         <is>
           <t>Sentiero di 5–6 km (sola andata) tra Praia da Marinha e Vale de Centeanes, con viste spettacolari.</t>
         </is>
       </c>
-      <c r="R46" s="6" t="inlineStr"/>
-      <c r="S46" s="5" t="inlineStr"/>
+      <c r="S46" s="6" t="inlineStr"/>
       <c r="T46" s="5" t="inlineStr"/>
       <c r="U46" s="5" t="inlineStr"/>
       <c r="V46" s="5" t="inlineStr"/>
       <c r="W46" s="5" t="inlineStr"/>
-      <c r="X46" s="6" t="inlineStr">
+      <c r="X46" s="5" t="inlineStr"/>
+      <c r="Y46" s="6" t="inlineStr">
         <is>
           <t>Todo o ano</t>
         </is>
       </c>
-      <c r="Y46" s="5" t="inlineStr">
+      <c r="Z46" s="5" t="inlineStr">
         <is>
           <t>All year round</t>
         </is>
       </c>
-      <c r="Z46" s="5" t="inlineStr">
+      <c r="AA46" s="5" t="inlineStr">
         <is>
           <t>Todo el año</t>
         </is>
       </c>
-      <c r="AA46" s="5" t="inlineStr">
+      <c r="AB46" s="5" t="inlineStr">
         <is>
           <t>Toute l’année</t>
         </is>
       </c>
-      <c r="AB46" s="5" t="inlineStr">
+      <c r="AC46" s="5" t="inlineStr">
         <is>
           <t>Ganzjährig</t>
         </is>
       </c>
-      <c r="AC46" s="5" t="inlineStr">
+      <c r="AD46" s="5" t="inlineStr">
         <is>
           <t>Tutto l’anno</t>
         </is>
@@ -12329,68 +12586,69 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="L47" s="6" t="inlineStr">
+      <c r="L47" s="5" t="inlineStr"/>
+      <c r="M47" s="6" t="inlineStr">
         <is>
           <t>Passadiço curto e acessível junto às falésias até às grutas e rochas esculpidas do Algar Seco.</t>
         </is>
       </c>
-      <c r="M47" s="5" t="inlineStr">
+      <c r="N47" s="5" t="inlineStr">
         <is>
           <t>Short, easy clifftop boardwalk leading to the caves and sculpted rocks of Algar Seco.</t>
         </is>
       </c>
-      <c r="N47" s="5" t="inlineStr">
+      <c r="O47" s="5" t="inlineStr">
         <is>
           <t>Pasarela corta y accesible sobre los acantilados hasta las cuevas y rocas esculpidas del Algar Seco.</t>
         </is>
       </c>
-      <c r="O47" s="5" t="inlineStr">
+      <c r="P47" s="5" t="inlineStr">
         <is>
           <t>Courte promenade accessible sur les falaises jusqu’aux grottes et rochers sculptés d’Algar Seco.</t>
         </is>
       </c>
-      <c r="P47" s="5" t="inlineStr">
+      <c r="Q47" s="5" t="inlineStr">
         <is>
           <t>Kurzer, leichter Klippenweg zu den Höhlen und Felsformationen von Algar Seco.</t>
         </is>
       </c>
-      <c r="Q47" s="5" t="inlineStr">
+      <c r="R47" s="5" t="inlineStr">
         <is>
           <t>Breve passerella accessibile sulle scogliere fino alle grotte e alle rocce scolpite di Algar Seco.</t>
         </is>
       </c>
-      <c r="R47" s="6" t="inlineStr"/>
-      <c r="S47" s="5" t="inlineStr"/>
+      <c r="S47" s="6" t="inlineStr"/>
       <c r="T47" s="5" t="inlineStr"/>
       <c r="U47" s="5" t="inlineStr"/>
       <c r="V47" s="5" t="inlineStr"/>
       <c r="W47" s="5" t="inlineStr"/>
-      <c r="X47" s="6" t="inlineStr">
+      <c r="X47" s="5" t="inlineStr"/>
+      <c r="Y47" s="6" t="inlineStr">
         <is>
           <t>Todo o ano</t>
         </is>
       </c>
-      <c r="Y47" s="5" t="inlineStr">
+      <c r="Z47" s="5" t="inlineStr">
         <is>
           <t>All year round</t>
         </is>
       </c>
-      <c r="Z47" s="5" t="inlineStr">
+      <c r="AA47" s="5" t="inlineStr">
         <is>
           <t>Todo el año</t>
         </is>
       </c>
-      <c r="AA47" s="5" t="inlineStr">
+      <c r="AB47" s="5" t="inlineStr">
         <is>
           <t>Toute l’année</t>
         </is>
       </c>
-      <c r="AB47" s="5" t="inlineStr">
+      <c r="AC47" s="5" t="inlineStr">
         <is>
           <t>Ganzjährig</t>
         </is>
       </c>
-      <c r="AC47" s="5" t="inlineStr">
+      <c r="AD47" s="5" t="inlineStr">
         <is>
           <t>Tutto l’anno</t>
         </is>
@@ -12428,68 +12686,69 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="L48" s="6" t="inlineStr">
+      <c r="L48" s="5" t="inlineStr"/>
+      <c r="M48" s="6" t="inlineStr">
         <is>
           <t>Parque natural junto ao rio Arade, com trilhos, zonas verdes e merendas.</t>
         </is>
       </c>
-      <c r="M48" s="5" t="inlineStr">
+      <c r="N48" s="5" t="inlineStr">
         <is>
           <t>Riverside nature park on the Arade, with trails, green spaces and picnic areas.</t>
         </is>
       </c>
-      <c r="N48" s="5" t="inlineStr">
+      <c r="O48" s="5" t="inlineStr">
         <is>
           <t>Parque natural junto al río Arade, con senderos, zonas verdes y áreas de pícnic.</t>
         </is>
       </c>
-      <c r="O48" s="5" t="inlineStr">
+      <c r="P48" s="5" t="inlineStr">
         <is>
           <t>Parc naturel au bord de l’Arade, avec sentiers, espaces verts et aires de pique-nique.</t>
         </is>
       </c>
-      <c r="P48" s="5" t="inlineStr">
+      <c r="Q48" s="5" t="inlineStr">
         <is>
           <t>Naturpark am Fluss Arade mit Wegen, Grünflächen und Picknickplätzen.</t>
         </is>
       </c>
-      <c r="Q48" s="5" t="inlineStr">
+      <c r="R48" s="5" t="inlineStr">
         <is>
           <t>Parco naturale sul fiume Arade, con sentieri, aree verdi e zone picnic.</t>
         </is>
       </c>
-      <c r="R48" s="6" t="inlineStr"/>
-      <c r="S48" s="5" t="inlineStr"/>
+      <c r="S48" s="6" t="inlineStr"/>
       <c r="T48" s="5" t="inlineStr"/>
       <c r="U48" s="5" t="inlineStr"/>
       <c r="V48" s="5" t="inlineStr"/>
       <c r="W48" s="5" t="inlineStr"/>
-      <c r="X48" s="6" t="inlineStr">
+      <c r="X48" s="5" t="inlineStr"/>
+      <c r="Y48" s="6" t="inlineStr">
         <is>
           <t>Todo o ano</t>
         </is>
       </c>
-      <c r="Y48" s="5" t="inlineStr">
+      <c r="Z48" s="5" t="inlineStr">
         <is>
           <t>All year round</t>
         </is>
       </c>
-      <c r="Z48" s="5" t="inlineStr">
+      <c r="AA48" s="5" t="inlineStr">
         <is>
           <t>Todo el año</t>
         </is>
       </c>
-      <c r="AA48" s="5" t="inlineStr">
+      <c r="AB48" s="5" t="inlineStr">
         <is>
           <t>Toute l’année</t>
         </is>
       </c>
-      <c r="AB48" s="5" t="inlineStr">
+      <c r="AC48" s="5" t="inlineStr">
         <is>
           <t>Ganzjährig</t>
         </is>
       </c>
-      <c r="AC48" s="5" t="inlineStr">
+      <c r="AD48" s="5" t="inlineStr">
         <is>
           <t>Tutto l’anno</t>
         </is>
@@ -12527,68 +12786,69 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="L49" s="6" t="inlineStr">
+      <c r="L49" s="5" t="inlineStr"/>
+      <c r="M49" s="6" t="inlineStr">
         <is>
           <t>Zona húmida de grande valor ecológico, ótima para observar aves migratórias.</t>
         </is>
       </c>
-      <c r="M49" s="5" t="inlineStr">
+      <c r="N49" s="5" t="inlineStr">
         <is>
           <t>Wetland of great ecological value, excellent for birdwatching.</t>
         </is>
       </c>
-      <c r="N49" s="5" t="inlineStr">
+      <c r="O49" s="5" t="inlineStr">
         <is>
           <t>Humedal de gran valor ecológico, ideal para observar aves migratorias.</t>
         </is>
       </c>
-      <c r="O49" s="5" t="inlineStr">
+      <c r="P49" s="5" t="inlineStr">
         <is>
           <t>Zone humide d’une grande richesse écologique, idéale pour observer les oiseaux.</t>
         </is>
       </c>
-      <c r="P49" s="5" t="inlineStr">
+      <c r="Q49" s="5" t="inlineStr">
         <is>
           <t>Ökologisch wertvolles Feuchtgebiet, ideal zur Vogelbeobachtung.</t>
         </is>
       </c>
-      <c r="Q49" s="5" t="inlineStr">
+      <c r="R49" s="5" t="inlineStr">
         <is>
           <t>Zona umida di grande valore ecologico, ideale per il birdwatching.</t>
         </is>
       </c>
-      <c r="R49" s="6" t="inlineStr"/>
-      <c r="S49" s="5" t="inlineStr"/>
+      <c r="S49" s="6" t="inlineStr"/>
       <c r="T49" s="5" t="inlineStr"/>
       <c r="U49" s="5" t="inlineStr"/>
       <c r="V49" s="5" t="inlineStr"/>
       <c r="W49" s="5" t="inlineStr"/>
-      <c r="X49" s="6" t="inlineStr">
+      <c r="X49" s="5" t="inlineStr"/>
+      <c r="Y49" s="6" t="inlineStr">
         <is>
           <t>Todo o ano</t>
         </is>
       </c>
-      <c r="Y49" s="5" t="inlineStr">
+      <c r="Z49" s="5" t="inlineStr">
         <is>
           <t>All year round</t>
         </is>
       </c>
-      <c r="Z49" s="5" t="inlineStr">
+      <c r="AA49" s="5" t="inlineStr">
         <is>
           <t>Todo el año</t>
         </is>
       </c>
-      <c r="AA49" s="5" t="inlineStr">
+      <c r="AB49" s="5" t="inlineStr">
         <is>
           <t>Toute l’année</t>
         </is>
       </c>
-      <c r="AB49" s="5" t="inlineStr">
+      <c r="AC49" s="5" t="inlineStr">
         <is>
           <t>Ganzjährig</t>
         </is>
       </c>
-      <c r="AC49" s="5" t="inlineStr">
+      <c r="AD49" s="5" t="inlineStr">
         <is>
           <t>Tutto l’anno</t>
         </is>
@@ -12626,68 +12886,69 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="L50" s="6" t="inlineStr">
+      <c r="L50" s="5" t="inlineStr"/>
+      <c r="M50" s="6" t="inlineStr">
         <is>
           <t>Passadiços sobre dunas e zonas húmidas com vista para a Ria de Alvor.</t>
         </is>
       </c>
-      <c r="M50" s="5" t="inlineStr">
+      <c r="N50" s="5" t="inlineStr">
         <is>
           <t>Boardwalks over dunes and wetlands overlooking the Alvor estuary.</t>
         </is>
       </c>
-      <c r="N50" s="5" t="inlineStr">
+      <c r="O50" s="5" t="inlineStr">
         <is>
           <t>Pasarelas sobre dunas y humedales con vistas a la Ría de Alvor.</t>
         </is>
       </c>
-      <c r="O50" s="5" t="inlineStr">
+      <c r="P50" s="5" t="inlineStr">
         <is>
           <t>Passerelles sur les dunes et zones humides face à la Ria de Alvor.</t>
         </is>
       </c>
-      <c r="P50" s="5" t="inlineStr">
+      <c r="Q50" s="5" t="inlineStr">
         <is>
           <t>Holzstege über Dünen und Feuchtgebiete mit Blick auf die Ria de Alvor.</t>
         </is>
       </c>
-      <c r="Q50" s="5" t="inlineStr">
+      <c r="R50" s="5" t="inlineStr">
         <is>
           <t>Passerelle su dune e zone umide con vista sulla Ria de Alvor.</t>
         </is>
       </c>
-      <c r="R50" s="6" t="inlineStr"/>
-      <c r="S50" s="5" t="inlineStr"/>
+      <c r="S50" s="6" t="inlineStr"/>
       <c r="T50" s="5" t="inlineStr"/>
       <c r="U50" s="5" t="inlineStr"/>
       <c r="V50" s="5" t="inlineStr"/>
       <c r="W50" s="5" t="inlineStr"/>
-      <c r="X50" s="6" t="inlineStr">
+      <c r="X50" s="5" t="inlineStr"/>
+      <c r="Y50" s="6" t="inlineStr">
         <is>
           <t>Todo o ano</t>
         </is>
       </c>
-      <c r="Y50" s="5" t="inlineStr">
+      <c r="Z50" s="5" t="inlineStr">
         <is>
           <t>All year round</t>
         </is>
       </c>
-      <c r="Z50" s="5" t="inlineStr">
+      <c r="AA50" s="5" t="inlineStr">
         <is>
           <t>Todo el año</t>
         </is>
       </c>
-      <c r="AA50" s="5" t="inlineStr">
+      <c r="AB50" s="5" t="inlineStr">
         <is>
           <t>Toute l’année</t>
         </is>
       </c>
-      <c r="AB50" s="5" t="inlineStr">
+      <c r="AC50" s="5" t="inlineStr">
         <is>
           <t>Ganzjährig</t>
         </is>
       </c>
-      <c r="AC50" s="5" t="inlineStr">
+      <c r="AD50" s="5" t="inlineStr">
         <is>
           <t>Tutto l’anno</t>
         </is>
@@ -12725,68 +12986,69 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="L51" s="6" t="inlineStr">
+      <c r="L51" s="5" t="inlineStr"/>
+      <c r="M51" s="6" t="inlineStr">
         <is>
           <t>Montanha, trilhos, aldeias, o miradouro da Fóia e as termas das Caldas de Monchique. Um dia diferente da praia.</t>
         </is>
       </c>
-      <c r="M51" s="5" t="inlineStr">
+      <c r="N51" s="5" t="inlineStr">
         <is>
           <t>Mountains, trails, villages, the Fóia viewpoint and the Caldas de Monchique spa. A change from the beach.</t>
         </is>
       </c>
-      <c r="N51" s="5" t="inlineStr">
+      <c r="O51" s="5" t="inlineStr">
         <is>
           <t>Montaña, senderos, aldeas, el mirador de Fóia y el balneario de Caldas de Monchique. Un día distinto a la playa.</t>
         </is>
       </c>
-      <c r="O51" s="5" t="inlineStr">
+      <c r="P51" s="5" t="inlineStr">
         <is>
           <t>Montagne, sentiers, villages, le belvédère de Fóia et les thermes de Caldas de Monchique. Une journée hors plage.</t>
         </is>
       </c>
-      <c r="P51" s="5" t="inlineStr">
+      <c r="Q51" s="5" t="inlineStr">
         <is>
           <t>Berge, Wanderwege, Dörfer, der Aussichtspunkt Fóia und das Thermalbad Caldas de Monchique. Abwechslung zum Strand.</t>
         </is>
       </c>
-      <c r="Q51" s="5" t="inlineStr">
+      <c r="R51" s="5" t="inlineStr">
         <is>
           <t>Montagna, sentieri, villaggi, il belvedere di Fóia e le terme di Caldas de Monchique. Una giornata diversa dal mare.</t>
         </is>
       </c>
-      <c r="R51" s="6" t="inlineStr"/>
-      <c r="S51" s="5" t="inlineStr"/>
+      <c r="S51" s="6" t="inlineStr"/>
       <c r="T51" s="5" t="inlineStr"/>
       <c r="U51" s="5" t="inlineStr"/>
       <c r="V51" s="5" t="inlineStr"/>
       <c r="W51" s="5" t="inlineStr"/>
-      <c r="X51" s="6" t="inlineStr">
+      <c r="X51" s="5" t="inlineStr"/>
+      <c r="Y51" s="6" t="inlineStr">
         <is>
           <t>Todo o ano</t>
         </is>
       </c>
-      <c r="Y51" s="5" t="inlineStr">
+      <c r="Z51" s="5" t="inlineStr">
         <is>
           <t>All year round</t>
         </is>
       </c>
-      <c r="Z51" s="5" t="inlineStr">
+      <c r="AA51" s="5" t="inlineStr">
         <is>
           <t>Todo el año</t>
         </is>
       </c>
-      <c r="AA51" s="5" t="inlineStr">
+      <c r="AB51" s="5" t="inlineStr">
         <is>
           <t>Toute l’année</t>
         </is>
       </c>
-      <c r="AB51" s="5" t="inlineStr">
+      <c r="AC51" s="5" t="inlineStr">
         <is>
           <t>Ganzjährig</t>
         </is>
       </c>
-      <c r="AC51" s="5" t="inlineStr">
+      <c r="AD51" s="5" t="inlineStr">
         <is>
           <t>Tutto l’anno</t>
         </is>
@@ -12824,68 +13086,69 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="L52" s="6" t="inlineStr">
+      <c r="L52" s="5" t="inlineStr"/>
+      <c r="M52" s="6" t="inlineStr">
         <is>
           <t>Falésias, arcos rochosos e grutas marítimas — uma das paisagens mais famosas do Algarve.</t>
         </is>
       </c>
-      <c r="M52" s="5" t="inlineStr">
+      <c r="N52" s="5" t="inlineStr">
         <is>
           <t>Cliffs, rock arches and sea caves — one of the Algarve’s most famous landscapes.</t>
         </is>
       </c>
-      <c r="N52" s="5" t="inlineStr">
+      <c r="O52" s="5" t="inlineStr">
         <is>
           <t>Acantilados, arcos de roca y cuevas marinas: uno de los paisajes más famosos del Algarve.</t>
         </is>
       </c>
-      <c r="O52" s="5" t="inlineStr">
+      <c r="P52" s="5" t="inlineStr">
         <is>
           <t>Falaises, arches rocheuses et grottes marines — l’un des paysages les plus célèbres de l’Algarve.</t>
         </is>
       </c>
-      <c r="P52" s="5" t="inlineStr">
+      <c r="Q52" s="5" t="inlineStr">
         <is>
           <t>Klippen, Felsbögen und Meereshöhlen – eine der berühmtesten Landschaften der Algarve.</t>
         </is>
       </c>
-      <c r="Q52" s="5" t="inlineStr">
+      <c r="R52" s="5" t="inlineStr">
         <is>
           <t>Scogliere, archi di roccia e grotte marine: uno dei paesaggi più famosi dell’Algarve.</t>
         </is>
       </c>
-      <c r="R52" s="6" t="inlineStr"/>
-      <c r="S52" s="5" t="inlineStr"/>
+      <c r="S52" s="6" t="inlineStr"/>
       <c r="T52" s="5" t="inlineStr"/>
       <c r="U52" s="5" t="inlineStr"/>
       <c r="V52" s="5" t="inlineStr"/>
       <c r="W52" s="5" t="inlineStr"/>
-      <c r="X52" s="6" t="inlineStr">
+      <c r="X52" s="5" t="inlineStr"/>
+      <c r="Y52" s="6" t="inlineStr">
         <is>
           <t>Todo o ano</t>
         </is>
       </c>
-      <c r="Y52" s="5" t="inlineStr">
+      <c r="Z52" s="5" t="inlineStr">
         <is>
           <t>All year round</t>
         </is>
       </c>
-      <c r="Z52" s="5" t="inlineStr">
+      <c r="AA52" s="5" t="inlineStr">
         <is>
           <t>Todo el año</t>
         </is>
       </c>
-      <c r="AA52" s="5" t="inlineStr">
+      <c r="AB52" s="5" t="inlineStr">
         <is>
           <t>Toute l’année</t>
         </is>
       </c>
-      <c r="AB52" s="5" t="inlineStr">
+      <c r="AC52" s="5" t="inlineStr">
         <is>
           <t>Ganzjährig</t>
         </is>
       </c>
-      <c r="AC52" s="5" t="inlineStr">
+      <c r="AD52" s="5" t="inlineStr">
         <is>
           <t>Tutto l’anno</t>
         </is>
@@ -12923,68 +13186,69 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="L53" s="6" t="inlineStr">
+      <c r="L53" s="5" t="inlineStr"/>
+      <c r="M53" s="6" t="inlineStr">
         <is>
           <t>Um dos castelos islâmicos mais importantes de Portugal, com muralhas e vista sobre a cidade.</t>
         </is>
       </c>
-      <c r="M53" s="5" t="inlineStr">
+      <c r="N53" s="5" t="inlineStr">
         <is>
           <t>One of Portugal’s most important Islamic castles, with ramparts and views over the town.</t>
         </is>
       </c>
-      <c r="N53" s="5" t="inlineStr">
+      <c r="O53" s="5" t="inlineStr">
         <is>
           <t>Uno de los castillos islámicos más importantes de Portugal, con murallas y vistas a la ciudad.</t>
         </is>
       </c>
-      <c r="O53" s="5" t="inlineStr">
+      <c r="P53" s="5" t="inlineStr">
         <is>
           <t>L’un des plus importants châteaux islamiques du Portugal, avec remparts et vue sur la ville.</t>
         </is>
       </c>
-      <c r="P53" s="5" t="inlineStr">
+      <c r="Q53" s="5" t="inlineStr">
         <is>
           <t>Eine der bedeutendsten islamischen Burgen Portugals mit Mauern und Blick über die Stadt.</t>
         </is>
       </c>
-      <c r="Q53" s="5" t="inlineStr">
+      <c r="R53" s="5" t="inlineStr">
         <is>
           <t>Uno dei castelli islamici più importanti del Portogallo, con mura e vista sulla città.</t>
         </is>
       </c>
-      <c r="R53" s="6" t="inlineStr"/>
-      <c r="S53" s="5" t="inlineStr"/>
+      <c r="S53" s="6" t="inlineStr"/>
       <c r="T53" s="5" t="inlineStr"/>
       <c r="U53" s="5" t="inlineStr"/>
       <c r="V53" s="5" t="inlineStr"/>
       <c r="W53" s="5" t="inlineStr"/>
-      <c r="X53" s="6" t="inlineStr">
+      <c r="X53" s="5" t="inlineStr"/>
+      <c r="Y53" s="6" t="inlineStr">
         <is>
           <t>Todo o ano</t>
         </is>
       </c>
-      <c r="Y53" s="5" t="inlineStr">
+      <c r="Z53" s="5" t="inlineStr">
         <is>
           <t>All year round</t>
         </is>
       </c>
-      <c r="Z53" s="5" t="inlineStr">
+      <c r="AA53" s="5" t="inlineStr">
         <is>
           <t>Todo el año</t>
         </is>
       </c>
-      <c r="AA53" s="5" t="inlineStr">
+      <c r="AB53" s="5" t="inlineStr">
         <is>
           <t>Toute l’année</t>
         </is>
       </c>
-      <c r="AB53" s="5" t="inlineStr">
+      <c r="AC53" s="5" t="inlineStr">
         <is>
           <t>Ganzjährig</t>
         </is>
       </c>
-      <c r="AC53" s="5" t="inlineStr">
+      <c r="AD53" s="5" t="inlineStr">
         <is>
           <t>Tutto l’anno</t>
         </is>
@@ -13022,68 +13286,73 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="L54" s="6" t="inlineStr">
+      <c r="L54" s="5" t="inlineStr">
+        <is>
+          <t>images/beaches_3.jpg</t>
+        </is>
+      </c>
+      <c r="M54" s="6" t="inlineStr">
         <is>
           <t>Saídas de Armação de Pêra, Benagil, Carvoeiro, Portimão e Albufeira pelas grutas e falésias.</t>
         </is>
       </c>
-      <c r="M54" s="5" t="inlineStr">
+      <c r="N54" s="5" t="inlineStr">
         <is>
           <t>Trips from Armação de Pêra, Benagil, Carvoeiro, Portimão and Albufeira along caves and cliffs.</t>
         </is>
       </c>
-      <c r="N54" s="5" t="inlineStr">
+      <c r="O54" s="5" t="inlineStr">
         <is>
           <t>Salidas desde Armação de Pêra, Benagil, Carvoeiro, Portimão y Albufeira por cuevas y acantilados.</t>
         </is>
       </c>
-      <c r="O54" s="5" t="inlineStr">
+      <c r="P54" s="5" t="inlineStr">
         <is>
           <t>Départs d’Armação de Pêra, Benagil, Carvoeiro, Portimão et Albufeira le long des grottes et falaises.</t>
         </is>
       </c>
-      <c r="P54" s="5" t="inlineStr">
+      <c r="Q54" s="5" t="inlineStr">
         <is>
           <t>Touren ab Armação de Pêra, Benagil, Carvoeiro, Portimão und Albufeira entlang Höhlen und Klippen.</t>
         </is>
       </c>
-      <c r="Q54" s="5" t="inlineStr">
+      <c r="R54" s="5" t="inlineStr">
         <is>
           <t>Partenze da Armação de Pêra, Benagil, Carvoeiro, Portimão e Albufeira tra grotte e scogliere.</t>
         </is>
       </c>
-      <c r="R54" s="6" t="inlineStr"/>
-      <c r="S54" s="5" t="inlineStr"/>
+      <c r="S54" s="6" t="inlineStr"/>
       <c r="T54" s="5" t="inlineStr"/>
       <c r="U54" s="5" t="inlineStr"/>
       <c r="V54" s="5" t="inlineStr"/>
       <c r="W54" s="5" t="inlineStr"/>
-      <c r="X54" s="6" t="inlineStr">
+      <c r="X54" s="5" t="inlineStr"/>
+      <c r="Y54" s="6" t="inlineStr">
         <is>
           <t>Primavera a início do outono, conforme o mar</t>
         </is>
       </c>
-      <c r="Y54" s="5" t="inlineStr">
+      <c r="Z54" s="5" t="inlineStr">
         <is>
           <t>Spring to early autumn, sea permitting</t>
         </is>
       </c>
-      <c r="Z54" s="5" t="inlineStr">
+      <c r="AA54" s="5" t="inlineStr">
         <is>
           <t>De primavera a principios de otoño, según el mar</t>
         </is>
       </c>
-      <c r="AA54" s="5" t="inlineStr">
+      <c r="AB54" s="5" t="inlineStr">
         <is>
           <t>Du printemps au début de l’automne, selon la mer</t>
         </is>
       </c>
-      <c r="AB54" s="5" t="inlineStr">
+      <c r="AC54" s="5" t="inlineStr">
         <is>
           <t>Frühling bis Frühherbst, je nach Seegang</t>
         </is>
       </c>
-      <c r="AC54" s="5" t="inlineStr">
+      <c r="AD54" s="5" t="inlineStr">
         <is>
           <t>Dalla primavera all’inizio dell’autunno, mare permettendo</t>
         </is>
@@ -13121,68 +13390,69 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="L55" s="6" t="inlineStr">
+      <c r="L55" s="5" t="inlineStr"/>
+      <c r="M55" s="6" t="inlineStr">
         <is>
           <t>Saídas de Portimão, Ferragudo e Albufeira para ver golfinhos no seu habitat (avistamento não garantido).</t>
         </is>
       </c>
-      <c r="M55" s="5" t="inlineStr">
+      <c r="N55" s="5" t="inlineStr">
         <is>
           <t>Trips from Portimão, Ferragudo and Albufeira to see dolphins in the wild (sightings not guaranteed).</t>
         </is>
       </c>
-      <c r="N55" s="5" t="inlineStr">
+      <c r="O55" s="5" t="inlineStr">
         <is>
           <t>Salidas desde Portimão, Ferragudo y Albufeira para ver delfines en libertad (avistamiento no garantizado).</t>
         </is>
       </c>
-      <c r="O55" s="5" t="inlineStr">
+      <c r="P55" s="5" t="inlineStr">
         <is>
           <t>Sorties depuis Portimão, Ferragudo et Albufeira pour observer les dauphins (observation non garantie).</t>
         </is>
       </c>
-      <c r="P55" s="5" t="inlineStr">
+      <c r="Q55" s="5" t="inlineStr">
         <is>
           <t>Ausfahrten ab Portimão, Ferragudo und Albufeira zu wilden Delfinen (Sichtung nicht garantiert).</t>
         </is>
       </c>
-      <c r="Q55" s="5" t="inlineStr">
+      <c r="R55" s="5" t="inlineStr">
         <is>
           <t>Uscite da Portimão, Ferragudo e Albufeira per vedere i delfini in libertà (avvistamento non garantito).</t>
         </is>
       </c>
-      <c r="R55" s="6" t="inlineStr"/>
-      <c r="S55" s="5" t="inlineStr"/>
+      <c r="S55" s="6" t="inlineStr"/>
       <c r="T55" s="5" t="inlineStr"/>
       <c r="U55" s="5" t="inlineStr"/>
       <c r="V55" s="5" t="inlineStr"/>
       <c r="W55" s="5" t="inlineStr"/>
-      <c r="X55" s="6" t="inlineStr">
+      <c r="X55" s="5" t="inlineStr"/>
+      <c r="Y55" s="6" t="inlineStr">
         <is>
           <t>Primavera a início do outono, conforme o mar</t>
         </is>
       </c>
-      <c r="Y55" s="5" t="inlineStr">
+      <c r="Z55" s="5" t="inlineStr">
         <is>
           <t>Spring to early autumn, sea permitting</t>
         </is>
       </c>
-      <c r="Z55" s="5" t="inlineStr">
+      <c r="AA55" s="5" t="inlineStr">
         <is>
           <t>De primavera a principios de otoño, según el mar</t>
         </is>
       </c>
-      <c r="AA55" s="5" t="inlineStr">
+      <c r="AB55" s="5" t="inlineStr">
         <is>
           <t>Du printemps au début de l’automne, selon la mer</t>
         </is>
       </c>
-      <c r="AB55" s="5" t="inlineStr">
+      <c r="AC55" s="5" t="inlineStr">
         <is>
           <t>Frühling bis Frühherbst, je nach Seegang</t>
         </is>
       </c>
-      <c r="AC55" s="5" t="inlineStr">
+      <c r="AD55" s="5" t="inlineStr">
         <is>
           <t>Dalla primavera all’inizio dell’autunno, mare permettendo</t>
         </is>
@@ -13220,68 +13490,69 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="L56" s="6" t="inlineStr">
+      <c r="L56" s="5" t="inlineStr"/>
+      <c r="M56" s="6" t="inlineStr">
         <is>
           <t>Explorar a costa e pequenas enseadas em atividades guiadas (Benagil, Armação de Pêra, Carvoeiro).</t>
         </is>
       </c>
-      <c r="M56" s="5" t="inlineStr">
+      <c r="N56" s="5" t="inlineStr">
         <is>
           <t>Explore the coast and hidden coves on guided tours (Benagil, Armação de Pêra, Carvoeiro).</t>
         </is>
       </c>
-      <c r="N56" s="5" t="inlineStr">
+      <c r="O56" s="5" t="inlineStr">
         <is>
           <t>Explorar la costa y pequeñas calas en actividades guiadas (Benagil, Armação de Pêra, Carvoeiro).</t>
         </is>
       </c>
-      <c r="O56" s="5" t="inlineStr">
+      <c r="P56" s="5" t="inlineStr">
         <is>
           <t>Explorer la côte et les criques lors de sorties guidées (Benagil, Armação de Pêra, Carvoeiro).</t>
         </is>
       </c>
-      <c r="P56" s="5" t="inlineStr">
+      <c r="Q56" s="5" t="inlineStr">
         <is>
           <t>Küste und kleine Buchten auf geführten Touren erkunden (Benagil, Armação de Pêra, Carvoeiro).</t>
         </is>
       </c>
-      <c r="Q56" s="5" t="inlineStr">
+      <c r="R56" s="5" t="inlineStr">
         <is>
           <t>Esplorare la costa e piccole calette con attività guidate (Benagil, Armação de Pêra, Carvoeiro).</t>
         </is>
       </c>
-      <c r="R56" s="6" t="inlineStr"/>
-      <c r="S56" s="5" t="inlineStr"/>
+      <c r="S56" s="6" t="inlineStr"/>
       <c r="T56" s="5" t="inlineStr"/>
       <c r="U56" s="5" t="inlineStr"/>
       <c r="V56" s="5" t="inlineStr"/>
       <c r="W56" s="5" t="inlineStr"/>
-      <c r="X56" s="6" t="inlineStr">
+      <c r="X56" s="5" t="inlineStr"/>
+      <c r="Y56" s="6" t="inlineStr">
         <is>
           <t>Primavera a início do outono, conforme o mar</t>
         </is>
       </c>
-      <c r="Y56" s="5" t="inlineStr">
+      <c r="Z56" s="5" t="inlineStr">
         <is>
           <t>Spring to early autumn, sea permitting</t>
         </is>
       </c>
-      <c r="Z56" s="5" t="inlineStr">
+      <c r="AA56" s="5" t="inlineStr">
         <is>
           <t>De primavera a principios de otoño, según el mar</t>
         </is>
       </c>
-      <c r="AA56" s="5" t="inlineStr">
+      <c r="AB56" s="5" t="inlineStr">
         <is>
           <t>Du printemps au début de l’automne, selon la mer</t>
         </is>
       </c>
-      <c r="AB56" s="5" t="inlineStr">
+      <c r="AC56" s="5" t="inlineStr">
         <is>
           <t>Frühling bis Frühherbst, je nach Seegang</t>
         </is>
       </c>
-      <c r="AC56" s="5" t="inlineStr">
+      <c r="AD56" s="5" t="inlineStr">
         <is>
           <t>Dalla primavera all’inizio dell’autunno, mare permettendo</t>
         </is>
@@ -13319,68 +13590,69 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="L57" s="6" t="inlineStr">
+      <c r="L57" s="5" t="inlineStr"/>
+      <c r="M57" s="6" t="inlineStr">
         <is>
           <t>Passeios ao fim da tarde a partir de Albufeira, Portimão e Armação de Pêra, alguns com jantar ou música.</t>
         </is>
       </c>
-      <c r="M57" s="5" t="inlineStr">
+      <c r="N57" s="5" t="inlineStr">
         <is>
           <t>Evening cruises from Albufeira, Portimão and Armação de Pêra, some with dinner or music.</t>
         </is>
       </c>
-      <c r="N57" s="5" t="inlineStr">
+      <c r="O57" s="5" t="inlineStr">
         <is>
           <t>Paseos al atardecer desde Albufeira, Portimão y Armação de Pêra, algunos con cena o música.</t>
         </is>
       </c>
-      <c r="O57" s="5" t="inlineStr">
+      <c r="P57" s="5" t="inlineStr">
         <is>
           <t>Croisières au coucher du soleil depuis Albufeira, Portimão et Armação de Pêra, certaines avec dîner ou musique.</t>
         </is>
       </c>
-      <c r="P57" s="5" t="inlineStr">
+      <c r="Q57" s="5" t="inlineStr">
         <is>
           <t>Abendfahrten ab Albufeira, Portimão und Armação de Pêra, teils mit Dinner oder Musik.</t>
         </is>
       </c>
-      <c r="Q57" s="5" t="inlineStr">
+      <c r="R57" s="5" t="inlineStr">
         <is>
           <t>Crociere al tramonto da Albufeira, Portimão e Armação de Pêra, alcune con cena o musica.</t>
         </is>
       </c>
-      <c r="R57" s="6" t="inlineStr"/>
-      <c r="S57" s="5" t="inlineStr"/>
+      <c r="S57" s="6" t="inlineStr"/>
       <c r="T57" s="5" t="inlineStr"/>
       <c r="U57" s="5" t="inlineStr"/>
       <c r="V57" s="5" t="inlineStr"/>
       <c r="W57" s="5" t="inlineStr"/>
-      <c r="X57" s="6" t="inlineStr">
+      <c r="X57" s="5" t="inlineStr"/>
+      <c r="Y57" s="6" t="inlineStr">
         <is>
           <t>Primavera a início do outono, conforme o mar</t>
         </is>
       </c>
-      <c r="Y57" s="5" t="inlineStr">
+      <c r="Z57" s="5" t="inlineStr">
         <is>
           <t>Spring to early autumn, sea permitting</t>
         </is>
       </c>
-      <c r="Z57" s="5" t="inlineStr">
+      <c r="AA57" s="5" t="inlineStr">
         <is>
           <t>De primavera a principios de otoño, según el mar</t>
         </is>
       </c>
-      <c r="AA57" s="5" t="inlineStr">
+      <c r="AB57" s="5" t="inlineStr">
         <is>
           <t>Du printemps au début de l’automne, selon la mer</t>
         </is>
       </c>
-      <c r="AB57" s="5" t="inlineStr">
+      <c r="AC57" s="5" t="inlineStr">
         <is>
           <t>Frühling bis Frühherbst, je nach Seegang</t>
         </is>
       </c>
-      <c r="AC57" s="5" t="inlineStr">
+      <c r="AD57" s="5" t="inlineStr">
         <is>
           <t>Dalla primavera all’inizio dell’autunno, mare permettendo</t>
         </is>
@@ -13418,68 +13690,69 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="L58" s="6" t="inlineStr">
+      <c r="L58" s="5" t="inlineStr"/>
+      <c r="M58" s="6" t="inlineStr">
         <is>
           <t>Mergulhos acompanhados por operadores especializados em Armação de Pêra, Carvoeiro e Portimão.</t>
         </is>
       </c>
-      <c r="M58" s="5" t="inlineStr">
+      <c r="N58" s="5" t="inlineStr">
         <is>
           <t>Guided dives with specialist operators in Armação de Pêra, Carvoeiro and Portimão.</t>
         </is>
       </c>
-      <c r="N58" s="5" t="inlineStr">
+      <c r="O58" s="5" t="inlineStr">
         <is>
           <t>Inmersiones guiadas con operadores especializados en Armação de Pêra, Carvoeiro y Portimão.</t>
         </is>
       </c>
-      <c r="O58" s="5" t="inlineStr">
+      <c r="P58" s="5" t="inlineStr">
         <is>
           <t>Plongées encadrées par des opérateurs spécialisés à Armação de Pêra, Carvoeiro et Portimão.</t>
         </is>
       </c>
-      <c r="P58" s="5" t="inlineStr">
+      <c r="Q58" s="5" t="inlineStr">
         <is>
           <t>Geführte Tauchgänge mit Fachanbietern in Armação de Pêra, Carvoeiro und Portimão.</t>
         </is>
       </c>
-      <c r="Q58" s="5" t="inlineStr">
+      <c r="R58" s="5" t="inlineStr">
         <is>
           <t>Immersioni guidate con operatori specializzati ad Armação de Pêra, Carvoeiro e Portimão.</t>
         </is>
       </c>
-      <c r="R58" s="6" t="inlineStr"/>
-      <c r="S58" s="5" t="inlineStr"/>
+      <c r="S58" s="6" t="inlineStr"/>
       <c r="T58" s="5" t="inlineStr"/>
       <c r="U58" s="5" t="inlineStr"/>
       <c r="V58" s="5" t="inlineStr"/>
       <c r="W58" s="5" t="inlineStr"/>
-      <c r="X58" s="6" t="inlineStr">
+      <c r="X58" s="5" t="inlineStr"/>
+      <c r="Y58" s="6" t="inlineStr">
         <is>
           <t>Primavera a início do outono, conforme o mar</t>
         </is>
       </c>
-      <c r="Y58" s="5" t="inlineStr">
+      <c r="Z58" s="5" t="inlineStr">
         <is>
           <t>Spring to early autumn, sea permitting</t>
         </is>
       </c>
-      <c r="Z58" s="5" t="inlineStr">
+      <c r="AA58" s="5" t="inlineStr">
         <is>
           <t>De primavera a principios de otoño, según el mar</t>
         </is>
       </c>
-      <c r="AA58" s="5" t="inlineStr">
+      <c r="AB58" s="5" t="inlineStr">
         <is>
           <t>Du printemps au début de l’automne, selon la mer</t>
         </is>
       </c>
-      <c r="AB58" s="5" t="inlineStr">
+      <c r="AC58" s="5" t="inlineStr">
         <is>
           <t>Frühling bis Frühherbst, je nach Seegang</t>
         </is>
       </c>
-      <c r="AC58" s="5" t="inlineStr">
+      <c r="AD58" s="5" t="inlineStr">
         <is>
           <t>Dalla primavera all’inizio dell’autunno, mare permettendo</t>
         </is>
@@ -13517,68 +13790,69 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="L59" s="6" t="inlineStr">
+      <c r="L59" s="5" t="inlineStr"/>
+      <c r="M59" s="6" t="inlineStr">
         <is>
           <t>Aulas para todas as idades e níveis em Albufeira, Alvor e na costa ocidental.</t>
         </is>
       </c>
-      <c r="M59" s="5" t="inlineStr">
+      <c r="N59" s="5" t="inlineStr">
         <is>
           <t>Lessons for all ages and levels in Albufeira, Alvor and on the west coast.</t>
         </is>
       </c>
-      <c r="N59" s="5" t="inlineStr">
+      <c r="O59" s="5" t="inlineStr">
         <is>
           <t>Clases para todas las edades y niveles en Albufeira, Alvor y la costa oeste.</t>
         </is>
       </c>
-      <c r="O59" s="5" t="inlineStr">
+      <c r="P59" s="5" t="inlineStr">
         <is>
           <t>Cours pour tous âges et niveaux à Albufeira, Alvor et sur la côte ouest.</t>
         </is>
       </c>
-      <c r="P59" s="5" t="inlineStr">
+      <c r="Q59" s="5" t="inlineStr">
         <is>
           <t>Kurse für jedes Alter und Niveau in Albufeira, Alvor und an der Westküste.</t>
         </is>
       </c>
-      <c r="Q59" s="5" t="inlineStr">
+      <c r="R59" s="5" t="inlineStr">
         <is>
           <t>Lezioni per tutte le età e livelli ad Albufeira, Alvor e sulla costa occidentale.</t>
         </is>
       </c>
-      <c r="R59" s="6" t="inlineStr"/>
-      <c r="S59" s="5" t="inlineStr"/>
+      <c r="S59" s="6" t="inlineStr"/>
       <c r="T59" s="5" t="inlineStr"/>
       <c r="U59" s="5" t="inlineStr"/>
       <c r="V59" s="5" t="inlineStr"/>
       <c r="W59" s="5" t="inlineStr"/>
-      <c r="X59" s="6" t="inlineStr">
+      <c r="X59" s="5" t="inlineStr"/>
+      <c r="Y59" s="6" t="inlineStr">
         <is>
           <t>Todo o ano</t>
         </is>
       </c>
-      <c r="Y59" s="5" t="inlineStr">
+      <c r="Z59" s="5" t="inlineStr">
         <is>
           <t>All year round</t>
         </is>
       </c>
-      <c r="Z59" s="5" t="inlineStr">
+      <c r="AA59" s="5" t="inlineStr">
         <is>
           <t>Todo el año</t>
         </is>
       </c>
-      <c r="AA59" s="5" t="inlineStr">
+      <c r="AB59" s="5" t="inlineStr">
         <is>
           <t>Toute l’année</t>
         </is>
       </c>
-      <c r="AB59" s="5" t="inlineStr">
+      <c r="AC59" s="5" t="inlineStr">
         <is>
           <t>Ganzjährig</t>
         </is>
       </c>
-      <c r="AC59" s="5" t="inlineStr">
+      <c r="AD59" s="5" t="inlineStr">
         <is>
           <t>Tutto l’anno</t>
         </is>
@@ -13616,72 +13890,73 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="L60" s="6" t="inlineStr">
+      <c r="L60" s="5" t="inlineStr"/>
+      <c r="M60" s="6" t="inlineStr">
         <is>
           <t>Festa religiosa e tradicional da comunidade de Porches.</t>
         </is>
       </c>
-      <c r="M60" s="5" t="inlineStr">
+      <c r="N60" s="5" t="inlineStr">
         <is>
           <t>Traditional religious festival of the Porches community.</t>
         </is>
       </c>
-      <c r="N60" s="5" t="inlineStr">
+      <c r="O60" s="5" t="inlineStr">
         <is>
           <t>Fiesta religiosa y tradicional de la comunidad de Porches.</t>
         </is>
       </c>
-      <c r="O60" s="5" t="inlineStr">
+      <c r="P60" s="5" t="inlineStr">
         <is>
           <t>Fête religieuse et traditionnelle de la communauté de Porches.</t>
         </is>
       </c>
-      <c r="P60" s="5" t="inlineStr">
+      <c r="Q60" s="5" t="inlineStr">
         <is>
           <t>Traditionelles religiöses Fest der Gemeinde Porches.</t>
         </is>
       </c>
-      <c r="Q60" s="5" t="inlineStr">
+      <c r="R60" s="5" t="inlineStr">
         <is>
           <t>Festa religiosa e tradizionale della comunità di Porches.</t>
         </is>
       </c>
-      <c r="R60" s="6" t="inlineStr">
+      <c r="S60" s="6" t="inlineStr">
         <is>
           <t>primeiro fim de semana de agosto</t>
         </is>
       </c>
-      <c r="S60" s="5" t="inlineStr">
+      <c r="T60" s="5" t="inlineStr">
         <is>
           <t>first weekend of August</t>
         </is>
       </c>
-      <c r="T60" s="5" t="inlineStr">
+      <c r="U60" s="5" t="inlineStr">
         <is>
           <t>primer fin de semana de agosto</t>
         </is>
       </c>
-      <c r="U60" s="5" t="inlineStr">
+      <c r="V60" s="5" t="inlineStr">
         <is>
           <t>premier week-end d’août</t>
         </is>
       </c>
-      <c r="V60" s="5" t="inlineStr">
+      <c r="W60" s="5" t="inlineStr">
         <is>
           <t>erstes Augustwochenende</t>
         </is>
       </c>
-      <c r="W60" s="5" t="inlineStr">
+      <c r="X60" s="5" t="inlineStr">
         <is>
           <t>primo fine settimana di agosto</t>
         </is>
       </c>
-      <c r="X60" s="6" t="inlineStr"/>
-      <c r="Y60" s="5" t="inlineStr"/>
+      <c r="Y60" s="6" t="inlineStr"/>
       <c r="Z60" s="5" t="inlineStr"/>
       <c r="AA60" s="5" t="inlineStr"/>
       <c r="AB60" s="5" t="inlineStr"/>
       <c r="AC60" s="5" t="inlineStr"/>
+      <c r="AD60" s="5" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
@@ -13715,72 +13990,77 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="L61" s="6" t="inlineStr">
+      <c r="L61" s="5" t="inlineStr">
+        <is>
+          <t>images/attractions_2.jpg</t>
+        </is>
+      </c>
+      <c r="M61" s="6" t="inlineStr">
         <is>
           <t>Festa popular e religiosa da freguesia de Porches.</t>
         </is>
       </c>
-      <c r="M61" s="5" t="inlineStr">
+      <c r="N61" s="5" t="inlineStr">
         <is>
           <t>Popular and religious festival of the parish of Porches.</t>
         </is>
       </c>
-      <c r="N61" s="5" t="inlineStr">
+      <c r="O61" s="5" t="inlineStr">
         <is>
           <t>Fiesta popular y religiosa de la parroquia de Porches.</t>
         </is>
       </c>
-      <c r="O61" s="5" t="inlineStr">
+      <c r="P61" s="5" t="inlineStr">
         <is>
           <t>Fête populaire et religieuse de la paroisse de Porches.</t>
         </is>
       </c>
-      <c r="P61" s="5" t="inlineStr">
+      <c r="Q61" s="5" t="inlineStr">
         <is>
           <t>Volks- und Kirchenfest der Gemeinde Porches.</t>
         </is>
       </c>
-      <c r="Q61" s="5" t="inlineStr">
+      <c r="R61" s="5" t="inlineStr">
         <is>
           <t>Festa popolare e religiosa della parrocchia di Porches.</t>
         </is>
       </c>
-      <c r="R61" s="6" t="inlineStr">
+      <c r="S61" s="6" t="inlineStr">
         <is>
           <t>primeiro fim de semana de setembro</t>
         </is>
       </c>
-      <c r="S61" s="5" t="inlineStr">
+      <c r="T61" s="5" t="inlineStr">
         <is>
           <t>first weekend of September</t>
         </is>
       </c>
-      <c r="T61" s="5" t="inlineStr">
+      <c r="U61" s="5" t="inlineStr">
         <is>
           <t>primer fin de semana de septiembre</t>
         </is>
       </c>
-      <c r="U61" s="5" t="inlineStr">
+      <c r="V61" s="5" t="inlineStr">
         <is>
           <t>premier week-end de septembre</t>
         </is>
       </c>
-      <c r="V61" s="5" t="inlineStr">
+      <c r="W61" s="5" t="inlineStr">
         <is>
           <t>erstes Septemberwochenende</t>
         </is>
       </c>
-      <c r="W61" s="5" t="inlineStr">
+      <c r="X61" s="5" t="inlineStr">
         <is>
           <t>primo fine settimana di settembre</t>
         </is>
       </c>
-      <c r="X61" s="6" t="inlineStr"/>
-      <c r="Y61" s="5" t="inlineStr"/>
+      <c r="Y61" s="6" t="inlineStr"/>
       <c r="Z61" s="5" t="inlineStr"/>
       <c r="AA61" s="5" t="inlineStr"/>
       <c r="AB61" s="5" t="inlineStr"/>
       <c r="AC61" s="5" t="inlineStr"/>
+      <c r="AD61" s="5" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
@@ -13814,72 +14094,73 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="L62" s="6" t="inlineStr">
+      <c r="L62" s="5" t="inlineStr"/>
+      <c r="M62" s="6" t="inlineStr">
         <is>
           <t>Antiguidades, objetos usados, decoração e artigos de coleção.</t>
         </is>
       </c>
-      <c r="M62" s="5" t="inlineStr">
+      <c r="N62" s="5" t="inlineStr">
         <is>
           <t>Antiques, second-hand goods, homeware and collectables.</t>
         </is>
       </c>
-      <c r="N62" s="5" t="inlineStr">
+      <c r="O62" s="5" t="inlineStr">
         <is>
           <t>Antigüedades, objetos de segunda mano, decoración y coleccionismo.</t>
         </is>
       </c>
-      <c r="O62" s="5" t="inlineStr">
+      <c r="P62" s="5" t="inlineStr">
         <is>
           <t>Antiquités, brocante, décoration et objets de collection.</t>
         </is>
       </c>
-      <c r="P62" s="5" t="inlineStr">
+      <c r="Q62" s="5" t="inlineStr">
         <is>
           <t>Antiquitäten, Second-Hand, Deko und Sammlerstücke.</t>
         </is>
       </c>
-      <c r="Q62" s="5" t="inlineStr">
+      <c r="R62" s="5" t="inlineStr">
         <is>
           <t>Antiquariato, oggetti usati, decorazioni e collezionismo.</t>
         </is>
       </c>
-      <c r="R62" s="6" t="inlineStr">
+      <c r="S62" s="6" t="inlineStr">
         <is>
           <t>4.º domingo de cada mês</t>
         </is>
       </c>
-      <c r="S62" s="5" t="inlineStr">
+      <c r="T62" s="5" t="inlineStr">
         <is>
           <t>4th Sunday of each month</t>
         </is>
       </c>
-      <c r="T62" s="5" t="inlineStr">
+      <c r="U62" s="5" t="inlineStr">
         <is>
           <t>4.º domingo de cada mes</t>
         </is>
       </c>
-      <c r="U62" s="5" t="inlineStr">
+      <c r="V62" s="5" t="inlineStr">
         <is>
           <t>4e dimanche du mois</t>
         </is>
       </c>
-      <c r="V62" s="5" t="inlineStr">
+      <c r="W62" s="5" t="inlineStr">
         <is>
           <t>jeden 4. Sonntag im Monat</t>
         </is>
       </c>
-      <c r="W62" s="5" t="inlineStr">
+      <c r="X62" s="5" t="inlineStr">
         <is>
           <t>4ª domenica del mese</t>
         </is>
       </c>
-      <c r="X62" s="6" t="inlineStr"/>
-      <c r="Y62" s="5" t="inlineStr"/>
+      <c r="Y62" s="6" t="inlineStr"/>
       <c r="Z62" s="5" t="inlineStr"/>
       <c r="AA62" s="5" t="inlineStr"/>
       <c r="AB62" s="5" t="inlineStr"/>
       <c r="AC62" s="5" t="inlineStr"/>
+      <c r="AD62" s="5" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
@@ -13913,72 +14194,73 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="L63" s="6" t="inlineStr">
+      <c r="L63" s="5" t="inlineStr"/>
+      <c r="M63" s="6" t="inlineStr">
         <is>
           <t>Mercado tradicional com roupa, acessórios e artigos para a casa.</t>
         </is>
       </c>
-      <c r="M63" s="5" t="inlineStr">
+      <c r="N63" s="5" t="inlineStr">
         <is>
           <t>Traditional market with clothes, accessories and household goods.</t>
         </is>
       </c>
-      <c r="N63" s="5" t="inlineStr">
+      <c r="O63" s="5" t="inlineStr">
         <is>
           <t>Mercado tradicional con ropa, accesorios y artículos para el hogar.</t>
         </is>
       </c>
-      <c r="O63" s="5" t="inlineStr">
+      <c r="P63" s="5" t="inlineStr">
         <is>
           <t>Marché traditionnel : vêtements, accessoires et articles pour la maison.</t>
         </is>
       </c>
-      <c r="P63" s="5" t="inlineStr">
+      <c r="Q63" s="5" t="inlineStr">
         <is>
           <t>Traditioneller Markt mit Kleidung, Accessoires und Haushaltswaren.</t>
         </is>
       </c>
-      <c r="Q63" s="5" t="inlineStr">
+      <c r="R63" s="5" t="inlineStr">
         <is>
           <t>Mercato tradizionale con abbigliamento, accessori e articoli per la casa.</t>
         </is>
       </c>
-      <c r="R63" s="6" t="inlineStr">
+      <c r="S63" s="6" t="inlineStr">
         <is>
           <t>2.º domingo de cada mês</t>
         </is>
       </c>
-      <c r="S63" s="5" t="inlineStr">
+      <c r="T63" s="5" t="inlineStr">
         <is>
           <t>2nd Sunday of each month</t>
         </is>
       </c>
-      <c r="T63" s="5" t="inlineStr">
+      <c r="U63" s="5" t="inlineStr">
         <is>
           <t>2.º domingo de cada mes</t>
         </is>
       </c>
-      <c r="U63" s="5" t="inlineStr">
+      <c r="V63" s="5" t="inlineStr">
         <is>
           <t>2e dimanche du mois</t>
         </is>
       </c>
-      <c r="V63" s="5" t="inlineStr">
+      <c r="W63" s="5" t="inlineStr">
         <is>
           <t>jeden 2. Sonntag im Monat</t>
         </is>
       </c>
-      <c r="W63" s="5" t="inlineStr">
+      <c r="X63" s="5" t="inlineStr">
         <is>
           <t>2ª domenica del mese</t>
         </is>
       </c>
-      <c r="X63" s="6" t="inlineStr"/>
-      <c r="Y63" s="5" t="inlineStr"/>
+      <c r="Y63" s="6" t="inlineStr"/>
       <c r="Z63" s="5" t="inlineStr"/>
       <c r="AA63" s="5" t="inlineStr"/>
       <c r="AB63" s="5" t="inlineStr"/>
       <c r="AC63" s="5" t="inlineStr"/>
+      <c r="AD63" s="5" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
@@ -14012,72 +14294,73 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="L64" s="6" t="inlineStr">
+      <c r="L64" s="5" t="inlineStr"/>
+      <c r="M64" s="6" t="inlineStr">
         <is>
           <t>Mercado tradicional de produtos frescos e sabores do Algarve, num edifício histórico.</t>
         </is>
       </c>
-      <c r="M64" s="5" t="inlineStr">
+      <c r="N64" s="5" t="inlineStr">
         <is>
           <t>Traditional market of fresh produce and Algarve flavours, in a historic building.</t>
         </is>
       </c>
-      <c r="N64" s="5" t="inlineStr">
+      <c r="O64" s="5" t="inlineStr">
         <is>
           <t>Mercado tradicional de productos frescos y sabores del Algarve, en un edificio histórico.</t>
         </is>
       </c>
-      <c r="O64" s="5" t="inlineStr">
+      <c r="P64" s="5" t="inlineStr">
         <is>
           <t>Marché traditionnel de produits frais et saveurs de l’Algarve, dans un bâtiment historique.</t>
         </is>
       </c>
-      <c r="P64" s="5" t="inlineStr">
+      <c r="Q64" s="5" t="inlineStr">
         <is>
           <t>Traditioneller Markt mit frischen Produkten und Algarve-Spezialitäten in einem historischen Gebäude.</t>
         </is>
       </c>
-      <c r="Q64" s="5" t="inlineStr">
+      <c r="R64" s="5" t="inlineStr">
         <is>
           <t>Mercato tradizionale di prodotti freschi e sapori dell’Algarve, in un edificio storico.</t>
         </is>
       </c>
-      <c r="R64" s="6" t="inlineStr">
+      <c r="S64" s="6" t="inlineStr">
         <is>
           <t>todos os dias; mais animado ao sábado</t>
         </is>
       </c>
-      <c r="S64" s="5" t="inlineStr">
+      <c r="T64" s="5" t="inlineStr">
         <is>
           <t>daily; liveliest on Saturdays</t>
         </is>
       </c>
-      <c r="T64" s="5" t="inlineStr">
+      <c r="U64" s="5" t="inlineStr">
         <is>
           <t>todos los días; más animado los sábados</t>
         </is>
       </c>
-      <c r="U64" s="5" t="inlineStr">
+      <c r="V64" s="5" t="inlineStr">
         <is>
           <t>tous les jours ; plus animé le samedi</t>
         </is>
       </c>
-      <c r="V64" s="5" t="inlineStr">
+      <c r="W64" s="5" t="inlineStr">
         <is>
           <t>täglich; samstags am lebhaftesten</t>
         </is>
       </c>
-      <c r="W64" s="5" t="inlineStr">
+      <c r="X64" s="5" t="inlineStr">
         <is>
           <t>tutti i giorni; più vivace il sabato</t>
         </is>
       </c>
-      <c r="X64" s="6" t="inlineStr"/>
-      <c r="Y64" s="5" t="inlineStr"/>
+      <c r="Y64" s="6" t="inlineStr"/>
       <c r="Z64" s="5" t="inlineStr"/>
       <c r="AA64" s="5" t="inlineStr"/>
       <c r="AB64" s="5" t="inlineStr"/>
       <c r="AC64" s="5" t="inlineStr"/>
+      <c r="AD64" s="5" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
@@ -14111,75 +14394,76 @@
           <t>sim</t>
         </is>
       </c>
-      <c r="L65" s="6" t="inlineStr">
+      <c r="L65" s="5" t="inlineStr"/>
+      <c r="M65" s="6" t="inlineStr">
         <is>
           <t>Iluminações, mercados de Natal, concertos e fogo de artifício em Lagoa, Carvoeiro, Armação de Pêra, Portimão, Albufeira e Silves.</t>
         </is>
       </c>
-      <c r="M65" s="5" t="inlineStr">
+      <c r="N65" s="5" t="inlineStr">
         <is>
           <t>Lights, Christmas markets, concerts and fireworks in Lagoa, Carvoeiro, Armação de Pêra, Portimão, Albufeira and Silves.</t>
         </is>
       </c>
-      <c r="N65" s="5" t="inlineStr">
+      <c r="O65" s="5" t="inlineStr">
         <is>
           <t>Iluminación, mercados navideños, conciertos y fuegos artificiales en Lagoa, Carvoeiro, Armação de Pêra, Portimão, Albufeira y Silves.</t>
         </is>
       </c>
-      <c r="O65" s="5" t="inlineStr">
+      <c r="P65" s="5" t="inlineStr">
         <is>
           <t>Illuminations, marchés de Noël, concerts et feux d’artifice à Lagoa, Carvoeiro, Armação de Pêra, Portimão, Albufeira et Silves.</t>
         </is>
       </c>
-      <c r="P65" s="5" t="inlineStr">
+      <c r="Q65" s="5" t="inlineStr">
         <is>
           <t>Lichter, Weihnachtsmärkte, Konzerte und Feuerwerk in Lagoa, Carvoeiro, Armação de Pêra, Portimão, Albufeira und Silves.</t>
         </is>
       </c>
-      <c r="Q65" s="5" t="inlineStr">
+      <c r="R65" s="5" t="inlineStr">
         <is>
           <t>Luminarie, mercatini di Natale, concerti e fuochi d’artificio a Lagoa, Carvoeiro, Armação de Pêra, Portimão, Albufeira e Silves.</t>
         </is>
       </c>
-      <c r="R65" s="6" t="inlineStr">
+      <c r="S65" s="6" t="inlineStr">
         <is>
           <t>dezembro e início de janeiro</t>
         </is>
       </c>
-      <c r="S65" s="5" t="inlineStr">
+      <c r="T65" s="5" t="inlineStr">
         <is>
           <t>December and early January</t>
         </is>
       </c>
-      <c r="T65" s="5" t="inlineStr">
+      <c r="U65" s="5" t="inlineStr">
         <is>
           <t>diciembre y principios de enero</t>
         </is>
       </c>
-      <c r="U65" s="5" t="inlineStr">
+      <c r="V65" s="5" t="inlineStr">
         <is>
           <t>décembre et début janvier</t>
         </is>
       </c>
-      <c r="V65" s="5" t="inlineStr">
+      <c r="W65" s="5" t="inlineStr">
         <is>
           <t>Dezember und Anfang Januar</t>
         </is>
       </c>
-      <c r="W65" s="5" t="inlineStr">
+      <c r="X65" s="5" t="inlineStr">
         <is>
           <t>dicembre e inizio gennaio</t>
         </is>
       </c>
-      <c r="X65" s="6" t="inlineStr"/>
-      <c r="Y65" s="5" t="inlineStr"/>
+      <c r="Y65" s="6" t="inlineStr"/>
       <c r="Z65" s="5" t="inlineStr"/>
       <c r="AA65" s="5" t="inlineStr"/>
       <c r="AB65" s="5" t="inlineStr"/>
       <c r="AC65" s="5" t="inlineStr"/>
+      <c r="AD65" s="5" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AC65"/>
+  <autoFilter ref="A1:AD65"/>
   <dataValidations count="3">
     <dataValidation sqref="A2:A500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Escolha um valor da lista" type="list">
       <formula1>"events,water,nature,sea,indoor,markets"</formula1>
@@ -15002,7 +15286,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M23"/>
+  <dimension ref="A1:N23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -15012,12 +15296,13 @@
     <col width="10" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
     <col width="28" customWidth="1" min="7" max="7"/>
-    <col width="44" customWidth="1" min="8" max="8"/>
+    <col width="26" customWidth="1" min="8" max="8"/>
     <col width="44" customWidth="1" min="9" max="9"/>
     <col width="44" customWidth="1" min="10" max="10"/>
     <col width="44" customWidth="1" min="11" max="11"/>
     <col width="44" customWidth="1" min="12" max="12"/>
     <col width="44" customWidth="1" min="13" max="13"/>
+    <col width="44" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -15058,30 +15343,35 @@
       </c>
       <c r="H1" s="4" t="inlineStr">
         <is>
+          <t>imagem</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
           <t>desc_pt</t>
         </is>
       </c>
-      <c r="I1" s="4" t="inlineStr">
+      <c r="J1" s="4" t="inlineStr">
         <is>
           <t>desc_en</t>
         </is>
       </c>
-      <c r="J1" s="4" t="inlineStr">
+      <c r="K1" s="4" t="inlineStr">
         <is>
           <t>desc_es</t>
         </is>
       </c>
-      <c r="K1" s="4" t="inlineStr">
+      <c r="L1" s="4" t="inlineStr">
         <is>
           <t>desc_fr</t>
         </is>
       </c>
-      <c r="L1" s="4" t="inlineStr">
+      <c r="M1" s="4" t="inlineStr">
         <is>
           <t>desc_de</t>
         </is>
       </c>
-      <c r="M1" s="4" t="inlineStr">
+      <c r="N1" s="4" t="inlineStr">
         <is>
           <t>desc_it</t>
         </is>
@@ -15119,32 +15409,37 @@
           <t>Praia Nossa Senhora da Rocha</t>
         </is>
       </c>
-      <c r="H2" s="6" t="inlineStr">
+      <c r="H2" s="5" t="inlineStr">
+        <is>
+          <t>images/beaches_1.jpg</t>
+        </is>
+      </c>
+      <c r="I2" s="6" t="inlineStr">
         <is>
           <t>Praia abrigada com a capela na falésia. Ideal para famílias.</t>
         </is>
       </c>
-      <c r="I2" s="5" t="inlineStr">
+      <c r="J2" s="5" t="inlineStr">
         <is>
           <t>Sheltered beach with the clifftop chapel. Great for families.</t>
         </is>
       </c>
-      <c r="J2" s="5" t="inlineStr">
+      <c r="K2" s="5" t="inlineStr">
         <is>
           <t>Playa resguardada con la capilla sobre el acantilado. Ideal para familias.</t>
         </is>
       </c>
-      <c r="K2" s="5" t="inlineStr">
+      <c r="L2" s="5" t="inlineStr">
         <is>
           <t>Plage abritée avec la chapelle sur la falaise. Idéale pour les familles.</t>
         </is>
       </c>
-      <c r="L2" s="5" t="inlineStr">
+      <c r="M2" s="5" t="inlineStr">
         <is>
           <t>Geschützter Strand mit der Kapelle auf der Klippe. Ideal für Familien.</t>
         </is>
       </c>
-      <c r="M2" s="5" t="inlineStr">
+      <c r="N2" s="5" t="inlineStr">
         <is>
           <t>Spiaggia riparata con la cappella sulla scogliera. Ideale per famiglie.</t>
         </is>
@@ -15182,32 +15477,37 @@
           <t>Praia de Armação de Pêra</t>
         </is>
       </c>
-      <c r="H3" s="6" t="inlineStr">
+      <c r="H3" s="5" t="inlineStr">
+        <is>
+          <t>images/beaches_4.jpg</t>
+        </is>
+      </c>
+      <c r="I3" s="6" t="inlineStr">
         <is>
           <t>Praia extensa com passeio marítimo, cafés e restaurantes.</t>
         </is>
       </c>
-      <c r="I3" s="5" t="inlineStr">
+      <c r="J3" s="5" t="inlineStr">
         <is>
           <t>Long sandy beach with a promenade, cafés and restaurants.</t>
         </is>
       </c>
-      <c r="J3" s="5" t="inlineStr">
+      <c r="K3" s="5" t="inlineStr">
         <is>
           <t>Playa extensa con paseo marítimo, cafés y restaurantes.</t>
         </is>
       </c>
-      <c r="K3" s="5" t="inlineStr">
+      <c r="L3" s="5" t="inlineStr">
         <is>
           <t>Longue plage de sable avec promenade, cafés et restaurants.</t>
         </is>
       </c>
-      <c r="L3" s="5" t="inlineStr">
+      <c r="M3" s="5" t="inlineStr">
         <is>
           <t>Langer Sandstrand mit Promenade, Cafés und Restaurants.</t>
         </is>
       </c>
-      <c r="M3" s="5" t="inlineStr">
+      <c r="N3" s="5" t="inlineStr">
         <is>
           <t>Lunga spiaggia con lungomare, bar e ristoranti.</t>
         </is>
@@ -15245,32 +15545,37 @@
           <t>Praia da Marinha</t>
         </is>
       </c>
-      <c r="H4" s="6" t="inlineStr">
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>images/beaches_0.jpg</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
         <is>
           <t>Uma das praias mais famosas da Europa: falésias, arcos e água cristalina. No verão chegue cedo — o estacionamento enche.</t>
         </is>
       </c>
-      <c r="I4" s="5" t="inlineStr">
+      <c r="J4" s="5" t="inlineStr">
         <is>
           <t>One of the most famous beaches in Europe: cliffs, arches and clear water. Arrive early in summer — parking fills up.</t>
         </is>
       </c>
-      <c r="J4" s="5" t="inlineStr">
+      <c r="K4" s="5" t="inlineStr">
         <is>
           <t>Una de las playas más famosas de Europa: acantilados, arcos y agua cristalina. En verano llegue temprano: el aparcamiento se llena.</t>
         </is>
       </c>
-      <c r="K4" s="5" t="inlineStr">
+      <c r="L4" s="5" t="inlineStr">
         <is>
           <t>L’une des plages les plus célèbres d’Europe : falaises, arches et eau cristalline. En été, arrivez tôt — le parking se remplit vite.</t>
         </is>
       </c>
-      <c r="L4" s="5" t="inlineStr">
+      <c r="M4" s="5" t="inlineStr">
         <is>
           <t>Einer der berühmtesten Strände Europas: Klippen, Felsbögen und klares Wasser. Im Sommer früh kommen – der Parkplatz ist schnell voll.</t>
         </is>
       </c>
-      <c r="M4" s="5" t="inlineStr">
+      <c r="N4" s="5" t="inlineStr">
         <is>
           <t>Una delle spiagge più famose d’Europa: scogliere, archi e acqua cristallina. In estate arrivate presto: il parcheggio si riempie.</t>
         </is>
@@ -15308,32 +15613,37 @@
           <t>Praia de Benagil</t>
         </is>
       </c>
-      <c r="H5" s="6" t="inlineStr">
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>images/beaches_3.jpg</t>
+        </is>
+      </c>
+      <c r="I5" s="6" t="inlineStr">
         <is>
           <t>Ponto de partida para passeios de barco e kayak à gruta de Benagil.</t>
         </is>
       </c>
-      <c r="I5" s="5" t="inlineStr">
+      <c r="J5" s="5" t="inlineStr">
         <is>
           <t>Starting point for boat and kayak trips to the Benagil sea cave.</t>
         </is>
       </c>
-      <c r="J5" s="5" t="inlineStr">
+      <c r="K5" s="5" t="inlineStr">
         <is>
           <t>Punto de salida de excursiones en barco y kayak a la cueva de Benagil.</t>
         </is>
       </c>
-      <c r="K5" s="5" t="inlineStr">
+      <c r="L5" s="5" t="inlineStr">
         <is>
           <t>Point de départ des excursions en bateau et en kayak vers la grotte de Benagil.</t>
         </is>
       </c>
-      <c r="L5" s="5" t="inlineStr">
+      <c r="M5" s="5" t="inlineStr">
         <is>
           <t>Ausgangspunkt für Boots- und Kajaktouren zur Benagil-Höhle.</t>
         </is>
       </c>
-      <c r="M5" s="5" t="inlineStr">
+      <c r="N5" s="5" t="inlineStr">
         <is>
           <t>Punto di partenza per gite in barca e kayak alla grotta di Benagil.</t>
         </is>
@@ -15371,32 +15681,37 @@
           <t>Praia do Vale de Centeanes</t>
         </is>
       </c>
-      <c r="H6" s="6" t="inlineStr">
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>images/beaches_2.jpg</t>
+        </is>
+      </c>
+      <c r="I6" s="6" t="inlineStr">
         <is>
           <t>Praia pequena e mais sossegada entre falésias.</t>
         </is>
       </c>
-      <c r="I6" s="5" t="inlineStr">
+      <c r="J6" s="5" t="inlineStr">
         <is>
           <t>Small, quieter beach between cliffs.</t>
         </is>
       </c>
-      <c r="J6" s="5" t="inlineStr">
+      <c r="K6" s="5" t="inlineStr">
         <is>
           <t>Playa pequeña y más tranquila entre acantilados.</t>
         </is>
       </c>
-      <c r="K6" s="5" t="inlineStr">
+      <c r="L6" s="5" t="inlineStr">
         <is>
           <t>Petite plage plus tranquille entre les falaises.</t>
         </is>
       </c>
-      <c r="L6" s="5" t="inlineStr">
+      <c r="M6" s="5" t="inlineStr">
         <is>
           <t>Kleiner, ruhigerer Strand zwischen Klippen.</t>
         </is>
       </c>
-      <c r="M6" s="5" t="inlineStr">
+      <c r="N6" s="5" t="inlineStr">
         <is>
           <t>Piccola spiaggia più tranquilla tra le scogliere.</t>
         </is>
@@ -15426,32 +15741,33 @@
           <t>Praia da Albandeira</t>
         </is>
       </c>
-      <c r="H7" s="6" t="inlineStr">
+      <c r="H7" s="5" t="inlineStr"/>
+      <c r="I7" s="6" t="inlineStr">
         <is>
           <t>Pequena enseada com arco natural na rocha.</t>
         </is>
       </c>
-      <c r="I7" s="5" t="inlineStr">
+      <c r="J7" s="5" t="inlineStr">
         <is>
           <t>Small cove with a natural rock arch.</t>
         </is>
       </c>
-      <c r="J7" s="5" t="inlineStr">
+      <c r="K7" s="5" t="inlineStr">
         <is>
           <t>Pequeña cala con un arco natural de roca.</t>
         </is>
       </c>
-      <c r="K7" s="5" t="inlineStr">
+      <c r="L7" s="5" t="inlineStr">
         <is>
           <t>Petite crique avec une arche rocheuse naturelle.</t>
         </is>
       </c>
-      <c r="L7" s="5" t="inlineStr">
+      <c r="M7" s="5" t="inlineStr">
         <is>
           <t>Kleine Bucht mit natürlichem Felsbogen.</t>
         </is>
       </c>
-      <c r="M7" s="5" t="inlineStr">
+      <c r="N7" s="5" t="inlineStr">
         <is>
           <t>Piccola caletta con un arco naturale nella roccia.</t>
         </is>
@@ -15485,32 +15801,33 @@
           <t>Tasca 26 Porches</t>
         </is>
       </c>
-      <c r="H8" s="6" t="inlineStr">
+      <c r="H8" s="5" t="inlineStr"/>
+      <c r="I8" s="6" t="inlineStr">
         <is>
           <t>Tasca tradicional, carnes grelhadas.</t>
         </is>
       </c>
-      <c r="I8" s="5" t="inlineStr">
+      <c r="J8" s="5" t="inlineStr">
         <is>
           <t>Traditional tavern, grilled meats.</t>
         </is>
       </c>
-      <c r="J8" s="5" t="inlineStr">
+      <c r="K8" s="5" t="inlineStr">
         <is>
           <t>Taberna tradicional, carnes a la brasa.</t>
         </is>
       </c>
-      <c r="K8" s="5" t="inlineStr">
+      <c r="L8" s="5" t="inlineStr">
         <is>
           <t>Taverne traditionnelle, viandes grillées.</t>
         </is>
       </c>
-      <c r="L8" s="5" t="inlineStr">
+      <c r="M8" s="5" t="inlineStr">
         <is>
           <t>Traditionelle Taverne, Grillfleisch.</t>
         </is>
       </c>
-      <c r="M8" s="5" t="inlineStr">
+      <c r="N8" s="5" t="inlineStr">
         <is>
           <t>Taverna tradizionale, carni alla griglia.</t>
         </is>
@@ -15548,32 +15865,33 @@
           <t>O Charneco Estômbar</t>
         </is>
       </c>
-      <c r="H9" s="6" t="inlineStr">
+      <c r="H9" s="5" t="inlineStr"/>
+      <c r="I9" s="6" t="inlineStr">
         <is>
           <t>Sem menu, preço fixo com vinho. Cozinha algarvia autêntica. Reserva obrigatória.</t>
         </is>
       </c>
-      <c r="I9" s="5" t="inlineStr">
+      <c r="J9" s="5" t="inlineStr">
         <is>
           <t>No menu, fixed price with wine. Authentic Algarve cooking. Booking essential.</t>
         </is>
       </c>
-      <c r="J9" s="5" t="inlineStr">
+      <c r="K9" s="5" t="inlineStr">
         <is>
           <t>Sin carta, precio fijo con vino incluido. Cocina algarvía auténtica. Reserva imprescindible.</t>
         </is>
       </c>
-      <c r="K9" s="5" t="inlineStr">
+      <c r="L9" s="5" t="inlineStr">
         <is>
           <t>Pas de carte, prix fixe vin compris. Cuisine authentique de l’Algarve. Réservation indispensable.</t>
         </is>
       </c>
-      <c r="L9" s="5" t="inlineStr">
+      <c r="M9" s="5" t="inlineStr">
         <is>
           <t>Keine Speisekarte, Festpreis inkl. Wein. Authentische Algarve-Küche. Reservierung erforderlich.</t>
         </is>
       </c>
-      <c r="M9" s="5" t="inlineStr">
+      <c r="N9" s="5" t="inlineStr">
         <is>
           <t>Niente menù, prezzo fisso con vino incluso. Autentica cucina dell’Algarve. Prenotazione obbligatoria.</t>
         </is>
@@ -15611,32 +15929,33 @@
           <t>O Ciclo Lagoa</t>
         </is>
       </c>
-      <c r="H10" s="6" t="inlineStr">
+      <c r="H10" s="5" t="inlineStr"/>
+      <c r="I10" s="6" t="inlineStr">
         <is>
           <t>Peixe fresco e pratos tradicionais no centro de Lagoa.</t>
         </is>
       </c>
-      <c r="I10" s="5" t="inlineStr">
+      <c r="J10" s="5" t="inlineStr">
         <is>
           <t>Fresh fish and traditional dishes in the centre of Lagoa.</t>
         </is>
       </c>
-      <c r="J10" s="5" t="inlineStr">
+      <c r="K10" s="5" t="inlineStr">
         <is>
           <t>Pescado fresco y platos tradicionales en el centro de Lagoa.</t>
         </is>
       </c>
-      <c r="K10" s="5" t="inlineStr">
+      <c r="L10" s="5" t="inlineStr">
         <is>
           <t>Poisson frais et plats traditionnels au centre de Lagoa.</t>
         </is>
       </c>
-      <c r="L10" s="5" t="inlineStr">
+      <c r="M10" s="5" t="inlineStr">
         <is>
           <t>Frischer Fisch und traditionelle Gerichte im Zentrum von Lagoa.</t>
         </is>
       </c>
-      <c r="M10" s="5" t="inlineStr">
+      <c r="N10" s="5" t="inlineStr">
         <is>
           <t>Pesce fresco e piatti tradizionali nel centro di Lagoa.</t>
         </is>
@@ -15674,32 +15993,33 @@
           <t>Rei das Praias Ferragudo</t>
         </is>
       </c>
-      <c r="H11" s="6" t="inlineStr">
+      <c r="H11" s="5" t="inlineStr"/>
+      <c r="I11" s="6" t="inlineStr">
         <is>
           <t>Peixe e marisco na Praia dos Caneiros, desde 1976.</t>
         </is>
       </c>
-      <c r="I11" s="5" t="inlineStr">
+      <c r="J11" s="5" t="inlineStr">
         <is>
           <t>Fish and seafood on Caneiros beach, since 1976.</t>
         </is>
       </c>
-      <c r="J11" s="5" t="inlineStr">
+      <c r="K11" s="5" t="inlineStr">
         <is>
           <t>Pescado y marisco en la playa de Caneiros, desde 1976.</t>
         </is>
       </c>
-      <c r="K11" s="5" t="inlineStr">
+      <c r="L11" s="5" t="inlineStr">
         <is>
           <t>Poissons et fruits de mer sur la plage de Caneiros, depuis 1976.</t>
         </is>
       </c>
-      <c r="L11" s="5" t="inlineStr">
+      <c r="M11" s="5" t="inlineStr">
         <is>
           <t>Fisch und Meeresfrüchte am Strand von Caneiros, seit 1976.</t>
         </is>
       </c>
-      <c r="M11" s="5" t="inlineStr">
+      <c r="N11" s="5" t="inlineStr">
         <is>
           <t>Pesce e frutti di mare sulla spiaggia di Caneiros, dal 1976.</t>
         </is>
@@ -15737,32 +16057,33 @@
           <t>Vista Restaurante Portimão</t>
         </is>
       </c>
-      <c r="H12" s="6" t="inlineStr">
+      <c r="H12" s="5" t="inlineStr"/>
+      <c r="I12" s="6" t="inlineStr">
         <is>
           <t>Alta cozinha junto ao mar, extensa carta de vinhos.</t>
         </is>
       </c>
-      <c r="I12" s="5" t="inlineStr">
+      <c r="J12" s="5" t="inlineStr">
         <is>
           <t>Fine dining by the sea, large wine list.</t>
         </is>
       </c>
-      <c r="J12" s="5" t="inlineStr">
+      <c r="K12" s="5" t="inlineStr">
         <is>
           <t>Alta cocina junto al mar, amplia carta de vinos.</t>
         </is>
       </c>
-      <c r="K12" s="5" t="inlineStr">
+      <c r="L12" s="5" t="inlineStr">
         <is>
           <t>Gastronomie en bord de mer, grande carte des vins.</t>
         </is>
       </c>
-      <c r="L12" s="5" t="inlineStr">
+      <c r="M12" s="5" t="inlineStr">
         <is>
           <t>Gehobene Küche am Meer, große Weinkarte.</t>
         </is>
       </c>
-      <c r="M12" s="5" t="inlineStr">
+      <c r="N12" s="5" t="inlineStr">
         <is>
           <t>Alta cucina sul mare, ampia carta dei vini.</t>
         </is>
@@ -15800,32 +16121,33 @@
           <t>Ocean Restaurant Vila Vita Parc</t>
         </is>
       </c>
-      <c r="H13" s="6" t="inlineStr">
+      <c r="H13" s="5" t="inlineStr"/>
+      <c r="I13" s="6" t="inlineStr">
         <is>
           <t>Restaurante com estrelas Michelin a poucos minutos. Reserve com antecedência.</t>
         </is>
       </c>
-      <c r="I13" s="5" t="inlineStr">
+      <c r="J13" s="5" t="inlineStr">
         <is>
           <t>Michelin-starred fine dining a few minutes away. Book well in advance.</t>
         </is>
       </c>
-      <c r="J13" s="5" t="inlineStr">
+      <c r="K13" s="5" t="inlineStr">
         <is>
           <t>Restaurante con estrellas Michelin a pocos minutos. Reserve con antelación.</t>
         </is>
       </c>
-      <c r="K13" s="5" t="inlineStr">
+      <c r="L13" s="5" t="inlineStr">
         <is>
           <t>Restaurant étoilé Michelin à quelques minutes. Réservez longtemps à l’avance.</t>
         </is>
       </c>
-      <c r="L13" s="5" t="inlineStr">
+      <c r="M13" s="5" t="inlineStr">
         <is>
           <t>Michelin-Sterne-Restaurant wenige Minuten entfernt. Frühzeitig reservieren.</t>
         </is>
       </c>
-      <c r="M13" s="5" t="inlineStr">
+      <c r="N13" s="5" t="inlineStr">
         <is>
           <t>Ristorante stellato Michelin a pochi minuti. Prenotate con largo anticipo.</t>
         </is>
@@ -15863,32 +16185,33 @@
           <t>Aqualand Algarve</t>
         </is>
       </c>
-      <c r="H14" s="6" t="inlineStr">
+      <c r="H14" s="5" t="inlineStr"/>
+      <c r="I14" s="6" t="inlineStr">
         <is>
           <t>Parque aquático — escorregas e piscinas (época de verão).</t>
         </is>
       </c>
-      <c r="I14" s="5" t="inlineStr">
+      <c r="J14" s="5" t="inlineStr">
         <is>
           <t>Water park — slides and pools for all ages (summer season).</t>
         </is>
       </c>
-      <c r="J14" s="5" t="inlineStr">
+      <c r="K14" s="5" t="inlineStr">
         <is>
           <t>Parque acuático: toboganes y piscinas (temporada de verano).</t>
         </is>
       </c>
-      <c r="K14" s="5" t="inlineStr">
+      <c r="L14" s="5" t="inlineStr">
         <is>
           <t>Parc aquatique — toboggans et piscines (saison estivale).</t>
         </is>
       </c>
-      <c r="L14" s="5" t="inlineStr">
+      <c r="M14" s="5" t="inlineStr">
         <is>
           <t>Wasserpark – Rutschen und Pools (Sommersaison).</t>
         </is>
       </c>
-      <c r="M14" s="5" t="inlineStr">
+      <c r="N14" s="5" t="inlineStr">
         <is>
           <t>Parco acquatico: scivoli e piscine (stagione estiva).</t>
         </is>
@@ -15926,32 +16249,33 @@
           <t>Slide and Splash Lagoa</t>
         </is>
       </c>
-      <c r="H15" s="6" t="inlineStr">
+      <c r="H15" s="5" t="inlineStr"/>
+      <c r="I15" s="6" t="inlineStr">
         <is>
           <t>Parque aquático em Lagoa (época de verão).</t>
         </is>
       </c>
-      <c r="I15" s="5" t="inlineStr">
+      <c r="J15" s="5" t="inlineStr">
         <is>
           <t>Water park in Lagoa (summer season).</t>
         </is>
       </c>
-      <c r="J15" s="5" t="inlineStr">
+      <c r="K15" s="5" t="inlineStr">
         <is>
           <t>Parque acuático en Lagoa (temporada de verano).</t>
         </is>
       </c>
-      <c r="K15" s="5" t="inlineStr">
+      <c r="L15" s="5" t="inlineStr">
         <is>
           <t>Parc aquatique à Lagoa (saison estivale).</t>
         </is>
       </c>
-      <c r="L15" s="5" t="inlineStr">
+      <c r="M15" s="5" t="inlineStr">
         <is>
           <t>Wasserpark in Lagoa (Sommersaison).</t>
         </is>
       </c>
-      <c r="M15" s="5" t="inlineStr">
+      <c r="N15" s="5" t="inlineStr">
         <is>
           <t>Parco acquatico a Lagoa (stagione estiva).</t>
         </is>
@@ -15989,32 +16313,33 @@
           <t>Zoomarine Algarve</t>
         </is>
       </c>
-      <c r="H16" s="6" t="inlineStr">
+      <c r="H16" s="5" t="inlineStr"/>
+      <c r="I16" s="6" t="inlineStr">
         <is>
           <t>Parque temático com golfinhos, aves e aquários.</t>
         </is>
       </c>
-      <c r="I16" s="5" t="inlineStr">
+      <c r="J16" s="5" t="inlineStr">
         <is>
           <t>Marine theme park with dolphins, birds and aquariums.</t>
         </is>
       </c>
-      <c r="J16" s="5" t="inlineStr">
+      <c r="K16" s="5" t="inlineStr">
         <is>
           <t>Parque temático marino con delfines, aves y acuarios.</t>
         </is>
       </c>
-      <c r="K16" s="5" t="inlineStr">
+      <c r="L16" s="5" t="inlineStr">
         <is>
           <t>Parc à thème marin avec dauphins, oiseaux et aquariums.</t>
         </is>
       </c>
-      <c r="L16" s="5" t="inlineStr">
+      <c r="M16" s="5" t="inlineStr">
         <is>
           <t>Meeres-Themenpark mit Delfinen, Vögeln und Aquarien.</t>
         </is>
       </c>
-      <c r="M16" s="5" t="inlineStr">
+      <c r="N16" s="5" t="inlineStr">
         <is>
           <t>Parco tematico marino con delfini, uccelli e acquari.</t>
         </is>
@@ -16052,32 +16377,33 @@
           <t>Vale da Pinta Golf</t>
         </is>
       </c>
-      <c r="H17" s="6" t="inlineStr">
+      <c r="H17" s="5" t="inlineStr"/>
+      <c r="I17" s="6" t="inlineStr">
         <is>
           <t>Dois campos de golfe de referência perto de casa.</t>
         </is>
       </c>
-      <c r="I17" s="5" t="inlineStr">
+      <c r="J17" s="5" t="inlineStr">
         <is>
           <t>Two top golf courses close to the house.</t>
         </is>
       </c>
-      <c r="J17" s="5" t="inlineStr">
+      <c r="K17" s="5" t="inlineStr">
         <is>
           <t>Dos campos de golf de referencia cerca de casa.</t>
         </is>
       </c>
-      <c r="K17" s="5" t="inlineStr">
+      <c r="L17" s="5" t="inlineStr">
         <is>
           <t>Deux parcours de golf réputés près de la maison.</t>
         </is>
       </c>
-      <c r="L17" s="5" t="inlineStr">
+      <c r="M17" s="5" t="inlineStr">
         <is>
           <t>Zwei renommierte Golfplätze in der Nähe.</t>
         </is>
       </c>
-      <c r="M17" s="5" t="inlineStr">
+      <c r="N17" s="5" t="inlineStr">
         <is>
           <t>Due rinomati campi da golf vicino a casa.</t>
         </is>
@@ -16111,32 +16437,33 @@
           <t>Benagil boat tours</t>
         </is>
       </c>
-      <c r="H18" s="6" t="inlineStr">
+      <c r="H18" s="5" t="inlineStr"/>
+      <c r="I18" s="6" t="inlineStr">
         <is>
           <t>Passeios à gruta de Benagil a partir de Benagil, Armação de Pêra e Portimão.</t>
         </is>
       </c>
-      <c r="I18" s="5" t="inlineStr">
+      <c r="J18" s="5" t="inlineStr">
         <is>
           <t>Tours to the Benagil cave from Benagil, Armação de Pêra and Portimão.</t>
         </is>
       </c>
-      <c r="J18" s="5" t="inlineStr">
+      <c r="K18" s="5" t="inlineStr">
         <is>
           <t>Excursiones a la cueva de Benagil desde Benagil, Armação de Pêra y Portimão.</t>
         </is>
       </c>
-      <c r="K18" s="5" t="inlineStr">
+      <c r="L18" s="5" t="inlineStr">
         <is>
           <t>Excursions vers la grotte de Benagil depuis Benagil, Armação de Pêra et Portimão.</t>
         </is>
       </c>
-      <c r="L18" s="5" t="inlineStr">
+      <c r="M18" s="5" t="inlineStr">
         <is>
           <t>Touren zur Benagil-Höhle ab Benagil, Armação de Pêra und Portimão.</t>
         </is>
       </c>
-      <c r="M18" s="5" t="inlineStr">
+      <c r="N18" s="5" t="inlineStr">
         <is>
           <t>Gite alla grotta di Benagil da Benagil, Armação de Pêra e Portimão.</t>
         </is>
@@ -16170,32 +16497,33 @@
           <t>Olaria Porchesa</t>
         </is>
       </c>
-      <c r="H19" s="6" t="inlineStr">
+      <c r="H19" s="5" t="inlineStr"/>
+      <c r="I19" s="6" t="inlineStr">
         <is>
           <t>Porches é conhecida pela sua olaria algarvia pintada à mão.</t>
         </is>
       </c>
-      <c r="I19" s="5" t="inlineStr">
+      <c r="J19" s="5" t="inlineStr">
         <is>
           <t>Porches is known for its hand-painted Algarve pottery.</t>
         </is>
       </c>
-      <c r="J19" s="5" t="inlineStr">
+      <c r="K19" s="5" t="inlineStr">
         <is>
           <t>Porches es conocida por su cerámica algarvía pintada a mano.</t>
         </is>
       </c>
-      <c r="K19" s="5" t="inlineStr">
+      <c r="L19" s="5" t="inlineStr">
         <is>
           <t>Porches est réputée pour sa poterie de l’Algarve peinte à la main.</t>
         </is>
       </c>
-      <c r="L19" s="5" t="inlineStr">
+      <c r="M19" s="5" t="inlineStr">
         <is>
           <t>Porches ist bekannt für seine handbemalte Algarve-Keramik.</t>
         </is>
       </c>
-      <c r="M19" s="5" t="inlineStr">
+      <c r="N19" s="5" t="inlineStr">
         <is>
           <t>Porches è famosa per le sue ceramiche dell’Algarve dipinte a mano.</t>
         </is>
@@ -16225,32 +16553,33 @@
           <t>Algar Seco Carvoeiro</t>
         </is>
       </c>
-      <c r="H20" s="6" t="inlineStr">
+      <c r="H20" s="5" t="inlineStr"/>
+      <c r="I20" s="6" t="inlineStr">
         <is>
           <t>Passadiço nas falésias e formações rochosas.</t>
         </is>
       </c>
-      <c r="I20" s="5" t="inlineStr">
+      <c r="J20" s="5" t="inlineStr">
         <is>
           <t>Clifftop boardwalk and rock formations.</t>
         </is>
       </c>
-      <c r="J20" s="5" t="inlineStr">
+      <c r="K20" s="5" t="inlineStr">
         <is>
           <t>Pasarela sobre los acantilados y formaciones rocosas.</t>
         </is>
       </c>
-      <c r="K20" s="5" t="inlineStr">
+      <c r="L20" s="5" t="inlineStr">
         <is>
           <t>Promenade sur les falaises et formations rocheuses.</t>
         </is>
       </c>
-      <c r="L20" s="5" t="inlineStr">
+      <c r="M20" s="5" t="inlineStr">
         <is>
           <t>Klippenpromenade und Felsformationen.</t>
         </is>
       </c>
-      <c r="M20" s="5" t="inlineStr">
+      <c r="N20" s="5" t="inlineStr">
         <is>
           <t>Passerella sulle scogliere e formazioni rocciose.</t>
         </is>
@@ -16280,32 +16609,33 @@
           <t>Ferragudo</t>
         </is>
       </c>
-      <c r="H21" s="6" t="inlineStr">
+      <c r="H21" s="5" t="inlineStr"/>
+      <c r="I21" s="6" t="inlineStr">
         <is>
           <t>Vila piscatória junto ao rio.</t>
         </is>
       </c>
-      <c r="I21" s="5" t="inlineStr">
+      <c r="J21" s="5" t="inlineStr">
         <is>
           <t>Charming fishing village by the river.</t>
         </is>
       </c>
-      <c r="J21" s="5" t="inlineStr">
+      <c r="K21" s="5" t="inlineStr">
         <is>
           <t>Encantador pueblo pesquero junto al río.</t>
         </is>
       </c>
-      <c r="K21" s="5" t="inlineStr">
+      <c r="L21" s="5" t="inlineStr">
         <is>
           <t>Charmant village de pêcheurs au bord de la rivière.</t>
         </is>
       </c>
-      <c r="L21" s="5" t="inlineStr">
+      <c r="M21" s="5" t="inlineStr">
         <is>
           <t>Malerisches Fischerdorf am Fluss.</t>
         </is>
       </c>
-      <c r="M21" s="5" t="inlineStr">
+      <c r="N21" s="5" t="inlineStr">
         <is>
           <t>Grazioso villaggio di pescatori sul fiume.</t>
         </is>
@@ -16335,32 +16665,33 @@
           <t>Castelo de Silves</t>
         </is>
       </c>
-      <c r="H22" s="6" t="inlineStr">
+      <c r="H22" s="5" t="inlineStr"/>
+      <c r="I22" s="6" t="inlineStr">
         <is>
           <t>Castelo medieval e centro histórico.</t>
         </is>
       </c>
-      <c r="I22" s="5" t="inlineStr">
+      <c r="J22" s="5" t="inlineStr">
         <is>
           <t>Medieval castle and old town.</t>
         </is>
       </c>
-      <c r="J22" s="5" t="inlineStr">
+      <c r="K22" s="5" t="inlineStr">
         <is>
           <t>Castillo medieval y casco histórico.</t>
         </is>
       </c>
-      <c r="K22" s="5" t="inlineStr">
+      <c r="L22" s="5" t="inlineStr">
         <is>
           <t>Château médiéval et vieille ville.</t>
         </is>
       </c>
-      <c r="L22" s="5" t="inlineStr">
+      <c r="M22" s="5" t="inlineStr">
         <is>
           <t>Mittelalterliche Burg und Altstadt.</t>
         </is>
       </c>
-      <c r="M22" s="5" t="inlineStr">
+      <c r="N22" s="5" t="inlineStr">
         <is>
           <t>Castello medievale e centro storico.</t>
         </is>
@@ -16394,39 +16725,40 @@
           <t>Hospital de Portimão</t>
         </is>
       </c>
-      <c r="H23" s="6" t="inlineStr">
+      <c r="H23" s="5" t="inlineStr"/>
+      <c r="I23" s="6" t="inlineStr">
         <is>
           <t>Hospital (urgência).</t>
         </is>
       </c>
-      <c r="I23" s="5" t="inlineStr">
+      <c r="J23" s="5" t="inlineStr">
         <is>
           <t>Hospital (A&amp;E).</t>
         </is>
       </c>
-      <c r="J23" s="5" t="inlineStr">
+      <c r="K23" s="5" t="inlineStr">
         <is>
           <t>Hospital (urgencias).</t>
         </is>
       </c>
-      <c r="K23" s="5" t="inlineStr">
+      <c r="L23" s="5" t="inlineStr">
         <is>
           <t>Hôpital (urgences).</t>
         </is>
       </c>
-      <c r="L23" s="5" t="inlineStr">
+      <c r="M23" s="5" t="inlineStr">
         <is>
           <t>Krankenhaus (Notaufnahme).</t>
         </is>
       </c>
-      <c r="M23" s="5" t="inlineStr">
+      <c r="N23" s="5" t="inlineStr">
         <is>
           <t>Ospedale (pronto soccorso).</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M23"/>
+  <autoFilter ref="A1:N23"/>
   <dataValidations count="2">
     <dataValidation sqref="A2:A500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Escolha um valor da lista" type="list">
       <formula1>"beach,food,fun,see,help"</formula1>

--- a/Conteudos_Site_Casa_Porches.xlsx
+++ b/Conteudos_Site_Casa_Porches.xlsx
@@ -18,14 +18,14 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pagina_Principal" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Casa'!$A$1:$C$3</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Textos'!$A$1:$G$113</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Casa'!$A$1:$C$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Textos'!$A$1:$G$124</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Restaurantes'!$A$1:$Q$41</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Eventos'!$A$1:$AG$76</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Sessoes'!$A$1:$D$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Localidades'!$A$1:$D$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Mapa'!$A$1:$N$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Pagina_Principal'!$A$1:$F$128</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Pagina_Principal'!$A$1:$F$144</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -554,7 +554,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Casa — rede e palavra-passe do Wi-Fi (o QR Code do Wi-Fi é gerado automaticamente).</t>
+          <t>Casa — Wi-Fi (o QR Code é gerado automaticamente) e notas/links do Airbnb, Booking e Vrbo (aparecem na página principal).</t>
         </is>
       </c>
     </row>
@@ -760,7 +760,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -819,8 +819,137 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>airbnb_nota</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>4.82</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>Nota no Airbnb (ex.: 4.82)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>airbnb_avaliacoes</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Nº de avaliações no Airbnb</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>airbnb_link</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>https://www.airbnb.pt/rooms/1123085919462636254</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Link do anúncio no Airbnb</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>booking_nota</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr"/>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Nota no Booking (ex.: 9.4) — vazio = não aparece</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>booking_avaliacoes</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr"/>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Nº de avaliações no Booking</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>booking_link</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr"/>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Link público do anúncio no Booking (aparece também o botão Reservar no Booking)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>vrbo_nota</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr"/>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Nota no Vrbo — vazio = não aparece</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>vrbo_avaliacoes</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr"/>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>Nº de avaliações no Vrbo</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>vrbo_link</t>
+        </is>
+      </c>
+      <c r="B12" s="5" t="inlineStr"/>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Link do anúncio no Vrbo</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:C3"/>
+  <autoFilter ref="A1:C12"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -831,7 +960,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G113"/>
+  <dimension ref="A1:G124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -962,32 +1091,32 @@
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>Tudo o que precisa para a sua estadia — Wi-Fi, regras da casa, praias, restaurantes e contactos úteis.</t>
+          <t>Tudo o que precisa durante a estadia — Wi-Fi, chegada, regras da casa e contactos úteis.</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>Everything you need for your stay — Wi-Fi, house rules, beaches, restaurants and useful contacts.</t>
+          <t>Everything you need during your stay — Wi-Fi, arrival, house rules and useful contacts.</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>Todo lo que necesita para su estancia: Wi-Fi, normas de la casa, playas, restaurantes y contactos útiles.</t>
+          <t>Todo lo que necesita durante su estancia: Wi-Fi, llegada, normas de la casa y contactos útiles.</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
-          <t>Tout ce qu’il vous faut pour votre séjour : Wi-Fi, règlement de la maison, plages, restaurants et contacts utiles.</t>
+          <t>Tout ce qu’il vous faut pendant votre séjour : Wi-Fi, arrivée, règlement et contacts utiles.</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>Alles für Ihren Aufenthalt – WLAN, Hausregeln, Strände, Restaurants und wichtige Kontakte.</t>
+          <t>Alles für Ihren Aufenthalt – WLAN, Anreise, Hausregeln und wichtige Kontakte.</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr">
         <is>
-          <t>Tutto ciò che serve per il vostro soggiorno: Wi-Fi, regole della casa, spiagge, ristoranti e contatti utili.</t>
+          <t>Tutto ciò che serve durante il soggiorno: Wi-Fi, arrivo, regole della casa e contatti utili.</t>
         </is>
       </c>
     </row>
@@ -3658,1374 +3787,1781 @@
     <row r="77">
       <c r="A77" s="5" t="inlineStr">
         <is>
-          <t>rest.cat.near</t>
+          <t>site.home</t>
         </is>
       </c>
       <c r="B77" s="6" t="inlineStr">
         <is>
-          <t>Perto de casa</t>
+          <t>A Casa</t>
         </is>
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>Close to the house</t>
+          <t>The House</t>
         </is>
       </c>
       <c r="D77" s="5" t="inlineStr">
         <is>
-          <t>Cerca de casa</t>
+          <t>La Casa</t>
         </is>
       </c>
       <c r="E77" s="5" t="inlineStr">
         <is>
-          <t>Près de la maison</t>
+          <t>La Maison</t>
         </is>
       </c>
       <c r="F77" s="5" t="inlineStr">
         <is>
-          <t>In der Nähe</t>
+          <t>Das Haus</t>
         </is>
       </c>
       <c r="G77" s="5" t="inlineStr">
         <is>
-          <t>Vicino a casa</t>
+          <t>La Casa</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
         <is>
-          <t>rest.cat.michelin</t>
+          <t>site.guide</t>
         </is>
       </c>
       <c r="B78" s="6" t="inlineStr">
         <is>
-          <t>Estrelas Michelin</t>
+          <t>Guia do Hóspede</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>Michelin stars</t>
+          <t>Guest Guide</t>
         </is>
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>Estrellas Michelin</t>
+          <t>Guía del huésped</t>
         </is>
       </c>
       <c r="E78" s="5" t="inlineStr">
         <is>
-          <t>Étoiles Michelin</t>
+          <t>Guide du voyageur</t>
         </is>
       </c>
       <c r="F78" s="5" t="inlineStr">
         <is>
-          <t>Michelin-Sterne</t>
+          <t>Gästeinfo</t>
         </is>
       </c>
       <c r="G78" s="5" t="inlineStr">
         <is>
-          <t>Stelle Michelin</t>
+          <t>Guida ospiti</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="5" t="inlineStr">
         <is>
-          <t>rest.cat.fine</t>
+          <t>site.explore</t>
         </is>
       </c>
       <c r="B79" s="6" t="inlineStr">
         <is>
-          <t>Requintados</t>
+          <t>Explorar o Algarve</t>
         </is>
       </c>
       <c r="C79" s="5" t="inlineStr">
         <is>
-          <t>Fine dining</t>
+          <t>Explore the Algarve</t>
         </is>
       </c>
       <c r="D79" s="5" t="inlineStr">
         <is>
-          <t>Alta cocina</t>
+          <t>Explorar el Algarve</t>
         </is>
       </c>
       <c r="E79" s="5" t="inlineStr">
         <is>
-          <t>Raffinés</t>
+          <t>Explorer l’Algarve</t>
         </is>
       </c>
       <c r="F79" s="5" t="inlineStr">
         <is>
-          <t>Gehobene Küche</t>
+          <t>Algarve entdecken</t>
         </is>
       </c>
       <c r="G79" s="5" t="inlineStr">
         <is>
-          <t>Raffinati</t>
+          <t>Esplora l’Algarve</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="5" t="inlineStr">
         <is>
-          <t>rest.cat.wine</t>
+          <t>site.book</t>
         </is>
       </c>
       <c r="B80" s="6" t="inlineStr">
         <is>
-          <t>Vinhos e petiscos</t>
+          <t>Reservar</t>
         </is>
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>Wine &amp; small plates</t>
+          <t>Book</t>
         </is>
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>Vinos y tapas</t>
+          <t>Reservar</t>
         </is>
       </c>
       <c r="E80" s="5" t="inlineStr">
         <is>
-          <t>Vins &amp; petites assiettes</t>
+          <t>Réserver</t>
         </is>
       </c>
       <c r="F80" s="5" t="inlineStr">
         <is>
-          <t>Wein &amp; Tapas</t>
+          <t>Buchen</t>
         </is>
       </c>
       <c r="G80" s="5" t="inlineStr">
         <is>
-          <t>Vini e stuzzichini</t>
+          <t>Prenota</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="5" t="inlineStr">
         <is>
-          <t>rest.cat.sea</t>
+          <t>explore.title</t>
         </is>
       </c>
       <c r="B81" s="6" t="inlineStr">
         <is>
-          <t>Peixe e vista mar</t>
+          <t>Explorar o Algarve | Casa Porches</t>
         </is>
       </c>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>Seafood &amp; sea views</t>
+          <t>Explore the Algarve | Casa Porches</t>
         </is>
       </c>
       <c r="D81" s="5" t="inlineStr">
         <is>
-          <t>Pescado y vistas al mar</t>
+          <t>Explorar el Algarve | Casa Porches</t>
         </is>
       </c>
       <c r="E81" s="5" t="inlineStr">
         <is>
-          <t>Poisson &amp; vue mer</t>
+          <t>Explorer l’Algarve | Casa Porches</t>
         </is>
       </c>
       <c r="F81" s="5" t="inlineStr">
         <is>
-          <t>Fisch &amp; Meerblick</t>
+          <t>Algarve entdecken | Casa Porches</t>
         </is>
       </c>
       <c r="G81" s="5" t="inlineStr">
         <is>
-          <t>Pesce e vista mare</t>
+          <t>Esplora l’Algarve | Casa Porches</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="5" t="inlineStr">
         <is>
-          <t>rest.cat.trad</t>
+          <t>explore.h1</t>
         </is>
       </c>
       <c r="B82" s="6" t="inlineStr">
         <is>
-          <t>Tradicionais</t>
+          <t>Explorar o Algarve</t>
         </is>
       </c>
       <c r="C82" s="5" t="inlineStr">
         <is>
-          <t>Traditional</t>
+          <t>Explore the Algarve</t>
         </is>
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>Tradicionales</t>
+          <t>Explorar el Algarve</t>
         </is>
       </c>
       <c r="E82" s="5" t="inlineStr">
         <is>
-          <t>Traditionnels</t>
+          <t>Explorer l’Algarve</t>
         </is>
       </c>
       <c r="F82" s="5" t="inlineStr">
         <is>
-          <t>Traditionell</t>
+          <t>Die Algarve entdecken</t>
         </is>
       </c>
       <c r="G82" s="5" t="inlineStr">
         <is>
-          <t>Tradizionali</t>
+          <t>Esplora l’Algarve</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="5" t="inlineStr">
         <is>
-          <t>rest.cat.intl</t>
+          <t>explore.sub</t>
         </is>
       </c>
       <c r="B83" s="6" t="inlineStr">
         <is>
-          <t>Internacional e famílias</t>
+          <t>Mapa, praias, restaurantes, eventos e experiências à volta da Casa Porches.</t>
         </is>
       </c>
       <c r="C83" s="5" t="inlineStr">
         <is>
-          <t>International &amp; families</t>
+          <t>Map, beaches, restaurants, events and experiences around Casa Porches.</t>
         </is>
       </c>
       <c r="D83" s="5" t="inlineStr">
         <is>
-          <t>Internacional y familias</t>
+          <t>Mapa, playas, restaurantes, eventos y experiencias alrededor de Casa Porches.</t>
         </is>
       </c>
       <c r="E83" s="5" t="inlineStr">
         <is>
-          <t>International &amp; familles</t>
+          <t>Carte, plages, restaurants, événements et expériences autour de la Casa Porches.</t>
         </is>
       </c>
       <c r="F83" s="5" t="inlineStr">
         <is>
-          <t>International &amp; Familien</t>
+          <t>Karte, Strände, Restaurants, Events und Erlebnisse rund um die Casa Porches.</t>
         </is>
       </c>
       <c r="G83" s="5" t="inlineStr">
         <is>
-          <t>Internazionale e famiglie</t>
+          <t>Mappa, spiagge, ristoranti, eventi ed esperienze intorno a Casa Porches.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="5" t="inlineStr">
         <is>
-          <t>rest.cat.cafe</t>
+          <t>guide.ctaTitle</t>
         </is>
       </c>
       <c r="B84" s="6" t="inlineStr">
         <is>
-          <t>Cafés e refeições leves</t>
+          <t>Explorar a região</t>
         </is>
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>Cafés &amp; light meals</t>
+          <t>Explore the area</t>
         </is>
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t>Cafés y comidas ligeras</t>
+          <t>Explorar la zona</t>
         </is>
       </c>
       <c r="E84" s="5" t="inlineStr">
         <is>
-          <t>Cafés &amp; repas légers</t>
+          <t>Explorer la région</t>
         </is>
       </c>
       <c r="F84" s="5" t="inlineStr">
         <is>
-          <t>Cafés &amp; leichte Küche</t>
+          <t>Die Umgebung entdecken</t>
         </is>
       </c>
       <c r="G84" s="5" t="inlineStr">
         <is>
-          <t>Caffè e pasti leggeri</t>
+          <t>Esplora la zona</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="5" t="inlineStr">
         <is>
-          <t>rest.ui.all</t>
+          <t>guide.ctaText</t>
         </is>
       </c>
       <c r="B85" s="6" t="inlineStr">
         <is>
-          <t>Todos</t>
+          <t>Mapa interativo, praias, 40 restaurantes recomendados, eventos e atividades ao ar livre.</t>
         </is>
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Interactive map, beaches, 40 recommended restaurants, events and outdoor activities.</t>
         </is>
       </c>
       <c r="D85" s="5" t="inlineStr">
         <is>
-          <t>Todos</t>
+          <t>Mapa interactivo, playas, 40 restaurantes recomendados, eventos y actividades al aire libre.</t>
         </is>
       </c>
       <c r="E85" s="5" t="inlineStr">
         <is>
-          <t>Tous</t>
+          <t>Carte interactive, plages, 40 restaurants recommandés, événements et activités de plein air.</t>
         </is>
       </c>
       <c r="F85" s="5" t="inlineStr">
         <is>
-          <t>Alle</t>
+          <t>Interaktive Karte, Strände, 40 Restaurant-Tipps, Events und Outdoor-Aktivitäten.</t>
         </is>
       </c>
       <c r="G85" s="5" t="inlineStr">
         <is>
-          <t>Tutti</t>
+          <t>Mappa interattiva, spiagge, 40 ristoranti consigliati, eventi e attività all’aperto.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="5" t="inlineStr">
         <is>
-          <t>rest.ui.price</t>
+          <t>guide.ctaBtn</t>
         </is>
       </c>
       <c r="B86" s="6" t="inlineStr">
         <is>
-          <t>Preço indicativo por pessoa, sem bebidas — confirme antes de reservar.</t>
+          <t>Abrir Explorar o Algarve →</t>
         </is>
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>Approximate price per person, excluding drinks — please check before booking.</t>
+          <t>Open Explore the Algarve →</t>
         </is>
       </c>
       <c r="D86" s="5" t="inlineStr">
         <is>
-          <t>Precio orientativo por persona, sin bebidas; confírmelo antes de reservar.</t>
+          <t>Abrir Explorar el Algarve →</t>
         </is>
       </c>
       <c r="E86" s="5" t="inlineStr">
         <is>
-          <t>Prix indicatif par personne, hors boissons — à vérifier avant de réserver.</t>
+          <t>Ouvrir Explorer l’Algarve →</t>
         </is>
       </c>
       <c r="F86" s="5" t="inlineStr">
         <is>
-          <t>Richtpreis pro Person ohne Getränke – bitte vor der Reservierung prüfen.</t>
+          <t>Algarve entdecken öffnen →</t>
         </is>
       </c>
       <c r="G86" s="5" t="inlineStr">
         <is>
-          <t>Prezzo indicativo a persona, bevande escluse: verificate prima di prenotare.</t>
+          <t>Apri Esplora l’Algarve →</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="5" t="inlineStr">
         <is>
-          <t>rest.ui.near</t>
+          <t>disclaimer</t>
         </is>
       </c>
       <c r="B87" s="6" t="inlineStr">
         <is>
-          <t>Perto de casa</t>
+          <t>Informação meramente indicativa, sem valor contratual. Não dispensa a leitura das condições da plataforma de reserva (Airbnb, Booking, etc.) e das regras da HostWise, que prevalecem em caso de diferença.</t>
         </is>
       </c>
       <c r="C87" s="5" t="inlineStr">
         <is>
-          <t>Near the house</t>
+          <t>For information only, with no contractual value. It does not replace the terms of the booking platform (Airbnb, Booking, etc.) or HostWise’s house rules, which prevail in case of any difference.</t>
         </is>
       </c>
       <c r="D87" s="5" t="inlineStr">
         <is>
-          <t>Cerca de casa</t>
+          <t>Información meramente orientativa y sin valor contractual. No sustituye las condiciones de la plataforma de reserva (Airbnb, Booking, etc.) ni las normas de HostWise, que prevalecen en caso de diferencia.</t>
         </is>
       </c>
       <c r="E87" s="5" t="inlineStr">
         <is>
-          <t>Près de la maison</t>
+          <t>Informations purement indicatives, sans valeur contractuelle. Elles ne remplacent pas les conditions de la plateforme de réservation (Airbnb, Booking, etc.) ni le règlement de HostWise, qui prévalent en cas de divergence.</t>
         </is>
       </c>
       <c r="F87" s="5" t="inlineStr">
         <is>
-          <t>In der Nähe</t>
+          <t>Nur zur Information, ohne vertragliche Bindung. Ersetzt nicht die Bedingungen der Buchungsplattform (Airbnb, Booking usw.) oder die Hausregeln von HostWise, die im Zweifel Vorrang haben.</t>
         </is>
       </c>
       <c r="G87" s="5" t="inlineStr">
         <is>
-          <t>Vicino a casa</t>
+          <t>Informazioni puramente indicative, senza valore contrattuale. Non sostituiscono le condizioni della piattaforma di prenotazione (Airbnb, Booking, ecc.) né le regole di HostWise, che prevalgono in caso di differenze.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="5" t="inlineStr">
         <is>
-          <t>ev.cat.upcoming</t>
+          <t>rest.cat.near</t>
         </is>
       </c>
       <c r="B88" s="6" t="inlineStr">
         <is>
-          <t>Próximos eventos</t>
+          <t>Perto de casa</t>
         </is>
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>Upcoming events</t>
+          <t>Close to the house</t>
         </is>
       </c>
       <c r="D88" s="5" t="inlineStr">
         <is>
-          <t>Próximos eventos</t>
+          <t>Cerca de casa</t>
         </is>
       </c>
       <c r="E88" s="5" t="inlineStr">
         <is>
-          <t>Événements à venir</t>
+          <t>Près de la maison</t>
         </is>
       </c>
       <c r="F88" s="5" t="inlineStr">
         <is>
-          <t>Kommende Events</t>
+          <t>In der Nähe</t>
         </is>
       </c>
       <c r="G88" s="5" t="inlineStr">
         <is>
-          <t>Prossimi eventi</t>
+          <t>Vicino a casa</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="5" t="inlineStr">
         <is>
-          <t>ev.cat.outdoor</t>
+          <t>rest.cat.michelin</t>
         </is>
       </c>
       <c r="B89" s="6" t="inlineStr">
         <is>
-          <t>Atividades ao ar livre</t>
+          <t>Estrelas Michelin</t>
         </is>
       </c>
       <c r="C89" s="5" t="inlineStr">
         <is>
-          <t>Outdoor activities</t>
+          <t>Michelin stars</t>
         </is>
       </c>
       <c r="D89" s="5" t="inlineStr">
         <is>
-          <t>Actividades al aire libre</t>
+          <t>Estrellas Michelin</t>
         </is>
       </c>
       <c r="E89" s="5" t="inlineStr">
         <is>
-          <t>Activités de plein air</t>
+          <t>Étoiles Michelin</t>
         </is>
       </c>
       <c r="F89" s="5" t="inlineStr">
         <is>
-          <t>Outdoor-Aktivitäten</t>
+          <t>Michelin-Sterne</t>
         </is>
       </c>
       <c r="G89" s="5" t="inlineStr">
         <is>
-          <t>Attività all’aperto</t>
+          <t>Stelle Michelin</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="5" t="inlineStr">
         <is>
-          <t>ev.cat.nature</t>
+          <t>rest.cat.fine</t>
         </is>
       </c>
       <c r="B90" s="6" t="inlineStr">
         <is>
-          <t>Natureza e praias</t>
+          <t>Requintados</t>
         </is>
       </c>
       <c r="C90" s="5" t="inlineStr">
         <is>
-          <t>Nature &amp; beaches</t>
+          <t>Fine dining</t>
         </is>
       </c>
       <c r="D90" s="5" t="inlineStr">
         <is>
-          <t>Naturaleza y playas</t>
+          <t>Alta cocina</t>
         </is>
       </c>
       <c r="E90" s="5" t="inlineStr">
         <is>
-          <t>Nature &amp; plages</t>
+          <t>Raffinés</t>
         </is>
       </c>
       <c r="F90" s="5" t="inlineStr">
         <is>
-          <t>Natur &amp; Strände</t>
+          <t>Gehobene Küche</t>
         </is>
       </c>
       <c r="G90" s="5" t="inlineStr">
         <is>
-          <t>Natura e spiagge</t>
+          <t>Raffinati</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="5" t="inlineStr">
         <is>
-          <t>ev.cat.sea</t>
+          <t>rest.cat.wine</t>
         </is>
       </c>
       <c r="B91" s="6" t="inlineStr">
         <is>
-          <t>Mar e aventura</t>
+          <t>Vinhos e petiscos</t>
         </is>
       </c>
       <c r="C91" s="5" t="inlineStr">
         <is>
-          <t>Sea &amp; adventure</t>
+          <t>Wine &amp; small plates</t>
         </is>
       </c>
       <c r="D91" s="5" t="inlineStr">
         <is>
-          <t>Mar y aventura</t>
+          <t>Vinos y tapas</t>
         </is>
       </c>
       <c r="E91" s="5" t="inlineStr">
         <is>
-          <t>Mer &amp; aventure</t>
+          <t>Vins &amp; petites assiettes</t>
         </is>
       </c>
       <c r="F91" s="5" t="inlineStr">
         <is>
-          <t>Meer &amp; Abenteuer</t>
+          <t>Wein &amp; Tapas</t>
         </is>
       </c>
       <c r="G91" s="5" t="inlineStr">
         <is>
-          <t>Mare e avventura</t>
+          <t>Vini e stuzzichini</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="5" t="inlineStr">
         <is>
-          <t>ev.cat.events</t>
+          <t>rest.cat.sea</t>
         </is>
       </c>
       <c r="B92" s="6" t="inlineStr">
         <is>
-          <t>Festivais e festas anuais</t>
+          <t>Peixe e vista mar</t>
         </is>
       </c>
       <c r="C92" s="5" t="inlineStr">
         <is>
-          <t>Annual festivals</t>
+          <t>Seafood &amp; sea views</t>
         </is>
       </c>
       <c r="D92" s="5" t="inlineStr">
         <is>
-          <t>Festivales y fiestas anuales</t>
+          <t>Pescado y vistas al mar</t>
         </is>
       </c>
       <c r="E92" s="5" t="inlineStr">
         <is>
-          <t>Festivals et fêtes annuels</t>
+          <t>Poisson &amp; vue mer</t>
         </is>
       </c>
       <c r="F92" s="5" t="inlineStr">
         <is>
-          <t>Jährliche Feste &amp; Festivals</t>
+          <t>Fisch &amp; Meerblick</t>
         </is>
       </c>
       <c r="G92" s="5" t="inlineStr">
         <is>
-          <t>Festival e feste annuali</t>
+          <t>Pesce e vista mare</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="5" t="inlineStr">
         <is>
-          <t>ev.cat.water</t>
+          <t>rest.cat.trad</t>
         </is>
       </c>
       <c r="B93" s="6" t="inlineStr">
         <is>
-          <t>Parques e atrações familiares</t>
+          <t>Tradicionais</t>
         </is>
       </c>
       <c r="C93" s="5" t="inlineStr">
         <is>
-          <t>Water &amp; theme parks</t>
+          <t>Traditional</t>
         </is>
       </c>
       <c r="D93" s="5" t="inlineStr">
         <is>
-          <t>Parques y atracciones familiares</t>
+          <t>Tradicionales</t>
         </is>
       </c>
       <c r="E93" s="5" t="inlineStr">
         <is>
-          <t>Parcs et attractions familiales</t>
+          <t>Traditionnels</t>
         </is>
       </c>
       <c r="F93" s="5" t="inlineStr">
         <is>
-          <t>Wasser- &amp; Freizeitparks</t>
+          <t>Traditionell</t>
         </is>
       </c>
       <c r="G93" s="5" t="inlineStr">
         <is>
-          <t>Parchi e attrazioni per famiglie</t>
+          <t>Tradizionali</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="5" t="inlineStr">
         <is>
-          <t>ev.cat.indoor</t>
+          <t>rest.cat.intl</t>
         </is>
       </c>
       <c r="B94" s="6" t="inlineStr">
         <is>
-          <t>Piscinas e dias de chuva</t>
+          <t>Internacional e famílias</t>
         </is>
       </c>
       <c r="C94" s="5" t="inlineStr">
         <is>
-          <t>Indoor &amp; rainy days</t>
+          <t>International &amp; families</t>
         </is>
       </c>
       <c r="D94" s="5" t="inlineStr">
         <is>
-          <t>Piscinas y días de lluvia</t>
+          <t>Internacional y familias</t>
         </is>
       </c>
       <c r="E94" s="5" t="inlineStr">
         <is>
-          <t>Piscines &amp; jours de pluie</t>
+          <t>International &amp; familles</t>
         </is>
       </c>
       <c r="F94" s="5" t="inlineStr">
         <is>
-          <t>Hallenbäder &amp; Regentage</t>
+          <t>International &amp; Familien</t>
         </is>
       </c>
       <c r="G94" s="5" t="inlineStr">
         <is>
-          <t>Piscine e giorni di pioggia</t>
+          <t>Internazionale e famiglie</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="5" t="inlineStr">
         <is>
-          <t>ev.cat.markets</t>
+          <t>rest.cat.cafe</t>
         </is>
       </c>
       <c r="B95" s="6" t="inlineStr">
         <is>
-          <t>Mercados e tradições</t>
+          <t>Cafés e refeições leves</t>
         </is>
       </c>
       <c r="C95" s="5" t="inlineStr">
         <is>
-          <t>Markets &amp; traditions</t>
+          <t>Cafés &amp; light meals</t>
         </is>
       </c>
       <c r="D95" s="5" t="inlineStr">
         <is>
-          <t>Mercados y tradiciones</t>
+          <t>Cafés y comidas ligeras</t>
         </is>
       </c>
       <c r="E95" s="5" t="inlineStr">
         <is>
-          <t>Marchés &amp; traditions</t>
+          <t>Cafés &amp; repas légers</t>
         </is>
       </c>
       <c r="F95" s="5" t="inlineStr">
         <is>
-          <t>Märkte &amp; Traditionen</t>
+          <t>Cafés &amp; leichte Küche</t>
         </is>
       </c>
       <c r="G95" s="5" t="inlineStr">
         <is>
-          <t>Mercati e tradizioni</t>
+          <t>Caffè e pasti leggeri</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="5" t="inlineStr">
         <is>
-          <t>ev.tag.fam</t>
+          <t>rest.ui.all</t>
         </is>
       </c>
       <c r="B96" s="6" t="inlineStr">
         <is>
-          <t>Famílias</t>
+          <t>Todos</t>
         </is>
       </c>
       <c r="C96" s="5" t="inlineStr">
         <is>
-          <t>Families</t>
+          <t>All</t>
         </is>
       </c>
       <c r="D96" s="5" t="inlineStr">
         <is>
-          <t>Familias</t>
+          <t>Todos</t>
         </is>
       </c>
       <c r="E96" s="5" t="inlineStr">
         <is>
-          <t>Familles</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="F96" s="5" t="inlineStr">
         <is>
-          <t>Familien</t>
+          <t>Alle</t>
         </is>
       </c>
       <c r="G96" s="5" t="inlineStr">
         <is>
-          <t>Famiglie</t>
+          <t>Tutti</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="5" t="inlineStr">
         <is>
-          <t>ev.tag.teen</t>
+          <t>rest.ui.price</t>
         </is>
       </c>
       <c r="B97" s="6" t="inlineStr">
         <is>
-          <t>Jovens</t>
+          <t>Preço indicativo por pessoa, sem bebidas — confirme antes de reservar.</t>
         </is>
       </c>
       <c r="C97" s="5" t="inlineStr">
         <is>
-          <t>Teens</t>
+          <t>Approximate price per person, excluding drinks — please check before booking.</t>
         </is>
       </c>
       <c r="D97" s="5" t="inlineStr">
         <is>
-          <t>Jóvenes</t>
+          <t>Precio orientativo por persona, sin bebidas; confírmelo antes de reservar.</t>
         </is>
       </c>
       <c r="E97" s="5" t="inlineStr">
         <is>
-          <t>Ados</t>
+          <t>Prix indicatif par personne, hors boissons — à vérifier avant de réserver.</t>
         </is>
       </c>
       <c r="F97" s="5" t="inlineStr">
         <is>
-          <t>Jugendliche</t>
+          <t>Richtpreis pro Person ohne Getränke – bitte vor der Reservierung prüfen.</t>
         </is>
       </c>
       <c r="G97" s="5" t="inlineStr">
         <is>
-          <t>Ragazzi</t>
+          <t>Prezzo indicativo a persona, bevande escluse: verificate prima di prenotare.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="5" t="inlineStr">
         <is>
-          <t>ev.tag.couple</t>
+          <t>rest.ui.near</t>
         </is>
       </c>
       <c r="B98" s="6" t="inlineStr">
         <is>
-          <t>Casais</t>
+          <t>Perto de casa</t>
         </is>
       </c>
       <c r="C98" s="5" t="inlineStr">
         <is>
-          <t>Couples</t>
+          <t>Near the house</t>
         </is>
       </c>
       <c r="D98" s="5" t="inlineStr">
         <is>
-          <t>Parejas</t>
+          <t>Cerca de casa</t>
         </is>
       </c>
       <c r="E98" s="5" t="inlineStr">
         <is>
-          <t>Couples</t>
+          <t>Près de la maison</t>
         </is>
       </c>
       <c r="F98" s="5" t="inlineStr">
         <is>
-          <t>Paare</t>
+          <t>In der Nähe</t>
         </is>
       </c>
       <c r="G98" s="5" t="inlineStr">
         <is>
-          <t>Coppie</t>
+          <t>Vicino a casa</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="5" t="inlineStr">
         <is>
-          <t>ev.tag.food</t>
+          <t>ev.cat.upcoming</t>
         </is>
       </c>
       <c r="B99" s="6" t="inlineStr">
         <is>
-          <t>Gastronomia</t>
+          <t>Próximos eventos</t>
         </is>
       </c>
       <c r="C99" s="5" t="inlineStr">
         <is>
-          <t>Food &amp; drink</t>
+          <t>Upcoming events</t>
         </is>
       </c>
       <c r="D99" s="5" t="inlineStr">
         <is>
-          <t>Gastronomía</t>
+          <t>Próximos eventos</t>
         </is>
       </c>
       <c r="E99" s="5" t="inlineStr">
         <is>
-          <t>Gastronomie</t>
+          <t>Événements à venir</t>
         </is>
       </c>
       <c r="F99" s="5" t="inlineStr">
         <is>
-          <t>Kulinarik</t>
+          <t>Kommende Events</t>
         </is>
       </c>
       <c r="G99" s="5" t="inlineStr">
         <is>
-          <t>Gastronomia</t>
+          <t>Prossimi eventi</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="5" t="inlineStr">
         <is>
-          <t>ev.tag.free</t>
+          <t>ev.cat.outdoor</t>
         </is>
       </c>
       <c r="B100" s="6" t="inlineStr">
         <is>
-          <t>Natureza / grátis</t>
+          <t>Atividades ao ar livre</t>
         </is>
       </c>
       <c r="C100" s="5" t="inlineStr">
         <is>
-          <t>Nature / free</t>
+          <t>Outdoor activities</t>
         </is>
       </c>
       <c r="D100" s="5" t="inlineStr">
         <is>
-          <t>Naturaleza / gratis</t>
+          <t>Actividades al aire libre</t>
         </is>
       </c>
       <c r="E100" s="5" t="inlineStr">
         <is>
-          <t>Nature / gratuit</t>
+          <t>Activités de plein air</t>
         </is>
       </c>
       <c r="F100" s="5" t="inlineStr">
         <is>
-          <t>Natur / gratis</t>
+          <t>Outdoor-Aktivitäten</t>
         </is>
       </c>
       <c r="G100" s="5" t="inlineStr">
         <is>
-          <t>Natura / gratis</t>
+          <t>Attività all’aperto</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="5" t="inlineStr">
         <is>
-          <t>ev.tag.winter</t>
+          <t>ev.cat.nature</t>
         </is>
       </c>
       <c r="B101" s="6" t="inlineStr">
         <is>
-          <t>Outono e inverno</t>
+          <t>Natureza e praias</t>
         </is>
       </c>
       <c r="C101" s="5" t="inlineStr">
         <is>
-          <t>Autumn &amp; winter</t>
+          <t>Nature &amp; beaches</t>
         </is>
       </c>
       <c r="D101" s="5" t="inlineStr">
         <is>
-          <t>Otoño e invierno</t>
+          <t>Naturaleza y playas</t>
         </is>
       </c>
       <c r="E101" s="5" t="inlineStr">
         <is>
-          <t>Automne &amp; hiver</t>
+          <t>Nature &amp; plages</t>
         </is>
       </c>
       <c r="F101" s="5" t="inlineStr">
         <is>
-          <t>Herbst &amp; Winter</t>
+          <t>Natur &amp; Strände</t>
         </is>
       </c>
       <c r="G101" s="5" t="inlineStr">
         <is>
-          <t>Autunno e inverno</t>
+          <t>Natura e spiagge</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="5" t="inlineStr">
         <is>
-          <t>ev.ui.title</t>
+          <t>ev.cat.sea</t>
         </is>
       </c>
       <c r="B102" s="6" t="inlineStr">
         <is>
-          <t>Eventos e experiências</t>
+          <t>Mar e aventura</t>
         </is>
       </c>
       <c r="C102" s="5" t="inlineStr">
         <is>
-          <t>Events &amp; experiences</t>
+          <t>Sea &amp; adventure</t>
         </is>
       </c>
       <c r="D102" s="5" t="inlineStr">
         <is>
-          <t>Eventos y experiencias</t>
+          <t>Mar y aventura</t>
         </is>
       </c>
       <c r="E102" s="5" t="inlineStr">
         <is>
-          <t>Événements &amp; expériences</t>
+          <t>Mer &amp; aventure</t>
         </is>
       </c>
       <c r="F102" s="5" t="inlineStr">
         <is>
-          <t>Events &amp; Erlebnisse</t>
+          <t>Meer &amp; Abenteuer</t>
         </is>
       </c>
       <c r="G102" s="5" t="inlineStr">
         <is>
-          <t>Eventi ed esperienze</t>
+          <t>Mare e avventura</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="5" t="inlineStr">
         <is>
-          <t>ev.ui.forWho</t>
+          <t>ev.cat.events</t>
         </is>
       </c>
       <c r="B103" s="6" t="inlineStr">
         <is>
-          <t>Para quem:</t>
+          <t>Festivais e festas anuais</t>
         </is>
       </c>
       <c r="C103" s="5" t="inlineStr">
         <is>
-          <t>Best for:</t>
+          <t>Annual festivals</t>
         </is>
       </c>
       <c r="D103" s="5" t="inlineStr">
         <is>
-          <t>Para quién:</t>
+          <t>Festivales y fiestas anuales</t>
         </is>
       </c>
       <c r="E103" s="5" t="inlineStr">
         <is>
-          <t>Pour qui :</t>
+          <t>Festivals et fêtes annuels</t>
         </is>
       </c>
       <c r="F103" s="5" t="inlineStr">
         <is>
-          <t>Ideal für:</t>
+          <t>Jährliche Feste &amp; Festivals</t>
         </is>
       </c>
       <c r="G103" s="5" t="inlineStr">
         <is>
-          <t>Per chi:</t>
+          <t>Festival e feste annuali</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="5" t="inlineStr">
         <is>
-          <t>ev.ui.anyone</t>
+          <t>ev.cat.water</t>
         </is>
       </c>
       <c r="B104" s="6" t="inlineStr">
         <is>
-          <t>Todos</t>
+          <t>Parques e atrações familiares</t>
         </is>
       </c>
       <c r="C104" s="5" t="inlineStr">
         <is>
-          <t>Everyone</t>
+          <t>Water &amp; theme parks</t>
         </is>
       </c>
       <c r="D104" s="5" t="inlineStr">
         <is>
-          <t>Todos</t>
+          <t>Parques y atracciones familiares</t>
         </is>
       </c>
       <c r="E104" s="5" t="inlineStr">
         <is>
-          <t>Tous</t>
+          <t>Parcs et attractions familiales</t>
         </is>
       </c>
       <c r="F104" s="5" t="inlineStr">
         <is>
-          <t>Alle</t>
+          <t>Wasser- &amp; Freizeitparks</t>
         </is>
       </c>
       <c r="G104" s="5" t="inlineStr">
         <is>
-          <t>Tutti</t>
+          <t>Parchi e attrazioni per famiglie</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="5" t="inlineStr">
         <is>
-          <t>ev.ui.confirmed</t>
+          <t>ev.cat.indoor</t>
         </is>
       </c>
       <c r="B105" s="6" t="inlineStr">
         <is>
-          <t>Confirmado</t>
+          <t>Piscinas e dias de chuva</t>
         </is>
       </c>
       <c r="C105" s="5" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Indoor &amp; rainy days</t>
         </is>
       </c>
       <c r="D105" s="5" t="inlineStr">
         <is>
-          <t>Confirmado</t>
+          <t>Piscinas y días de lluvia</t>
         </is>
       </c>
       <c r="E105" s="5" t="inlineStr">
         <is>
-          <t>Confirmé</t>
+          <t>Piscines &amp; jours de pluie</t>
         </is>
       </c>
       <c r="F105" s="5" t="inlineStr">
         <is>
-          <t>Bestätigt</t>
+          <t>Hallenbäder &amp; Regentage</t>
         </is>
       </c>
       <c r="G105" s="5" t="inlineStr">
         <is>
-          <t>Confermato</t>
+          <t>Piscine e giorni di pioggia</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="5" t="inlineStr">
         <is>
-          <t>ev.ui.usually</t>
+          <t>ev.cat.markets</t>
         </is>
       </c>
       <c r="B106" s="6" t="inlineStr">
         <is>
-          <t>Habitualmente</t>
+          <t>Mercados e tradições</t>
         </is>
       </c>
       <c r="C106" s="5" t="inlineStr">
         <is>
-          <t>Usually</t>
+          <t>Markets &amp; traditions</t>
         </is>
       </c>
       <c r="D106" s="5" t="inlineStr">
         <is>
-          <t>Normalmente</t>
+          <t>Mercados y tradiciones</t>
         </is>
       </c>
       <c r="E106" s="5" t="inlineStr">
         <is>
-          <t>Habituellement</t>
+          <t>Marchés &amp; traditions</t>
         </is>
       </c>
       <c r="F106" s="5" t="inlineStr">
         <is>
-          <t>Üblicherweise</t>
+          <t>Märkte &amp; Traditionen</t>
         </is>
       </c>
       <c r="G106" s="5" t="inlineStr">
         <is>
-          <t>Di solito</t>
+          <t>Mercati e tradizioni</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="5" t="inlineStr">
         <is>
-          <t>ev.ui.last</t>
+          <t>ev.tag.fam</t>
         </is>
       </c>
       <c r="B107" s="6" t="inlineStr">
         <is>
-          <t>Última edição</t>
+          <t>Famílias</t>
         </is>
       </c>
       <c r="C107" s="5" t="inlineStr">
         <is>
-          <t>Last edition</t>
+          <t>Families</t>
         </is>
       </c>
       <c r="D107" s="5" t="inlineStr">
         <is>
-          <t>Última edición</t>
+          <t>Familias</t>
         </is>
       </c>
       <c r="E107" s="5" t="inlineStr">
         <is>
-          <t>Dernière édition</t>
+          <t>Familles</t>
         </is>
       </c>
       <c r="F107" s="5" t="inlineStr">
         <is>
-          <t>Letzte Ausgabe</t>
+          <t>Familien</t>
         </is>
       </c>
       <c r="G107" s="5" t="inlineStr">
         <is>
-          <t>Ultima edizione</t>
+          <t>Famiglie</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="5" t="inlineStr">
         <is>
-          <t>ev.ui.now</t>
+          <t>ev.tag.teen</t>
         </is>
       </c>
       <c r="B108" s="6" t="inlineStr">
         <is>
-          <t>A decorrer</t>
+          <t>Jovens</t>
         </is>
       </c>
       <c r="C108" s="5" t="inlineStr">
         <is>
-          <t>On now</t>
+          <t>Teens</t>
         </is>
       </c>
       <c r="D108" s="5" t="inlineStr">
         <is>
-          <t>En curso</t>
+          <t>Jóvenes</t>
         </is>
       </c>
       <c r="E108" s="5" t="inlineStr">
         <is>
-          <t>En cours</t>
+          <t>Ados</t>
         </is>
       </c>
       <c r="F108" s="5" t="inlineStr">
         <is>
-          <t>Läuft gerade</t>
+          <t>Jugendliche</t>
         </is>
       </c>
       <c r="G108" s="5" t="inlineStr">
         <is>
-          <t>In corso</t>
+          <t>Ragazzi</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="5" t="inlineStr">
         <is>
-          <t>ev.ui.fromHouse</t>
+          <t>ev.tag.couple</t>
         </is>
       </c>
       <c r="B109" s="6" t="inlineStr">
         <is>
-          <t>da casa</t>
+          <t>Casais</t>
         </is>
       </c>
       <c r="C109" s="5" t="inlineStr">
         <is>
-          <t>from the house</t>
+          <t>Couples</t>
         </is>
       </c>
       <c r="D109" s="5" t="inlineStr">
         <is>
-          <t>desde la casa</t>
+          <t>Parejas</t>
         </is>
       </c>
       <c r="E109" s="5" t="inlineStr">
         <is>
-          <t>de la maison</t>
+          <t>Couples</t>
         </is>
       </c>
       <c r="F109" s="5" t="inlineStr">
         <is>
-          <t>vom Haus</t>
+          <t>Paare</t>
         </is>
       </c>
       <c r="G109" s="5" t="inlineStr">
         <is>
-          <t>dalla casa</t>
+          <t>Coppie</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="5" t="inlineStr">
         <is>
-          <t>ev.ui.inPorches</t>
+          <t>ev.tag.food</t>
         </is>
       </c>
       <c r="B110" s="6" t="inlineStr">
         <is>
-          <t>Em Porches</t>
+          <t>Gastronomia</t>
         </is>
       </c>
       <c r="C110" s="5" t="inlineStr">
         <is>
-          <t>In Porches</t>
+          <t>Food &amp; drink</t>
         </is>
       </c>
       <c r="D110" s="5" t="inlineStr">
         <is>
-          <t>En Porches</t>
+          <t>Gastronomía</t>
         </is>
       </c>
       <c r="E110" s="5" t="inlineStr">
         <is>
-          <t>À Porches</t>
+          <t>Gastronomie</t>
         </is>
       </c>
       <c r="F110" s="5" t="inlineStr">
         <is>
-          <t>In Porches</t>
+          <t>Kulinarik</t>
         </is>
       </c>
       <c r="G110" s="5" t="inlineStr">
         <is>
-          <t>A Porches</t>
+          <t>Gastronomia</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="5" t="inlineStr">
         <is>
-          <t>ev.ui.website</t>
+          <t>ev.tag.free</t>
         </is>
       </c>
       <c r="B111" s="6" t="inlineStr">
         <is>
-          <t>Website</t>
+          <t>Natureza / grátis</t>
         </is>
       </c>
       <c r="C111" s="5" t="inlineStr">
         <is>
-          <t>Website</t>
+          <t>Nature / free</t>
         </is>
       </c>
       <c r="D111" s="5" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>Naturaleza / gratis</t>
         </is>
       </c>
       <c r="E111" s="5" t="inlineStr">
         <is>
-          <t>Site web</t>
+          <t>Nature / gratuit</t>
         </is>
       </c>
       <c r="F111" s="5" t="inlineStr">
         <is>
-          <t>Website</t>
+          <t>Natur / gratis</t>
         </is>
       </c>
       <c r="G111" s="5" t="inlineStr">
         <is>
-          <t>Sito web</t>
+          <t>Natura / gratis</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="5" t="inlineStr">
         <is>
-          <t>ev.ui.none</t>
+          <t>ev.tag.winter</t>
         </is>
       </c>
       <c r="B112" s="6" t="inlineStr">
         <is>
-          <t>Nada para mostrar com estes filtros.</t>
+          <t>Outono e inverno</t>
         </is>
       </c>
       <c r="C112" s="5" t="inlineStr">
         <is>
-          <t>Nothing to show with these filters.</t>
+          <t>Autumn &amp; winter</t>
         </is>
       </c>
       <c r="D112" s="5" t="inlineStr">
         <is>
-          <t>No hay resultados con estos filtros.</t>
+          <t>Otoño e invierno</t>
         </is>
       </c>
       <c r="E112" s="5" t="inlineStr">
         <is>
-          <t>Aucun résultat avec ces filtres.</t>
+          <t>Automne &amp; hiver</t>
         </is>
       </c>
       <c r="F112" s="5" t="inlineStr">
         <is>
-          <t>Keine Ergebnisse mit diesen Filtern.</t>
+          <t>Herbst &amp; Winter</t>
         </is>
       </c>
       <c r="G112" s="5" t="inlineStr">
         <is>
-          <t>Nessun risultato con questi filtri.</t>
+          <t>Autunno e inverno</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="5" t="inlineStr">
         <is>
+          <t>ev.ui.title</t>
+        </is>
+      </c>
+      <c r="B113" s="6" t="inlineStr">
+        <is>
+          <t>Eventos e experiências</t>
+        </is>
+      </c>
+      <c r="C113" s="5" t="inlineStr">
+        <is>
+          <t>Events &amp; experiences</t>
+        </is>
+      </c>
+      <c r="D113" s="5" t="inlineStr">
+        <is>
+          <t>Eventos y experiencias</t>
+        </is>
+      </c>
+      <c r="E113" s="5" t="inlineStr">
+        <is>
+          <t>Événements &amp; expériences</t>
+        </is>
+      </c>
+      <c r="F113" s="5" t="inlineStr">
+        <is>
+          <t>Events &amp; Erlebnisse</t>
+        </is>
+      </c>
+      <c r="G113" s="5" t="inlineStr">
+        <is>
+          <t>Eventi ed esperienze</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="5" t="inlineStr">
+        <is>
+          <t>ev.ui.forWho</t>
+        </is>
+      </c>
+      <c r="B114" s="6" t="inlineStr">
+        <is>
+          <t>Para quem:</t>
+        </is>
+      </c>
+      <c r="C114" s="5" t="inlineStr">
+        <is>
+          <t>Best for:</t>
+        </is>
+      </c>
+      <c r="D114" s="5" t="inlineStr">
+        <is>
+          <t>Para quién:</t>
+        </is>
+      </c>
+      <c r="E114" s="5" t="inlineStr">
+        <is>
+          <t>Pour qui :</t>
+        </is>
+      </c>
+      <c r="F114" s="5" t="inlineStr">
+        <is>
+          <t>Ideal für:</t>
+        </is>
+      </c>
+      <c r="G114" s="5" t="inlineStr">
+        <is>
+          <t>Per chi:</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="5" t="inlineStr">
+        <is>
+          <t>ev.ui.anyone</t>
+        </is>
+      </c>
+      <c r="B115" s="6" t="inlineStr">
+        <is>
+          <t>Todos</t>
+        </is>
+      </c>
+      <c r="C115" s="5" t="inlineStr">
+        <is>
+          <t>Everyone</t>
+        </is>
+      </c>
+      <c r="D115" s="5" t="inlineStr">
+        <is>
+          <t>Todos</t>
+        </is>
+      </c>
+      <c r="E115" s="5" t="inlineStr">
+        <is>
+          <t>Tous</t>
+        </is>
+      </c>
+      <c r="F115" s="5" t="inlineStr">
+        <is>
+          <t>Alle</t>
+        </is>
+      </c>
+      <c r="G115" s="5" t="inlineStr">
+        <is>
+          <t>Tutti</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="5" t="inlineStr">
+        <is>
+          <t>ev.ui.confirmed</t>
+        </is>
+      </c>
+      <c r="B116" s="6" t="inlineStr">
+        <is>
+          <t>Confirmado</t>
+        </is>
+      </c>
+      <c r="C116" s="5" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="D116" s="5" t="inlineStr">
+        <is>
+          <t>Confirmado</t>
+        </is>
+      </c>
+      <c r="E116" s="5" t="inlineStr">
+        <is>
+          <t>Confirmé</t>
+        </is>
+      </c>
+      <c r="F116" s="5" t="inlineStr">
+        <is>
+          <t>Bestätigt</t>
+        </is>
+      </c>
+      <c r="G116" s="5" t="inlineStr">
+        <is>
+          <t>Confermato</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="5" t="inlineStr">
+        <is>
+          <t>ev.ui.usually</t>
+        </is>
+      </c>
+      <c r="B117" s="6" t="inlineStr">
+        <is>
+          <t>Habitualmente</t>
+        </is>
+      </c>
+      <c r="C117" s="5" t="inlineStr">
+        <is>
+          <t>Usually</t>
+        </is>
+      </c>
+      <c r="D117" s="5" t="inlineStr">
+        <is>
+          <t>Normalmente</t>
+        </is>
+      </c>
+      <c r="E117" s="5" t="inlineStr">
+        <is>
+          <t>Habituellement</t>
+        </is>
+      </c>
+      <c r="F117" s="5" t="inlineStr">
+        <is>
+          <t>Üblicherweise</t>
+        </is>
+      </c>
+      <c r="G117" s="5" t="inlineStr">
+        <is>
+          <t>Di solito</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="5" t="inlineStr">
+        <is>
+          <t>ev.ui.last</t>
+        </is>
+      </c>
+      <c r="B118" s="6" t="inlineStr">
+        <is>
+          <t>Última edição</t>
+        </is>
+      </c>
+      <c r="C118" s="5" t="inlineStr">
+        <is>
+          <t>Last edition</t>
+        </is>
+      </c>
+      <c r="D118" s="5" t="inlineStr">
+        <is>
+          <t>Última edición</t>
+        </is>
+      </c>
+      <c r="E118" s="5" t="inlineStr">
+        <is>
+          <t>Dernière édition</t>
+        </is>
+      </c>
+      <c r="F118" s="5" t="inlineStr">
+        <is>
+          <t>Letzte Ausgabe</t>
+        </is>
+      </c>
+      <c r="G118" s="5" t="inlineStr">
+        <is>
+          <t>Ultima edizione</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="5" t="inlineStr">
+        <is>
+          <t>ev.ui.now</t>
+        </is>
+      </c>
+      <c r="B119" s="6" t="inlineStr">
+        <is>
+          <t>A decorrer</t>
+        </is>
+      </c>
+      <c r="C119" s="5" t="inlineStr">
+        <is>
+          <t>On now</t>
+        </is>
+      </c>
+      <c r="D119" s="5" t="inlineStr">
+        <is>
+          <t>En curso</t>
+        </is>
+      </c>
+      <c r="E119" s="5" t="inlineStr">
+        <is>
+          <t>En cours</t>
+        </is>
+      </c>
+      <c r="F119" s="5" t="inlineStr">
+        <is>
+          <t>Läuft gerade</t>
+        </is>
+      </c>
+      <c r="G119" s="5" t="inlineStr">
+        <is>
+          <t>In corso</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="5" t="inlineStr">
+        <is>
+          <t>ev.ui.fromHouse</t>
+        </is>
+      </c>
+      <c r="B120" s="6" t="inlineStr">
+        <is>
+          <t>da casa</t>
+        </is>
+      </c>
+      <c r="C120" s="5" t="inlineStr">
+        <is>
+          <t>from the house</t>
+        </is>
+      </c>
+      <c r="D120" s="5" t="inlineStr">
+        <is>
+          <t>desde la casa</t>
+        </is>
+      </c>
+      <c r="E120" s="5" t="inlineStr">
+        <is>
+          <t>de la maison</t>
+        </is>
+      </c>
+      <c r="F120" s="5" t="inlineStr">
+        <is>
+          <t>vom Haus</t>
+        </is>
+      </c>
+      <c r="G120" s="5" t="inlineStr">
+        <is>
+          <t>dalla casa</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="5" t="inlineStr">
+        <is>
+          <t>ev.ui.inPorches</t>
+        </is>
+      </c>
+      <c r="B121" s="6" t="inlineStr">
+        <is>
+          <t>Em Porches</t>
+        </is>
+      </c>
+      <c r="C121" s="5" t="inlineStr">
+        <is>
+          <t>In Porches</t>
+        </is>
+      </c>
+      <c r="D121" s="5" t="inlineStr">
+        <is>
+          <t>En Porches</t>
+        </is>
+      </c>
+      <c r="E121" s="5" t="inlineStr">
+        <is>
+          <t>À Porches</t>
+        </is>
+      </c>
+      <c r="F121" s="5" t="inlineStr">
+        <is>
+          <t>In Porches</t>
+        </is>
+      </c>
+      <c r="G121" s="5" t="inlineStr">
+        <is>
+          <t>A Porches</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="5" t="inlineStr">
+        <is>
+          <t>ev.ui.website</t>
+        </is>
+      </c>
+      <c r="B122" s="6" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
+      <c r="C122" s="5" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
+      <c r="D122" s="5" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="E122" s="5" t="inlineStr">
+        <is>
+          <t>Site web</t>
+        </is>
+      </c>
+      <c r="F122" s="5" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
+      <c r="G122" s="5" t="inlineStr">
+        <is>
+          <t>Sito web</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="5" t="inlineStr">
+        <is>
+          <t>ev.ui.none</t>
+        </is>
+      </c>
+      <c r="B123" s="6" t="inlineStr">
+        <is>
+          <t>Nada para mostrar com estes filtros.</t>
+        </is>
+      </c>
+      <c r="C123" s="5" t="inlineStr">
+        <is>
+          <t>Nothing to show with these filters.</t>
+        </is>
+      </c>
+      <c r="D123" s="5" t="inlineStr">
+        <is>
+          <t>No hay resultados con estos filtros.</t>
+        </is>
+      </c>
+      <c r="E123" s="5" t="inlineStr">
+        <is>
+          <t>Aucun résultat avec ces filtres.</t>
+        </is>
+      </c>
+      <c r="F123" s="5" t="inlineStr">
+        <is>
+          <t>Keine Ergebnisse mit diesen Filtern.</t>
+        </is>
+      </c>
+      <c r="G123" s="5" t="inlineStr">
+        <is>
+          <t>Nessun risultato con questi filtri.</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="5" t="inlineStr">
+        <is>
           <t>ev.ui.note</t>
         </is>
       </c>
-      <c r="B113" s="6" t="inlineStr">
+      <c r="B124" s="6" t="inlineStr">
         <is>
           <t>Datas, horários e preços são indicativos — confirme sempre com os organizadores. Distâncias aproximadas por estrada.</t>
         </is>
       </c>
-      <c r="C113" s="5" t="inlineStr">
+      <c r="C124" s="5" t="inlineStr">
         <is>
           <t>Dates, times and prices are indicative — always check with the organisers. Road distances are approximate.</t>
         </is>
       </c>
-      <c r="D113" s="5" t="inlineStr">
+      <c r="D124" s="5" t="inlineStr">
         <is>
           <t>Fechas, horarios y precios son orientativos; confírmelos siempre con los organizadores. Distancias aproximadas por carretera.</t>
         </is>
       </c>
-      <c r="E113" s="5" t="inlineStr">
+      <c r="E124" s="5" t="inlineStr">
         <is>
           <t>Dates, horaires et prix indicatifs — vérifiez toujours auprès des organisateurs. Distances routières approximatives.</t>
         </is>
       </c>
-      <c r="F113" s="5" t="inlineStr">
+      <c r="F124" s="5" t="inlineStr">
         <is>
           <t>Termine, Zeiten und Preise ohne Gewähr – bitte immer beim Veranstalter prüfen. Straßenentfernungen ca.</t>
         </is>
       </c>
-      <c r="G113" s="5" t="inlineStr">
+      <c r="G124" s="5" t="inlineStr">
         <is>
           <t>Date, orari e prezzi indicativi: verificate sempre con gli organizzatori. Distanze stradali approssimative.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G113"/>
+  <autoFilter ref="A1:G124"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -18326,7 +18862,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F128"/>
+  <dimension ref="A1:F144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="48" customWidth="1" min="1" max="1"/>
@@ -22433,8 +22969,520 @@
         </is>
       </c>
     </row>
+    <row r="129">
+      <c r="A129" s="6" t="inlineStr">
+        <is>
+          <t>Toldo motorizado</t>
+        </is>
+      </c>
+      <c r="B129" s="5" t="inlineStr">
+        <is>
+          <t>Motorised awning</t>
+        </is>
+      </c>
+      <c r="C129" s="5" t="inlineStr">
+        <is>
+          <t>Toldo motorizado</t>
+        </is>
+      </c>
+      <c r="D129" s="5" t="inlineStr">
+        <is>
+          <t>Store banne motorisé</t>
+        </is>
+      </c>
+      <c r="E129" s="5" t="inlineStr">
+        <is>
+          <t>Motorisierte Markise</t>
+        </is>
+      </c>
+      <c r="F129" s="5" t="inlineStr">
+        <is>
+          <t>Tenda da sole motorizzata</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="6" t="inlineStr">
+        <is>
+          <t>Garagem e estacionamento privativo dentro do lote</t>
+        </is>
+      </c>
+      <c r="B130" s="5" t="inlineStr">
+        <is>
+          <t>Garage and private parking within the property</t>
+        </is>
+      </c>
+      <c r="C130" s="5" t="inlineStr">
+        <is>
+          <t>Garaje y aparcamiento privado dentro de la parcela</t>
+        </is>
+      </c>
+      <c r="D130" s="5" t="inlineStr">
+        <is>
+          <t>Garage et parking privé dans la propriété</t>
+        </is>
+      </c>
+      <c r="E130" s="5" t="inlineStr">
+        <is>
+          <t>Garage und privater Parkplatz auf dem Grundstück</t>
+        </is>
+      </c>
+      <c r="F130" s="5" t="inlineStr">
+        <is>
+          <t>Garage e parcheggio privato all’interno della proprietà</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="6" t="inlineStr">
+        <is>
+          <t>Sala de Jantar</t>
+        </is>
+      </c>
+      <c r="B131" s="5" t="inlineStr">
+        <is>
+          <t>Dining Room</t>
+        </is>
+      </c>
+      <c r="C131" s="5" t="inlineStr">
+        <is>
+          <t>Comedor</t>
+        </is>
+      </c>
+      <c r="D131" s="5" t="inlineStr">
+        <is>
+          <t>Salle à manger</t>
+        </is>
+      </c>
+      <c r="E131" s="5" t="inlineStr">
+        <is>
+          <t>Esszimmer</t>
+        </is>
+      </c>
+      <c r="F131" s="5" t="inlineStr">
+        <is>
+          <t>Sala da pranzo</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="6" t="inlineStr">
+        <is>
+          <t>Explorar o Algarve</t>
+        </is>
+      </c>
+      <c r="B132" s="5" t="inlineStr">
+        <is>
+          <t>Explore the Algarve</t>
+        </is>
+      </c>
+      <c r="C132" s="5" t="inlineStr">
+        <is>
+          <t>Explorar el Algarve</t>
+        </is>
+      </c>
+      <c r="D132" s="5" t="inlineStr">
+        <is>
+          <t>Explorer l’Algarve</t>
+        </is>
+      </c>
+      <c r="E132" s="5" t="inlineStr">
+        <is>
+          <t>Algarve entdecken</t>
+        </is>
+      </c>
+      <c r="F132" s="5" t="inlineStr">
+        <is>
+          <t>Esplora l’Algarve</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="6" t="inlineStr">
+        <is>
+          <t>À Volta da Casa</t>
+        </is>
+      </c>
+      <c r="B133" s="5" t="inlineStr">
+        <is>
+          <t>Around the House</t>
+        </is>
+      </c>
+      <c r="C133" s="5" t="inlineStr">
+        <is>
+          <t>Alrededor de la casa</t>
+        </is>
+      </c>
+      <c r="D133" s="5" t="inlineStr">
+        <is>
+          <t>Autour de la maison</t>
+        </is>
+      </c>
+      <c r="E133" s="5" t="inlineStr">
+        <is>
+          <t>Rund ums Haus</t>
+        </is>
+      </c>
+      <c r="F133" s="5" t="inlineStr">
+        <is>
+          <t>Intorno alla casa</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="6" t="inlineStr">
+        <is>
+          <t>Praias, restaurantes, eventos e experiências — tudo num só sítio, com mapa interativo.</t>
+        </is>
+      </c>
+      <c r="B134" s="5" t="inlineStr">
+        <is>
+          <t>Beaches, restaurants, events and experiences — all in one place, with an interactive map.</t>
+        </is>
+      </c>
+      <c r="C134" s="5" t="inlineStr">
+        <is>
+          <t>Playas, restaurantes, eventos y experiencias, todo en un solo lugar y con mapa interactivo.</t>
+        </is>
+      </c>
+      <c r="D134" s="5" t="inlineStr">
+        <is>
+          <t>Plages, restaurants, événements et expériences — tout au même endroit, avec une carte interactive.</t>
+        </is>
+      </c>
+      <c r="E134" s="5" t="inlineStr">
+        <is>
+          <t>Strände, Restaurants, Events und Erlebnisse – alles an einem Ort, mit interaktiver Karte.</t>
+        </is>
+      </c>
+      <c r="F134" s="5" t="inlineStr">
+        <is>
+          <t>Spiagge, ristoranti, eventi ed esperienze: tutto in un unico posto, con mappa interattiva.</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="6" t="inlineStr">
+        <is>
+          <t>Mapa interativo</t>
+        </is>
+      </c>
+      <c r="B135" s="5" t="inlineStr">
+        <is>
+          <t>Interactive map</t>
+        </is>
+      </c>
+      <c r="C135" s="5" t="inlineStr">
+        <is>
+          <t>Mapa interactivo</t>
+        </is>
+      </c>
+      <c r="D135" s="5" t="inlineStr">
+        <is>
+          <t>Carte interactive</t>
+        </is>
+      </c>
+      <c r="E135" s="5" t="inlineStr">
+        <is>
+          <t>Interaktive Karte</t>
+        </is>
+      </c>
+      <c r="F135" s="5" t="inlineStr">
+        <is>
+          <t>Mappa interattiva</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="6" t="inlineStr">
+        <is>
+          <t>Todos os pontos à volta da casa</t>
+        </is>
+      </c>
+      <c r="B136" s="5" t="inlineStr">
+        <is>
+          <t>Every spot around the house</t>
+        </is>
+      </c>
+      <c r="C136" s="5" t="inlineStr">
+        <is>
+          <t>Todos los puntos alrededor de la casa</t>
+        </is>
+      </c>
+      <c r="D136" s="5" t="inlineStr">
+        <is>
+          <t>Tous les lieux autour de la maison</t>
+        </is>
+      </c>
+      <c r="E136" s="5" t="inlineStr">
+        <is>
+          <t>Alle Orte rund ums Haus</t>
+        </is>
+      </c>
+      <c r="F136" s="5" t="inlineStr">
+        <is>
+          <t>Tutti i luoghi intorno alla casa</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="6" t="inlineStr">
+        <is>
+          <t>As mais bonitas a poucos minutos</t>
+        </is>
+      </c>
+      <c r="B137" s="5" t="inlineStr">
+        <is>
+          <t>The most beautiful ones, minutes away</t>
+        </is>
+      </c>
+      <c r="C137" s="5" t="inlineStr">
+        <is>
+          <t>Las más bonitas, a pocos minutos</t>
+        </is>
+      </c>
+      <c r="D137" s="5" t="inlineStr">
+        <is>
+          <t>Les plus belles, à quelques minutes</t>
+        </is>
+      </c>
+      <c r="E137" s="5" t="inlineStr">
+        <is>
+          <t>Die schönsten, nur Minuten entfernt</t>
+        </is>
+      </c>
+      <c r="F137" s="5" t="inlineStr">
+        <is>
+          <t>Le più belle, a pochi minuti</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="6" t="inlineStr">
+        <is>
+          <t>40 sugestões, de tascas a estrelas Michelin</t>
+        </is>
+      </c>
+      <c r="B138" s="5" t="inlineStr">
+        <is>
+          <t>40 picks, from taverns to Michelin stars</t>
+        </is>
+      </c>
+      <c r="C138" s="5" t="inlineStr">
+        <is>
+          <t>40 sugerencias, de tabernas a estrellas Michelin</t>
+        </is>
+      </c>
+      <c r="D138" s="5" t="inlineStr">
+        <is>
+          <t>40 adresses, des tavernes aux étoilés Michelin</t>
+        </is>
+      </c>
+      <c r="E138" s="5" t="inlineStr">
+        <is>
+          <t>40 Tipps, von Tavernen bis Michelin-Sterne</t>
+        </is>
+      </c>
+      <c r="F138" s="5" t="inlineStr">
+        <is>
+          <t>40 consigli, dalle taverne alle stelle Michelin</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="6" t="inlineStr">
+        <is>
+          <t>Eventos e Experiências</t>
+        </is>
+      </c>
+      <c r="B139" s="5" t="inlineStr">
+        <is>
+          <t>Events &amp; Experiences</t>
+        </is>
+      </c>
+      <c r="C139" s="5" t="inlineStr">
+        <is>
+          <t>Eventos y experiencias</t>
+        </is>
+      </c>
+      <c r="D139" s="5" t="inlineStr">
+        <is>
+          <t>Événements &amp; expériences</t>
+        </is>
+      </c>
+      <c r="E139" s="5" t="inlineStr">
+        <is>
+          <t>Events &amp; Erlebnisse</t>
+        </is>
+      </c>
+      <c r="F139" s="5" t="inlineStr">
+        <is>
+          <t>Eventi ed esperienze</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="6" t="inlineStr">
+        <is>
+          <t>Festas, ar livre, natureza e muito mais</t>
+        </is>
+      </c>
+      <c r="B140" s="5" t="inlineStr">
+        <is>
+          <t>Festivals, outdoors, nature and more</t>
+        </is>
+      </c>
+      <c r="C140" s="5" t="inlineStr">
+        <is>
+          <t>Fiestas, aire libre, naturaleza y mucho más</t>
+        </is>
+      </c>
+      <c r="D140" s="5" t="inlineStr">
+        <is>
+          <t>Fêtes, plein air, nature et plus encore</t>
+        </is>
+      </c>
+      <c r="E140" s="5" t="inlineStr">
+        <is>
+          <t>Feste, Outdoor, Natur und mehr</t>
+        </is>
+      </c>
+      <c r="F140" s="5" t="inlineStr">
+        <is>
+          <t>Feste, aria aperta, natura e molto altro</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="6" t="inlineStr">
+        <is>
+          <t>Abrir Explorar o Algarve</t>
+        </is>
+      </c>
+      <c r="B141" s="5" t="inlineStr">
+        <is>
+          <t>Open Explore the Algarve</t>
+        </is>
+      </c>
+      <c r="C141" s="5" t="inlineStr">
+        <is>
+          <t>Abrir Explorar el Algarve</t>
+        </is>
+      </c>
+      <c r="D141" s="5" t="inlineStr">
+        <is>
+          <t>Ouvrir Explorer l’Algarve</t>
+        </is>
+      </c>
+      <c r="E141" s="5" t="inlineStr">
+        <is>
+          <t>Algarve entdecken öffnen</t>
+        </is>
+      </c>
+      <c r="F141" s="5" t="inlineStr">
+        <is>
+          <t>Apri Esplora l’Algarve</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="6" t="inlineStr">
+        <is>
+          <t>Reservar no Booking</t>
+        </is>
+      </c>
+      <c r="B142" s="5" t="inlineStr">
+        <is>
+          <t>Book on Booking.com</t>
+        </is>
+      </c>
+      <c r="C142" s="5" t="inlineStr">
+        <is>
+          <t>Reservar en Booking</t>
+        </is>
+      </c>
+      <c r="D142" s="5" t="inlineStr">
+        <is>
+          <t>Réserver sur Booking</t>
+        </is>
+      </c>
+      <c r="E142" s="5" t="inlineStr">
+        <is>
+          <t>Auf Booking buchen</t>
+        </is>
+      </c>
+      <c r="F142" s="5" t="inlineStr">
+        <is>
+          <t>Prenota su Booking</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="6" t="inlineStr">
+        <is>
+          <t>Gerido por HostWise</t>
+        </is>
+      </c>
+      <c r="B143" s="5" t="inlineStr">
+        <is>
+          <t>Managed by HostWise</t>
+        </is>
+      </c>
+      <c r="C143" s="5" t="inlineStr">
+        <is>
+          <t>Gestionado por HostWise</t>
+        </is>
+      </c>
+      <c r="D143" s="5" t="inlineStr">
+        <is>
+          <t>Géré par HostWise</t>
+        </is>
+      </c>
+      <c r="E143" s="5" t="inlineStr">
+        <is>
+          <t>Verwaltet von HostWise</t>
+        </is>
+      </c>
+      <c r="F143" s="5" t="inlineStr">
+        <is>
+          <t>Gestito da HostWise</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="6" t="inlineStr">
+        <is>
+          <t>Informação meramente indicativa, sem valor contratual. Não dispensa a leitura das condições da plataforma de reserva (Airbnb, Booking, etc.) e das regras da HostWise, que prevalecem em caso de diferença.</t>
+        </is>
+      </c>
+      <c r="B144" s="5" t="inlineStr">
+        <is>
+          <t>For information only, with no contractual value. It does not replace the terms of the booking platform (Airbnb, Booking, etc.) or HostWise’s house rules, which prevail in case of any difference.</t>
+        </is>
+      </c>
+      <c r="C144" s="5" t="inlineStr">
+        <is>
+          <t>Información meramente orientativa y sin valor contractual. No sustituye las condiciones de la plataforma de reserva (Airbnb, Booking, etc.) ni las normas de HostWise, que prevalecen en caso de diferencia.</t>
+        </is>
+      </c>
+      <c r="D144" s="5" t="inlineStr">
+        <is>
+          <t>Informations purement indicatives, sans valeur contractuelle. Elles ne remplacent pas les conditions de la plateforme de réservation (Airbnb, Booking, etc.) ni le règlement de HostWise, qui prévalent en cas de divergence.</t>
+        </is>
+      </c>
+      <c r="E144" s="5" t="inlineStr">
+        <is>
+          <t>Nur zur Information, ohne vertragliche Bindung. Ersetzt nicht die Bedingungen der Buchungsplattform (Airbnb, Booking usw.) oder die Hausregeln von HostWise, die im Zweifel Vorrang haben.</t>
+        </is>
+      </c>
+      <c r="F144" s="5" t="inlineStr">
+        <is>
+          <t>Informazioni puramente indicative, senza valore contrattuale. Non sostituiscono le condizioni della piattaforma di prenotazione (Airbnb, Booking, ecc.) né le regole di HostWise, che prevalgono in caso di differenze.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F128"/>
+  <autoFilter ref="A1:F144"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/Conteudos_Site_Casa_Porches.xlsx
+++ b/Conteudos_Site_Casa_Porches.xlsx
@@ -876,7 +876,11 @@
           <t>booking_nota</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr"/>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>9.8</t>
+        </is>
+      </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
           <t>Nota no Booking (ex.: 9.4) — vazio = não aparece</t>
@@ -889,7 +893,11 @@
           <t>booking_avaliacoes</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr"/>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
           <t>Nº de avaliações no Booking</t>
@@ -902,7 +910,11 @@
           <t>booking_link</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr"/>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>https://www.booking.com/hotel/pt/host-wise-bright-spacious-house-swimming-pool.html</t>
+        </is>
+      </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
           <t>Link público do anúncio no Booking (aparece também o botão Reservar no Booking)</t>

--- a/Conteudos_Site_Casa_Porches.xlsx
+++ b/Conteudos_Site_Casa_Porches.xlsx
@@ -19,12 +19,12 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Casa'!$A$1:$C$12</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Textos'!$A$1:$G$124</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Restaurantes'!$A$1:$Q$41</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Eventos'!$A$1:$AG$76</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Textos'!$A$1:$G$135</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Restaurantes'!$A$1:$Q$47</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Eventos'!$A$1:$AG$82</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Sessoes'!$A$1:$D$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Localidades'!$A$1:$D$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Mapa'!$A$1:$N$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Mapa'!$A$1:$N$27</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Pagina_Principal'!$A$1:$F$144</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -720,7 +720,7 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>Eventos › categoria: outdoor (atividades ao ar livre), events (festivais), water (parques e atrações), nature (natureza e praias), sea (mar e aventura), indoor (piscinas e chuva), markets (mercados e tradições).</t>
+          <t>Eventos › categoria: cities (vilas e cidades), outdoor (atividades ao ar livre), events (festivais), water (parques e atrações), nature (natureza e praias), sea (mar e aventura), indoor (piscinas e chuva), markets (mercados e tradições).</t>
         </is>
       </c>
     </row>
@@ -734,7 +734,7 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>Mapa › categoria: beach, food, fun, see, help.</t>
+          <t>Mapa › categoria: beach (praias), food, fun, see (locais), help (saúde), shop (compras).</t>
         </is>
       </c>
     </row>
@@ -972,7 +972,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G124"/>
+  <dimension ref="A1:G135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -3281,1302 +3281,1302 @@
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>beachesTitle</t>
+          <t>cats.shop</t>
         </is>
       </c>
       <c r="B63" s="6" t="inlineStr">
         <is>
-          <t>Praias perto</t>
+          <t>Compras</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>Beaches nearby</t>
+          <t>Shopping</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>Playas cercanas</t>
+          <t>Compras</t>
         </is>
       </c>
       <c r="E63" s="5" t="inlineStr">
         <is>
-          <t>Plages à proximité</t>
+          <t>Courses</t>
         </is>
       </c>
       <c r="F63" s="5" t="inlineStr">
         <is>
-          <t>Strände in der Nähe</t>
+          <t>Einkaufen</t>
         </is>
       </c>
       <c r="G63" s="5" t="inlineStr">
         <is>
-          <t>Spiagge vicine</t>
+          <t>Spesa</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
-          <t>beachTip</t>
+          <t>beachesTitle</t>
         </is>
       </c>
       <c r="B64" s="6" t="inlineStr">
         <is>
-          <t>Dica: o Percurso dos Sete Vales Suspensos liga a Marinha a Benagil pelas falésias — melhor de manhã cedo ou ao fim da tarde.</t>
+          <t>Praias perto</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>Tip: the Seven Hanging Valleys trail (Percurso dos Sete Vales Suspensos) links Marinha and Benagil along the clifftops — best early morning or late afternoon.</t>
+          <t>Beaches nearby</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>Consejo: la ruta de los Siete Valles Colgantes (Percurso dos Sete Vales Suspensos) une Marinha y Benagil por los acantilados; mejor a primera hora o al final de la tarde.</t>
+          <t>Playas cercanas</t>
         </is>
       </c>
       <c r="E64" s="5" t="inlineStr">
         <is>
-          <t>Astuce : le sentier des Sept Vallées Suspendues (Percurso dos Sete Vales Suspensos) relie Marinha à Benagil par les falaises — idéal tôt le matin ou en fin d’après-midi.</t>
+          <t>Plages à proximité</t>
         </is>
       </c>
       <c r="F64" s="5" t="inlineStr">
         <is>
-          <t>Tipp: Der Wanderweg der Sieben Hängenden Täler (Percurso dos Sete Vales Suspensos) verbindet Marinha und Benagil entlang der Klippen – am schönsten früh morgens oder am späten Nachmittag.</t>
+          <t>Strände in der Nähe</t>
         </is>
       </c>
       <c r="G64" s="5" t="inlineStr">
         <is>
-          <t>Consiglio: il sentiero delle Sette Valli Sospese (Percurso dos Sete Vales Suspensos) collega Marinha e Benagil lungo le scogliere — ideale al mattino presto o nel tardo pomeriggio.</t>
+          <t>Spiagge vicine</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="5" t="inlineStr">
         <is>
-          <t>foodTitle</t>
+          <t>beachTip</t>
         </is>
       </c>
       <c r="B65" s="6" t="inlineStr">
         <is>
-          <t>Restaurantes</t>
+          <t>Dica: o Percurso dos Sete Vales Suspensos liga a Marinha a Benagil pelas falésias — melhor de manhã cedo ou ao fim da tarde.</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>Restaurants</t>
+          <t>Tip: the Seven Hanging Valleys trail (Percurso dos Sete Vales Suspensos) links Marinha and Benagil along the clifftops — best early morning or late afternoon.</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>Restaurantes</t>
+          <t>Consejo: la ruta de los Siete Valles Colgantes (Percurso dos Sete Vales Suspensos) une Marinha y Benagil por los acantilados; mejor a primera hora o al final de la tarde.</t>
         </is>
       </c>
       <c r="E65" s="5" t="inlineStr">
         <is>
-          <t>Restaurants</t>
+          <t>Astuce : le sentier des Sept Vallées Suspendues (Percurso dos Sete Vales Suspensos) relie Marinha à Benagil par les falaises — idéal tôt le matin ou en fin d’après-midi.</t>
         </is>
       </c>
       <c r="F65" s="5" t="inlineStr">
         <is>
-          <t>Restaurants</t>
+          <t>Tipp: Der Wanderweg der Sieben Hängenden Täler (Percurso dos Sete Vales Suspensos) verbindet Marinha und Benagil entlang der Klippen – am schönsten früh morgens oder am späten Nachmittag.</t>
         </is>
       </c>
       <c r="G65" s="5" t="inlineStr">
         <is>
-          <t>Ristoranti</t>
+          <t>Consiglio: il sentiero delle Sette Valli Sospese (Percurso dos Sete Vales Suspensos) collega Marinha e Benagil lungo le scogliere — ideale al mattino presto o nel tardo pomeriggio.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>todoTitle</t>
+          <t>foodTitle</t>
         </is>
       </c>
       <c r="B66" s="6" t="inlineStr">
         <is>
-          <t>O que fazer</t>
+          <t>Restaurantes</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>Things to do</t>
+          <t>Restaurants</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>Qué hacer</t>
+          <t>Restaurantes</t>
         </is>
       </c>
       <c r="E66" s="5" t="inlineStr">
         <is>
-          <t>À faire</t>
+          <t>Restaurants</t>
         </is>
       </c>
       <c r="F66" s="5" t="inlineStr">
         <is>
-          <t>Ausflüge &amp; Aktivitäten</t>
+          <t>Restaurants</t>
         </is>
       </c>
       <c r="G66" s="5" t="inlineStr">
         <is>
-          <t>Cosa fare</t>
+          <t>Ristoranti</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="5" t="inlineStr">
         <is>
-          <t>golf</t>
+          <t>todoTitle</t>
         </is>
       </c>
       <c r="B67" s="6" t="inlineStr">
         <is>
-          <t>Golfe</t>
+          <t>O que fazer</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>Golf</t>
+          <t>Things to do</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>Golf</t>
+          <t>Qué hacer</t>
         </is>
       </c>
       <c r="E67" s="5" t="inlineStr">
         <is>
-          <t>Golf</t>
+          <t>À faire</t>
         </is>
       </c>
       <c r="F67" s="5" t="inlineStr">
         <is>
-          <t>Golf</t>
+          <t>Ausflüge &amp; Aktivitäten</t>
         </is>
       </c>
       <c r="G67" s="5" t="inlineStr">
         <is>
-          <t>Golf</t>
+          <t>Cosa fare</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="5" t="inlineStr">
         <is>
-          <t>inVillage</t>
+          <t>golf</t>
         </is>
       </c>
       <c r="B68" s="6" t="inlineStr">
         <is>
-          <t>Na vila</t>
+          <t>Golfe</t>
         </is>
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>In the village</t>
+          <t>Golf</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>En el pueblo</t>
+          <t>Golf</t>
         </is>
       </c>
       <c r="E68" s="5" t="inlineStr">
         <is>
-          <t>Au village</t>
+          <t>Golf</t>
         </is>
       </c>
       <c r="F68" s="5" t="inlineStr">
         <is>
-          <t>Im Ort</t>
+          <t>Golf</t>
         </is>
       </c>
       <c r="G68" s="5" t="inlineStr">
         <is>
-          <t>In paese</t>
+          <t>Golf</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>departureTitle</t>
+          <t>inVillage</t>
         </is>
       </c>
       <c r="B69" s="6" t="inlineStr">
         <is>
-          <t>Antes de sair</t>
+          <t>Na vila</t>
         </is>
       </c>
       <c r="C69" s="5" t="inlineStr">
         <is>
-          <t>Before you leave</t>
+          <t>In the village</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>Antes de irse</t>
+          <t>En el pueblo</t>
         </is>
       </c>
       <c r="E69" s="5" t="inlineStr">
         <is>
-          <t>Avant de partir</t>
+          <t>Au village</t>
         </is>
       </c>
       <c r="F69" s="5" t="inlineStr">
         <is>
-          <t>Vor der Abreise</t>
+          <t>Im Ort</t>
         </is>
       </c>
       <c r="G69" s="5" t="inlineStr">
         <is>
-          <t>Prima di partire</t>
+          <t>In paese</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="5" t="inlineStr">
         <is>
-          <t>departure.1</t>
+          <t>departureTitle</t>
         </is>
       </c>
       <c r="B70" s="6" t="inlineStr">
         <is>
-          <t>Check-out até às 11:00 (check-out tardio a pedido pelo Airbnb).</t>
+          <t>Antes de sair</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>Check-out by 11:00 (late check-out on request through Airbnb).</t>
+          <t>Before you leave</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>Check-out hasta las 11:00 (salida tardía bajo petición a través de Airbnb).</t>
+          <t>Antes de irse</t>
         </is>
       </c>
       <c r="E70" s="5" t="inlineStr">
         <is>
-          <t>Départ avant 11h00 (départ tardif sur demande via Airbnb).</t>
+          <t>Avant de partir</t>
         </is>
       </c>
       <c r="F70" s="5" t="inlineStr">
         <is>
-          <t>Check-out bis 11:00 Uhr (später Check-out auf Anfrage über Airbnb).</t>
+          <t>Vor der Abreise</t>
         </is>
       </c>
       <c r="G70" s="5" t="inlineStr">
         <is>
-          <t>Check-out entro le 11:00 (check-out posticipato su richiesta tramite Airbnb).</t>
+          <t>Prima di partire</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="5" t="inlineStr">
         <is>
-          <t>departure.2</t>
+          <t>departure.1</t>
         </is>
       </c>
       <c r="B71" s="6" t="inlineStr">
         <is>
-          <t>Desligue o ar condicionado e as luzes e feche janelas e portas.</t>
+          <t>Check-out até às 11:00 (check-out tardio a pedido pelo Airbnb).</t>
         </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>Switch off the air conditioning and lights, and close windows and doors.</t>
+          <t>Check-out by 11:00 (late check-out on request through Airbnb).</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>Apague el aire acondicionado y las luces y cierre puertas y ventanas.</t>
+          <t>Check-out hasta las 11:00 (salida tardía bajo petición a través de Airbnb).</t>
         </is>
       </c>
       <c r="E71" s="5" t="inlineStr">
         <is>
-          <t>Éteignez la climatisation et les lumières, fermez portes et fenêtres.</t>
+          <t>Départ avant 11h00 (départ tardif sur demande via Airbnb).</t>
         </is>
       </c>
       <c r="F71" s="5" t="inlineStr">
         <is>
-          <t>Schalten Sie Klimaanlage und Licht aus und schließen Sie Fenster und Türen.</t>
+          <t>Check-out bis 11:00 Uhr (später Check-out auf Anfrage über Airbnb).</t>
         </is>
       </c>
       <c r="G71" s="5" t="inlineStr">
         <is>
-          <t>Spegnete l’aria condizionata e le luci e chiudete porte e finestre.</t>
+          <t>Check-out entro le 11:00 (check-out posticipato su richiesta tramite Airbnb).</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="5" t="inlineStr">
         <is>
-          <t>departure.3</t>
+          <t>departure.2</t>
         </is>
       </c>
       <c r="B72" s="6" t="inlineStr">
         <is>
-          <t>Deixe o lixo nos contentores da vila e coloque a loiça na máquina.</t>
+          <t>Desligue o ar condicionado e as luzes e feche janelas e portas.</t>
         </is>
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>Put the rubbish in the village bins and load the dishwasher.</t>
+          <t>Switch off the air conditioning and lights, and close windows and doors.</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>Deje la basura en los contenedores del pueblo y ponga la vajilla en el lavavajillas.</t>
+          <t>Apague el aire acondicionado y las luces y cierre puertas y ventanas.</t>
         </is>
       </c>
       <c r="E72" s="5" t="inlineStr">
         <is>
-          <t>Déposez les déchets dans les conteneurs du village et mettez la vaisselle dans le lave-vaisselle.</t>
+          <t>Éteignez la climatisation et les lumières, fermez portes et fenêtres.</t>
         </is>
       </c>
       <c r="F72" s="5" t="inlineStr">
         <is>
-          <t>Bringen Sie den Müll zu den Containern im Ort und räumen Sie das Geschirr in die Spülmaschine.</t>
+          <t>Schalten Sie Klimaanlage und Licht aus und schließen Sie Fenster und Türen.</t>
         </is>
       </c>
       <c r="G72" s="5" t="inlineStr">
         <is>
-          <t>Lasciate i rifiuti nei contenitori del paese e mettete le stoviglie in lavastoviglie.</t>
+          <t>Spegnete l’aria condizionata e le luci e chiudete porte e finestre.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="5" t="inlineStr">
         <is>
-          <t>departure.4</t>
+          <t>departure.3</t>
         </is>
       </c>
       <c r="B73" s="6" t="inlineStr">
         <is>
-          <t>Devolva as chaves ao cofre e baralhe o código.</t>
+          <t>Deixe o lixo nos contentores da vila e coloque a loiça na máquina.</t>
         </is>
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>Return the keys to the key safe and scramble the code.</t>
+          <t>Put the rubbish in the village bins and load the dishwasher.</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>Devuelva las llaves a la caja de seguridad y cambie la combinación.</t>
+          <t>Deje la basura en los contenedores del pueblo y ponga la vajilla en el lavavajillas.</t>
         </is>
       </c>
       <c r="E73" s="5" t="inlineStr">
         <is>
-          <t>Remettez les clés dans la boîte à clés et brouillez le code.</t>
+          <t>Déposez les déchets dans les conteneurs du village et mettez la vaisselle dans le lave-vaisselle.</t>
         </is>
       </c>
       <c r="F73" s="5" t="inlineStr">
         <is>
-          <t>Legen Sie die Schlüssel zurück in den Schlüsseltresor und verstellen Sie den Code.</t>
+          <t>Bringen Sie den Müll zu den Containern im Ort und räumen Sie das Geschirr in die Spülmaschine.</t>
         </is>
       </c>
       <c r="G73" s="5" t="inlineStr">
         <is>
-          <t>Rimettete le chiavi nella cassetta di sicurezza e cambiate la combinazione.</t>
+          <t>Lasciate i rifiuti nei contenitori del paese e mettete le stoviglie in lavastoviglie.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="5" t="inlineStr">
         <is>
-          <t>departure.5</t>
+          <t>departure.4</t>
         </is>
       </c>
       <c r="B74" s="6" t="inlineStr">
         <is>
-          <t>Obrigado pela estadia — uma avaliação no Airbnb ajuda-nos muito!</t>
+          <t>Devolva as chaves ao cofre e baralhe o código.</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>Thank you for staying with us — a review on Airbnb helps us a lot!</t>
+          <t>Return the keys to the key safe and scramble the code.</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>¡Gracias por su estancia! Una valoración en Airbnb nos ayuda mucho.</t>
+          <t>Devuelva las llaves a la caja de seguridad y cambie la combinación.</t>
         </is>
       </c>
       <c r="E74" s="5" t="inlineStr">
         <is>
-          <t>Merci pour votre séjour — un commentaire sur Airbnb nous aide beaucoup !</t>
+          <t>Remettez les clés dans la boîte à clés et brouillez le code.</t>
         </is>
       </c>
       <c r="F74" s="5" t="inlineStr">
         <is>
-          <t>Danke für Ihren Aufenthalt – eine Bewertung auf Airbnb hilft uns sehr!</t>
+          <t>Legen Sie die Schlüssel zurück in den Schlüsseltresor und verstellen Sie den Code.</t>
         </is>
       </c>
       <c r="G74" s="5" t="inlineStr">
         <is>
-          <t>Grazie per il soggiorno: una recensione su Airbnb ci aiuta molto!</t>
+          <t>Rimettete le chiavi nella cassetta di sicurezza e cambiate la combinazione.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="5" t="inlineStr">
         <is>
-          <t>complaints</t>
+          <t>departure.5</t>
         </is>
       </c>
       <c r="B75" s="6" t="inlineStr">
         <is>
-          <t>Livro de Reclamações Eletrónico</t>
+          <t>Obrigado pela estadia — uma avaliação no Airbnb ajuda-nos muito!</t>
         </is>
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>Complaints book (Livro de Reclamações)</t>
+          <t>Thank you for staying with us — a review on Airbnb helps us a lot!</t>
         </is>
       </c>
       <c r="D75" s="5" t="inlineStr">
         <is>
-          <t>Libro de reclamaciones (Livro de Reclamações)</t>
+          <t>¡Gracias por su estancia! Una valoración en Airbnb nos ayuda mucho.</t>
         </is>
       </c>
       <c r="E75" s="5" t="inlineStr">
         <is>
-          <t>Livre de réclamations (Livro de Reclamações)</t>
+          <t>Merci pour votre séjour — un commentaire sur Airbnb nous aide beaucoup !</t>
         </is>
       </c>
       <c r="F75" s="5" t="inlineStr">
         <is>
-          <t>Beschwerdebuch (Livro de Reclamações)</t>
+          <t>Danke für Ihren Aufenthalt – eine Bewertung auf Airbnb hilft uns sehr!</t>
         </is>
       </c>
       <c r="G75" s="5" t="inlineStr">
         <is>
-          <t>Libro dei reclami (Livro de Reclamações)</t>
+          <t>Grazie per il soggiorno: una recensione su Airbnb ci aiuta molto!</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="5" t="inlineStr">
         <is>
-          <t>about</t>
+          <t>complaints</t>
         </is>
       </c>
       <c r="B76" s="6" t="inlineStr">
         <is>
-          <t>Sobre a casa</t>
+          <t>Livro de Reclamações Eletrónico</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>About the house</t>
+          <t>Complaints book (Livro de Reclamações)</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>Sobre la casa</t>
+          <t>Libro de reclamaciones (Livro de Reclamações)</t>
         </is>
       </c>
       <c r="E76" s="5" t="inlineStr">
         <is>
-          <t>À propos de la maison</t>
+          <t>Livre de réclamations (Livro de Reclamações)</t>
         </is>
       </c>
       <c r="F76" s="5" t="inlineStr">
         <is>
-          <t>Über das Haus</t>
+          <t>Beschwerdebuch (Livro de Reclamações)</t>
         </is>
       </c>
       <c r="G76" s="5" t="inlineStr">
         <is>
-          <t>La casa</t>
+          <t>Libro dei reclami (Livro de Reclamações)</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="5" t="inlineStr">
         <is>
-          <t>site.home</t>
+          <t>about</t>
         </is>
       </c>
       <c r="B77" s="6" t="inlineStr">
         <is>
-          <t>A Casa</t>
+          <t>Sobre a casa</t>
         </is>
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>The House</t>
+          <t>About the house</t>
         </is>
       </c>
       <c r="D77" s="5" t="inlineStr">
         <is>
-          <t>La Casa</t>
+          <t>Sobre la casa</t>
         </is>
       </c>
       <c r="E77" s="5" t="inlineStr">
         <is>
-          <t>La Maison</t>
+          <t>À propos de la maison</t>
         </is>
       </c>
       <c r="F77" s="5" t="inlineStr">
         <is>
-          <t>Das Haus</t>
+          <t>Über das Haus</t>
         </is>
       </c>
       <c r="G77" s="5" t="inlineStr">
         <is>
-          <t>La Casa</t>
+          <t>La casa</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="5" t="inlineStr">
         <is>
-          <t>site.guide</t>
+          <t>site.home</t>
         </is>
       </c>
       <c r="B78" s="6" t="inlineStr">
         <is>
-          <t>Guia do Hóspede</t>
+          <t>A Casa</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>Guest Guide</t>
+          <t>The House</t>
         </is>
       </c>
       <c r="D78" s="5" t="inlineStr">
         <is>
-          <t>Guía del huésped</t>
+          <t>La Casa</t>
         </is>
       </c>
       <c r="E78" s="5" t="inlineStr">
         <is>
-          <t>Guide du voyageur</t>
+          <t>La Maison</t>
         </is>
       </c>
       <c r="F78" s="5" t="inlineStr">
         <is>
-          <t>Gästeinfo</t>
+          <t>Das Haus</t>
         </is>
       </c>
       <c r="G78" s="5" t="inlineStr">
         <is>
-          <t>Guida ospiti</t>
+          <t>La Casa</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="5" t="inlineStr">
         <is>
-          <t>site.explore</t>
+          <t>site.guide</t>
         </is>
       </c>
       <c r="B79" s="6" t="inlineStr">
         <is>
-          <t>Explorar o Algarve</t>
+          <t>Guia do Hóspede</t>
         </is>
       </c>
       <c r="C79" s="5" t="inlineStr">
         <is>
-          <t>Explore the Algarve</t>
+          <t>Guest Guide</t>
         </is>
       </c>
       <c r="D79" s="5" t="inlineStr">
         <is>
-          <t>Explorar el Algarve</t>
+          <t>Guía del huésped</t>
         </is>
       </c>
       <c r="E79" s="5" t="inlineStr">
         <is>
-          <t>Explorer l’Algarve</t>
+          <t>Guide du voyageur</t>
         </is>
       </c>
       <c r="F79" s="5" t="inlineStr">
         <is>
-          <t>Algarve entdecken</t>
+          <t>Gästeinfo</t>
         </is>
       </c>
       <c r="G79" s="5" t="inlineStr">
         <is>
-          <t>Esplora l’Algarve</t>
+          <t>Guida ospiti</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="5" t="inlineStr">
         <is>
-          <t>site.book</t>
+          <t>site.explore</t>
         </is>
       </c>
       <c r="B80" s="6" t="inlineStr">
         <is>
-          <t>Reservar</t>
+          <t>Explorar o Algarve</t>
         </is>
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>Book</t>
+          <t>Explore the Algarve</t>
         </is>
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>Reservar</t>
+          <t>Explorar el Algarve</t>
         </is>
       </c>
       <c r="E80" s="5" t="inlineStr">
         <is>
-          <t>Réserver</t>
+          <t>Explorer l’Algarve</t>
         </is>
       </c>
       <c r="F80" s="5" t="inlineStr">
         <is>
-          <t>Buchen</t>
+          <t>Algarve entdecken</t>
         </is>
       </c>
       <c r="G80" s="5" t="inlineStr">
         <is>
-          <t>Prenota</t>
+          <t>Esplora l’Algarve</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="5" t="inlineStr">
         <is>
-          <t>explore.title</t>
+          <t>site.book</t>
         </is>
       </c>
       <c r="B81" s="6" t="inlineStr">
         <is>
-          <t>Explorar o Algarve | Casa Porches</t>
+          <t>Reservar</t>
         </is>
       </c>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>Explore the Algarve | Casa Porches</t>
+          <t>Book</t>
         </is>
       </c>
       <c r="D81" s="5" t="inlineStr">
         <is>
-          <t>Explorar el Algarve | Casa Porches</t>
+          <t>Reservar</t>
         </is>
       </c>
       <c r="E81" s="5" t="inlineStr">
         <is>
-          <t>Explorer l’Algarve | Casa Porches</t>
+          <t>Réserver</t>
         </is>
       </c>
       <c r="F81" s="5" t="inlineStr">
         <is>
-          <t>Algarve entdecken | Casa Porches</t>
+          <t>Buchen</t>
         </is>
       </c>
       <c r="G81" s="5" t="inlineStr">
         <is>
-          <t>Esplora l’Algarve | Casa Porches</t>
+          <t>Prenota</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="5" t="inlineStr">
         <is>
-          <t>explore.h1</t>
+          <t>explore.title</t>
         </is>
       </c>
       <c r="B82" s="6" t="inlineStr">
         <is>
-          <t>Explorar o Algarve</t>
+          <t>Explorar o Algarve | Casa Porches</t>
         </is>
       </c>
       <c r="C82" s="5" t="inlineStr">
         <is>
-          <t>Explore the Algarve</t>
+          <t>Explore the Algarve | Casa Porches</t>
         </is>
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>Explorar el Algarve</t>
+          <t>Explorar el Algarve | Casa Porches</t>
         </is>
       </c>
       <c r="E82" s="5" t="inlineStr">
         <is>
-          <t>Explorer l’Algarve</t>
+          <t>Explorer l’Algarve | Casa Porches</t>
         </is>
       </c>
       <c r="F82" s="5" t="inlineStr">
         <is>
-          <t>Die Algarve entdecken</t>
+          <t>Algarve entdecken | Casa Porches</t>
         </is>
       </c>
       <c r="G82" s="5" t="inlineStr">
         <is>
-          <t>Esplora l’Algarve</t>
+          <t>Esplora l’Algarve | Casa Porches</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="5" t="inlineStr">
         <is>
-          <t>explore.sub</t>
+          <t>explore.h1</t>
         </is>
       </c>
       <c r="B83" s="6" t="inlineStr">
         <is>
-          <t>Mapa, praias, restaurantes, eventos e experiências à volta da Casa Porches.</t>
+          <t>Explorar o Algarve</t>
         </is>
       </c>
       <c r="C83" s="5" t="inlineStr">
         <is>
-          <t>Map, beaches, restaurants, events and experiences around Casa Porches.</t>
+          <t>Explore the Algarve</t>
         </is>
       </c>
       <c r="D83" s="5" t="inlineStr">
         <is>
-          <t>Mapa, playas, restaurantes, eventos y experiencias alrededor de Casa Porches.</t>
+          <t>Explorar el Algarve</t>
         </is>
       </c>
       <c r="E83" s="5" t="inlineStr">
         <is>
-          <t>Carte, plages, restaurants, événements et expériences autour de la Casa Porches.</t>
+          <t>Explorer l’Algarve</t>
         </is>
       </c>
       <c r="F83" s="5" t="inlineStr">
         <is>
-          <t>Karte, Strände, Restaurants, Events und Erlebnisse rund um die Casa Porches.</t>
+          <t>Die Algarve entdecken</t>
         </is>
       </c>
       <c r="G83" s="5" t="inlineStr">
         <is>
-          <t>Mappa, spiagge, ristoranti, eventi ed esperienze intorno a Casa Porches.</t>
+          <t>Esplora l’Algarve</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="5" t="inlineStr">
         <is>
-          <t>guide.ctaTitle</t>
+          <t>explore.sub</t>
         </is>
       </c>
       <c r="B84" s="6" t="inlineStr">
         <is>
-          <t>Explorar a região</t>
+          <t>Mapa, praias, restaurantes, eventos e experiências à volta da Casa Porches.</t>
         </is>
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>Explore the area</t>
+          <t>Map, beaches, restaurants, events and experiences around Casa Porches.</t>
         </is>
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t>Explorar la zona</t>
+          <t>Mapa, playas, restaurantes, eventos y experiencias alrededor de Casa Porches.</t>
         </is>
       </c>
       <c r="E84" s="5" t="inlineStr">
         <is>
-          <t>Explorer la région</t>
+          <t>Carte, plages, restaurants, événements et expériences autour de la Casa Porches.</t>
         </is>
       </c>
       <c r="F84" s="5" t="inlineStr">
         <is>
-          <t>Die Umgebung entdecken</t>
+          <t>Karte, Strände, Restaurants, Events und Erlebnisse rund um die Casa Porches.</t>
         </is>
       </c>
       <c r="G84" s="5" t="inlineStr">
         <is>
-          <t>Esplora la zona</t>
+          <t>Mappa, spiagge, ristoranti, eventi ed esperienze intorno a Casa Porches.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="5" t="inlineStr">
         <is>
-          <t>guide.ctaText</t>
+          <t>guide.ctaTitle</t>
         </is>
       </c>
       <c r="B85" s="6" t="inlineStr">
         <is>
-          <t>Mapa interativo, praias, 40 restaurantes recomendados, eventos e atividades ao ar livre.</t>
+          <t>Explorar a região</t>
         </is>
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>Interactive map, beaches, 40 recommended restaurants, events and outdoor activities.</t>
+          <t>Explore the area</t>
         </is>
       </c>
       <c r="D85" s="5" t="inlineStr">
         <is>
-          <t>Mapa interactivo, playas, 40 restaurantes recomendados, eventos y actividades al aire libre.</t>
+          <t>Explorar la zona</t>
         </is>
       </c>
       <c r="E85" s="5" t="inlineStr">
         <is>
-          <t>Carte interactive, plages, 40 restaurants recommandés, événements et activités de plein air.</t>
+          <t>Explorer la région</t>
         </is>
       </c>
       <c r="F85" s="5" t="inlineStr">
         <is>
-          <t>Interaktive Karte, Strände, 40 Restaurant-Tipps, Events und Outdoor-Aktivitäten.</t>
+          <t>Die Umgebung entdecken</t>
         </is>
       </c>
       <c r="G85" s="5" t="inlineStr">
         <is>
-          <t>Mappa interattiva, spiagge, 40 ristoranti consigliati, eventi e attività all’aperto.</t>
+          <t>Esplora la zona</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="5" t="inlineStr">
         <is>
-          <t>guide.ctaBtn</t>
+          <t>guide.ctaText</t>
         </is>
       </c>
       <c r="B86" s="6" t="inlineStr">
         <is>
-          <t>Abrir Explorar o Algarve →</t>
+          <t>Mapa interativo, praias, mais de 40 restaurantes recomendados, eventos e atividades ao ar livre.</t>
         </is>
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>Open Explore the Algarve →</t>
+          <t>Interactive map, beaches, 40+ recommended restaurants, events and outdoor activities.</t>
         </is>
       </c>
       <c r="D86" s="5" t="inlineStr">
         <is>
-          <t>Abrir Explorar el Algarve →</t>
+          <t>Mapa interactivo, playas, más de 40 restaurantes recomendados, eventos y actividades al aire libre.</t>
         </is>
       </c>
       <c r="E86" s="5" t="inlineStr">
         <is>
-          <t>Ouvrir Explorer l’Algarve →</t>
+          <t>Carte interactive, plages, plus de 40 restaurants recommandés, événements et activités de plein air.</t>
         </is>
       </c>
       <c r="F86" s="5" t="inlineStr">
         <is>
-          <t>Algarve entdecken öffnen →</t>
+          <t>Interaktive Karte, Strände, über 40 Restaurant-Tipps, Events und Outdoor-Aktivitäten.</t>
         </is>
       </c>
       <c r="G86" s="5" t="inlineStr">
         <is>
-          <t>Apri Esplora l’Algarve →</t>
+          <t>Mappa interattiva, spiagge, oltre 40 ristoranti consigliati, eventi e attività all’aperto.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="5" t="inlineStr">
         <is>
-          <t>disclaimer</t>
+          <t>guide.ctaBtn</t>
         </is>
       </c>
       <c r="B87" s="6" t="inlineStr">
         <is>
-          <t>Informação meramente indicativa, sem valor contratual. Não dispensa a leitura das condições da plataforma de reserva (Airbnb, Booking, etc.) e das regras da HostWise, que prevalecem em caso de diferença.</t>
+          <t>Abrir Explorar o Algarve →</t>
         </is>
       </c>
       <c r="C87" s="5" t="inlineStr">
         <is>
-          <t>For information only, with no contractual value. It does not replace the terms of the booking platform (Airbnb, Booking, etc.) or HostWise’s house rules, which prevail in case of any difference.</t>
+          <t>Open Explore the Algarve →</t>
         </is>
       </c>
       <c r="D87" s="5" t="inlineStr">
         <is>
-          <t>Información meramente orientativa y sin valor contractual. No sustituye las condiciones de la plataforma de reserva (Airbnb, Booking, etc.) ni las normas de HostWise, que prevalecen en caso de diferencia.</t>
+          <t>Abrir Explorar el Algarve →</t>
         </is>
       </c>
       <c r="E87" s="5" t="inlineStr">
         <is>
-          <t>Informations purement indicatives, sans valeur contractuelle. Elles ne remplacent pas les conditions de la plateforme de réservation (Airbnb, Booking, etc.) ni le règlement de HostWise, qui prévalent en cas de divergence.</t>
+          <t>Ouvrir Explorer l’Algarve →</t>
         </is>
       </c>
       <c r="F87" s="5" t="inlineStr">
         <is>
-          <t>Nur zur Information, ohne vertragliche Bindung. Ersetzt nicht die Bedingungen der Buchungsplattform (Airbnb, Booking usw.) oder die Hausregeln von HostWise, die im Zweifel Vorrang haben.</t>
+          <t>Algarve entdecken öffnen →</t>
         </is>
       </c>
       <c r="G87" s="5" t="inlineStr">
         <is>
-          <t>Informazioni puramente indicative, senza valore contrattuale. Non sostituiscono le condizioni della piattaforma di prenotazione (Airbnb, Booking, ecc.) né le regole di HostWise, che prevalgono in caso di differenze.</t>
+          <t>Apri Esplora l’Algarve →</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="5" t="inlineStr">
         <is>
-          <t>rest.cat.near</t>
+          <t>disclaimer</t>
         </is>
       </c>
       <c r="B88" s="6" t="inlineStr">
         <is>
-          <t>Perto de casa</t>
+          <t>Informação meramente indicativa, sem valor contratual. Não dispensa a leitura das condições da plataforma de reserva (Airbnb, Booking, etc.) e das regras da HostWise, que prevalecem em caso de diferença.</t>
         </is>
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>Close to the house</t>
+          <t>For information only, with no contractual value. It does not replace the terms of the booking platform (Airbnb, Booking, etc.) or HostWise’s house rules, which prevail in case of any difference.</t>
         </is>
       </c>
       <c r="D88" s="5" t="inlineStr">
         <is>
-          <t>Cerca de casa</t>
+          <t>Información meramente orientativa y sin valor contractual. No sustituye las condiciones de la plataforma de reserva (Airbnb, Booking, etc.) ni las normas de HostWise, que prevalecen en caso de diferencia.</t>
         </is>
       </c>
       <c r="E88" s="5" t="inlineStr">
         <is>
-          <t>Près de la maison</t>
+          <t>Informations purement indicatives, sans valeur contractuelle. Elles ne remplacent pas les conditions de la plateforme de réservation (Airbnb, Booking, etc.) ni le règlement de HostWise, qui prévalent en cas de divergence.</t>
         </is>
       </c>
       <c r="F88" s="5" t="inlineStr">
         <is>
-          <t>In der Nähe</t>
+          <t>Nur zur Information, ohne vertragliche Bindung. Ersetzt nicht die Bedingungen der Buchungsplattform (Airbnb, Booking usw.) oder die Hausregeln von HostWise, die im Zweifel Vorrang haben.</t>
         </is>
       </c>
       <c r="G88" s="5" t="inlineStr">
         <is>
-          <t>Vicino a casa</t>
+          <t>Informazioni puramente indicative, senza valore contrattuale. Non sostituiscono le condizioni della piattaforma di prenotazione (Airbnb, Booking, ecc.) né le regole di HostWise, che prevalgono in caso di differenze.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="5" t="inlineStr">
         <is>
-          <t>rest.cat.michelin</t>
+          <t>hcPorches</t>
         </is>
       </c>
       <c r="B89" s="6" t="inlineStr">
         <is>
-          <t>Estrelas Michelin</t>
+          <t>Centro de Saúde de Porches</t>
         </is>
       </c>
       <c r="C89" s="5" t="inlineStr">
         <is>
-          <t>Michelin stars</t>
+          <t>Porches Health Centre</t>
         </is>
       </c>
       <c r="D89" s="5" t="inlineStr">
         <is>
-          <t>Estrellas Michelin</t>
+          <t>Centro de Salud de Porches</t>
         </is>
       </c>
       <c r="E89" s="5" t="inlineStr">
         <is>
-          <t>Étoiles Michelin</t>
+          <t>Centre de santé de Porches</t>
         </is>
       </c>
       <c r="F89" s="5" t="inlineStr">
         <is>
-          <t>Michelin-Sterne</t>
+          <t>Gesundheitszentrum Porches</t>
         </is>
       </c>
       <c r="G89" s="5" t="inlineStr">
         <is>
-          <t>Stelle Michelin</t>
+          <t>Centro sanitario di Porches</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="5" t="inlineStr">
         <is>
-          <t>rest.cat.fine</t>
+          <t>hcPorchesDesc</t>
         </is>
       </c>
       <c r="B90" s="6" t="inlineStr">
         <is>
-          <t>Requintados</t>
+          <t>Extensão do centro de saúde (SNS), na Rua da Escola, a poucos minutos a pé. Confirme o horário de atendimento.</t>
         </is>
       </c>
       <c r="C90" s="5" t="inlineStr">
         <is>
-          <t>Fine dining</t>
+          <t>Public health centre branch (SNS) on Rua da Escola, a few minutes’ walk away. Please check opening hours.</t>
         </is>
       </c>
       <c r="D90" s="5" t="inlineStr">
         <is>
-          <t>Alta cocina</t>
+          <t>Consultorio del centro de salud público (SNS) en la Rua da Escola, a pocos minutos a pie. Consulte el horario.</t>
         </is>
       </c>
       <c r="E90" s="5" t="inlineStr">
         <is>
-          <t>Raffinés</t>
+          <t>Antenne du centre de santé public (SNS), Rua da Escola, à quelques minutes à pied. Vérifiez les horaires.</t>
         </is>
       </c>
       <c r="F90" s="5" t="inlineStr">
         <is>
-          <t>Gehobene Küche</t>
+          <t>Außenstelle des öffentlichen Gesundheitszentrums (SNS) in der Rua da Escola, wenige Gehminuten entfernt. Bitte Öffnungszeiten prüfen.</t>
         </is>
       </c>
       <c r="G90" s="5" t="inlineStr">
         <is>
-          <t>Raffinati</t>
+          <t>Sede distaccata del centro sanitario pubblico (SNS) in Rua da Escola, a pochi minuti a piedi. Verificate gli orari.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="5" t="inlineStr">
         <is>
-          <t>rest.cat.wine</t>
+          <t>walk</t>
         </is>
       </c>
       <c r="B91" s="6" t="inlineStr">
         <is>
-          <t>Vinhos e petiscos</t>
+          <t>a pé</t>
         </is>
       </c>
       <c r="C91" s="5" t="inlineStr">
         <is>
-          <t>Wine &amp; small plates</t>
+          <t>on foot</t>
         </is>
       </c>
       <c r="D91" s="5" t="inlineStr">
         <is>
-          <t>Vinos y tapas</t>
+          <t>a pie</t>
         </is>
       </c>
       <c r="E91" s="5" t="inlineStr">
         <is>
-          <t>Vins &amp; petites assiettes</t>
+          <t>à pied</t>
         </is>
       </c>
       <c r="F91" s="5" t="inlineStr">
         <is>
-          <t>Wein &amp; Tapas</t>
+          <t>zu Fuß</t>
         </is>
       </c>
       <c r="G91" s="5" t="inlineStr">
         <is>
-          <t>Vini e stuzzichini</t>
+          <t>a piedi</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="5" t="inlineStr">
         <is>
-          <t>rest.cat.sea</t>
+          <t>pharmPorches</t>
         </is>
       </c>
       <c r="B92" s="6" t="inlineStr">
         <is>
-          <t>Peixe e vista mar</t>
+          <t>Farmácia em Porches, no centro da vila. Para farmácias de serviço à noite e ao fim de semana, use o Google Maps.</t>
         </is>
       </c>
       <c r="C92" s="5" t="inlineStr">
         <is>
-          <t>Seafood &amp; sea views</t>
+          <t>Pharmacy in the centre of Porches. For on-duty pharmacies at night and at weekends, use Google Maps.</t>
         </is>
       </c>
       <c r="D92" s="5" t="inlineStr">
         <is>
-          <t>Pescado y vistas al mar</t>
+          <t>Farmacia en el centro de Porches. Para farmacias de guardia por la noche y los fines de semana, use Google Maps.</t>
         </is>
       </c>
       <c r="E92" s="5" t="inlineStr">
         <is>
-          <t>Poisson &amp; vue mer</t>
+          <t>Pharmacie au centre de Porches. Pour les pharmacies de garde la nuit et le week-end, utilisez Google Maps.</t>
         </is>
       </c>
       <c r="F92" s="5" t="inlineStr">
         <is>
-          <t>Fisch &amp; Meerblick</t>
+          <t>Apotheke im Ortszentrum von Porches. Notdienst-Apotheken nachts und am Wochenende über Google Maps.</t>
         </is>
       </c>
       <c r="G92" s="5" t="inlineStr">
         <is>
-          <t>Pesce e vista mare</t>
+          <t>Farmacia nel centro di Porches. Per le farmacie di turno di notte e nel fine settimana, usate Google Maps.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="5" t="inlineStr">
         <is>
-          <t>rest.cat.trad</t>
+          <t>hospSns</t>
         </is>
       </c>
       <c r="B93" s="6" t="inlineStr">
         <is>
-          <t>Tradicionais</t>
+          <t>Hospital público com urgência 24 horas.</t>
         </is>
       </c>
       <c r="C93" s="5" t="inlineStr">
         <is>
-          <t>Traditional</t>
+          <t>Public hospital with a 24-hour emergency department.</t>
         </is>
       </c>
       <c r="D93" s="5" t="inlineStr">
         <is>
-          <t>Tradicionales</t>
+          <t>Hospital público con urgencias 24 horas.</t>
         </is>
       </c>
       <c r="E93" s="5" t="inlineStr">
         <is>
-          <t>Traditionnels</t>
+          <t>Hôpital public avec urgences 24h/24.</t>
         </is>
       </c>
       <c r="F93" s="5" t="inlineStr">
         <is>
-          <t>Traditionell</t>
+          <t>Öffentliches Krankenhaus mit 24-Stunden-Notaufnahme.</t>
         </is>
       </c>
       <c r="G93" s="5" t="inlineStr">
         <is>
-          <t>Tradizionali</t>
+          <t>Ospedale pubblico con pronto soccorso 24 ore.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="5" t="inlineStr">
         <is>
-          <t>rest.cat.intl</t>
+          <t>hospPrivate</t>
         </is>
       </c>
       <c r="B94" s="6" t="inlineStr">
         <is>
-          <t>Internacional e famílias</t>
+          <t>Hospitais privados</t>
         </is>
       </c>
       <c r="C94" s="5" t="inlineStr">
         <is>
-          <t>International &amp; families</t>
+          <t>Private hospitals</t>
         </is>
       </c>
       <c r="D94" s="5" t="inlineStr">
         <is>
-          <t>Internacional y familias</t>
+          <t>Hospitales privados</t>
         </is>
       </c>
       <c r="E94" s="5" t="inlineStr">
         <is>
-          <t>International &amp; familles</t>
+          <t>Hôpitaux privés</t>
         </is>
       </c>
       <c r="F94" s="5" t="inlineStr">
         <is>
-          <t>International &amp; Familien</t>
+          <t>Privatkliniken</t>
         </is>
       </c>
       <c r="G94" s="5" t="inlineStr">
         <is>
-          <t>Internazionale e famiglie</t>
+          <t>Ospedali privati</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="5" t="inlineStr">
         <is>
-          <t>rest.cat.cafe</t>
+          <t>hospPrivateDesc</t>
         </is>
       </c>
       <c r="B95" s="6" t="inlineStr">
         <is>
-          <t>Cafés e refeições leves</t>
+          <t>Hospital Lusíadas Albufeira (~20 min) e Hospital Particular do Algarve – Alvor (~30 min). Atendimento pago; confirme horários e seguro.</t>
         </is>
       </c>
       <c r="C95" s="5" t="inlineStr">
         <is>
-          <t>Cafés &amp; light meals</t>
+          <t>Hospital Lusíadas Albufeira (~20 min) and Hospital Particular do Algarve – Alvor (~30 min). Paid care; check hours and insurance.</t>
         </is>
       </c>
       <c r="D95" s="5" t="inlineStr">
         <is>
-          <t>Cafés y comidas ligeras</t>
+          <t>Hospital Lusíadas Albufeira (~20 min) y Hospital Particular do Algarve – Alvor (~30 min). Atención de pago; consulte horarios y seguro.</t>
         </is>
       </c>
       <c r="E95" s="5" t="inlineStr">
         <is>
-          <t>Cafés &amp; repas légers</t>
+          <t>Hospital Lusíadas Albufeira (~20 min) et Hospital Particular do Algarve – Alvor (~30 min). Soins payants ; vérifiez horaires et assurance.</t>
         </is>
       </c>
       <c r="F95" s="5" t="inlineStr">
         <is>
-          <t>Cafés &amp; leichte Küche</t>
+          <t>Hospital Lusíadas Albufeira (~20 Min.) und Hospital Particular do Algarve – Alvor (~30 Min.). Kostenpflichtig; Zeiten und Versicherung prüfen.</t>
         </is>
       </c>
       <c r="G95" s="5" t="inlineStr">
         <is>
-          <t>Caffè e pasti leggeri</t>
+          <t>Hospital Lusíadas Albufeira (~20 min) e Hospital Particular do Algarve – Alvor (~30 min). A pagamento; verificate orari e assicurazione.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="5" t="inlineStr">
         <is>
-          <t>rest.ui.all</t>
+          <t>shopsWalk</t>
         </is>
       </c>
       <c r="B96" s="6" t="inlineStr">
         <is>
-          <t>Todos</t>
+          <t>Mercearias a pé</t>
         </is>
       </c>
       <c r="C96" s="5" t="inlineStr">
         <is>
-          <t>All</t>
+          <t>Grocery shops on foot</t>
         </is>
       </c>
       <c r="D96" s="5" t="inlineStr">
         <is>
-          <t>Todos</t>
+          <t>Tiendas a pie</t>
         </is>
       </c>
       <c r="E96" s="5" t="inlineStr">
         <is>
-          <t>Tous</t>
+          <t>Épiceries à pied</t>
         </is>
       </c>
       <c r="F96" s="5" t="inlineStr">
         <is>
-          <t>Alle</t>
+          <t>Lebensmittel zu Fuß</t>
         </is>
       </c>
       <c r="G96" s="5" t="inlineStr">
         <is>
-          <t>Tutti</t>
+          <t>Alimentari a piedi</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="5" t="inlineStr">
         <is>
-          <t>rest.ui.price</t>
+          <t>shopsWalkDesc</t>
         </is>
       </c>
       <c r="B97" s="6" t="inlineStr">
         <is>
-          <t>Preço indicativo por pessoa, sem bebidas — confirme antes de reservar.</t>
+          <t>Minimercado da Vila e supermercado Laginha, a 2 minutos a pé, no centro de Porches — práticos para pão, fruta e o essencial. Para compras maiores há supermercados em Lagoa e Armação de Pêra (10 min de carro).</t>
         </is>
       </c>
       <c r="C97" s="5" t="inlineStr">
         <is>
-          <t>Approximate price per person, excluding drinks — please check before booking.</t>
+          <t>Minimercado da Vila and Laginha supermarket, a 2-minute walk away in the centre of Porches — handy for bread, fruit and essentials. For a big shop there are supermarkets in Lagoa and Armação de Pêra (10 min by car).</t>
         </is>
       </c>
       <c r="D97" s="5" t="inlineStr">
         <is>
-          <t>Precio orientativo por persona, sin bebidas; confírmelo antes de reservar.</t>
+          <t>Minimercado da Vila y el supermercado Laginha, a 2 minutos a pie en el centro de Porches: prácticos para pan, fruta y lo básico. Para compras grandes hay supermercados en Lagoa y Armação de Pêra (10 min en coche).</t>
         </is>
       </c>
       <c r="E97" s="5" t="inlineStr">
         <is>
-          <t>Prix indicatif par personne, hors boissons — à vérifier avant de réserver.</t>
+          <t>Minimercado da Vila et le supermarché Laginha, à 2 minutes à pied au centre de Porches — pratiques pour le pain, les fruits et l’essentiel. Pour les grosses courses, supermarchés à Lagoa et Armação de Pêra (10 min en voiture).</t>
         </is>
       </c>
       <c r="F97" s="5" t="inlineStr">
         <is>
-          <t>Richtpreis pro Person ohne Getränke – bitte vor der Reservierung prüfen.</t>
+          <t>Minimercado da Vila und Supermarkt Laginha, 2 Gehminuten entfernt im Ortszentrum – praktisch für Brot, Obst und das Nötigste. Für größere Einkäufe gibt es Supermärkte in Lagoa und Armação de Pêra (10 Min. mit dem Auto).</t>
         </is>
       </c>
       <c r="G97" s="5" t="inlineStr">
         <is>
-          <t>Prezzo indicativo a persona, bevande escluse: verificate prima di prenotare.</t>
+          <t>Minimercado da Vila e il supermercato Laginha, a 2 minuti a piedi nel centro di Porches: comodi per pane, frutta e l’essenziale. Per la spesa grande ci sono supermercati a Lagoa e Armação de Pêra (10 min in auto).</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="5" t="inlineStr">
         <is>
-          <t>rest.ui.near</t>
+          <t>rest.cat.near</t>
         </is>
       </c>
       <c r="B98" s="6" t="inlineStr">
@@ -4586,7 +4586,7 @@
       </c>
       <c r="C98" s="5" t="inlineStr">
         <is>
-          <t>Near the house</t>
+          <t>Close to the house</t>
         </is>
       </c>
       <c r="D98" s="5" t="inlineStr">
@@ -4613,967 +4613,1374 @@
     <row r="99">
       <c r="A99" s="5" t="inlineStr">
         <is>
-          <t>ev.cat.upcoming</t>
+          <t>rest.cat.michelin</t>
         </is>
       </c>
       <c r="B99" s="6" t="inlineStr">
         <is>
-          <t>Próximos eventos</t>
+          <t>Estrelas Michelin</t>
         </is>
       </c>
       <c r="C99" s="5" t="inlineStr">
         <is>
-          <t>Upcoming events</t>
+          <t>Michelin stars</t>
         </is>
       </c>
       <c r="D99" s="5" t="inlineStr">
         <is>
-          <t>Próximos eventos</t>
+          <t>Estrellas Michelin</t>
         </is>
       </c>
       <c r="E99" s="5" t="inlineStr">
         <is>
-          <t>Événements à venir</t>
+          <t>Étoiles Michelin</t>
         </is>
       </c>
       <c r="F99" s="5" t="inlineStr">
         <is>
-          <t>Kommende Events</t>
+          <t>Michelin-Sterne</t>
         </is>
       </c>
       <c r="G99" s="5" t="inlineStr">
         <is>
-          <t>Prossimi eventi</t>
+          <t>Stelle Michelin</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="5" t="inlineStr">
         <is>
-          <t>ev.cat.outdoor</t>
+          <t>rest.cat.fine</t>
         </is>
       </c>
       <c r="B100" s="6" t="inlineStr">
         <is>
-          <t>Atividades ao ar livre</t>
+          <t>Requintados</t>
         </is>
       </c>
       <c r="C100" s="5" t="inlineStr">
         <is>
-          <t>Outdoor activities</t>
+          <t>Fine dining</t>
         </is>
       </c>
       <c r="D100" s="5" t="inlineStr">
         <is>
-          <t>Actividades al aire libre</t>
+          <t>Alta cocina</t>
         </is>
       </c>
       <c r="E100" s="5" t="inlineStr">
         <is>
-          <t>Activités de plein air</t>
+          <t>Raffinés</t>
         </is>
       </c>
       <c r="F100" s="5" t="inlineStr">
         <is>
-          <t>Outdoor-Aktivitäten</t>
+          <t>Gehobene Küche</t>
         </is>
       </c>
       <c r="G100" s="5" t="inlineStr">
         <is>
-          <t>Attività all’aperto</t>
+          <t>Raffinati</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="5" t="inlineStr">
         <is>
-          <t>ev.cat.nature</t>
+          <t>rest.cat.wine</t>
         </is>
       </c>
       <c r="B101" s="6" t="inlineStr">
         <is>
-          <t>Natureza e praias</t>
+          <t>Vinhos e petiscos</t>
         </is>
       </c>
       <c r="C101" s="5" t="inlineStr">
         <is>
-          <t>Nature &amp; beaches</t>
+          <t>Wine &amp; small plates</t>
         </is>
       </c>
       <c r="D101" s="5" t="inlineStr">
         <is>
-          <t>Naturaleza y playas</t>
+          <t>Vinos y tapas</t>
         </is>
       </c>
       <c r="E101" s="5" t="inlineStr">
         <is>
-          <t>Nature &amp; plages</t>
+          <t>Vins &amp; petites assiettes</t>
         </is>
       </c>
       <c r="F101" s="5" t="inlineStr">
         <is>
-          <t>Natur &amp; Strände</t>
+          <t>Wein &amp; Tapas</t>
         </is>
       </c>
       <c r="G101" s="5" t="inlineStr">
         <is>
-          <t>Natura e spiagge</t>
+          <t>Vini e stuzzichini</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="5" t="inlineStr">
         <is>
-          <t>ev.cat.sea</t>
+          <t>rest.cat.sea</t>
         </is>
       </c>
       <c r="B102" s="6" t="inlineStr">
         <is>
-          <t>Mar e aventura</t>
+          <t>Peixe e vista mar</t>
         </is>
       </c>
       <c r="C102" s="5" t="inlineStr">
         <is>
-          <t>Sea &amp; adventure</t>
+          <t>Seafood &amp; sea views</t>
         </is>
       </c>
       <c r="D102" s="5" t="inlineStr">
         <is>
-          <t>Mar y aventura</t>
+          <t>Pescado y vistas al mar</t>
         </is>
       </c>
       <c r="E102" s="5" t="inlineStr">
         <is>
-          <t>Mer &amp; aventure</t>
+          <t>Poisson &amp; vue mer</t>
         </is>
       </c>
       <c r="F102" s="5" t="inlineStr">
         <is>
-          <t>Meer &amp; Abenteuer</t>
+          <t>Fisch &amp; Meerblick</t>
         </is>
       </c>
       <c r="G102" s="5" t="inlineStr">
         <is>
-          <t>Mare e avventura</t>
+          <t>Pesce e vista mare</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="5" t="inlineStr">
         <is>
-          <t>ev.cat.events</t>
+          <t>rest.cat.trad</t>
         </is>
       </c>
       <c r="B103" s="6" t="inlineStr">
         <is>
-          <t>Festivais e festas anuais</t>
+          <t>Tradicionais</t>
         </is>
       </c>
       <c r="C103" s="5" t="inlineStr">
         <is>
-          <t>Annual festivals</t>
+          <t>Traditional</t>
         </is>
       </c>
       <c r="D103" s="5" t="inlineStr">
         <is>
-          <t>Festivales y fiestas anuales</t>
+          <t>Tradicionales</t>
         </is>
       </c>
       <c r="E103" s="5" t="inlineStr">
         <is>
-          <t>Festivals et fêtes annuels</t>
+          <t>Traditionnels</t>
         </is>
       </c>
       <c r="F103" s="5" t="inlineStr">
         <is>
-          <t>Jährliche Feste &amp; Festivals</t>
+          <t>Traditionell</t>
         </is>
       </c>
       <c r="G103" s="5" t="inlineStr">
         <is>
-          <t>Festival e feste annuali</t>
+          <t>Tradizionali</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="5" t="inlineStr">
         <is>
-          <t>ev.cat.water</t>
+          <t>rest.cat.intl</t>
         </is>
       </c>
       <c r="B104" s="6" t="inlineStr">
         <is>
-          <t>Parques e atrações familiares</t>
+          <t>Internacional e famílias</t>
         </is>
       </c>
       <c r="C104" s="5" t="inlineStr">
         <is>
-          <t>Water &amp; theme parks</t>
+          <t>International &amp; families</t>
         </is>
       </c>
       <c r="D104" s="5" t="inlineStr">
         <is>
-          <t>Parques y atracciones familiares</t>
+          <t>Internacional y familias</t>
         </is>
       </c>
       <c r="E104" s="5" t="inlineStr">
         <is>
-          <t>Parcs et attractions familiales</t>
+          <t>International &amp; familles</t>
         </is>
       </c>
       <c r="F104" s="5" t="inlineStr">
         <is>
-          <t>Wasser- &amp; Freizeitparks</t>
+          <t>International &amp; Familien</t>
         </is>
       </c>
       <c r="G104" s="5" t="inlineStr">
         <is>
-          <t>Parchi e attrazioni per famiglie</t>
+          <t>Internazionale e famiglie</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="5" t="inlineStr">
         <is>
-          <t>ev.cat.indoor</t>
+          <t>rest.cat.cafe</t>
         </is>
       </c>
       <c r="B105" s="6" t="inlineStr">
         <is>
-          <t>Piscinas e dias de chuva</t>
+          <t>Cafés e refeições leves</t>
         </is>
       </c>
       <c r="C105" s="5" t="inlineStr">
         <is>
-          <t>Indoor &amp; rainy days</t>
+          <t>Cafés &amp; light meals</t>
         </is>
       </c>
       <c r="D105" s="5" t="inlineStr">
         <is>
-          <t>Piscinas y días de lluvia</t>
+          <t>Cafés y comidas ligeras</t>
         </is>
       </c>
       <c r="E105" s="5" t="inlineStr">
         <is>
-          <t>Piscines &amp; jours de pluie</t>
+          <t>Cafés &amp; repas légers</t>
         </is>
       </c>
       <c r="F105" s="5" t="inlineStr">
         <is>
-          <t>Hallenbäder &amp; Regentage</t>
+          <t>Cafés &amp; leichte Küche</t>
         </is>
       </c>
       <c r="G105" s="5" t="inlineStr">
         <is>
-          <t>Piscine e giorni di pioggia</t>
+          <t>Caffè e pasti leggeri</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="5" t="inlineStr">
         <is>
-          <t>ev.cat.markets</t>
+          <t>rest.ui.all</t>
         </is>
       </c>
       <c r="B106" s="6" t="inlineStr">
         <is>
-          <t>Mercados e tradições</t>
+          <t>Todos</t>
         </is>
       </c>
       <c r="C106" s="5" t="inlineStr">
         <is>
-          <t>Markets &amp; traditions</t>
+          <t>All</t>
         </is>
       </c>
       <c r="D106" s="5" t="inlineStr">
         <is>
-          <t>Mercados y tradiciones</t>
+          <t>Todos</t>
         </is>
       </c>
       <c r="E106" s="5" t="inlineStr">
         <is>
-          <t>Marchés &amp; traditions</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="F106" s="5" t="inlineStr">
         <is>
-          <t>Märkte &amp; Traditionen</t>
+          <t>Alle</t>
         </is>
       </c>
       <c r="G106" s="5" t="inlineStr">
         <is>
-          <t>Mercati e tradizioni</t>
+          <t>Tutti</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="5" t="inlineStr">
         <is>
-          <t>ev.tag.fam</t>
+          <t>rest.ui.price</t>
         </is>
       </c>
       <c r="B107" s="6" t="inlineStr">
         <is>
-          <t>Famílias</t>
+          <t>Preço indicativo por pessoa, sem bebidas — confirme antes de reservar.</t>
         </is>
       </c>
       <c r="C107" s="5" t="inlineStr">
         <is>
-          <t>Families</t>
+          <t>Approximate price per person, excluding drinks — please check before booking.</t>
         </is>
       </c>
       <c r="D107" s="5" t="inlineStr">
         <is>
-          <t>Familias</t>
+          <t>Precio orientativo por persona, sin bebidas; confírmelo antes de reservar.</t>
         </is>
       </c>
       <c r="E107" s="5" t="inlineStr">
         <is>
-          <t>Familles</t>
+          <t>Prix indicatif par personne, hors boissons — à vérifier avant de réserver.</t>
         </is>
       </c>
       <c r="F107" s="5" t="inlineStr">
         <is>
-          <t>Familien</t>
+          <t>Richtpreis pro Person ohne Getränke – bitte vor der Reservierung prüfen.</t>
         </is>
       </c>
       <c r="G107" s="5" t="inlineStr">
         <is>
-          <t>Famiglie</t>
+          <t>Prezzo indicativo a persona, bevande escluse: verificate prima di prenotare.</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="5" t="inlineStr">
         <is>
-          <t>ev.tag.teen</t>
+          <t>rest.ui.near</t>
         </is>
       </c>
       <c r="B108" s="6" t="inlineStr">
         <is>
-          <t>Jovens</t>
+          <t>Perto de casa</t>
         </is>
       </c>
       <c r="C108" s="5" t="inlineStr">
         <is>
-          <t>Teens</t>
+          <t>Near the house</t>
         </is>
       </c>
       <c r="D108" s="5" t="inlineStr">
         <is>
-          <t>Jóvenes</t>
+          <t>Cerca de casa</t>
         </is>
       </c>
       <c r="E108" s="5" t="inlineStr">
         <is>
-          <t>Ados</t>
+          <t>Près de la maison</t>
         </is>
       </c>
       <c r="F108" s="5" t="inlineStr">
         <is>
-          <t>Jugendliche</t>
+          <t>In der Nähe</t>
         </is>
       </c>
       <c r="G108" s="5" t="inlineStr">
         <is>
-          <t>Ragazzi</t>
+          <t>Vicino a casa</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="5" t="inlineStr">
         <is>
-          <t>ev.tag.couple</t>
+          <t>ev.cat.upcoming</t>
         </is>
       </c>
       <c r="B109" s="6" t="inlineStr">
         <is>
-          <t>Casais</t>
+          <t>Próximos eventos</t>
         </is>
       </c>
       <c r="C109" s="5" t="inlineStr">
         <is>
-          <t>Couples</t>
+          <t>Upcoming events</t>
         </is>
       </c>
       <c r="D109" s="5" t="inlineStr">
         <is>
-          <t>Parejas</t>
+          <t>Próximos eventos</t>
         </is>
       </c>
       <c r="E109" s="5" t="inlineStr">
         <is>
-          <t>Couples</t>
+          <t>Événements à venir</t>
         </is>
       </c>
       <c r="F109" s="5" t="inlineStr">
         <is>
-          <t>Paare</t>
+          <t>Kommende Events</t>
         </is>
       </c>
       <c r="G109" s="5" t="inlineStr">
         <is>
-          <t>Coppie</t>
+          <t>Prossimi eventi</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="5" t="inlineStr">
         <is>
-          <t>ev.tag.food</t>
+          <t>ev.cat.outdoor</t>
         </is>
       </c>
       <c r="B110" s="6" t="inlineStr">
         <is>
-          <t>Gastronomia</t>
+          <t>Atividades ao ar livre</t>
         </is>
       </c>
       <c r="C110" s="5" t="inlineStr">
         <is>
-          <t>Food &amp; drink</t>
+          <t>Outdoor activities</t>
         </is>
       </c>
       <c r="D110" s="5" t="inlineStr">
         <is>
-          <t>Gastronomía</t>
+          <t>Actividades al aire libre</t>
         </is>
       </c>
       <c r="E110" s="5" t="inlineStr">
         <is>
-          <t>Gastronomie</t>
+          <t>Activités de plein air</t>
         </is>
       </c>
       <c r="F110" s="5" t="inlineStr">
         <is>
-          <t>Kulinarik</t>
+          <t>Outdoor-Aktivitäten</t>
         </is>
       </c>
       <c r="G110" s="5" t="inlineStr">
         <is>
-          <t>Gastronomia</t>
+          <t>Attività all’aperto</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="5" t="inlineStr">
         <is>
-          <t>ev.tag.free</t>
+          <t>ev.cat.nature</t>
         </is>
       </c>
       <c r="B111" s="6" t="inlineStr">
         <is>
-          <t>Natureza / grátis</t>
+          <t>Natureza e praias</t>
         </is>
       </c>
       <c r="C111" s="5" t="inlineStr">
         <is>
-          <t>Nature / free</t>
+          <t>Nature &amp; beaches</t>
         </is>
       </c>
       <c r="D111" s="5" t="inlineStr">
         <is>
-          <t>Naturaleza / gratis</t>
+          <t>Naturaleza y playas</t>
         </is>
       </c>
       <c r="E111" s="5" t="inlineStr">
         <is>
-          <t>Nature / gratuit</t>
+          <t>Nature &amp; plages</t>
         </is>
       </c>
       <c r="F111" s="5" t="inlineStr">
         <is>
-          <t>Natur / gratis</t>
+          <t>Natur &amp; Strände</t>
         </is>
       </c>
       <c r="G111" s="5" t="inlineStr">
         <is>
-          <t>Natura / gratis</t>
+          <t>Natura e spiagge</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="5" t="inlineStr">
         <is>
-          <t>ev.tag.winter</t>
+          <t>ev.cat.cities</t>
         </is>
       </c>
       <c r="B112" s="6" t="inlineStr">
         <is>
-          <t>Outono e inverno</t>
+          <t>Vilas e cidades</t>
         </is>
       </c>
       <c r="C112" s="5" t="inlineStr">
         <is>
-          <t>Autumn &amp; winter</t>
+          <t>Towns &amp; sightseeing</t>
         </is>
       </c>
       <c r="D112" s="5" t="inlineStr">
         <is>
-          <t>Otoño e invierno</t>
+          <t>Pueblos y ciudades</t>
         </is>
       </c>
       <c r="E112" s="5" t="inlineStr">
         <is>
-          <t>Automne &amp; hiver</t>
+          <t>Villes &amp; villages</t>
         </is>
       </c>
       <c r="F112" s="5" t="inlineStr">
         <is>
-          <t>Herbst &amp; Winter</t>
+          <t>Orte &amp; Sehenswertes</t>
         </is>
       </c>
       <c r="G112" s="5" t="inlineStr">
         <is>
-          <t>Autunno e inverno</t>
+          <t>Paesi e città</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="5" t="inlineStr">
         <is>
-          <t>ev.ui.title</t>
+          <t>ev.cat.sea</t>
         </is>
       </c>
       <c r="B113" s="6" t="inlineStr">
         <is>
-          <t>Eventos e experiências</t>
+          <t>Mar e aventura</t>
         </is>
       </c>
       <c r="C113" s="5" t="inlineStr">
         <is>
-          <t>Events &amp; experiences</t>
+          <t>Sea &amp; adventure</t>
         </is>
       </c>
       <c r="D113" s="5" t="inlineStr">
         <is>
-          <t>Eventos y experiencias</t>
+          <t>Mar y aventura</t>
         </is>
       </c>
       <c r="E113" s="5" t="inlineStr">
         <is>
-          <t>Événements &amp; expériences</t>
+          <t>Mer &amp; aventure</t>
         </is>
       </c>
       <c r="F113" s="5" t="inlineStr">
         <is>
-          <t>Events &amp; Erlebnisse</t>
+          <t>Meer &amp; Abenteuer</t>
         </is>
       </c>
       <c r="G113" s="5" t="inlineStr">
         <is>
-          <t>Eventi ed esperienze</t>
+          <t>Mare e avventura</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="5" t="inlineStr">
         <is>
-          <t>ev.ui.forWho</t>
+          <t>ev.cat.events</t>
         </is>
       </c>
       <c r="B114" s="6" t="inlineStr">
         <is>
-          <t>Para quem:</t>
+          <t>Festivais e festas anuais</t>
         </is>
       </c>
       <c r="C114" s="5" t="inlineStr">
         <is>
-          <t>Best for:</t>
+          <t>Annual festivals</t>
         </is>
       </c>
       <c r="D114" s="5" t="inlineStr">
         <is>
-          <t>Para quién:</t>
+          <t>Festivales y fiestas anuales</t>
         </is>
       </c>
       <c r="E114" s="5" t="inlineStr">
         <is>
-          <t>Pour qui :</t>
+          <t>Festivals et fêtes annuels</t>
         </is>
       </c>
       <c r="F114" s="5" t="inlineStr">
         <is>
-          <t>Ideal für:</t>
+          <t>Jährliche Feste &amp; Festivals</t>
         </is>
       </c>
       <c r="G114" s="5" t="inlineStr">
         <is>
-          <t>Per chi:</t>
+          <t>Festival e feste annuali</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="5" t="inlineStr">
         <is>
-          <t>ev.ui.anyone</t>
+          <t>ev.cat.water</t>
         </is>
       </c>
       <c r="B115" s="6" t="inlineStr">
         <is>
-          <t>Todos</t>
+          <t>Parques e atrações familiares</t>
         </is>
       </c>
       <c r="C115" s="5" t="inlineStr">
         <is>
-          <t>Everyone</t>
+          <t>Water &amp; theme parks</t>
         </is>
       </c>
       <c r="D115" s="5" t="inlineStr">
         <is>
-          <t>Todos</t>
+          <t>Parques y atracciones familiares</t>
         </is>
       </c>
       <c r="E115" s="5" t="inlineStr">
         <is>
-          <t>Tous</t>
+          <t>Parcs et attractions familiales</t>
         </is>
       </c>
       <c r="F115" s="5" t="inlineStr">
         <is>
-          <t>Alle</t>
+          <t>Wasser- &amp; Freizeitparks</t>
         </is>
       </c>
       <c r="G115" s="5" t="inlineStr">
         <is>
-          <t>Tutti</t>
+          <t>Parchi e attrazioni per famiglie</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="5" t="inlineStr">
         <is>
-          <t>ev.ui.confirmed</t>
+          <t>ev.cat.indoor</t>
         </is>
       </c>
       <c r="B116" s="6" t="inlineStr">
         <is>
-          <t>Confirmado</t>
+          <t>Piscinas e dias de chuva</t>
         </is>
       </c>
       <c r="C116" s="5" t="inlineStr">
         <is>
-          <t>Confirmed</t>
+          <t>Indoor &amp; rainy days</t>
         </is>
       </c>
       <c r="D116" s="5" t="inlineStr">
         <is>
-          <t>Confirmado</t>
+          <t>Piscinas y días de lluvia</t>
         </is>
       </c>
       <c r="E116" s="5" t="inlineStr">
         <is>
-          <t>Confirmé</t>
+          <t>Piscines &amp; jours de pluie</t>
         </is>
       </c>
       <c r="F116" s="5" t="inlineStr">
         <is>
-          <t>Bestätigt</t>
+          <t>Hallenbäder &amp; Regentage</t>
         </is>
       </c>
       <c r="G116" s="5" t="inlineStr">
         <is>
-          <t>Confermato</t>
+          <t>Piscine e giorni di pioggia</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="5" t="inlineStr">
         <is>
-          <t>ev.ui.usually</t>
+          <t>ev.cat.markets</t>
         </is>
       </c>
       <c r="B117" s="6" t="inlineStr">
         <is>
-          <t>Habitualmente</t>
+          <t>Mercados e tradições</t>
         </is>
       </c>
       <c r="C117" s="5" t="inlineStr">
         <is>
-          <t>Usually</t>
+          <t>Markets &amp; traditions</t>
         </is>
       </c>
       <c r="D117" s="5" t="inlineStr">
         <is>
-          <t>Normalmente</t>
+          <t>Mercados y tradiciones</t>
         </is>
       </c>
       <c r="E117" s="5" t="inlineStr">
         <is>
-          <t>Habituellement</t>
+          <t>Marchés &amp; traditions</t>
         </is>
       </c>
       <c r="F117" s="5" t="inlineStr">
         <is>
-          <t>Üblicherweise</t>
+          <t>Märkte &amp; Traditionen</t>
         </is>
       </c>
       <c r="G117" s="5" t="inlineStr">
         <is>
-          <t>Di solito</t>
+          <t>Mercati e tradizioni</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="5" t="inlineStr">
         <is>
-          <t>ev.ui.last</t>
+          <t>ev.tag.fam</t>
         </is>
       </c>
       <c r="B118" s="6" t="inlineStr">
         <is>
-          <t>Última edição</t>
+          <t>Famílias</t>
         </is>
       </c>
       <c r="C118" s="5" t="inlineStr">
         <is>
-          <t>Last edition</t>
+          <t>Families</t>
         </is>
       </c>
       <c r="D118" s="5" t="inlineStr">
         <is>
-          <t>Última edición</t>
+          <t>Familias</t>
         </is>
       </c>
       <c r="E118" s="5" t="inlineStr">
         <is>
-          <t>Dernière édition</t>
+          <t>Familles</t>
         </is>
       </c>
       <c r="F118" s="5" t="inlineStr">
         <is>
-          <t>Letzte Ausgabe</t>
+          <t>Familien</t>
         </is>
       </c>
       <c r="G118" s="5" t="inlineStr">
         <is>
-          <t>Ultima edizione</t>
+          <t>Famiglie</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="5" t="inlineStr">
         <is>
-          <t>ev.ui.now</t>
+          <t>ev.tag.teen</t>
         </is>
       </c>
       <c r="B119" s="6" t="inlineStr">
         <is>
-          <t>A decorrer</t>
+          <t>Jovens</t>
         </is>
       </c>
       <c r="C119" s="5" t="inlineStr">
         <is>
-          <t>On now</t>
+          <t>Teens</t>
         </is>
       </c>
       <c r="D119" s="5" t="inlineStr">
         <is>
-          <t>En curso</t>
+          <t>Jóvenes</t>
         </is>
       </c>
       <c r="E119" s="5" t="inlineStr">
         <is>
-          <t>En cours</t>
+          <t>Ados</t>
         </is>
       </c>
       <c r="F119" s="5" t="inlineStr">
         <is>
-          <t>Läuft gerade</t>
+          <t>Jugendliche</t>
         </is>
       </c>
       <c r="G119" s="5" t="inlineStr">
         <is>
-          <t>In corso</t>
+          <t>Ragazzi</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="5" t="inlineStr">
         <is>
-          <t>ev.ui.fromHouse</t>
+          <t>ev.tag.couple</t>
         </is>
       </c>
       <c r="B120" s="6" t="inlineStr">
         <is>
-          <t>da casa</t>
+          <t>Casais</t>
         </is>
       </c>
       <c r="C120" s="5" t="inlineStr">
         <is>
-          <t>from the house</t>
+          <t>Couples</t>
         </is>
       </c>
       <c r="D120" s="5" t="inlineStr">
         <is>
-          <t>desde la casa</t>
+          <t>Parejas</t>
         </is>
       </c>
       <c r="E120" s="5" t="inlineStr">
         <is>
-          <t>de la maison</t>
+          <t>Couples</t>
         </is>
       </c>
       <c r="F120" s="5" t="inlineStr">
         <is>
-          <t>vom Haus</t>
+          <t>Paare</t>
         </is>
       </c>
       <c r="G120" s="5" t="inlineStr">
         <is>
-          <t>dalla casa</t>
+          <t>Coppie</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="5" t="inlineStr">
         <is>
-          <t>ev.ui.inPorches</t>
+          <t>ev.tag.food</t>
         </is>
       </c>
       <c r="B121" s="6" t="inlineStr">
         <is>
-          <t>Em Porches</t>
+          <t>Gastronomia</t>
         </is>
       </c>
       <c r="C121" s="5" t="inlineStr">
         <is>
-          <t>In Porches</t>
+          <t>Food &amp; drink</t>
         </is>
       </c>
       <c r="D121" s="5" t="inlineStr">
         <is>
-          <t>En Porches</t>
+          <t>Gastronomía</t>
         </is>
       </c>
       <c r="E121" s="5" t="inlineStr">
         <is>
-          <t>À Porches</t>
+          <t>Gastronomie</t>
         </is>
       </c>
       <c r="F121" s="5" t="inlineStr">
         <is>
-          <t>In Porches</t>
+          <t>Kulinarik</t>
         </is>
       </c>
       <c r="G121" s="5" t="inlineStr">
         <is>
-          <t>A Porches</t>
+          <t>Gastronomia</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="5" t="inlineStr">
         <is>
-          <t>ev.ui.website</t>
+          <t>ev.tag.free</t>
         </is>
       </c>
       <c r="B122" s="6" t="inlineStr">
         <is>
-          <t>Website</t>
+          <t>Natureza / grátis</t>
         </is>
       </c>
       <c r="C122" s="5" t="inlineStr">
         <is>
-          <t>Website</t>
+          <t>Nature / free</t>
         </is>
       </c>
       <c r="D122" s="5" t="inlineStr">
         <is>
-          <t>Web</t>
+          <t>Naturaleza / gratis</t>
         </is>
       </c>
       <c r="E122" s="5" t="inlineStr">
         <is>
-          <t>Site web</t>
+          <t>Nature / gratuit</t>
         </is>
       </c>
       <c r="F122" s="5" t="inlineStr">
         <is>
-          <t>Website</t>
+          <t>Natur / gratis</t>
         </is>
       </c>
       <c r="G122" s="5" t="inlineStr">
         <is>
-          <t>Sito web</t>
+          <t>Natura / gratis</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="5" t="inlineStr">
         <is>
-          <t>ev.ui.none</t>
+          <t>ev.tag.winter</t>
         </is>
       </c>
       <c r="B123" s="6" t="inlineStr">
         <is>
-          <t>Nada para mostrar com estes filtros.</t>
+          <t>Outono e inverno</t>
         </is>
       </c>
       <c r="C123" s="5" t="inlineStr">
         <is>
-          <t>Nothing to show with these filters.</t>
+          <t>Autumn &amp; winter</t>
         </is>
       </c>
       <c r="D123" s="5" t="inlineStr">
         <is>
-          <t>No hay resultados con estos filtros.</t>
+          <t>Otoño e invierno</t>
         </is>
       </c>
       <c r="E123" s="5" t="inlineStr">
         <is>
-          <t>Aucun résultat avec ces filtres.</t>
+          <t>Automne &amp; hiver</t>
         </is>
       </c>
       <c r="F123" s="5" t="inlineStr">
         <is>
-          <t>Keine Ergebnisse mit diesen Filtern.</t>
+          <t>Herbst &amp; Winter</t>
         </is>
       </c>
       <c r="G123" s="5" t="inlineStr">
         <is>
-          <t>Nessun risultato con questi filtri.</t>
+          <t>Autunno e inverno</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="5" t="inlineStr">
         <is>
+          <t>ev.ui.title</t>
+        </is>
+      </c>
+      <c r="B124" s="6" t="inlineStr">
+        <is>
+          <t>Eventos e experiências</t>
+        </is>
+      </c>
+      <c r="C124" s="5" t="inlineStr">
+        <is>
+          <t>Events &amp; experiences</t>
+        </is>
+      </c>
+      <c r="D124" s="5" t="inlineStr">
+        <is>
+          <t>Eventos y experiencias</t>
+        </is>
+      </c>
+      <c r="E124" s="5" t="inlineStr">
+        <is>
+          <t>Événements &amp; expériences</t>
+        </is>
+      </c>
+      <c r="F124" s="5" t="inlineStr">
+        <is>
+          <t>Events &amp; Erlebnisse</t>
+        </is>
+      </c>
+      <c r="G124" s="5" t="inlineStr">
+        <is>
+          <t>Eventi ed esperienze</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="5" t="inlineStr">
+        <is>
+          <t>ev.ui.forWho</t>
+        </is>
+      </c>
+      <c r="B125" s="6" t="inlineStr">
+        <is>
+          <t>Para quem:</t>
+        </is>
+      </c>
+      <c r="C125" s="5" t="inlineStr">
+        <is>
+          <t>Best for:</t>
+        </is>
+      </c>
+      <c r="D125" s="5" t="inlineStr">
+        <is>
+          <t>Para quién:</t>
+        </is>
+      </c>
+      <c r="E125" s="5" t="inlineStr">
+        <is>
+          <t>Pour qui :</t>
+        </is>
+      </c>
+      <c r="F125" s="5" t="inlineStr">
+        <is>
+          <t>Ideal für:</t>
+        </is>
+      </c>
+      <c r="G125" s="5" t="inlineStr">
+        <is>
+          <t>Per chi:</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="5" t="inlineStr">
+        <is>
+          <t>ev.ui.anyone</t>
+        </is>
+      </c>
+      <c r="B126" s="6" t="inlineStr">
+        <is>
+          <t>Todos</t>
+        </is>
+      </c>
+      <c r="C126" s="5" t="inlineStr">
+        <is>
+          <t>Everyone</t>
+        </is>
+      </c>
+      <c r="D126" s="5" t="inlineStr">
+        <is>
+          <t>Todos</t>
+        </is>
+      </c>
+      <c r="E126" s="5" t="inlineStr">
+        <is>
+          <t>Tous</t>
+        </is>
+      </c>
+      <c r="F126" s="5" t="inlineStr">
+        <is>
+          <t>Alle</t>
+        </is>
+      </c>
+      <c r="G126" s="5" t="inlineStr">
+        <is>
+          <t>Tutti</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="5" t="inlineStr">
+        <is>
+          <t>ev.ui.confirmed</t>
+        </is>
+      </c>
+      <c r="B127" s="6" t="inlineStr">
+        <is>
+          <t>Confirmado</t>
+        </is>
+      </c>
+      <c r="C127" s="5" t="inlineStr">
+        <is>
+          <t>Confirmed</t>
+        </is>
+      </c>
+      <c r="D127" s="5" t="inlineStr">
+        <is>
+          <t>Confirmado</t>
+        </is>
+      </c>
+      <c r="E127" s="5" t="inlineStr">
+        <is>
+          <t>Confirmé</t>
+        </is>
+      </c>
+      <c r="F127" s="5" t="inlineStr">
+        <is>
+          <t>Bestätigt</t>
+        </is>
+      </c>
+      <c r="G127" s="5" t="inlineStr">
+        <is>
+          <t>Confermato</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="5" t="inlineStr">
+        <is>
+          <t>ev.ui.usually</t>
+        </is>
+      </c>
+      <c r="B128" s="6" t="inlineStr">
+        <is>
+          <t>Habitualmente</t>
+        </is>
+      </c>
+      <c r="C128" s="5" t="inlineStr">
+        <is>
+          <t>Usually</t>
+        </is>
+      </c>
+      <c r="D128" s="5" t="inlineStr">
+        <is>
+          <t>Normalmente</t>
+        </is>
+      </c>
+      <c r="E128" s="5" t="inlineStr">
+        <is>
+          <t>Habituellement</t>
+        </is>
+      </c>
+      <c r="F128" s="5" t="inlineStr">
+        <is>
+          <t>Üblicherweise</t>
+        </is>
+      </c>
+      <c r="G128" s="5" t="inlineStr">
+        <is>
+          <t>Di solito</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="5" t="inlineStr">
+        <is>
+          <t>ev.ui.last</t>
+        </is>
+      </c>
+      <c r="B129" s="6" t="inlineStr">
+        <is>
+          <t>Última edição</t>
+        </is>
+      </c>
+      <c r="C129" s="5" t="inlineStr">
+        <is>
+          <t>Last edition</t>
+        </is>
+      </c>
+      <c r="D129" s="5" t="inlineStr">
+        <is>
+          <t>Última edición</t>
+        </is>
+      </c>
+      <c r="E129" s="5" t="inlineStr">
+        <is>
+          <t>Dernière édition</t>
+        </is>
+      </c>
+      <c r="F129" s="5" t="inlineStr">
+        <is>
+          <t>Letzte Ausgabe</t>
+        </is>
+      </c>
+      <c r="G129" s="5" t="inlineStr">
+        <is>
+          <t>Ultima edizione</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="5" t="inlineStr">
+        <is>
+          <t>ev.ui.now</t>
+        </is>
+      </c>
+      <c r="B130" s="6" t="inlineStr">
+        <is>
+          <t>A decorrer</t>
+        </is>
+      </c>
+      <c r="C130" s="5" t="inlineStr">
+        <is>
+          <t>On now</t>
+        </is>
+      </c>
+      <c r="D130" s="5" t="inlineStr">
+        <is>
+          <t>En curso</t>
+        </is>
+      </c>
+      <c r="E130" s="5" t="inlineStr">
+        <is>
+          <t>En cours</t>
+        </is>
+      </c>
+      <c r="F130" s="5" t="inlineStr">
+        <is>
+          <t>Läuft gerade</t>
+        </is>
+      </c>
+      <c r="G130" s="5" t="inlineStr">
+        <is>
+          <t>In corso</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="5" t="inlineStr">
+        <is>
+          <t>ev.ui.fromHouse</t>
+        </is>
+      </c>
+      <c r="B131" s="6" t="inlineStr">
+        <is>
+          <t>da casa</t>
+        </is>
+      </c>
+      <c r="C131" s="5" t="inlineStr">
+        <is>
+          <t>from the house</t>
+        </is>
+      </c>
+      <c r="D131" s="5" t="inlineStr">
+        <is>
+          <t>desde la casa</t>
+        </is>
+      </c>
+      <c r="E131" s="5" t="inlineStr">
+        <is>
+          <t>de la maison</t>
+        </is>
+      </c>
+      <c r="F131" s="5" t="inlineStr">
+        <is>
+          <t>vom Haus</t>
+        </is>
+      </c>
+      <c r="G131" s="5" t="inlineStr">
+        <is>
+          <t>dalla casa</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="5" t="inlineStr">
+        <is>
+          <t>ev.ui.inPorches</t>
+        </is>
+      </c>
+      <c r="B132" s="6" t="inlineStr">
+        <is>
+          <t>Em Porches</t>
+        </is>
+      </c>
+      <c r="C132" s="5" t="inlineStr">
+        <is>
+          <t>In Porches</t>
+        </is>
+      </c>
+      <c r="D132" s="5" t="inlineStr">
+        <is>
+          <t>En Porches</t>
+        </is>
+      </c>
+      <c r="E132" s="5" t="inlineStr">
+        <is>
+          <t>À Porches</t>
+        </is>
+      </c>
+      <c r="F132" s="5" t="inlineStr">
+        <is>
+          <t>In Porches</t>
+        </is>
+      </c>
+      <c r="G132" s="5" t="inlineStr">
+        <is>
+          <t>A Porches</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="5" t="inlineStr">
+        <is>
+          <t>ev.ui.website</t>
+        </is>
+      </c>
+      <c r="B133" s="6" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
+      <c r="C133" s="5" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
+      <c r="D133" s="5" t="inlineStr">
+        <is>
+          <t>Web</t>
+        </is>
+      </c>
+      <c r="E133" s="5" t="inlineStr">
+        <is>
+          <t>Site web</t>
+        </is>
+      </c>
+      <c r="F133" s="5" t="inlineStr">
+        <is>
+          <t>Website</t>
+        </is>
+      </c>
+      <c r="G133" s="5" t="inlineStr">
+        <is>
+          <t>Sito web</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="5" t="inlineStr">
+        <is>
+          <t>ev.ui.none</t>
+        </is>
+      </c>
+      <c r="B134" s="6" t="inlineStr">
+        <is>
+          <t>Nada para mostrar com estes filtros.</t>
+        </is>
+      </c>
+      <c r="C134" s="5" t="inlineStr">
+        <is>
+          <t>Nothing to show with these filters.</t>
+        </is>
+      </c>
+      <c r="D134" s="5" t="inlineStr">
+        <is>
+          <t>No hay resultados con estos filtros.</t>
+        </is>
+      </c>
+      <c r="E134" s="5" t="inlineStr">
+        <is>
+          <t>Aucun résultat avec ces filtres.</t>
+        </is>
+      </c>
+      <c r="F134" s="5" t="inlineStr">
+        <is>
+          <t>Keine Ergebnisse mit diesen Filtern.</t>
+        </is>
+      </c>
+      <c r="G134" s="5" t="inlineStr">
+        <is>
+          <t>Nessun risultato con questi filtri.</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="5" t="inlineStr">
+        <is>
           <t>ev.ui.note</t>
         </is>
       </c>
-      <c r="B124" s="6" t="inlineStr">
+      <c r="B135" s="6" t="inlineStr">
         <is>
           <t>Datas, horários e preços são indicativos — confirme sempre com os organizadores. Distâncias aproximadas por estrada.</t>
         </is>
       </c>
-      <c r="C124" s="5" t="inlineStr">
+      <c r="C135" s="5" t="inlineStr">
         <is>
           <t>Dates, times and prices are indicative — always check with the organisers. Road distances are approximate.</t>
         </is>
       </c>
-      <c r="D124" s="5" t="inlineStr">
+      <c r="D135" s="5" t="inlineStr">
         <is>
           <t>Fechas, horarios y precios son orientativos; confírmelos siempre con los organizadores. Distancias aproximadas por carretera.</t>
         </is>
       </c>
-      <c r="E124" s="5" t="inlineStr">
+      <c r="E135" s="5" t="inlineStr">
         <is>
           <t>Dates, horaires et prix indicatifs — vérifiez toujours auprès des organisateurs. Distances routières approximatives.</t>
         </is>
       </c>
-      <c r="F124" s="5" t="inlineStr">
+      <c r="F135" s="5" t="inlineStr">
         <is>
           <t>Termine, Zeiten und Preise ohne Gewähr – bitte immer beim Veranstalter prüfen. Straßenentfernungen ca.</t>
         </is>
       </c>
-      <c r="G124" s="5" t="inlineStr">
+      <c r="G135" s="5" t="inlineStr">
         <is>
           <t>Date, orari e prezzi indicativi: verificate sempre con gli organizzatori. Distanze stradali approssimative.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G124"/>
+  <autoFilter ref="A1:G135"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5585,7 +5992,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q41"/>
+  <dimension ref="A1:Q47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -8694,8 +9101,458 @@
         </is>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>trad</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>O Marinheiro</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="inlineStr">
+        <is>
+          <t>Sesmarias (Praia da Coelha), Albufeira</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>€€–€€€</t>
+        </is>
+      </c>
+      <c r="F42" s="5" t="inlineStr">
+        <is>
+          <t>O Marinheiro Albufeira</t>
+        </is>
+      </c>
+      <c r="G42" s="5" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="H42" s="5" t="inlineStr">
+        <is>
+          <t>🐟</t>
+        </is>
+      </c>
+      <c r="I42" s="5" t="inlineStr"/>
+      <c r="J42" s="5" t="n">
+        <v>37.07967</v>
+      </c>
+      <c r="K42" s="5" t="n">
+        <v>-8.29176</v>
+      </c>
+      <c r="L42" s="6" t="inlineStr">
+        <is>
+          <t>Cozinha tradicional portuguesa perto da Praia da Coelha. Muito bem avaliado (Google 4,7 · 2 mil opiniões).</t>
+        </is>
+      </c>
+      <c r="M42" s="5" t="inlineStr">
+        <is>
+          <t>Traditional Portuguese cooking near Praia da Coelha. Very highly rated (Google 4.7 · 2,000 reviews).</t>
+        </is>
+      </c>
+      <c r="N42" s="5" t="inlineStr">
+        <is>
+          <t>Cocina tradicional portuguesa cerca de la Praia da Coelha. Muy bien valorado (Google 4,7 · 2.000 opiniones).</t>
+        </is>
+      </c>
+      <c r="O42" s="5" t="inlineStr">
+        <is>
+          <t>Cuisine portugaise traditionnelle près de la Praia da Coelha. Très bien noté (Google 4,7 · 2 000 avis).</t>
+        </is>
+      </c>
+      <c r="P42" s="5" t="inlineStr">
+        <is>
+          <t>Traditionelle portugiesische Küche nahe der Praia da Coelha. Sehr gut bewertet (Google 4,7 · 2.000 Bewertungen).</t>
+        </is>
+      </c>
+      <c r="Q42" s="5" t="inlineStr">
+        <is>
+          <t>Cucina tradizionale portoghese vicino alla Praia da Coelha. Ottime recensioni (Google 4,7 · 2.000).</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>fine</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>Versatile</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>Olhos de Água, Albufeira</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>€€€</t>
+        </is>
+      </c>
+      <c r="F43" s="5" t="inlineStr">
+        <is>
+          <t>Versatile Restaurante Olhos de Água</t>
+        </is>
+      </c>
+      <c r="G43" s="5" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="H43" s="5" t="inlineStr"/>
+      <c r="I43" s="5" t="inlineStr"/>
+      <c r="J43" s="5" t="n">
+        <v>37.09379</v>
+      </c>
+      <c r="K43" s="5" t="n">
+        <v>-8.192539999999999</v>
+      </c>
+      <c r="L43" s="6" t="inlineStr">
+        <is>
+          <t>Cozinha de autor portuguesa contemporânea. Excelente avaliação (Google 4,8). Reserva obrigatória.</t>
+        </is>
+      </c>
+      <c r="M43" s="5" t="inlineStr">
+        <is>
+          <t>Contemporary Portuguese signature cuisine. Excellent rating (Google 4.8). Booking required.</t>
+        </is>
+      </c>
+      <c r="N43" s="5" t="inlineStr">
+        <is>
+          <t>Cocina de autor portuguesa contemporánea. Valoración excelente (Google 4,8). Reserva obligatoria.</t>
+        </is>
+      </c>
+      <c r="O43" s="5" t="inlineStr">
+        <is>
+          <t>Cuisine d’auteur portugaise contemporaine. Excellente note (Google 4,8). Réservation obligatoire.</t>
+        </is>
+      </c>
+      <c r="P43" s="5" t="inlineStr">
+        <is>
+          <t>Moderne portugiesische Autorenküche. Hervorragend bewertet (Google 4,8). Reservierung erforderlich.</t>
+        </is>
+      </c>
+      <c r="Q43" s="5" t="inlineStr">
+        <is>
+          <t>Cucina d’autore portoghese contemporanea. Valutazione eccellente (Google 4,8). Prenotazione obbligatoria.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>fine</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>Windmill (só adultos)</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="inlineStr">
+        <is>
+          <t>Albufeira (cidade)</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="inlineStr">
+        <is>
+          <t>€€€</t>
+        </is>
+      </c>
+      <c r="F44" s="5" t="inlineStr">
+        <is>
+          <t>Windmill Adults Only Albufeira</t>
+        </is>
+      </c>
+      <c r="G44" s="5" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="H44" s="5" t="inlineStr">
+        <is>
+          <t>🌬️</t>
+        </is>
+      </c>
+      <c r="I44" s="5" t="inlineStr"/>
+      <c r="J44" s="5" t="n"/>
+      <c r="K44" s="5" t="n"/>
+      <c r="L44" s="6" t="inlineStr">
+        <is>
+          <t>Jantar num antigo moinho de vento com vista sobre Albufeira. Só para adultos; reserva obrigatória (Google 4,7).</t>
+        </is>
+      </c>
+      <c r="M44" s="5" t="inlineStr">
+        <is>
+          <t>Dinner in an old windmill overlooking Albufeira. Adults only; booking required (Google 4.7).</t>
+        </is>
+      </c>
+      <c r="N44" s="5" t="inlineStr">
+        <is>
+          <t>Cena en un antiguo molino con vistas a Albufeira. Solo adultos; reserva obligatoria (Google 4,7).</t>
+        </is>
+      </c>
+      <c r="O44" s="5" t="inlineStr">
+        <is>
+          <t>Dîner dans un ancien moulin à vent dominant Albufeira. Adultes uniquement ; réservation obligatoire (Google 4,7).</t>
+        </is>
+      </c>
+      <c r="P44" s="5" t="inlineStr">
+        <is>
+          <t>Dinner in einer alten Windmühle über Albufeira. Nur für Erwachsene; Reservierung erforderlich (Google 4,7).</t>
+        </is>
+      </c>
+      <c r="Q44" s="5" t="inlineStr">
+        <is>
+          <t>Cena in un antico mulino a vento con vista su Albufeira. Solo adulti; prenotazione obbligatoria (Google 4,7).</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>sea</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>Jardim Rústico</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>Oura, Albufeira</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="inlineStr">
+        <is>
+          <t>€€–€€€</t>
+        </is>
+      </c>
+      <c r="F45" s="5" t="inlineStr">
+        <is>
+          <t>Jardim Rústico Albufeira</t>
+        </is>
+      </c>
+      <c r="G45" s="5" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="H45" s="5" t="inlineStr"/>
+      <c r="I45" s="5" t="inlineStr"/>
+      <c r="J45" s="5" t="n"/>
+      <c r="K45" s="5" t="n"/>
+      <c r="L45" s="6" t="inlineStr">
+        <is>
+          <t>Marisco, peixe grelhado e cataplanas, com esplanada e noites de fado. Travellers’ Choice 2026 (Google 4,6).</t>
+        </is>
+      </c>
+      <c r="M45" s="5" t="inlineStr">
+        <is>
+          <t>Seafood, grilled fish and cataplanas, with a terrace and fado nights. Travellers’ Choice 2026 (Google 4.6).</t>
+        </is>
+      </c>
+      <c r="N45" s="5" t="inlineStr">
+        <is>
+          <t>Marisco, pescado a la parrilla y cataplanas, con terraza y noches de fado. Travellers’ Choice 2026 (Google 4,6).</t>
+        </is>
+      </c>
+      <c r="O45" s="5" t="inlineStr">
+        <is>
+          <t>Fruits de mer, poisson grillé et cataplanas, terrasse et soirées fado. Travellers’ Choice 2026 (Google 4,6).</t>
+        </is>
+      </c>
+      <c r="P45" s="5" t="inlineStr">
+        <is>
+          <t>Meeresfrüchte, gegrillter Fisch und Cataplanas, mit Terrasse und Fado-Abenden. Travellers’ Choice 2026 (Google 4,6).</t>
+        </is>
+      </c>
+      <c r="Q45" s="5" t="inlineStr">
+        <is>
+          <t>Frutti di mare, pesce alla griglia e cataplane, con terrazza e serate di fado. Travellers’ Choice 2026 (Google 4,6).</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>wine</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>Taberna Vicentina</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="inlineStr">
+        <is>
+          <t>Centro histórico, Albufeira</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="inlineStr">
+        <is>
+          <t>€€</t>
+        </is>
+      </c>
+      <c r="F46" s="5" t="inlineStr">
+        <is>
+          <t>Taberna Vicentina Albufeira</t>
+        </is>
+      </c>
+      <c r="G46" s="5" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="H46" s="5" t="inlineStr"/>
+      <c r="I46" s="5" t="inlineStr"/>
+      <c r="J46" s="5" t="n"/>
+      <c r="K46" s="5" t="n"/>
+      <c r="L46" s="6" t="inlineStr">
+        <is>
+          <t>Petiscos portugueses no centro histórico, junto à Praia dos Pescadores (Google 4,6 · 1,5 mil opiniões).</t>
+        </is>
+      </c>
+      <c r="M46" s="5" t="inlineStr">
+        <is>
+          <t>Portuguese small plates in the old town, by Praia dos Pescadores (Google 4.6 · 1,500 reviews).</t>
+        </is>
+      </c>
+      <c r="N46" s="5" t="inlineStr">
+        <is>
+          <t>Tapas portuguesas en el casco antiguo, junto a la Praia dos Pescadores (Google 4,6 · 1.500 opiniones).</t>
+        </is>
+      </c>
+      <c r="O46" s="5" t="inlineStr">
+        <is>
+          <t>Petites assiettes portugaises dans la vieille ville, près de la Praia dos Pescadores (Google 4,6 · 1 500 avis).</t>
+        </is>
+      </c>
+      <c r="P46" s="5" t="inlineStr">
+        <is>
+          <t>Portugiesische Tapas in der Altstadt bei der Praia dos Pescadores (Google 4,6 · 1.500 Bewertungen).</t>
+        </is>
+      </c>
+      <c r="Q46" s="5" t="inlineStr">
+        <is>
+          <t>Stuzzichini portoghesi nel centro storico, vicino alla Praia dos Pescadores (Google 4,6 · 1.500 recensioni).</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>trad</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>não</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>Mato à Vista</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>Cabanita, Paderne (Albufeira)</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="inlineStr">
+        <is>
+          <t>€€€</t>
+        </is>
+      </c>
+      <c r="F47" s="5" t="inlineStr">
+        <is>
+          <t>Mato à Vista Paderne</t>
+        </is>
+      </c>
+      <c r="G47" s="5" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="H47" s="5" t="inlineStr">
+        <is>
+          <t>🌳</t>
+        </is>
+      </c>
+      <c r="I47" s="5" t="inlineStr"/>
+      <c r="J47" s="5" t="n">
+        <v>37.1944</v>
+      </c>
+      <c r="K47" s="5" t="n">
+        <v>-8.222390000000001</v>
+      </c>
+      <c r="L47" s="6" t="inlineStr">
+        <is>
+          <t>Restaurante no campo, com lareira e esplanada, cozinha portuguesa (Google 4,5 · 2,2 mil opiniões). Reserve.</t>
+        </is>
+      </c>
+      <c r="M47" s="5" t="inlineStr">
+        <is>
+          <t>Countryside restaurant with fireplace and terrace, Portuguese cooking (Google 4.5 · 2,200 reviews). Book ahead.</t>
+        </is>
+      </c>
+      <c r="N47" s="5" t="inlineStr">
+        <is>
+          <t>Restaurante de campo con chimenea y terraza, cocina portuguesa (Google 4,5 · 2.200 opiniones). Reserve.</t>
+        </is>
+      </c>
+      <c r="O47" s="5" t="inlineStr">
+        <is>
+          <t>Restaurant à la campagne avec cheminée et terrasse, cuisine portugaise (Google 4,5 · 2 200 avis). Réservez.</t>
+        </is>
+      </c>
+      <c r="P47" s="5" t="inlineStr">
+        <is>
+          <t>Landrestaurant mit Kamin und Terrasse, portugiesische Küche (Google 4,5 · 2.200 Bewertungen). Reservieren.</t>
+        </is>
+      </c>
+      <c r="Q47" s="5" t="inlineStr">
+        <is>
+          <t>Ristorante in campagna con camino e terrazza, cucina portoghese (Google 4,5 · 2.200 recensioni). Prenotate.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:Q41"/>
+  <autoFilter ref="A1:Q47"/>
   <dataValidations count="3">
     <dataValidation sqref="A2:A500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Escolha um valor da lista" type="list">
       <formula1>"michelin,fine,wine,sea,trad,intl,cafe"</formula1>
@@ -8718,7 +9575,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG76"/>
+  <dimension ref="A1:AG82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -9896,8 +10753,12 @@
         </is>
       </c>
       <c r="M11" s="5" t="inlineStr"/>
-      <c r="N11" s="5" t="n"/>
-      <c r="O11" s="5" t="n"/>
+      <c r="N11" s="5" t="n">
+        <v>37.11658</v>
+      </c>
+      <c r="O11" s="5" t="n">
+        <v>-8.529640000000001</v>
+      </c>
       <c r="P11" s="6" t="inlineStr">
         <is>
           <t>Cervejas internacionais, comida de rua e música na Fortaleza de Santa Catarina, Praia da Rocha.</t>
@@ -17004,11 +17865,677 @@
         </is>
       </c>
     </row>
+    <row r="77">
+      <c r="A77" s="5" t="inlineStr">
+        <is>
+          <t>cities</t>
+        </is>
+      </c>
+      <c r="B77" s="5" t="inlineStr">
+        <is>
+          <t>albufeira</t>
+        </is>
+      </c>
+      <c r="C77" s="5" t="inlineStr">
+        <is>
+          <t>Centro histórico de Albufeira e Praia dos Pescadores</t>
+        </is>
+      </c>
+      <c r="D77" s="7" t="n"/>
+      <c r="E77" s="7" t="n"/>
+      <c r="F77" s="7" t="n"/>
+      <c r="G77" s="7" t="n"/>
+      <c r="H77" s="5" t="inlineStr">
+        <is>
+          <t>couple, fam, free</t>
+        </is>
+      </c>
+      <c r="I77" s="5" t="inlineStr"/>
+      <c r="J77" s="5" t="inlineStr"/>
+      <c r="K77" s="5" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="L77" s="5" t="inlineStr">
+        <is>
+          <t>🏘️</t>
+        </is>
+      </c>
+      <c r="M77" s="5" t="inlineStr"/>
+      <c r="N77" s="5" t="n">
+        <v>37.08698</v>
+      </c>
+      <c r="O77" s="5" t="n">
+        <v>-8.24823</v>
+      </c>
+      <c r="P77" s="6" t="inlineStr">
+        <is>
+          <t>Ruas brancas, a Praia dos Pescadores e o miradouro do Pau da Bandeira, com vista sobre a baía. Animado à noite.</t>
+        </is>
+      </c>
+      <c r="Q77" s="5" t="inlineStr">
+        <is>
+          <t>White streets, Fishermen’s Beach and the Pau da Bandeira viewpoint over the bay. Lively at night.</t>
+        </is>
+      </c>
+      <c r="R77" s="5" t="inlineStr">
+        <is>
+          <t>Calles blancas, la Playa de los Pescadores y el mirador de Pau da Bandeira sobre la bahía. Animado de noche.</t>
+        </is>
+      </c>
+      <c r="S77" s="5" t="inlineStr">
+        <is>
+          <t>Ruelles blanches, la plage des Pêcheurs et le belvédère de Pau da Bandeira sur la baie. Animé le soir.</t>
+        </is>
+      </c>
+      <c r="T77" s="5" t="inlineStr">
+        <is>
+          <t>Weiße Gassen, der Fischerstrand und der Aussichtspunkt Pau da Bandeira über der Bucht. Abends lebhaft.</t>
+        </is>
+      </c>
+      <c r="U77" s="5" t="inlineStr">
+        <is>
+          <t>Vicoli bianchi, la spiaggia dei Pescatori e il belvedere di Pau da Bandeira sulla baia. Vivace la sera.</t>
+        </is>
+      </c>
+      <c r="V77" s="6" t="inlineStr"/>
+      <c r="W77" s="5" t="inlineStr"/>
+      <c r="X77" s="5" t="inlineStr"/>
+      <c r="Y77" s="5" t="inlineStr"/>
+      <c r="Z77" s="5" t="inlineStr"/>
+      <c r="AA77" s="5" t="inlineStr"/>
+      <c r="AB77" s="6" t="inlineStr">
+        <is>
+          <t>Todo o ano</t>
+        </is>
+      </c>
+      <c r="AC77" s="5" t="inlineStr">
+        <is>
+          <t>All year round</t>
+        </is>
+      </c>
+      <c r="AD77" s="5" t="inlineStr">
+        <is>
+          <t>Todo el año</t>
+        </is>
+      </c>
+      <c r="AE77" s="5" t="inlineStr">
+        <is>
+          <t>Toute l’année</t>
+        </is>
+      </c>
+      <c r="AF77" s="5" t="inlineStr">
+        <is>
+          <t>Ganzjährig</t>
+        </is>
+      </c>
+      <c r="AG77" s="5" t="inlineStr">
+        <is>
+          <t>Tutto l’anno</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="5" t="inlineStr">
+        <is>
+          <t>cities</t>
+        </is>
+      </c>
+      <c r="B78" s="5" t="inlineStr">
+        <is>
+          <t>albufeira</t>
+        </is>
+      </c>
+      <c r="C78" s="5" t="inlineStr">
+        <is>
+          <t>Marina de Albufeira</t>
+        </is>
+      </c>
+      <c r="D78" s="7" t="n"/>
+      <c r="E78" s="7" t="n"/>
+      <c r="F78" s="7" t="n"/>
+      <c r="G78" s="7" t="n"/>
+      <c r="H78" s="5" t="inlineStr">
+        <is>
+          <t>fam, couple</t>
+        </is>
+      </c>
+      <c r="I78" s="5" t="inlineStr"/>
+      <c r="J78" s="5" t="inlineStr"/>
+      <c r="K78" s="5" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="L78" s="5" t="inlineStr">
+        <is>
+          <t>⛵</t>
+        </is>
+      </c>
+      <c r="M78" s="5" t="inlineStr"/>
+      <c r="N78" s="5" t="n">
+        <v>37.08649</v>
+      </c>
+      <c r="O78" s="5" t="n">
+        <v>-8.267010000000001</v>
+      </c>
+      <c r="P78" s="6" t="inlineStr">
+        <is>
+          <t>Marina colorida com restaurantes e esplanadas; ponto de partida de passeios de barco e golfinhos.</t>
+        </is>
+      </c>
+      <c r="Q78" s="5" t="inlineStr">
+        <is>
+          <t>Colourful marina with restaurants and terraces; departure point for boat and dolphin trips.</t>
+        </is>
+      </c>
+      <c r="R78" s="5" t="inlineStr">
+        <is>
+          <t>Puerto deportivo colorido con restaurantes y terrazas; salida de paseos en barco y avistamiento de delfines.</t>
+        </is>
+      </c>
+      <c r="S78" s="5" t="inlineStr">
+        <is>
+          <t>Marina colorée avec restaurants et terrasses ; départ des sorties en bateau et dauphins.</t>
+        </is>
+      </c>
+      <c r="T78" s="5" t="inlineStr">
+        <is>
+          <t>Bunte Marina mit Restaurants und Terrassen; Start für Boots- und Delfintouren.</t>
+        </is>
+      </c>
+      <c r="U78" s="5" t="inlineStr">
+        <is>
+          <t>Marina colorata con ristoranti e terrazze; partenza di gite in barca e delfini.</t>
+        </is>
+      </c>
+      <c r="V78" s="6" t="inlineStr"/>
+      <c r="W78" s="5" t="inlineStr"/>
+      <c r="X78" s="5" t="inlineStr"/>
+      <c r="Y78" s="5" t="inlineStr"/>
+      <c r="Z78" s="5" t="inlineStr"/>
+      <c r="AA78" s="5" t="inlineStr"/>
+      <c r="AB78" s="6" t="inlineStr">
+        <is>
+          <t>Todo o ano</t>
+        </is>
+      </c>
+      <c r="AC78" s="5" t="inlineStr">
+        <is>
+          <t>All year round</t>
+        </is>
+      </c>
+      <c r="AD78" s="5" t="inlineStr">
+        <is>
+          <t>Todo el año</t>
+        </is>
+      </c>
+      <c r="AE78" s="5" t="inlineStr">
+        <is>
+          <t>Toute l’année</t>
+        </is>
+      </c>
+      <c r="AF78" s="5" t="inlineStr">
+        <is>
+          <t>Ganzjährig</t>
+        </is>
+      </c>
+      <c r="AG78" s="5" t="inlineStr">
+        <is>
+          <t>Tutto l’anno</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="5" t="inlineStr">
+        <is>
+          <t>cities</t>
+        </is>
+      </c>
+      <c r="B79" s="5" t="inlineStr">
+        <is>
+          <t>portimao</t>
+        </is>
+      </c>
+      <c r="C79" s="5" t="inlineStr">
+        <is>
+          <t>Praia da Rocha e Fortaleza de Santa Catarina</t>
+        </is>
+      </c>
+      <c r="D79" s="7" t="n"/>
+      <c r="E79" s="7" t="n"/>
+      <c r="F79" s="7" t="n"/>
+      <c r="G79" s="7" t="n"/>
+      <c r="H79" s="5" t="inlineStr">
+        <is>
+          <t>couple, free</t>
+        </is>
+      </c>
+      <c r="I79" s="5" t="inlineStr"/>
+      <c r="J79" s="5" t="inlineStr"/>
+      <c r="K79" s="5" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="L79" s="5" t="inlineStr">
+        <is>
+          <t>🏰</t>
+        </is>
+      </c>
+      <c r="M79" s="5" t="inlineStr"/>
+      <c r="N79" s="5" t="n">
+        <v>37.11658</v>
+      </c>
+      <c r="O79" s="5" t="n">
+        <v>-8.529640000000001</v>
+      </c>
+      <c r="P79" s="6" t="inlineStr">
+        <is>
+          <t>Miradouro da fortaleza sobre a praia e a foz do Arade; marginal com bares e restaurantes.</t>
+        </is>
+      </c>
+      <c r="Q79" s="5" t="inlineStr">
+        <is>
+          <t>Fortress viewpoint over the beach and the Arade estuary; promenade with bars and restaurants.</t>
+        </is>
+      </c>
+      <c r="R79" s="5" t="inlineStr">
+        <is>
+          <t>Mirador de la fortaleza sobre la playa y la desembocadura del Arade; paseo con bares y restaurantes.</t>
+        </is>
+      </c>
+      <c r="S79" s="5" t="inlineStr">
+        <is>
+          <t>Belvédère de la forteresse sur la plage et l’estuaire de l’Arade ; promenade avec bars et restaurants.</t>
+        </is>
+      </c>
+      <c r="T79" s="5" t="inlineStr">
+        <is>
+          <t>Aussicht von der Festung über Strand und Arade-Mündung; Promenade mit Bars und Restaurants.</t>
+        </is>
+      </c>
+      <c r="U79" s="5" t="inlineStr">
+        <is>
+          <t>Belvedere della fortezza sulla spiaggia e la foce dell’Arade; lungomare con bar e ristoranti.</t>
+        </is>
+      </c>
+      <c r="V79" s="6" t="inlineStr"/>
+      <c r="W79" s="5" t="inlineStr"/>
+      <c r="X79" s="5" t="inlineStr"/>
+      <c r="Y79" s="5" t="inlineStr"/>
+      <c r="Z79" s="5" t="inlineStr"/>
+      <c r="AA79" s="5" t="inlineStr"/>
+      <c r="AB79" s="6" t="inlineStr">
+        <is>
+          <t>Todo o ano</t>
+        </is>
+      </c>
+      <c r="AC79" s="5" t="inlineStr">
+        <is>
+          <t>All year round</t>
+        </is>
+      </c>
+      <c r="AD79" s="5" t="inlineStr">
+        <is>
+          <t>Todo el año</t>
+        </is>
+      </c>
+      <c r="AE79" s="5" t="inlineStr">
+        <is>
+          <t>Toute l’année</t>
+        </is>
+      </c>
+      <c r="AF79" s="5" t="inlineStr">
+        <is>
+          <t>Ganzjährig</t>
+        </is>
+      </c>
+      <c r="AG79" s="5" t="inlineStr">
+        <is>
+          <t>Tutto l’anno</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="5" t="inlineStr">
+        <is>
+          <t>cities</t>
+        </is>
+      </c>
+      <c r="B80" s="5" t="inlineStr">
+        <is>
+          <t>ferragudo</t>
+        </is>
+      </c>
+      <c r="C80" s="5" t="inlineStr">
+        <is>
+          <t>Ferragudo</t>
+        </is>
+      </c>
+      <c r="D80" s="7" t="n"/>
+      <c r="E80" s="7" t="n"/>
+      <c r="F80" s="7" t="n"/>
+      <c r="G80" s="7" t="n"/>
+      <c r="H80" s="5" t="inlineStr">
+        <is>
+          <t>couple, fam, free</t>
+        </is>
+      </c>
+      <c r="I80" s="5" t="inlineStr"/>
+      <c r="J80" s="5" t="inlineStr"/>
+      <c r="K80" s="5" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="L80" s="5" t="inlineStr">
+        <is>
+          <t>🎣</t>
+        </is>
+      </c>
+      <c r="M80" s="5" t="inlineStr"/>
+      <c r="N80" s="5" t="n">
+        <v>37.124</v>
+      </c>
+      <c r="O80" s="5" t="n">
+        <v>-8.519</v>
+      </c>
+      <c r="P80" s="6" t="inlineStr">
+        <is>
+          <t>Vila piscatória à beira do rio Arade, com ruas estreitas e peixe grelhado junto ao cais.</t>
+        </is>
+      </c>
+      <c r="Q80" s="5" t="inlineStr">
+        <is>
+          <t>Fishing village on the Arade river, with narrow streets and grilled fish by the quay.</t>
+        </is>
+      </c>
+      <c r="R80" s="5" t="inlineStr">
+        <is>
+          <t>Pueblo pesquero junto al río Arade, con calles estrechas y pescado a la parrilla junto al muelle.</t>
+        </is>
+      </c>
+      <c r="S80" s="5" t="inlineStr">
+        <is>
+          <t>Village de pêcheurs au bord de l’Arade, ruelles et poisson grillé sur le quai.</t>
+        </is>
+      </c>
+      <c r="T80" s="5" t="inlineStr">
+        <is>
+          <t>Fischerdorf am Arade mit engen Gassen und gegrilltem Fisch am Kai.</t>
+        </is>
+      </c>
+      <c r="U80" s="5" t="inlineStr">
+        <is>
+          <t>Borgo di pescatori sul fiume Arade, vicoli stretti e pesce alla griglia sul molo.</t>
+        </is>
+      </c>
+      <c r="V80" s="6" t="inlineStr"/>
+      <c r="W80" s="5" t="inlineStr"/>
+      <c r="X80" s="5" t="inlineStr"/>
+      <c r="Y80" s="5" t="inlineStr"/>
+      <c r="Z80" s="5" t="inlineStr"/>
+      <c r="AA80" s="5" t="inlineStr"/>
+      <c r="AB80" s="6" t="inlineStr">
+        <is>
+          <t>Todo o ano</t>
+        </is>
+      </c>
+      <c r="AC80" s="5" t="inlineStr">
+        <is>
+          <t>All year round</t>
+        </is>
+      </c>
+      <c r="AD80" s="5" t="inlineStr">
+        <is>
+          <t>Todo el año</t>
+        </is>
+      </c>
+      <c r="AE80" s="5" t="inlineStr">
+        <is>
+          <t>Toute l’année</t>
+        </is>
+      </c>
+      <c r="AF80" s="5" t="inlineStr">
+        <is>
+          <t>Ganzjährig</t>
+        </is>
+      </c>
+      <c r="AG80" s="5" t="inlineStr">
+        <is>
+          <t>Tutto l’anno</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="5" t="inlineStr">
+        <is>
+          <t>cities</t>
+        </is>
+      </c>
+      <c r="B81" s="5" t="inlineStr">
+        <is>
+          <t>carvoeiro</t>
+        </is>
+      </c>
+      <c r="C81" s="5" t="inlineStr">
+        <is>
+          <t>Carvoeiro</t>
+        </is>
+      </c>
+      <c r="D81" s="7" t="n"/>
+      <c r="E81" s="7" t="n"/>
+      <c r="F81" s="7" t="n"/>
+      <c r="G81" s="7" t="n"/>
+      <c r="H81" s="5" t="inlineStr">
+        <is>
+          <t>couple, fam, free</t>
+        </is>
+      </c>
+      <c r="I81" s="5" t="inlineStr"/>
+      <c r="J81" s="5" t="inlineStr"/>
+      <c r="K81" s="5" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="L81" s="5" t="inlineStr">
+        <is>
+          <t>🏖️</t>
+        </is>
+      </c>
+      <c r="M81" s="5" t="inlineStr"/>
+      <c r="N81" s="5" t="n">
+        <v>37.0966</v>
+      </c>
+      <c r="O81" s="5" t="n">
+        <v>-8.4717</v>
+      </c>
+      <c r="P81" s="6" t="inlineStr">
+        <is>
+          <t>Vila de casas brancas à volta de uma pequena praia, com passadiço nas falésias até ao Algar Seco.</t>
+        </is>
+      </c>
+      <c r="Q81" s="5" t="inlineStr">
+        <is>
+          <t>Village of white houses around a small beach, with a clifftop boardwalk to Algar Seco.</t>
+        </is>
+      </c>
+      <c r="R81" s="5" t="inlineStr">
+        <is>
+          <t>Pueblo de casas blancas alrededor de una pequeña playa, con pasarela sobre los acantilados hasta Algar Seco.</t>
+        </is>
+      </c>
+      <c r="S81" s="5" t="inlineStr">
+        <is>
+          <t>Village de maisons blanches autour d’une petite plage, avec promenade sur les falaises jusqu’à Algar Seco.</t>
+        </is>
+      </c>
+      <c r="T81" s="5" t="inlineStr">
+        <is>
+          <t>Ort mit weißen Häusern um einen kleinen Strand, mit Klippenweg nach Algar Seco.</t>
+        </is>
+      </c>
+      <c r="U81" s="5" t="inlineStr">
+        <is>
+          <t>Paese di case bianche intorno a una piccola spiaggia, con passerella sulle falesie fino ad Algar Seco.</t>
+        </is>
+      </c>
+      <c r="V81" s="6" t="inlineStr"/>
+      <c r="W81" s="5" t="inlineStr"/>
+      <c r="X81" s="5" t="inlineStr"/>
+      <c r="Y81" s="5" t="inlineStr"/>
+      <c r="Z81" s="5" t="inlineStr"/>
+      <c r="AA81" s="5" t="inlineStr"/>
+      <c r="AB81" s="6" t="inlineStr">
+        <is>
+          <t>Todo o ano</t>
+        </is>
+      </c>
+      <c r="AC81" s="5" t="inlineStr">
+        <is>
+          <t>All year round</t>
+        </is>
+      </c>
+      <c r="AD81" s="5" t="inlineStr">
+        <is>
+          <t>Todo el año</t>
+        </is>
+      </c>
+      <c r="AE81" s="5" t="inlineStr">
+        <is>
+          <t>Toute l’année</t>
+        </is>
+      </c>
+      <c r="AF81" s="5" t="inlineStr">
+        <is>
+          <t>Ganzjährig</t>
+        </is>
+      </c>
+      <c r="AG81" s="5" t="inlineStr">
+        <is>
+          <t>Tutto l’anno</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="5" t="inlineStr">
+        <is>
+          <t>indoor</t>
+        </is>
+      </c>
+      <c r="B82" s="5" t="inlineStr">
+        <is>
+          <t>portimao</t>
+        </is>
+      </c>
+      <c r="C82" s="5" t="inlineStr">
+        <is>
+          <t>Museu de Portimão</t>
+        </is>
+      </c>
+      <c r="D82" s="7" t="n"/>
+      <c r="E82" s="7" t="n"/>
+      <c r="F82" s="7" t="n"/>
+      <c r="G82" s="7" t="n"/>
+      <c r="H82" s="5" t="inlineStr">
+        <is>
+          <t>fam, winter</t>
+        </is>
+      </c>
+      <c r="I82" s="5" t="inlineStr"/>
+      <c r="J82" s="5" t="inlineStr"/>
+      <c r="K82" s="5" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="L82" s="5" t="inlineStr">
+        <is>
+          <t>🏛️</t>
+        </is>
+      </c>
+      <c r="M82" s="5" t="inlineStr"/>
+      <c r="N82" s="5" t="n">
+        <v>37.13067</v>
+      </c>
+      <c r="O82" s="5" t="n">
+        <v>-8.53457</v>
+      </c>
+      <c r="P82" s="6" t="inlineStr">
+        <is>
+          <t>Antiga fábrica de conservas transformada em museu premiado sobre a história e a pesca da região. Ótimo em dias de chuva.</t>
+        </is>
+      </c>
+      <c r="Q82" s="5" t="inlineStr">
+        <is>
+          <t>Former fish cannery turned award-winning museum on the region’s history and fishing. Great on rainy days.</t>
+        </is>
+      </c>
+      <c r="R82" s="5" t="inlineStr">
+        <is>
+          <t>Antigua conservera convertida en museo premiado sobre la historia y la pesca de la región. Ideal en días de lluvia.</t>
+        </is>
+      </c>
+      <c r="S82" s="5" t="inlineStr">
+        <is>
+          <t>Ancienne conserverie devenue musée primé sur l’histoire et la pêche de la région. Idéal par temps de pluie.</t>
+        </is>
+      </c>
+      <c r="T82" s="5" t="inlineStr">
+        <is>
+          <t>Ehemalige Fischkonservenfabrik, heute preisgekröntes Museum über Geschichte und Fischerei. Ideal bei Regen.</t>
+        </is>
+      </c>
+      <c r="U82" s="5" t="inlineStr">
+        <is>
+          <t>Ex conservificio diventato museo premiato sulla storia e la pesca della regione. Ottimo nei giorni di pioggia.</t>
+        </is>
+      </c>
+      <c r="V82" s="6" t="inlineStr"/>
+      <c r="W82" s="5" t="inlineStr"/>
+      <c r="X82" s="5" t="inlineStr"/>
+      <c r="Y82" s="5" t="inlineStr"/>
+      <c r="Z82" s="5" t="inlineStr"/>
+      <c r="AA82" s="5" t="inlineStr"/>
+      <c r="AB82" s="6" t="inlineStr">
+        <is>
+          <t>Todo o ano</t>
+        </is>
+      </c>
+      <c r="AC82" s="5" t="inlineStr">
+        <is>
+          <t>All year round</t>
+        </is>
+      </c>
+      <c r="AD82" s="5" t="inlineStr">
+        <is>
+          <t>Todo el año</t>
+        </is>
+      </c>
+      <c r="AE82" s="5" t="inlineStr">
+        <is>
+          <t>Toute l’année</t>
+        </is>
+      </c>
+      <c r="AF82" s="5" t="inlineStr">
+        <is>
+          <t>Ganzjährig</t>
+        </is>
+      </c>
+      <c r="AG82" s="5" t="inlineStr">
+        <is>
+          <t>Tutto l’anno</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AG76"/>
+  <autoFilter ref="A1:AG82"/>
   <dataValidations count="3">
     <dataValidation sqref="A2:A500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Escolha um valor da lista" type="list">
-      <formula1>"outdoor,nature,sea,events,water,indoor,markets"</formula1>
+      <formula1>"outdoor,nature,cities,sea,events,water,indoor,markets"</formula1>
     </dataValidation>
     <dataValidation sqref="B2:B500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Escolha um valor da lista" type="list">
       <formula1>"porches,senhora,albandeira,armacao,alcantarilha,marinha,benagil,lagoa,salgados,carvoeiro,guia,estombar,algoz,albufeira,ferragudo,silves,portimao,aia,paderne,alvor,messines,quarteira,lagos,loule,monchique,aljezur,varios,salir,querenca,arade"</formula1>
@@ -17882,7 +19409,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N15"/>
+  <dimension ref="A1:N27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -18740,56 +20267,60 @@
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>see</t>
+          <t>help</t>
         </is>
       </c>
       <c r="B14" s="5" t="inlineStr"/>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>Ferragudo</t>
-        </is>
-      </c>
-      <c r="D14" s="5" t="inlineStr"/>
+          <t>Hospital de Portimão</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>~25 min</t>
+        </is>
+      </c>
       <c r="E14" s="5" t="n">
-        <v>37.124</v>
+        <v>37.15545</v>
       </c>
       <c r="F14" s="5" t="n">
-        <v>-8.519</v>
+        <v>-8.539300000000001</v>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>Ferragudo</t>
+          <t>Hospital de Portimão</t>
         </is>
       </c>
       <c r="H14" s="5" t="inlineStr"/>
       <c r="I14" s="6" t="inlineStr">
         <is>
-          <t>Vila piscatória junto ao rio.</t>
+          <t>Hospital (urgência).</t>
         </is>
       </c>
       <c r="J14" s="5" t="inlineStr">
         <is>
-          <t>Charming fishing village by the river.</t>
+          <t>Hospital (A&amp;E).</t>
         </is>
       </c>
       <c r="K14" s="5" t="inlineStr">
         <is>
-          <t>Encantador pueblo pesquero junto al río.</t>
+          <t>Hospital (urgencias).</t>
         </is>
       </c>
       <c r="L14" s="5" t="inlineStr">
         <is>
-          <t>Charmant village de pêcheurs au bord de la rivière.</t>
+          <t>Hôpital (urgences).</t>
         </is>
       </c>
       <c r="M14" s="5" t="inlineStr">
         <is>
-          <t>Malerisches Fischerdorf am Fluss.</t>
+          <t>Krankenhaus (Notaufnahme).</t>
         </is>
       </c>
       <c r="N14" s="5" t="inlineStr">
         <is>
-          <t>Grazioso villaggio di pescatori sul fiume.</t>
+          <t>Ospedale (pronto soccorso).</t>
         </is>
       </c>
     </row>
@@ -18802,62 +20333,778 @@
       <c r="B15" s="5" t="inlineStr"/>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>Hospital de Portimão</t>
-        </is>
-      </c>
-      <c r="D15" s="5" t="inlineStr">
-        <is>
-          <t>~25 min</t>
-        </is>
-      </c>
+          <t>Centro de Saúde de Porches</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr"/>
       <c r="E15" s="5" t="n">
-        <v>37.145</v>
+        <v>37.12709</v>
       </c>
       <c r="F15" s="5" t="n">
-        <v>-8.547000000000001</v>
+        <v>-8.39761</v>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>Hospital de Portimão</t>
-        </is>
-      </c>
-      <c r="H15" s="5" t="inlineStr"/>
+          <t>Centro de Saúde de Porches</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="n"/>
       <c r="I15" s="6" t="inlineStr">
         <is>
-          <t>Hospital (urgência).</t>
+          <t>Extensão do centro de saúde (SNS), na Rua da Escola, a poucos minutos a pé. Confirme o horário de atendimento.</t>
         </is>
       </c>
       <c r="J15" s="5" t="inlineStr">
         <is>
-          <t>Hospital (A&amp;E).</t>
+          <t>Public health centre branch (SNS) on Rua da Escola, a few minutes’ walk away. Please check opening hours.</t>
         </is>
       </c>
       <c r="K15" s="5" t="inlineStr">
         <is>
-          <t>Hospital (urgencias).</t>
+          <t>Consultorio del centro de salud público (SNS) en la Rua da Escola, a pocos minutos a pie. Consulte el horario.</t>
         </is>
       </c>
       <c r="L15" s="5" t="inlineStr">
         <is>
-          <t>Hôpital (urgences).</t>
+          <t>Antenne du centre de santé public (SNS), Rua da Escola, à quelques minutes à pied. Vérifiez les horaires.</t>
         </is>
       </c>
       <c r="M15" s="5" t="inlineStr">
         <is>
-          <t>Krankenhaus (Notaufnahme).</t>
+          <t>Außenstelle des öffentlichen Gesundheitszentrums (SNS) in der Rua da Escola, wenige Gehminuten entfernt. Bitte Öffnungszeiten prüfen.</t>
         </is>
       </c>
       <c r="N15" s="5" t="inlineStr">
         <is>
-          <t>Ospedale (pronto soccorso).</t>
+          <t>Sede distaccata del centro sanitario pubblico (SNS) in Rua da Escola, a pochi minuti a piedi. Verificate gli orari.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>help</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr"/>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>Farmácia de Porches</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr"/>
+      <c r="E16" s="5" t="n">
+        <v>37.12672</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>-8.40067</v>
+      </c>
+      <c r="G16" s="5" t="inlineStr">
+        <is>
+          <t>Farmácia Porches</t>
+        </is>
+      </c>
+      <c r="H16" s="5" t="n"/>
+      <c r="I16" s="6" t="inlineStr">
+        <is>
+          <t>Farmácia no centro de Porches.</t>
+        </is>
+      </c>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>Pharmacy in the centre of Porches.</t>
+        </is>
+      </c>
+      <c r="K16" s="5" t="inlineStr">
+        <is>
+          <t>Farmacia en el centro de Porches.</t>
+        </is>
+      </c>
+      <c r="L16" s="5" t="inlineStr">
+        <is>
+          <t>Pharmacie au centre de Porches.</t>
+        </is>
+      </c>
+      <c r="M16" s="5" t="inlineStr">
+        <is>
+          <t>Apotheke im Ortszentrum.</t>
+        </is>
+      </c>
+      <c r="N16" s="5" t="inlineStr">
+        <is>
+          <t>Farmacia nel centro di Porches.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
+          <t>help</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr"/>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>Hospital Lusíadas Albufeira</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr"/>
+      <c r="E17" s="5" t="n">
+        <v>37.10287</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-8.23329</v>
+      </c>
+      <c r="G17" s="5" t="inlineStr">
+        <is>
+          <t>Hospital Lusíadas Albufeira</t>
+        </is>
+      </c>
+      <c r="H17" s="5" t="n"/>
+      <c r="I17" s="6" t="inlineStr">
+        <is>
+          <t>Hospital privado (atendimento pago).</t>
+        </is>
+      </c>
+      <c r="J17" s="5" t="inlineStr">
+        <is>
+          <t>Private hospital (paid care).</t>
+        </is>
+      </c>
+      <c r="K17" s="5" t="inlineStr">
+        <is>
+          <t>Hospital privado (de pago).</t>
+        </is>
+      </c>
+      <c r="L17" s="5" t="inlineStr">
+        <is>
+          <t>Hôpital privé (payant).</t>
+        </is>
+      </c>
+      <c r="M17" s="5" t="inlineStr">
+        <is>
+          <t>Privatklinik (kostenpflichtig).</t>
+        </is>
+      </c>
+      <c r="N17" s="5" t="inlineStr">
+        <is>
+          <t>Ospedale privato (a pagamento).</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>help</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr"/>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>Hospital Particular do Algarve – Alvor</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr"/>
+      <c r="E18" s="5" t="n">
+        <v>37.13069</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>-8.581950000000001</v>
+      </c>
+      <c r="G18" s="5" t="inlineStr">
+        <is>
+          <t>Hospital Particular do Algarve Alvor</t>
+        </is>
+      </c>
+      <c r="H18" s="5" t="n"/>
+      <c r="I18" s="6" t="inlineStr">
+        <is>
+          <t>Hospital privado (atendimento pago).</t>
+        </is>
+      </c>
+      <c r="J18" s="5" t="inlineStr">
+        <is>
+          <t>Private hospital (paid care).</t>
+        </is>
+      </c>
+      <c r="K18" s="5" t="inlineStr">
+        <is>
+          <t>Hospital privado (de pago).</t>
+        </is>
+      </c>
+      <c r="L18" s="5" t="inlineStr">
+        <is>
+          <t>Hôpital privé (payant).</t>
+        </is>
+      </c>
+      <c r="M18" s="5" t="inlineStr">
+        <is>
+          <t>Privatklinik (kostenpflichtig).</t>
+        </is>
+      </c>
+      <c r="N18" s="5" t="inlineStr">
+        <is>
+          <t>Ospedale privato (a pagamento).</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>help</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr"/>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>Extensão de Saúde de Armação de Pêra</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr"/>
+      <c r="E19" s="5" t="n">
+        <v>37.10605</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>-8.35777</v>
+      </c>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>Extensão de Saúde Armação de Pêra</t>
+        </is>
+      </c>
+      <c r="H19" s="5" t="n"/>
+      <c r="I19" s="6" t="inlineStr">
+        <is>
+          <t>Extensão do centro de saúde (SNS). Confirme o horário.</t>
+        </is>
+      </c>
+      <c r="J19" s="5" t="inlineStr">
+        <is>
+          <t>Public health centre branch (SNS). Check opening hours.</t>
+        </is>
+      </c>
+      <c r="K19" s="5" t="inlineStr">
+        <is>
+          <t>Consultorio público (SNS). Consulte el horario.</t>
+        </is>
+      </c>
+      <c r="L19" s="5" t="inlineStr">
+        <is>
+          <t>Antenne de santé publique (SNS). Vérifiez les horaires.</t>
+        </is>
+      </c>
+      <c r="M19" s="5" t="inlineStr">
+        <is>
+          <t>Öffentliche Gesundheitsstelle (SNS). Öffnungszeiten prüfen.</t>
+        </is>
+      </c>
+      <c r="N19" s="5" t="inlineStr">
+        <is>
+          <t>Presidio sanitario pubblico (SNS). Verificate gli orari.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>shop</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr"/>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>Minimercado da Vila</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr"/>
+      <c r="E20" s="5" t="n">
+        <v>37.12606</v>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>-8.39953</v>
+      </c>
+      <c r="G20" s="5" t="inlineStr">
+        <is>
+          <t>Minimercado da Vila Porches</t>
+        </is>
+      </c>
+      <c r="H20" s="5" t="n"/>
+      <c r="I20" s="6" t="inlineStr">
+        <is>
+          <t>Mercearia no centro de Porches, a 2 min a pé.</t>
+        </is>
+      </c>
+      <c r="J20" s="5" t="inlineStr">
+        <is>
+          <t>Grocery shop in the centre of Porches, 2 min on foot.</t>
+        </is>
+      </c>
+      <c r="K20" s="5" t="inlineStr">
+        <is>
+          <t>Tienda de comestibles en el centro, a 2 min a pie.</t>
+        </is>
+      </c>
+      <c r="L20" s="5" t="inlineStr">
+        <is>
+          <t>Épicerie au centre de Porches, à 2 min à pied.</t>
+        </is>
+      </c>
+      <c r="M20" s="5" t="inlineStr">
+        <is>
+          <t>Lebensmittelladen im Ortszentrum, 2 Gehminuten.</t>
+        </is>
+      </c>
+      <c r="N20" s="5" t="inlineStr">
+        <is>
+          <t>Alimentari nel centro di Porches, a 2 min a piedi.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>shop</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr"/>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>Supermercado Laginha</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr"/>
+      <c r="E21" s="5" t="n">
+        <v>37.12624</v>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>-8.39875</v>
+      </c>
+      <c r="G21" s="5" t="inlineStr">
+        <is>
+          <t>Laginha Porches</t>
+        </is>
+      </c>
+      <c r="H21" s="5" t="n"/>
+      <c r="I21" s="6" t="inlineStr">
+        <is>
+          <t>Pequeno supermercado no centro de Porches, a 2 min a pé.</t>
+        </is>
+      </c>
+      <c r="J21" s="5" t="inlineStr">
+        <is>
+          <t>Small supermarket in the centre of Porches, 2 min on foot.</t>
+        </is>
+      </c>
+      <c r="K21" s="5" t="inlineStr">
+        <is>
+          <t>Pequeño supermercado en el centro, a 2 min a pie.</t>
+        </is>
+      </c>
+      <c r="L21" s="5" t="inlineStr">
+        <is>
+          <t>Petit supermarché au centre de Porches, à 2 min à pied.</t>
+        </is>
+      </c>
+      <c r="M21" s="5" t="inlineStr">
+        <is>
+          <t>Kleiner Supermarkt im Ortszentrum, 2 Gehminuten.</t>
+        </is>
+      </c>
+      <c r="N21" s="5" t="inlineStr">
+        <is>
+          <t>Piccolo supermercato nel centro di Porches, a 2 min a piedi.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>beach</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>beaches</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>Praia da Galé</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>Albufeira · ~15 min</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>37.08186</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>-8.317880000000001</v>
+      </c>
+      <c r="G22" s="5" t="inlineStr">
+        <is>
+          <t>Praia da Galé</t>
+        </is>
+      </c>
+      <c r="H22" s="5" t="n"/>
+      <c r="I22" s="6" t="inlineStr">
+        <is>
+          <t>Longo areal com rochedos, a nascente de Armação de Pêra. Considerada uma das melhores praias do país.</t>
+        </is>
+      </c>
+      <c r="J22" s="5" t="inlineStr">
+        <is>
+          <t>Long sandy beach with rock formations, east of Armação de Pêra. Rated among Portugal’s best beaches.</t>
+        </is>
+      </c>
+      <c r="K22" s="5" t="inlineStr">
+        <is>
+          <t>Larga playa de arena con rocas, al este de Armação de Pêra. Considerada una de las mejores del país.</t>
+        </is>
+      </c>
+      <c r="L22" s="5" t="inlineStr">
+        <is>
+          <t>Longue plage de sable et rochers, à l’est d’Armação de Pêra. Classée parmi les meilleures du pays.</t>
+        </is>
+      </c>
+      <c r="M22" s="5" t="inlineStr">
+        <is>
+          <t>Langer Sandstrand mit Felsen, östlich von Armação de Pêra. Gilt als einer der besten Strände Portugals.</t>
+        </is>
+      </c>
+      <c r="N22" s="5" t="inlineStr">
+        <is>
+          <t>Lunga spiaggia sabbiosa con rocce, a est di Armação de Pêra. Tra le migliori del Paese.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>beach</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>beaches</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>Praia de São Rafael</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>Albufeira · ~20 min</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>37.07479</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>-8.280670000000001</v>
+      </c>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>Praia de São Rafael</t>
+        </is>
+      </c>
+      <c r="H23" s="5" t="n"/>
+      <c r="I23" s="6" t="inlineStr">
+        <is>
+          <t>Pequena enseada de água transparente entre rochas douradas; ótima para snorkeling.</t>
+        </is>
+      </c>
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t>Small cove with clear water between golden rocks; great for snorkelling.</t>
+        </is>
+      </c>
+      <c r="K23" s="5" t="inlineStr">
+        <is>
+          <t>Pequeña cala de agua cristalina entre rocas doradas; ideal para snorkel.</t>
+        </is>
+      </c>
+      <c r="L23" s="5" t="inlineStr">
+        <is>
+          <t>Petite crique aux eaux limpides entre rochers dorés ; idéale pour le snorkeling.</t>
+        </is>
+      </c>
+      <c r="M23" s="5" t="inlineStr">
+        <is>
+          <t>Kleine Bucht mit klarem Wasser zwischen goldenen Felsen; ideal zum Schnorcheln.</t>
+        </is>
+      </c>
+      <c r="N23" s="5" t="inlineStr">
+        <is>
+          <t>Piccola caletta di acqua limpida tra rocce dorate; ottima per lo snorkeling.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>beach</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>beaches</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>Praia da Falésia</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>Albufeira · ~30 min</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>37.0805</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>-8.149459999999999</v>
+      </c>
+      <c r="G24" s="5" t="inlineStr">
+        <is>
+          <t>Praia da Falésia</t>
+        </is>
+      </c>
+      <c r="H24" s="5" t="n"/>
+      <c r="I24" s="6" t="inlineStr">
+        <is>
+          <t>Areal de vários quilómetros junto a falésias vermelhas e brancas. Eleita várias vezes a melhor praia de Portugal.</t>
+        </is>
+      </c>
+      <c r="J24" s="5" t="inlineStr">
+        <is>
+          <t>Several kilometres of sand below red and white cliffs. Repeatedly voted Portugal’s best beach.</t>
+        </is>
+      </c>
+      <c r="K24" s="5" t="inlineStr">
+        <is>
+          <t>Varios kilómetros de arena bajo acantilados rojos y blancos. Elegida varias veces la mejor playa de Portugal.</t>
+        </is>
+      </c>
+      <c r="L24" s="5" t="inlineStr">
+        <is>
+          <t>Plusieurs kilomètres de sable au pied de falaises rouges et blanches. Souvent élue meilleure plage du Portugal.</t>
+        </is>
+      </c>
+      <c r="M24" s="5" t="inlineStr">
+        <is>
+          <t>Kilometerlanger Sandstrand unter roten und weißen Klippen. Mehrfach zum besten Strand Portugals gewählt.</t>
+        </is>
+      </c>
+      <c r="N24" s="5" t="inlineStr">
+        <is>
+          <t>Chilometri di sabbia sotto falesie rosse e bianche. Più volte eletta la miglior spiaggia del Portogallo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>beach</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>beaches</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>Praia da Rocha</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>Portimão · ~25 min</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="n">
+        <v>37.11551</v>
+      </c>
+      <c r="F25" s="5" t="n">
+        <v>-8.532080000000001</v>
+      </c>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>Praia da Rocha</t>
+        </is>
+      </c>
+      <c r="H25" s="5" t="n"/>
+      <c r="I25" s="6" t="inlineStr">
+        <is>
+          <t>Grande praia com marginal animada, restaurantes e a Fortaleza de Santa Catarina com vista sobre o mar.</t>
+        </is>
+      </c>
+      <c r="J25" s="5" t="inlineStr">
+        <is>
+          <t>Big beach with a lively promenade, restaurants and the Santa Catarina fortress overlooking the sea.</t>
+        </is>
+      </c>
+      <c r="K25" s="5" t="inlineStr">
+        <is>
+          <t>Gran playa con un animado paseo, restaurantes y la Fortaleza de Santa Catarina con vistas al mar.</t>
+        </is>
+      </c>
+      <c r="L25" s="5" t="inlineStr">
+        <is>
+          <t>Grande plage avec promenade animée, restaurants et la forteresse de Santa Catarina face à la mer.</t>
+        </is>
+      </c>
+      <c r="M25" s="5" t="inlineStr">
+        <is>
+          <t>Großer Strand mit belebter Promenade, Restaurants und der Festung Santa Catarina mit Meerblick.</t>
+        </is>
+      </c>
+      <c r="N25" s="5" t="inlineStr">
+        <is>
+          <t>Grande spiaggia con lungomare animato, ristoranti e la Fortezza di Santa Catarina sul mare.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>beach</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>beaches</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>Praia do João de Arens</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>Portimão · ~25 min</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="n">
+        <v>37.11621</v>
+      </c>
+      <c r="F26" s="5" t="n">
+        <v>-8.567830000000001</v>
+      </c>
+      <c r="G26" s="5" t="inlineStr">
+        <is>
+          <t>Praia do João de Arens</t>
+        </is>
+      </c>
+      <c r="H26" s="5" t="n"/>
+      <c r="I26" s="6" t="inlineStr">
+        <is>
+          <t>Pequena praia escondida entre falésias, acessível por escadaria; mais sossegada.</t>
+        </is>
+      </c>
+      <c r="J26" s="5" t="inlineStr">
+        <is>
+          <t>Small hidden beach between cliffs, reached by steps; quieter.</t>
+        </is>
+      </c>
+      <c r="K26" s="5" t="inlineStr">
+        <is>
+          <t>Pequeña playa escondida entre acantilados, con acceso por escaleras; más tranquila.</t>
+        </is>
+      </c>
+      <c r="L26" s="5" t="inlineStr">
+        <is>
+          <t>Petite plage cachée entre falaises, accessible par un escalier ; plus calme.</t>
+        </is>
+      </c>
+      <c r="M26" s="5" t="inlineStr">
+        <is>
+          <t>Kleiner versteckter Strand zwischen Klippen, über Treppen erreichbar; ruhiger.</t>
+        </is>
+      </c>
+      <c r="N26" s="5" t="inlineStr">
+        <is>
+          <t>Piccola spiaggia nascosta tra le falesie, raggiungibile con una scalinata; più tranquilla.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>beach</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>beaches</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>Praia dos Três Irmãos</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>Alvor · ~30 min</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="n">
+        <v>37.11971</v>
+      </c>
+      <c r="F27" s="5" t="n">
+        <v>-8.581289999999999</v>
+      </c>
+      <c r="G27" s="5" t="inlineStr">
+        <is>
+          <t>Praia dos Três Irmãos</t>
+        </is>
+      </c>
+      <c r="H27" s="5" t="n"/>
+      <c r="I27" s="6" t="inlineStr">
+        <is>
+          <t>Rochedos, grutas e arcos naturais junto ao extenso areal de Alvor.</t>
+        </is>
+      </c>
+      <c r="J27" s="5" t="inlineStr">
+        <is>
+          <t>Rocks, caves and natural arches next to the long Alvor beach.</t>
+        </is>
+      </c>
+      <c r="K27" s="5" t="inlineStr">
+        <is>
+          <t>Rocas, cuevas y arcos naturales junto a la extensa playa de Alvor.</t>
+        </is>
+      </c>
+      <c r="L27" s="5" t="inlineStr">
+        <is>
+          <t>Rochers, grottes et arches naturelles près de la longue plage d’Alvor.</t>
+        </is>
+      </c>
+      <c r="M27" s="5" t="inlineStr">
+        <is>
+          <t>Felsen, Grotten und Felsbögen am langen Strand von Alvor.</t>
+        </is>
+      </c>
+      <c r="N27" s="5" t="inlineStr">
+        <is>
+          <t>Scogli, grotte e archi naturali accanto alla lunga spiaggia di Alvor.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:N15"/>
+  <autoFilter ref="A1:N27"/>
   <dataValidations count="2">
     <dataValidation sqref="A2:A500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Escolha um valor da lista" type="list">
-      <formula1>"beach,food,fun,see,help"</formula1>
+      <formula1>"beach,food,fun,see,help,shop"</formula1>
     </dataValidation>
     <dataValidation sqref="B2:B500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Escolha um valor da lista" type="list">
       <formula1>"beaches,food,todo"</formula1>
@@ -23272,32 +25519,32 @@
     <row r="138">
       <c r="A138" s="6" t="inlineStr">
         <is>
-          <t>40 sugestões, de tascas a estrelas Michelin</t>
+          <t>Mais de 40 sugestões, de tascas a estrelas Michelin</t>
         </is>
       </c>
       <c r="B138" s="5" t="inlineStr">
         <is>
-          <t>40 picks, from taverns to Michelin stars</t>
+          <t>40+ picks, from taverns to Michelin stars</t>
         </is>
       </c>
       <c r="C138" s="5" t="inlineStr">
         <is>
-          <t>40 sugerencias, de tabernas a estrellas Michelin</t>
+          <t>Más de 40 sugerencias, de tabernas a estrellas Michelin</t>
         </is>
       </c>
       <c r="D138" s="5" t="inlineStr">
         <is>
-          <t>40 adresses, des tavernes aux étoilés Michelin</t>
+          <t>Plus de 40 adresses, des tavernes aux étoilés Michelin</t>
         </is>
       </c>
       <c r="E138" s="5" t="inlineStr">
         <is>
-          <t>40 Tipps, von Tavernen bis Michelin-Sterne</t>
+          <t>Über 40 Tipps, von Tavernen bis Michelin-Sterne</t>
         </is>
       </c>
       <c r="F138" s="5" t="inlineStr">
         <is>
-          <t>40 consigli, dalle taverne alle stelle Michelin</t>
+          <t>Oltre 40 consigli, dalle taverne alle stelle Michelin</t>
         </is>
       </c>
     </row>

--- a/Conteudos_Site_Casa_Porches.xlsx
+++ b/Conteudos_Site_Casa_Porches.xlsx
@@ -24,7 +24,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Eventos'!$A$1:$AG$82</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Sessoes'!$A$1:$D$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'Localidades'!$A$1:$D$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Mapa'!$A$1:$N$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Mapa'!$A$1:$N$41</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Pagina_Principal'!$A$1:$F$144</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -4544,32 +4544,32 @@
       </c>
       <c r="B97" s="6" t="inlineStr">
         <is>
-          <t>Minimercado da Vila e supermercado Laginha, a 2 minutos a pé, no centro de Porches — práticos para pão, fruta e o essencial. Para compras maiores há supermercados em Lagoa e Armação de Pêra (10 min de carro).</t>
+          <t>Minimercado da Vila e supermercado Laginha, a 2 minutos a pé, no centro de Porches — práticos para pão, fruta e o essencial. Para compras maiores há supermercados em Lagoa e Armação de Pêra (10 min de carro). Os supermercados maiores estão no mapa, na categoria "Compras".</t>
         </is>
       </c>
       <c r="C97" s="5" t="inlineStr">
         <is>
-          <t>Minimercado da Vila and Laginha supermarket, a 2-minute walk away in the centre of Porches — handy for bread, fruit and essentials. For a big shop there are supermarkets in Lagoa and Armação de Pêra (10 min by car).</t>
+          <t>Minimercado da Vila and Laginha supermarket, a 2-minute walk away in the centre of Porches — handy for bread, fruit and essentials. For a big shop there are supermarkets in Lagoa and Armação de Pêra (10 min by car). Larger supermarkets are on the map under "Shopping".</t>
         </is>
       </c>
       <c r="D97" s="5" t="inlineStr">
         <is>
-          <t>Minimercado da Vila y el supermercado Laginha, a 2 minutos a pie en el centro de Porches: prácticos para pan, fruta y lo básico. Para compras grandes hay supermercados en Lagoa y Armação de Pêra (10 min en coche).</t>
+          <t>Minimercado da Vila y el supermercado Laginha, a 2 minutos a pie en el centro de Porches: prácticos para pan, fruta y lo básico. Para compras grandes hay supermercados en Lagoa y Armação de Pêra (10 min en coche). Los supermercados grandes están en el mapa, en "Compras".</t>
         </is>
       </c>
       <c r="E97" s="5" t="inlineStr">
         <is>
-          <t>Minimercado da Vila et le supermarché Laginha, à 2 minutes à pied au centre de Porches — pratiques pour le pain, les fruits et l’essentiel. Pour les grosses courses, supermarchés à Lagoa et Armação de Pêra (10 min en voiture).</t>
+          <t>Minimercado da Vila et le supermarché Laginha, à 2 minutes à pied au centre de Porches — pratiques pour le pain, les fruits et l’essentiel. Pour les grosses courses, supermarchés à Lagoa et Armação de Pêra (10 min en voiture). Les grands supermarchés sont sur la carte, rubrique « Courses ».</t>
         </is>
       </c>
       <c r="F97" s="5" t="inlineStr">
         <is>
-          <t>Minimercado da Vila und Supermarkt Laginha, 2 Gehminuten entfernt im Ortszentrum – praktisch für Brot, Obst und das Nötigste. Für größere Einkäufe gibt es Supermärkte in Lagoa und Armação de Pêra (10 Min. mit dem Auto).</t>
+          <t>Minimercado da Vila und Supermarkt Laginha, 2 Gehminuten entfernt im Ortszentrum – praktisch für Brot, Obst und das Nötigste. Für größere Einkäufe gibt es Supermärkte in Lagoa und Armação de Pêra (10 Min. mit dem Auto). Größere Supermärkte finden Sie auf der Karte unter „Einkaufen“.</t>
         </is>
       </c>
       <c r="G97" s="5" t="inlineStr">
         <is>
-          <t>Minimercado da Vila e il supermercato Laginha, a 2 minuti a piedi nel centro di Porches: comodi per pane, frutta e l’essenziale. Per la spesa grande ci sono supermercati a Lagoa e Armação de Pêra (10 min in auto).</t>
+          <t>Minimercado da Vila e il supermercato Laginha, a 2 minuti a piedi nel centro di Porches: comodi per pane, frutta e l’essenziale. Per la spesa grande ci sono supermercati a Lagoa e Armação de Pêra (10 min in auto). I supermercati più grandi sono sulla mappa, alla voce «Spesa».</t>
         </is>
       </c>
     </row>
@@ -19409,7 +19409,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N27"/>
+  <dimension ref="A1:N41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -21100,8 +21100,848 @@
         </is>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>shop</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr"/>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>Continente Bom Dia · Alcantarilha (EN125)</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>4 km</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>37.13156</v>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>-8.35976</v>
+      </c>
+      <c r="G28" s="5" t="inlineStr">
+        <is>
+          <t>Continente Bom Dia Alcantarilha</t>
+        </is>
+      </c>
+      <c r="H28" s="5" t="n"/>
+      <c r="I28" s="6" t="inlineStr">
+        <is>
+          <t>Supermercado · ≈ 4 km</t>
+        </is>
+      </c>
+      <c r="J28" s="5" t="inlineStr">
+        <is>
+          <t>Supermarket · ≈ 4 km</t>
+        </is>
+      </c>
+      <c r="K28" s="5" t="inlineStr">
+        <is>
+          <t>Supermercado · ≈ 4 km</t>
+        </is>
+      </c>
+      <c r="L28" s="5" t="inlineStr">
+        <is>
+          <t>Supermarché · ≈ 4 km</t>
+        </is>
+      </c>
+      <c r="M28" s="5" t="inlineStr">
+        <is>
+          <t>Supermarkt · ≈ 4 km</t>
+        </is>
+      </c>
+      <c r="N28" s="5" t="inlineStr">
+        <is>
+          <t>Supermercato · ≈ 4 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>shop</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr"/>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>Aldi · Alcantarilha (EN125)</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>4,5 km</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>37.1305</v>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>-8.349170000000001</v>
+      </c>
+      <c r="G29" s="5" t="inlineStr">
+        <is>
+          <t>Aldi Alcantarilha</t>
+        </is>
+      </c>
+      <c r="H29" s="5" t="n"/>
+      <c r="I29" s="6" t="inlineStr">
+        <is>
+          <t>Supermercado · ≈ 4,5 km</t>
+        </is>
+      </c>
+      <c r="J29" s="5" t="inlineStr">
+        <is>
+          <t>Supermarket · ≈ 4,5 km</t>
+        </is>
+      </c>
+      <c r="K29" s="5" t="inlineStr">
+        <is>
+          <t>Supermercado · ≈ 4,5 km</t>
+        </is>
+      </c>
+      <c r="L29" s="5" t="inlineStr">
+        <is>
+          <t>Supermarché · ≈ 4,5 km</t>
+        </is>
+      </c>
+      <c r="M29" s="5" t="inlineStr">
+        <is>
+          <t>Supermarkt · ≈ 4,5 km</t>
+        </is>
+      </c>
+      <c r="N29" s="5" t="inlineStr">
+        <is>
+          <t>Supermercato · ≈ 4,5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>shop</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr"/>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>Continente Bom Dia · Armação de Pêra</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>4 km</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>37.10676</v>
+      </c>
+      <c r="F30" s="5" t="n">
+        <v>-8.362220000000001</v>
+      </c>
+      <c r="G30" s="5" t="inlineStr">
+        <is>
+          <t>Continente Bom Dia Armação de Pêra</t>
+        </is>
+      </c>
+      <c r="H30" s="5" t="n"/>
+      <c r="I30" s="6" t="inlineStr">
+        <is>
+          <t>Supermercado · ≈ 4 km</t>
+        </is>
+      </c>
+      <c r="J30" s="5" t="inlineStr">
+        <is>
+          <t>Supermarket · ≈ 4 km</t>
+        </is>
+      </c>
+      <c r="K30" s="5" t="inlineStr">
+        <is>
+          <t>Supermercado · ≈ 4 km</t>
+        </is>
+      </c>
+      <c r="L30" s="5" t="inlineStr">
+        <is>
+          <t>Supermarché · ≈ 4 km</t>
+        </is>
+      </c>
+      <c r="M30" s="5" t="inlineStr">
+        <is>
+          <t>Supermarkt · ≈ 4 km</t>
+        </is>
+      </c>
+      <c r="N30" s="5" t="inlineStr">
+        <is>
+          <t>Supermercato · ≈ 4 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>shop</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr"/>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>Pingo Doce · Armação de Pêra</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>4 km</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="n">
+        <v>37.10664</v>
+      </c>
+      <c r="F31" s="5" t="n">
+        <v>-8.359719999999999</v>
+      </c>
+      <c r="G31" s="5" t="inlineStr">
+        <is>
+          <t>Pingo Doce Armação de Pêra</t>
+        </is>
+      </c>
+      <c r="H31" s="5" t="n"/>
+      <c r="I31" s="6" t="inlineStr">
+        <is>
+          <t>Supermercado · ≈ 4 km</t>
+        </is>
+      </c>
+      <c r="J31" s="5" t="inlineStr">
+        <is>
+          <t>Supermarket · ≈ 4 km</t>
+        </is>
+      </c>
+      <c r="K31" s="5" t="inlineStr">
+        <is>
+          <t>Supermercado · ≈ 4 km</t>
+        </is>
+      </c>
+      <c r="L31" s="5" t="inlineStr">
+        <is>
+          <t>Supermarché · ≈ 4 km</t>
+        </is>
+      </c>
+      <c r="M31" s="5" t="inlineStr">
+        <is>
+          <t>Supermarkt · ≈ 4 km</t>
+        </is>
+      </c>
+      <c r="N31" s="5" t="inlineStr">
+        <is>
+          <t>Supermercato · ≈ 4 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>shop</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr"/>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>Lidl · Armação de Pêra</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>4 km</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="n">
+        <v>37.10362</v>
+      </c>
+      <c r="F32" s="5" t="n">
+        <v>-8.363149999999999</v>
+      </c>
+      <c r="G32" s="5" t="inlineStr">
+        <is>
+          <t>Lidl Armação de Pêra</t>
+        </is>
+      </c>
+      <c r="H32" s="5" t="n"/>
+      <c r="I32" s="6" t="inlineStr">
+        <is>
+          <t>Supermercado · ≈ 4 km</t>
+        </is>
+      </c>
+      <c r="J32" s="5" t="inlineStr">
+        <is>
+          <t>Supermarket · ≈ 4 km</t>
+        </is>
+      </c>
+      <c r="K32" s="5" t="inlineStr">
+        <is>
+          <t>Supermercado · ≈ 4 km</t>
+        </is>
+      </c>
+      <c r="L32" s="5" t="inlineStr">
+        <is>
+          <t>Supermarché · ≈ 4 km</t>
+        </is>
+      </c>
+      <c r="M32" s="5" t="inlineStr">
+        <is>
+          <t>Supermarkt · ≈ 4 km</t>
+        </is>
+      </c>
+      <c r="N32" s="5" t="inlineStr">
+        <is>
+          <t>Supermercato · ≈ 4 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>shop</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr"/>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>Intermarché · Armação de Pêra</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>4 km</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="n">
+        <v>37.10233</v>
+      </c>
+      <c r="F33" s="5" t="n">
+        <v>-8.363020000000001</v>
+      </c>
+      <c r="G33" s="5" t="inlineStr">
+        <is>
+          <t>Intermarché Armação de Pêra</t>
+        </is>
+      </c>
+      <c r="H33" s="5" t="n"/>
+      <c r="I33" s="6" t="inlineStr">
+        <is>
+          <t>Supermercado · ≈ 4 km</t>
+        </is>
+      </c>
+      <c r="J33" s="5" t="inlineStr">
+        <is>
+          <t>Supermarket · ≈ 4 km</t>
+        </is>
+      </c>
+      <c r="K33" s="5" t="inlineStr">
+        <is>
+          <t>Supermercado · ≈ 4 km</t>
+        </is>
+      </c>
+      <c r="L33" s="5" t="inlineStr">
+        <is>
+          <t>Supermarché · ≈ 4 km</t>
+        </is>
+      </c>
+      <c r="M33" s="5" t="inlineStr">
+        <is>
+          <t>Supermarkt · ≈ 4 km</t>
+        </is>
+      </c>
+      <c r="N33" s="5" t="inlineStr">
+        <is>
+          <t>Supermercato · ≈ 4 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>shop</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr"/>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>Apolónia · Lagoa</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>5 km</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="n">
+        <v>37.12623</v>
+      </c>
+      <c r="F34" s="5" t="n">
+        <v>-8.453110000000001</v>
+      </c>
+      <c r="G34" s="5" t="inlineStr">
+        <is>
+          <t>Apolónia Lagoa</t>
+        </is>
+      </c>
+      <c r="H34" s="5" t="n"/>
+      <c r="I34" s="6" t="inlineStr">
+        <is>
+          <t>Supermercado · ≈ 5 km</t>
+        </is>
+      </c>
+      <c r="J34" s="5" t="inlineStr">
+        <is>
+          <t>Supermarket · ≈ 5 km</t>
+        </is>
+      </c>
+      <c r="K34" s="5" t="inlineStr">
+        <is>
+          <t>Supermercado · ≈ 5 km</t>
+        </is>
+      </c>
+      <c r="L34" s="5" t="inlineStr">
+        <is>
+          <t>Supermarché · ≈ 5 km</t>
+        </is>
+      </c>
+      <c r="M34" s="5" t="inlineStr">
+        <is>
+          <t>Supermarkt · ≈ 5 km</t>
+        </is>
+      </c>
+      <c r="N34" s="5" t="inlineStr">
+        <is>
+          <t>Supermercato · ≈ 5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>shop</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr"/>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>Aldi · Lagoa</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>5 km</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="n">
+        <v>37.12697</v>
+      </c>
+      <c r="F35" s="5" t="n">
+        <v>-8.453469999999999</v>
+      </c>
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>Aldi Lagoa</t>
+        </is>
+      </c>
+      <c r="H35" s="5" t="n"/>
+      <c r="I35" s="6" t="inlineStr">
+        <is>
+          <t>Supermercado · ≈ 5 km</t>
+        </is>
+      </c>
+      <c r="J35" s="5" t="inlineStr">
+        <is>
+          <t>Supermarket · ≈ 5 km</t>
+        </is>
+      </c>
+      <c r="K35" s="5" t="inlineStr">
+        <is>
+          <t>Supermercado · ≈ 5 km</t>
+        </is>
+      </c>
+      <c r="L35" s="5" t="inlineStr">
+        <is>
+          <t>Supermarché · ≈ 5 km</t>
+        </is>
+      </c>
+      <c r="M35" s="5" t="inlineStr">
+        <is>
+          <t>Supermarkt · ≈ 5 km</t>
+        </is>
+      </c>
+      <c r="N35" s="5" t="inlineStr">
+        <is>
+          <t>Supermercato · ≈ 5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>shop</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr"/>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>Pingo Doce · Lagoa</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>5 km</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="n">
+        <v>37.13135</v>
+      </c>
+      <c r="F36" s="5" t="n">
+        <v>-8.454370000000001</v>
+      </c>
+      <c r="G36" s="5" t="inlineStr">
+        <is>
+          <t>Pingo Doce Lagoa</t>
+        </is>
+      </c>
+      <c r="H36" s="5" t="n"/>
+      <c r="I36" s="6" t="inlineStr">
+        <is>
+          <t>Supermercado · ≈ 5 km</t>
+        </is>
+      </c>
+      <c r="J36" s="5" t="inlineStr">
+        <is>
+          <t>Supermarket · ≈ 5 km</t>
+        </is>
+      </c>
+      <c r="K36" s="5" t="inlineStr">
+        <is>
+          <t>Supermercado · ≈ 5 km</t>
+        </is>
+      </c>
+      <c r="L36" s="5" t="inlineStr">
+        <is>
+          <t>Supermarché · ≈ 5 km</t>
+        </is>
+      </c>
+      <c r="M36" s="5" t="inlineStr">
+        <is>
+          <t>Supermarkt · ≈ 5 km</t>
+        </is>
+      </c>
+      <c r="N36" s="5" t="inlineStr">
+        <is>
+          <t>Supermercato · ≈ 5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>shop</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr"/>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>Intermarché Super · Lagoa</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>5 km</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="n">
+        <v>37.13221</v>
+      </c>
+      <c r="F37" s="5" t="n">
+        <v>-8.448930000000001</v>
+      </c>
+      <c r="G37" s="5" t="inlineStr">
+        <is>
+          <t>Intermarché Super Lagoa</t>
+        </is>
+      </c>
+      <c r="H37" s="5" t="n"/>
+      <c r="I37" s="6" t="inlineStr">
+        <is>
+          <t>Supermercado · ≈ 5 km</t>
+        </is>
+      </c>
+      <c r="J37" s="5" t="inlineStr">
+        <is>
+          <t>Supermarket · ≈ 5 km</t>
+        </is>
+      </c>
+      <c r="K37" s="5" t="inlineStr">
+        <is>
+          <t>Supermercado · ≈ 5 km</t>
+        </is>
+      </c>
+      <c r="L37" s="5" t="inlineStr">
+        <is>
+          <t>Supermarché · ≈ 5 km</t>
+        </is>
+      </c>
+      <c r="M37" s="5" t="inlineStr">
+        <is>
+          <t>Supermarkt · ≈ 5 km</t>
+        </is>
+      </c>
+      <c r="N37" s="5" t="inlineStr">
+        <is>
+          <t>Supermercato · ≈ 5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>shop</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="inlineStr"/>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>Auchan · Lagoa (EN125)</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t>6 km</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="n">
+        <v>37.13689</v>
+      </c>
+      <c r="F38" s="5" t="n">
+        <v>-8.4651</v>
+      </c>
+      <c r="G38" s="5" t="inlineStr">
+        <is>
+          <t>Auchan Lagoa</t>
+        </is>
+      </c>
+      <c r="H38" s="5" t="n"/>
+      <c r="I38" s="6" t="inlineStr">
+        <is>
+          <t>Supermercado · ≈ 6 km</t>
+        </is>
+      </c>
+      <c r="J38" s="5" t="inlineStr">
+        <is>
+          <t>Supermarket · ≈ 6 km</t>
+        </is>
+      </c>
+      <c r="K38" s="5" t="inlineStr">
+        <is>
+          <t>Supermercado · ≈ 6 km</t>
+        </is>
+      </c>
+      <c r="L38" s="5" t="inlineStr">
+        <is>
+          <t>Supermarché · ≈ 6 km</t>
+        </is>
+      </c>
+      <c r="M38" s="5" t="inlineStr">
+        <is>
+          <t>Supermarkt · ≈ 6 km</t>
+        </is>
+      </c>
+      <c r="N38" s="5" t="inlineStr">
+        <is>
+          <t>Supermercato · ≈ 6 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>shop</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr"/>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>Intermarché · Carvoeiro</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>5 km</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="n">
+        <v>37.11514</v>
+      </c>
+      <c r="F39" s="5" t="n">
+        <v>-8.45614</v>
+      </c>
+      <c r="G39" s="5" t="inlineStr">
+        <is>
+          <t>Intermarché Carvoeiro</t>
+        </is>
+      </c>
+      <c r="H39" s="5" t="n"/>
+      <c r="I39" s="6" t="inlineStr">
+        <is>
+          <t>Supermercado · ≈ 5 km</t>
+        </is>
+      </c>
+      <c r="J39" s="5" t="inlineStr">
+        <is>
+          <t>Supermarket · ≈ 5 km</t>
+        </is>
+      </c>
+      <c r="K39" s="5" t="inlineStr">
+        <is>
+          <t>Supermercado · ≈ 5 km</t>
+        </is>
+      </c>
+      <c r="L39" s="5" t="inlineStr">
+        <is>
+          <t>Supermarché · ≈ 5 km</t>
+        </is>
+      </c>
+      <c r="M39" s="5" t="inlineStr">
+        <is>
+          <t>Supermarkt · ≈ 5 km</t>
+        </is>
+      </c>
+      <c r="N39" s="5" t="inlineStr">
+        <is>
+          <t>Supermercato · ≈ 5 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>shop</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="inlineStr"/>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>Apolónia · Galé (Albufeira)</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="inlineStr">
+        <is>
+          <t>9 km</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="n">
+        <v>37.08255</v>
+      </c>
+      <c r="F40" s="5" t="n">
+        <v>-8.31246</v>
+      </c>
+      <c r="G40" s="5" t="inlineStr">
+        <is>
+          <t>Apolónia Galé</t>
+        </is>
+      </c>
+      <c r="H40" s="5" t="n"/>
+      <c r="I40" s="6" t="inlineStr">
+        <is>
+          <t>Supermercado · ≈ 9 km</t>
+        </is>
+      </c>
+      <c r="J40" s="5" t="inlineStr">
+        <is>
+          <t>Supermarket · ≈ 9 km</t>
+        </is>
+      </c>
+      <c r="K40" s="5" t="inlineStr">
+        <is>
+          <t>Supermercado · ≈ 9 km</t>
+        </is>
+      </c>
+      <c r="L40" s="5" t="inlineStr">
+        <is>
+          <t>Supermarché · ≈ 9 km</t>
+        </is>
+      </c>
+      <c r="M40" s="5" t="inlineStr">
+        <is>
+          <t>Supermarkt · ≈ 9 km</t>
+        </is>
+      </c>
+      <c r="N40" s="5" t="inlineStr">
+        <is>
+          <t>Supermercato · ≈ 9 km</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>shop</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr"/>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>Continente Modelo · Silves</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>8 km</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="n">
+        <v>37.1878</v>
+      </c>
+      <c r="F41" s="5" t="n">
+        <v>-8.44815</v>
+      </c>
+      <c r="G41" s="5" t="inlineStr">
+        <is>
+          <t>Continente Modelo Silves</t>
+        </is>
+      </c>
+      <c r="H41" s="5" t="n"/>
+      <c r="I41" s="6" t="inlineStr">
+        <is>
+          <t>Supermercado · ≈ 8 km</t>
+        </is>
+      </c>
+      <c r="J41" s="5" t="inlineStr">
+        <is>
+          <t>Supermarket · ≈ 8 km</t>
+        </is>
+      </c>
+      <c r="K41" s="5" t="inlineStr">
+        <is>
+          <t>Supermercado · ≈ 8 km</t>
+        </is>
+      </c>
+      <c r="L41" s="5" t="inlineStr">
+        <is>
+          <t>Supermarché · ≈ 8 km</t>
+        </is>
+      </c>
+      <c r="M41" s="5" t="inlineStr">
+        <is>
+          <t>Supermarkt · ≈ 8 km</t>
+        </is>
+      </c>
+      <c r="N41" s="5" t="inlineStr">
+        <is>
+          <t>Supermercato · ≈ 8 km</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:N27"/>
+  <autoFilter ref="A1:N41"/>
   <dataValidations count="2">
     <dataValidation sqref="A2:A500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Escolha um valor da lista" type="list">
       <formula1>"beach,food,fun,see,help,shop"</formula1>
